--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31571,6 +31571,79 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="D413" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="E413" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="F413" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="G413" t="n">
+        <v>10120231</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="O413" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>-1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>27.29</v>
@@ -687,7 +687,7 @@
         <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>27.34</v>
@@ -762,7 +762,7 @@
         <v>-1.61</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.36</v>
@@ -841,7 +841,7 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>27.38</v>
@@ -916,7 +916,7 @@
         <v>1.34</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>27.44</v>
@@ -991,7 +991,7 @@
         <v>2.57</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>27.56</v>
@@ -1066,7 +1066,7 @@
         <v>-0.73</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>27.67</v>
@@ -1141,7 +1141,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>27.75</v>
@@ -1216,7 +1216,7 @@
         <v>1.92</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>27.87</v>
@@ -1291,7 +1291,7 @@
         <v>0.44</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>27.97</v>
@@ -1366,7 +1366,7 @@
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>28.07</v>
@@ -1441,7 +1441,7 @@
         <v>-1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>28.16</v>
@@ -1516,7 +1516,7 @@
         <v>0.59</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>28.24</v>
@@ -1591,7 +1591,7 @@
         <v>-0.68</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>28.34</v>
@@ -1666,7 +1666,7 @@
         <v>1.17</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>28.44</v>
@@ -1741,7 +1741,7 @@
         <v>0.41</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>28.52</v>
@@ -1816,7 +1816,7 @@
         <v>-0.51</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>28.58</v>
@@ -1891,7 +1891,7 @@
         <v>2.05</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>28.7</v>
@@ -1966,7 +1966,7 @@
         <v>-0.33</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>28.79</v>
@@ -2041,7 +2041,7 @@
         <v>0.47</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>28.88</v>
@@ -2116,7 +2116,7 @@
         <v>-1.2</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>28.97</v>
@@ -2191,7 +2191,7 @@
         <v>-0.51</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>29.05</v>
@@ -2266,7 +2266,7 @@
         <v>-2.07</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>29.12</v>
@@ -2345,7 +2345,7 @@
         <v>0.38</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>29.18</v>
@@ -2420,7 +2420,7 @@
         <v>-1.87</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>29.2</v>
@@ -2495,7 +2495,7 @@
         <v>-0.32</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>29.18</v>
@@ -2574,7 +2574,7 @@
         <v>1.55</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>29.19</v>
@@ -2649,7 +2649,7 @@
         <v>0.87</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.21</v>
@@ -2724,7 +2724,7 @@
         <v>2.66</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.24</v>
@@ -2799,7 +2799,7 @@
         <v>-0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.26</v>
@@ -2874,7 +2874,7 @@
         <v>-0.34</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.27</v>
@@ -2949,7 +2949,7 @@
         <v>-1.62</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.27</v>
@@ -3032,7 +3032,7 @@
         <v>2.92</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.31</v>
@@ -3111,7 +3111,7 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.37</v>
@@ -3186,7 +3186,7 @@
         <v>1.72</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.44</v>
@@ -3261,7 +3261,7 @@
         <v>-0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.5</v>
@@ -3336,7 +3336,7 @@
         <v>0.33</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.58</v>
@@ -3411,7 +3411,7 @@
         <v>0.13</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>29.62</v>
@@ -3486,7 +3486,7 @@
         <v>-0.32</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>29.67</v>
@@ -3561,7 +3561,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>29.7</v>
@@ -3636,7 +3636,7 @@
         <v>-1.57</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>29.72</v>
@@ -3711,7 +3711,7 @@
         <v>-0.2</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>29.75</v>
@@ -3786,7 +3786,7 @@
         <v>2.07</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>29.83</v>
@@ -3861,7 +3861,7 @@
         <v>-0.16</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>29.91</v>
@@ -3936,7 +3936,7 @@
         <v>2.59</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>30.06</v>
@@ -4011,7 +4011,7 @@
         <v>-1.02</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>30.19</v>
@@ -4086,7 +4086,7 @@
         <v>-0.03</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>30.3</v>
@@ -4161,7 +4161,7 @@
         <v>-1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>30.39</v>
@@ -4236,7 +4236,7 @@
         <v>0.42</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>30.44</v>
@@ -4311,7 +4311,7 @@
         <v>-6.08</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>30.4</v>
@@ -4394,7 +4394,7 @@
         <v>-6.27</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>30.27</v>
@@ -4477,7 +4477,7 @@
         <v>0.22</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>30.17</v>
@@ -4560,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>30.03</v>
@@ -4643,7 +4643,7 @@
         <v>3.39</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.92</v>
@@ -4722,7 +4722,7 @@
         <v>0.78</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.8</v>
@@ -4801,7 +4801,7 @@
         <v>3.22</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.72</v>
@@ -4880,7 +4880,7 @@
         <v>0.65</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.65</v>
@@ -4955,7 +4955,7 @@
         <v>0.1</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.58</v>
@@ -5030,7 +5030,7 @@
         <v>1.19</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.53</v>
@@ -5109,7 +5109,7 @@
         <v>-0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.48</v>
@@ -5188,7 +5188,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.47</v>
@@ -5263,7 +5263,7 @@
         <v>-0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.45</v>
@@ -5338,7 +5338,7 @@
         <v>3.59</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.45</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.45</v>
@@ -5492,7 +5492,7 @@
         <v>-1.67</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>29.39</v>
@@ -5567,7 +5567,7 @@
         <v>0.47</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>29.35</v>
@@ -5642,7 +5642,7 @@
         <v>-1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>29.29</v>
@@ -5717,7 +5717,7 @@
         <v>-0.77</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>29.24</v>
@@ -5796,7 +5796,7 @@
         <v>-0.71</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>29.17</v>
@@ -5871,7 +5871,7 @@
         <v>-0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>29.18</v>
@@ -5950,7 +5950,7 @@
         <v>1.24</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>29.3</v>
@@ -6025,7 +6025,7 @@
         <v>2.51</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>29.45</v>
@@ -6100,7 +6100,7 @@
         <v>-2.42</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>29.57</v>
@@ -6179,7 +6179,7 @@
         <v>-0.1</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>29.64</v>
@@ -6254,7 +6254,7 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>29.72</v>
@@ -6329,7 +6329,7 @@
         <v>-0.57</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>29.74</v>
@@ -6408,7 +6408,7 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>29.77</v>
@@ -6483,7 +6483,7 @@
         <v>-2.27</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>29.76</v>
@@ -6562,7 +6562,7 @@
         <v>1.23</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>29.75</v>
@@ -6637,7 +6637,7 @@
         <v>-1.05</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>29.74</v>
@@ -6712,7 +6712,7 @@
         <v>0.41</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>29.72</v>
@@ -6787,7 +6787,7 @@
         <v>2.41</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>29.75</v>
@@ -6862,7 +6862,7 @@
         <v>1.26</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>29.75</v>
@@ -6937,7 +6937,7 @@
         <v>-1.57</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>29.72</v>
@@ -7012,7 +7012,7 @@
         <v>1.4</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>29.74</v>
@@ -7087,7 +7087,7 @@
         <v>-0.72</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>29.74</v>
@@ -7162,7 +7162,7 @@
         <v>-0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>29.75</v>
@@ -7237,7 +7237,7 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>29.79</v>
@@ -7312,7 +7312,7 @@
         <v>-0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>29.82</v>
@@ -7387,7 +7387,7 @@
         <v>5.3</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>29.94</v>
@@ -7462,7 +7462,7 @@
         <v>-0.47</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>30.04</v>
@@ -7537,7 +7537,7 @@
         <v>-0.32</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>30.09</v>
@@ -7612,7 +7612,7 @@
         <v>3.54</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>30.24</v>
@@ -7687,7 +7687,7 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>30.4</v>
@@ -7762,7 +7762,7 @@
         <v>2.14</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>30.58</v>
@@ -7837,7 +7837,7 @@
         <v>-0.48</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>30.76</v>
@@ -7912,7 +7912,7 @@
         <v>-0.84</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>30.91</v>
@@ -7987,7 +7987,7 @@
         <v>0.33</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>31.1</v>
@@ -8062,7 +8062,7 @@
         <v>-0.27</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>31.27</v>
@@ -8137,7 +8137,7 @@
         <v>0.18</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>31.46</v>
@@ -8212,7 +8212,7 @@
         <v>2.15</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>31.68</v>
@@ -8287,7 +8287,7 @@
         <v>-1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>31.83</v>
@@ -8362,7 +8362,7 @@
         <v>-1.65</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>31.94</v>
@@ -8437,7 +8437,7 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>32.09</v>
@@ -8512,7 +8512,7 @@
         <v>-1.06</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>32.2</v>
@@ -8587,7 +8587,7 @@
         <v>1.23</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>32.34</v>
@@ -8662,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>32.5</v>
@@ -8737,7 +8737,7 @@
         <v>-2.16</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>32.62</v>
@@ -8812,7 +8812,7 @@
         <v>0.58</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>32.76</v>
@@ -8887,7 +8887,7 @@
         <v>-0.24</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>32.82</v>
@@ -8966,7 +8966,7 @@
         <v>1.56</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>32.91</v>
@@ -9041,7 +9041,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>33.02</v>
@@ -9116,7 +9116,7 @@
         <v>-0.24</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>33.07</v>
@@ -9191,7 +9191,7 @@
         <v>-0.42</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>33.1</v>
@@ -9266,7 +9266,7 @@
         <v>-0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>33.08</v>
@@ -9345,7 +9345,7 @@
         <v>2.27</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>33.1</v>
@@ -9420,7 +9420,7 @@
         <v>3.79</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>33.21</v>
@@ -9495,7 +9495,7 @@
         <v>-1.14</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>33.28</v>
@@ -9570,7 +9570,7 @@
         <v>-1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>33.35</v>
@@ -9645,7 +9645,7 @@
         <v>0.44</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>33.42</v>
@@ -9720,7 +9720,7 @@
         <v>0.7</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>33.46</v>
@@ -9795,7 +9795,7 @@
         <v>-0.12</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>33.53</v>
@@ -9870,7 +9870,7 @@
         <v>2.14</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>33.66</v>
@@ -9945,7 +9945,7 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>33.8</v>
@@ -10020,7 +10020,7 @@
         <v>-0.08</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>33.95</v>
@@ -10095,7 +10095,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.08</v>
@@ -10170,7 +10170,7 @@
         <v>-2.34</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.14</v>
@@ -10245,7 +10245,7 @@
         <v>-0.06</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>34.24</v>
@@ -10320,7 +10320,7 @@
         <v>0.06</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>34.34</v>
@@ -10395,7 +10395,7 @@
         <v>-3.32</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>34.38</v>
@@ -10474,7 +10474,7 @@
         <v>-0.57</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>34.38</v>
@@ -10549,7 +10549,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>34.38</v>
@@ -10624,7 +10624,7 @@
         <v>1.16</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>34.41</v>
@@ -10699,7 +10699,7 @@
         <v>1.09</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>34.46</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>34.53</v>
@@ -10849,7 +10849,7 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>34.58</v>
@@ -10924,7 +10924,7 @@
         <v>0.35</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>34.58</v>
@@ -10999,7 +10999,7 @@
         <v>-2.01</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>34.55</v>
@@ -11078,7 +11078,7 @@
         <v>0.67</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>34.56</v>
@@ -11153,7 +11153,7 @@
         <v>1.71</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>34.59</v>
@@ -11228,7 +11228,7 @@
         <v>-1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>34.58</v>
@@ -11307,7 +11307,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>34.58</v>
@@ -11382,7 +11382,7 @@
         <v>0.14</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>34.54</v>
@@ -11457,7 +11457,7 @@
         <v>-1.97</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>34.44</v>
@@ -11536,7 +11536,7 @@
         <v>1.65</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>34.38</v>
@@ -11611,7 +11611,7 @@
         <v>0.52</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>34.34</v>
@@ -11686,7 +11686,7 @@
         <v>2.11</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>34.37</v>
@@ -11761,7 +11761,7 @@
         <v>-0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>34.39</v>
@@ -11836,7 +11836,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>34.41</v>
@@ -11911,7 +11911,7 @@
         <v>-0.09</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>34.48</v>
@@ -11986,7 +11986,7 @@
         <v>1.51</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>34.59</v>
@@ -12061,7 +12061,7 @@
         <v>1.89</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>34.72</v>
@@ -12136,7 +12136,7 @@
         <v>2.65</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>34.88</v>
@@ -12211,7 +12211,7 @@
         <v>0.51</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>35.03</v>
@@ -12286,7 +12286,7 @@
         <v>-1.1</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>35.16</v>
@@ -12361,7 +12361,7 @@
         <v>0.76</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>35.28</v>
@@ -12436,7 +12436,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>35.41</v>
@@ -12511,7 +12511,7 @@
         <v>-0.88</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>35.56</v>
@@ -12586,7 +12586,7 @@
         <v>0.62</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>35.71</v>
@@ -12661,7 +12661,7 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>35.85</v>
@@ -12736,7 +12736,7 @@
         <v>1.46</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>36.04</v>
@@ -12811,7 +12811,7 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>36.26</v>
@@ -12886,7 +12886,7 @@
         <v>-0.41</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>36.46</v>
@@ -12961,7 +12961,7 @@
         <v>-2.1</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>36.66</v>
@@ -13036,7 +13036,7 @@
         <v>0.53</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>36.83</v>
@@ -13111,7 +13111,7 @@
         <v>2.76</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>37.06</v>
@@ -13186,7 +13186,7 @@
         <v>2.56</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>37.29</v>
@@ -13261,7 +13261,7 @@
         <v>-0.2</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>37.54</v>
@@ -13336,7 +13336,7 @@
         <v>-0.35</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>37.78</v>
@@ -13411,7 +13411,7 @@
         <v>3.04</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>38.08</v>
@@ -13486,7 +13486,7 @@
         <v>2.02</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>38.4</v>
@@ -13561,7 +13561,7 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>38.71</v>
@@ -13636,7 +13636,7 @@
         <v>-0.31</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>38.97</v>
@@ -13711,7 +13711,7 @@
         <v>1.27</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>39.25</v>
@@ -13786,7 +13786,7 @@
         <v>-0.89</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>39.53</v>
@@ -13861,7 +13861,7 @@
         <v>2.33</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>39.85</v>
@@ -13936,7 +13936,7 @@
         <v>1.24</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>40.17</v>
@@ -14011,7 +14011,7 @@
         <v>-1.52</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>40.49</v>
@@ -14086,7 +14086,7 @@
         <v>2.7</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>40.84</v>
@@ -14161,7 +14161,7 @@
         <v>0.34</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>41.19</v>
@@ -14236,7 +14236,7 @@
         <v>1.61</v>
       </c>
       <c r="I182" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>41.54</v>
@@ -14311,7 +14311,7 @@
         <v>4.03</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>41.97</v>
@@ -14386,7 +14386,7 @@
         <v>-0.97</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>42.38</v>
@@ -14461,7 +14461,7 @@
         <v>3.27</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>42.91</v>
@@ -14536,7 +14536,7 @@
         <v>1.74</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>43.46</v>
@@ -14611,7 +14611,7 @@
         <v>-4.43</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>43.86</v>
@@ -14686,7 +14686,7 @@
         <v>1.55</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>44.25</v>
@@ -14761,7 +14761,7 @@
         <v>-8.24</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>44.44</v>
@@ -14840,7 +14840,7 @@
         <v>0.21</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>44.64</v>
@@ -14915,7 +14915,7 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>44.8</v>
@@ -14990,7 +14990,7 @@
         <v>-0.43</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>44.9</v>
@@ -15065,7 +15065,7 @@
         <v>-3.61</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>44.9</v>
@@ -15140,7 +15140,7 @@
         <v>0.71</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>44.92</v>
@@ -15215,7 +15215,7 @@
         <v>1.24</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>44.93</v>
@@ -15290,7 +15290,7 @@
         <v>2.57</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>45.02</v>
@@ -15365,7 +15365,7 @@
         <v>-0.74</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>45.05</v>
@@ -15440,7 +15440,7 @@
         <v>-0.57</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>45.03</v>
@@ -15515,7 +15515,7 @@
         <v>-2.33</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>45</v>
@@ -15590,7 +15590,7 @@
         <v>2.13</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>44.95</v>
@@ -15665,7 +15665,7 @@
         <v>-0.23</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>44.9</v>
@@ -15740,7 +15740,7 @@
         <v>0.85</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>44.82</v>
@@ -15815,7 +15815,7 @@
         <v>4.26</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>44.75</v>
@@ -15890,7 +15890,7 @@
         <v>1.44</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>44.73</v>
@@ -15965,7 +15965,7 @@
         <v>4.03</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>44.73</v>
@@ -16040,7 +16040,7 @@
         <v>-1.86</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>44.64</v>
@@ -16115,7 +16115,7 @@
         <v>-3.08</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>44.59</v>
@@ -16190,7 +16190,7 @@
         <v>-1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>44.48</v>
@@ -16265,7 +16265,7 @@
         <v>1.39</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>44.59</v>
@@ -16340,7 +16340,7 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>44.72</v>
@@ -16415,7 +16415,7 @@
         <v>-1.44</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>44.8</v>
@@ -16494,7 +16494,7 @@
         <v>-1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>44.87</v>
@@ -16569,7 +16569,7 @@
         <v>2.94</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>45.08</v>
@@ -16644,7 +16644,7 @@
         <v>0.09</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>45.28</v>
@@ -16719,7 +16719,7 @@
         <v>3.71</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>45.54</v>
@@ -16794,7 +16794,7 @@
         <v>5.81</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>45.88</v>
@@ -16869,7 +16869,7 @@
         <v>2.56</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>46.3</v>
@@ -16944,7 +16944,7 @@
         <v>1.16</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>46.77</v>
@@ -17019,7 +17019,7 @@
         <v>-0.11</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>47.29</v>
@@ -17094,7 +17094,7 @@
         <v>-2.47</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>47.7</v>
@@ -17169,7 +17169,7 @@
         <v>2.3</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>48.16</v>
@@ -17244,7 +17244,7 @@
         <v>-0.45</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>48.6</v>
@@ -17319,7 +17319,7 @@
         <v>4.67</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>49.07</v>
@@ -17394,7 +17394,7 @@
         <v>1.63</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>49.55</v>
@@ -17469,7 +17469,7 @@
         <v>2.76</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>50.02</v>
@@ -17544,7 +17544,7 @@
         <v>-2.64</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>50.45</v>
@@ -17619,7 +17619,7 @@
         <v>3.58</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>51.06</v>
@@ -17694,7 +17694,7 @@
         <v>-0.65</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>51.67</v>
@@ -17769,7 +17769,7 @@
         <v>4.38</v>
       </c>
       <c r="I229" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>52.38</v>
@@ -17844,7 +17844,7 @@
         <v>-1.56</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>53.03</v>
@@ -17919,7 +17919,7 @@
         <v>2.71</v>
       </c>
       <c r="I231" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>53.78</v>
@@ -17994,7 +17994,7 @@
         <v>2.53</v>
       </c>
       <c r="I232" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>54.64</v>
@@ -18069,7 +18069,7 @@
         <v>3.79</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>55.55</v>
@@ -18144,7 +18144,7 @@
         <v>0.59</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>56.48</v>
@@ -18219,7 +18219,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>57.62</v>
@@ -18294,7 +18294,7 @@
         <v>-7.19</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>58.36</v>
@@ -18369,7 +18369,7 @@
         <v>4.5</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>59.18</v>
@@ -18444,7 +18444,7 @@
         <v>-6.61</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>59.74</v>
@@ -18519,7 +18519,7 @@
         <v>2.06</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>60.38</v>
@@ -18594,7 +18594,7 @@
         <v>5.06</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>61.24</v>
@@ -18669,7 +18669,7 @@
         <v>6.7</v>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>62.28</v>
@@ -18744,7 +18744,7 @@
         <v>-3.73</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>63.19</v>
@@ -18819,7 +18819,7 @@
         <v>-1.76</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>63.92</v>
@@ -18894,7 +18894,7 @@
         <v>3.83</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>64.73999999999999</v>
@@ -18969,7 +18969,7 @@
         <v>6.7</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>65.72</v>
@@ -19044,7 +19044,7 @@
         <v>1.77</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>66.84</v>
@@ -19119,7 +19119,7 @@
         <v>7.58</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>68.16</v>
@@ -19194,7 +19194,7 @@
         <v>-1.47</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>69.44</v>
@@ -19269,7 +19269,7 @@
         <v>-2.76</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>70.48</v>
@@ -19344,7 +19344,7 @@
         <v>5.39</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>71.78</v>
@@ -19419,7 +19419,7 @@
         <v>-1.67</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>72.94</v>
@@ -19494,7 +19494,7 @@
         <v>3.78</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>74.17</v>
@@ -19569,7 +19569,7 @@
         <v>6.63</v>
       </c>
       <c r="I253" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>75.56999999999999</v>
@@ -19644,7 +19644,7 @@
         <v>5.84</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>77.23</v>
@@ -19719,7 +19719,7 @@
         <v>3.3</v>
       </c>
       <c r="I255" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>78.75</v>
@@ -19794,7 +19794,7 @@
         <v>3.95</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>80.73</v>
@@ -19869,7 +19869,7 @@
         <v>-0.03</v>
       </c>
       <c r="I257" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>82.56</v>
@@ -19944,7 +19944,7 @@
         <v>-28.54</v>
       </c>
       <c r="I258" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>83.11</v>
@@ -20023,7 +20023,7 @@
         <v>-3.98</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>83.45</v>
@@ -20098,7 +20098,7 @@
         <v>6.24</v>
       </c>
       <c r="I260" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>83.84</v>
@@ -20173,7 +20173,7 @@
         <v>2.88</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>84.11</v>
@@ -20248,7 +20248,7 @@
         <v>-15.77</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" s="4" t="n">
         <v>83.90000000000001</v>
@@ -20323,7 +20323,7 @@
         <v>5.25</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>83.92</v>
@@ -20398,7 +20398,7 @@
         <v>8.33</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>84.11</v>
@@ -20473,7 +20473,7 @@
         <v>-3.46</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>83.92</v>
@@ -20548,7 +20548,7 @@
         <v>4.29</v>
       </c>
       <c r="I266" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" t="n">
         <v>83.81999999999999</v>
@@ -20623,7 +20623,7 @@
         <v>-11.53</v>
       </c>
       <c r="I267" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" s="4" t="n">
         <v>82.97</v>
@@ -20698,7 +20698,7 @@
         <v>2.94</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>82.29000000000001</v>
@@ -20773,7 +20773,7 @@
         <v>-4.8</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>81.56</v>
@@ -20852,7 +20852,7 @@
         <v>5.6</v>
       </c>
       <c r="I270" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>80.8</v>
@@ -20927,7 +20927,7 @@
         <v>1.31</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>80.15000000000001</v>
@@ -21002,7 +21002,7 @@
         <v>7.9</v>
       </c>
       <c r="I272" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>79.62</v>
@@ -21077,7 +21077,7 @@
         <v>5.16</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>79.01000000000001</v>
@@ -21152,7 +21152,7 @@
         <v>-1.85</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>78.04000000000001</v>
@@ -21227,7 +21227,7 @@
         <v>1.21</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>76.97</v>
@@ -21302,7 +21302,7 @@
         <v>0.51</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>75.70999999999999</v>
@@ -21377,7 +21377,7 @@
         <v>5.64</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>74.68000000000001</v>
@@ -21452,7 +21452,7 @@
         <v>-4.02</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>74.98999999999999</v>
@@ -21527,7 +21527,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I279" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21606,7 +21606,7 @@
         <v>0.88</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>75.02</v>
@@ -21681,7 +21681,7 @@
         <v>-1.42</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>74.77</v>
@@ -21760,7 +21760,7 @@
         <v>2.25</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>75.23</v>
@@ -21839,7 +21839,7 @@
         <v>3.06</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>75.64</v>
@@ -21914,7 +21914,7 @@
         <v>2.34</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>75.84</v>
@@ -21989,7 +21989,7 @@
         <v>-2.72</v>
       </c>
       <c r="I285" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>76.06</v>
@@ -22064,7 +22064,7 @@
         <v>-1.84</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>76.06</v>
@@ -22133,7 +22133,7 @@
         <v>-4.96</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>76.31</v>
@@ -22216,7 +22216,7 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>76.48</v>
@@ -22291,7 +22291,7 @@
         <v>-2.13</v>
       </c>
       <c r="I289" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>76.75</v>
@@ -22366,7 +22366,7 @@
         <v>-4.13</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>76.68000000000001</v>
@@ -22441,7 +22441,7 @@
         <v>-4.4</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>76.41</v>
@@ -22516,7 +22516,7 @@
         <v>-6.33</v>
       </c>
       <c r="I292" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" s="4" t="n">
         <v>75.66</v>
@@ -22599,7 +22599,7 @@
         <v>1.54</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>74.75</v>
@@ -22674,7 +22674,7 @@
         <v>0.77</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>73.95</v>
@@ -22749,7 +22749,7 @@
         <v>3.59</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>73.2</v>
@@ -22824,7 +22824,7 @@
         <v>-6.81</v>
       </c>
       <c r="I296" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" s="4" t="n">
         <v>72.22</v>
@@ -22903,7 +22903,7 @@
         <v>4.39</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>71.14</v>
@@ -22982,7 +22982,7 @@
         <v>0.13</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>70.23999999999999</v>
@@ -23057,7 +23057,7 @@
         <v>7.27</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>69.91</v>
@@ -23132,7 +23132,7 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>69.55</v>
@@ -23207,7 +23207,7 @@
         <v>-3.45</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>69.13</v>
@@ -23282,7 +23282,7 @@
         <v>0.46</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>68.64</v>
@@ -23357,7 +23357,7 @@
         <v>-0.23</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>68.02</v>
@@ -23436,7 +23436,7 @@
         <v>2.32</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>67.39</v>
@@ -23511,7 +23511,7 @@
         <v>1.36</v>
       </c>
       <c r="I305" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>66.91</v>
@@ -23586,7 +23586,7 @@
         <v>1.01</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>66.54000000000001</v>
@@ -23661,7 +23661,7 @@
         <v>-1.16</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>66.31999999999999</v>
@@ -23736,7 +23736,7 @@
         <v>5.51</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>66.26000000000001</v>
@@ -23811,7 +23811,7 @@
         <v>-0.28</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>66.27</v>
@@ -23886,7 +23886,7 @@
         <v>-0.84</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>66.40000000000001</v>
@@ -23961,7 +23961,7 @@
         <v>3.35</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>66.8</v>
@@ -24036,7 +24036,7 @@
         <v>-2.01</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>67.33</v>
@@ -24111,7 +24111,7 @@
         <v>-5.07</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>67.63</v>
@@ -24186,7 +24186,7 @@
         <v>2.74</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>68</v>
@@ -24261,7 +24261,7 @@
         <v>-2.83</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>68.16</v>
@@ -24336,7 +24336,7 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>68.56</v>
@@ -24411,7 +24411,7 @@
         <v>-0.67</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>68.8</v>
@@ -24490,7 +24490,7 @@
         <v>-3.12</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>68.94</v>
@@ -24569,7 +24569,7 @@
         <v>-2.05</v>
       </c>
       <c r="I319" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>68.77</v>
@@ -24644,7 +24644,7 @@
         <v>2.81</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>68.7</v>
@@ -24719,7 +24719,7 @@
         <v>2.45</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>68.81999999999999</v>
@@ -24794,7 +24794,7 @@
         <v>-3.44</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>68.81999999999999</v>
@@ -24873,7 +24873,7 @@
         <v>-0.05</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>68.81999999999999</v>
@@ -24948,7 +24948,7 @@
         <v>6.4</v>
       </c>
       <c r="I324" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>68.95</v>
@@ -25023,7 +25023,7 @@
         <v>2.1</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>69.11</v>
@@ -25098,7 +25098,7 @@
         <v>1.97</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>69.31</v>
@@ -25173,7 +25173,7 @@
         <v>6.83</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>69.79000000000001</v>
@@ -25248,7 +25248,7 @@
         <v>0.71</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>70.12</v>
@@ -25323,7 +25323,7 @@
         <v>1.02</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>70.48999999999999</v>
@@ -25398,7 +25398,7 @@
         <v>-4.84</v>
       </c>
       <c r="I330" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" t="n">
         <v>70.70999999999999</v>
@@ -25473,7 +25473,7 @@
         <v>-8.57</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>70.48</v>
@@ -25552,7 +25552,7 @@
         <v>1.3</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>70.37</v>
@@ -25627,7 +25627,7 @@
         <v>-4.35</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>70.29000000000001</v>
@@ -25702,7 +25702,7 @@
         <v>2.74</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>70.20999999999999</v>
@@ -25777,7 +25777,7 @@
         <v>1.05</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>70.26000000000001</v>
@@ -25852,7 +25852,7 @@
         <v>-1.57</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>70.23999999999999</v>
@@ -25927,7 +25927,7 @@
         <v>1.99</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>70.31</v>
@@ -26002,7 +26002,7 @@
         <v>-3.18</v>
       </c>
       <c r="I338" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>70.37</v>
@@ -26077,7 +26077,7 @@
         <v>1.27</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>70.55</v>
@@ -26152,7 +26152,7 @@
         <v>-0.04</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>70.63</v>
@@ -26227,7 +26227,7 @@
         <v>-0.97</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>70.59999999999999</v>
@@ -26302,7 +26302,7 @@
         <v>0.47</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>70.7</v>
@@ -26377,7 +26377,7 @@
         <v>-2.62</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>70.72</v>
@@ -26452,7 +26452,7 @@
         <v>1.16</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>70.56</v>
@@ -26527,7 +26527,7 @@
         <v>-8.08</v>
       </c>
       <c r="I345" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>70.06</v>
@@ -26602,7 +26602,7 @@
         <v>0.02</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>69.48999999999999</v>
@@ -26677,7 +26677,7 @@
         <v>-4.17</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>68.54000000000001</v>
@@ -26756,7 +26756,7 @@
         <v>-2.29</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>67.48999999999999</v>
@@ -26835,7 +26835,7 @@
         <v>5.48</v>
       </c>
       <c r="I349" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>66.56999999999999</v>
@@ -26910,7 +26910,7 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>65.86</v>
@@ -26985,7 +26985,7 @@
         <v>3.56</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>65.58</v>
@@ -27060,7 +27060,7 @@
         <v>-0.13</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>65.25</v>
@@ -27135,7 +27135,7 @@
         <v>-4.39</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>64.94</v>
@@ -27210,7 +27210,7 @@
         <v>-1.81</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>64.47</v>
@@ -27285,7 +27285,7 @@
         <v>-1.01</v>
       </c>
       <c r="I355" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>63.95</v>
@@ -27360,7 +27360,7 @@
         <v>-5.4</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>63.32</v>
@@ -27439,7 +27439,7 @@
         <v>-7.09</v>
       </c>
       <c r="I357" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>62.42</v>
@@ -27518,7 +27518,7 @@
         <v>1.12</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>61.66</v>
@@ -27597,7 +27597,7 @@
         <v>1.76</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>60.91</v>
@@ -27672,7 +27672,7 @@
         <v>-1.13</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>60.12</v>
@@ -27747,7 +27747,7 @@
         <v>1.5</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>59.42</v>
@@ -27822,7 +27822,7 @@
         <v>0.21</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>58.69</v>
@@ -27897,7 +27897,7 @@
         <v>2.69</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>58.14</v>
@@ -27972,7 +27972,7 @@
         <v>1.98</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>57.59</v>
@@ -28047,7 +28047,7 @@
         <v>-2.94</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>57.24</v>
@@ -28126,7 +28126,7 @@
         <v>-2.99</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>56.8</v>
@@ -28205,7 +28205,7 @@
         <v>2.48</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>56.55</v>
@@ -28280,7 +28280,7 @@
         <v>-0.35</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>56.37</v>
@@ -28355,7 +28355,7 @@
         <v>-3.32</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>55.94</v>
@@ -28430,7 +28430,7 @@
         <v>1.94</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>55.53</v>
@@ -28505,7 +28505,7 @@
         <v>-1.81</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>54.97</v>
@@ -28580,7 +28580,7 @@
         <v>-3.49</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>54.32</v>
@@ -28655,7 +28655,7 @@
         <v>0.77</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>53.83</v>
@@ -28730,7 +28730,7 @@
         <v>0.39</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>53.4</v>
@@ -28803,7 +28803,7 @@
         <v>4.12</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>53.11</v>
@@ -28876,7 +28876,7 @@
         <v>1.58</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>53.02</v>
@@ -28949,7 +28949,7 @@
         <v>-3.45</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>53.03</v>
@@ -29026,7 +29026,7 @@
         <v>1.02</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>53.04</v>
@@ -29099,7 +29099,7 @@
         <v>0.65</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>53.03</v>
@@ -29172,7 +29172,7 @@
         <v>-2.32</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>52.98</v>
@@ -29245,7 +29245,7 @@
         <v>0.14</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>52.89</v>
@@ -29318,7 +29318,7 @@
         <v>3.34</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>52.89</v>
@@ -29391,7 +29391,7 @@
         <v>-2.13</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>52.75</v>
@@ -29468,7 +29468,7 @@
         <v>0.19</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>52.57</v>
@@ -29541,7 +29541,7 @@
         <v>2.63</v>
       </c>
       <c r="I385" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>52.54</v>
@@ -29614,7 +29614,7 @@
         <v>4.14</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>52.7</v>
@@ -29687,7 +29687,7 @@
         <v>-0.39</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>52.79</v>
@@ -29760,7 +29760,7 @@
         <v>2.95</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>52.97</v>
@@ -29833,7 +29833,7 @@
         <v>3.32</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>53.33</v>
@@ -29906,7 +29906,7 @@
         <v>-1.45</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>53.6</v>
@@ -29979,7 +29979,7 @@
         <v>0.87</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>53.94</v>
@@ -30052,7 +30052,7 @@
         <v>-1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>54.33</v>
@@ -30125,7 +30125,7 @@
         <v>0.55</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>54.71</v>
@@ -30198,7 +30198,7 @@
         <v>1.86</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>55.14</v>
@@ -30271,7 +30271,7 @@
         <v>-3.58</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>55.36</v>
@@ -30348,7 +30348,7 @@
         <v>4.47</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>55.67</v>
@@ -30421,7 +30421,7 @@
         <v>2.75</v>
       </c>
       <c r="I397" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>56.15</v>
@@ -30494,7 +30494,7 @@
         <v>1.72</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>56.65</v>
@@ -30567,7 +30567,7 @@
         <v>-0.83</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>57.12</v>
@@ -30640,7 +30640,7 @@
         <v>0.19</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>57.65</v>
@@ -30713,7 +30713,7 @@
         <v>-1.17</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>58.14</v>
@@ -30786,7 +30786,7 @@
         <v>1.92</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>58.6</v>
@@ -30859,7 +30859,7 @@
         <v>-4.38</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>58.98</v>
@@ -30932,7 +30932,7 @@
         <v>0.18</v>
       </c>
       <c r="I404" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>59.37</v>
@@ -31005,7 +31005,7 @@
         <v>-3.68</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>59.57</v>
@@ -31082,7 +31082,7 @@
         <v>1.99</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>59.72</v>
@@ -31155,7 +31155,7 @@
         <v>2.51</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>59.96</v>
@@ -31228,7 +31228,7 @@
         <v>-1.21</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>60.07</v>
@@ -31305,7 +31305,7 @@
         <v>-0.75</v>
       </c>
       <c r="I409" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" t="n">
         <v>60.07</v>
@@ -31378,7 +31378,7 @@
         <v>2.27</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>60.18</v>
@@ -31451,7 +31451,7 @@
         <v>-5.3</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>60.1</v>
@@ -31528,7 +31528,7 @@
         <v>1.08</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>60.1</v>
@@ -31592,31 +31592,31 @@
         <v>56.65</v>
       </c>
       <c r="F413" t="n">
-        <v>57.49</v>
+        <v>56.84</v>
       </c>
       <c r="G413" t="n">
-        <v>10120231</v>
+        <v>14091770</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.08</v>
+        <v>-2.2</v>
       </c>
       <c r="I413" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>60.05</v>
+        <v>60.02</v>
       </c>
       <c r="K413" t="n">
-        <v>56.2</v>
+        <v>56.19</v>
       </c>
       <c r="L413" t="n">
-        <v>61.91</v>
+        <v>61.9</v>
       </c>
       <c r="M413" t="n">
         <v>65.63</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>35.92</v>
+        <v>34.58</v>
       </c>
       <c r="O413" t="n">
         <v>31</v>
@@ -31633,16 +31633,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31443,7 +31443,7 @@
         <v>58.12</v>
       </c>
       <c r="G411" t="n">
-        <v>15669800</v>
+        <v>15711600</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>1.08</v>
@@ -31503,28 +31503,44 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="D412" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="E412" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="F412" t="n">
+        <v>56.84</v>
+      </c>
       <c r="G412" t="n">
-        <v>14091770</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>14116900</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>-2.2</v>
       </c>
       <c r="I412" t="n">
         <v>5.2</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="K412" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="L412" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="M412" t="n">
+        <v>65.63</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>37.33</v>
+        <v>34.58</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31543,9 +31559,7 @@
       <c r="T412" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>152.1</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>27.34</v>
@@ -683,7 +683,7 @@
         <v>-1.61</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>27.36</v>
@@ -762,7 +762,7 @@
         <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>27.38</v>
@@ -837,7 +837,7 @@
         <v>1.34</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>27.44</v>
@@ -912,7 +912,7 @@
         <v>2.57</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>27.56</v>
@@ -987,7 +987,7 @@
         <v>-0.73</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>27.67</v>
@@ -1062,7 +1062,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>27.75</v>
@@ -1137,7 +1137,7 @@
         <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>27.87</v>
@@ -1212,7 +1212,7 @@
         <v>0.44</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>27.97</v>
@@ -1287,7 +1287,7 @@
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>28.07</v>
@@ -1362,7 +1362,7 @@
         <v>-1.19</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>28.16</v>
@@ -1437,7 +1437,7 @@
         <v>0.59</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>28.24</v>
@@ -1512,7 +1512,7 @@
         <v>-0.68</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>28.34</v>
@@ -1587,7 +1587,7 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>28.44</v>
@@ -1662,7 +1662,7 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>28.52</v>
@@ -1737,7 +1737,7 @@
         <v>-0.51</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>28.58</v>
@@ -1812,7 +1812,7 @@
         <v>2.05</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>28.7</v>
@@ -1887,7 +1887,7 @@
         <v>-0.33</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>28.79</v>
@@ -1962,7 +1962,7 @@
         <v>0.47</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>28.88</v>
@@ -2037,7 +2037,7 @@
         <v>-1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>28.97</v>
@@ -2112,7 +2112,7 @@
         <v>-0.51</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.05</v>
@@ -2187,7 +2187,7 @@
         <v>-2.07</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.12</v>
@@ -2266,7 +2266,7 @@
         <v>0.38</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.18</v>
@@ -2341,7 +2341,7 @@
         <v>-1.87</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.2</v>
@@ -2416,7 +2416,7 @@
         <v>-0.32</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.18</v>
@@ -2495,7 +2495,7 @@
         <v>1.55</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.19</v>
@@ -2570,7 +2570,7 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.21</v>
@@ -2645,7 +2645,7 @@
         <v>2.66</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.24</v>
@@ -2720,7 +2720,7 @@
         <v>-0.27</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.26</v>
@@ -2795,7 +2795,7 @@
         <v>-0.34</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.27</v>
@@ -2870,7 +2870,7 @@
         <v>-1.62</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.27</v>
@@ -2953,7 +2953,7 @@
         <v>2.92</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.31</v>
@@ -3032,7 +3032,7 @@
         <v>0.87</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.37</v>
@@ -3107,7 +3107,7 @@
         <v>1.72</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.44</v>
@@ -3182,7 +3182,7 @@
         <v>-0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.5</v>
@@ -3257,7 +3257,7 @@
         <v>0.33</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.58</v>
@@ -3332,7 +3332,7 @@
         <v>0.13</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>29.62</v>
@@ -3407,7 +3407,7 @@
         <v>-0.32</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>29.67</v>
@@ -3482,7 +3482,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>29.7</v>
@@ -3557,7 +3557,7 @@
         <v>-1.57</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>29.72</v>
@@ -3632,7 +3632,7 @@
         <v>-0.2</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>29.75</v>
@@ -3707,7 +3707,7 @@
         <v>2.07</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>29.83</v>
@@ -3782,7 +3782,7 @@
         <v>-0.16</v>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>29.91</v>
@@ -3857,7 +3857,7 @@
         <v>2.59</v>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>30.06</v>
@@ -3932,7 +3932,7 @@
         <v>-1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>30.19</v>
@@ -4007,7 +4007,7 @@
         <v>-0.03</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>30.3</v>
@@ -4082,7 +4082,7 @@
         <v>-1.16</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>30.39</v>
@@ -4157,7 +4157,7 @@
         <v>0.42</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>30.44</v>
@@ -4232,7 +4232,7 @@
         <v>-6.08</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>30.4</v>
@@ -4315,7 +4315,7 @@
         <v>-6.27</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>30.27</v>
@@ -4398,7 +4398,7 @@
         <v>0.22</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>30.17</v>
@@ -4481,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>30.03</v>
@@ -4564,7 +4564,7 @@
         <v>3.39</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.92</v>
@@ -4643,7 +4643,7 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.8</v>
@@ -4722,7 +4722,7 @@
         <v>3.22</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.72</v>
@@ -4801,7 +4801,7 @@
         <v>0.65</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.65</v>
@@ -4876,7 +4876,7 @@
         <v>0.1</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.58</v>
@@ -4951,7 +4951,7 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.53</v>
@@ -5030,7 +5030,7 @@
         <v>-0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.48</v>
@@ -5109,7 +5109,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.47</v>
@@ -5184,7 +5184,7 @@
         <v>-0.97</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.45</v>
@@ -5259,7 +5259,7 @@
         <v>3.59</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.45</v>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.45</v>
@@ -5413,7 +5413,7 @@
         <v>-1.67</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.39</v>
@@ -5488,7 +5488,7 @@
         <v>0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.35</v>
@@ -5563,7 +5563,7 @@
         <v>-1.19</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.29</v>
@@ -5638,7 +5638,7 @@
         <v>-0.77</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.24</v>
@@ -5717,7 +5717,7 @@
         <v>-0.71</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.17</v>
@@ -5792,7 +5792,7 @@
         <v>-0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.18</v>
@@ -5871,7 +5871,7 @@
         <v>1.24</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.3</v>
@@ -5946,7 +5946,7 @@
         <v>2.51</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.45</v>
@@ -6021,7 +6021,7 @@
         <v>-2.42</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.57</v>
@@ -6100,7 +6100,7 @@
         <v>-0.1</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.64</v>
@@ -6175,7 +6175,7 @@
         <v>1.15</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6250,7 +6250,7 @@
         <v>-0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.74</v>
@@ -6329,7 +6329,7 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.77</v>
@@ -6404,7 +6404,7 @@
         <v>-2.27</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.76</v>
@@ -6483,7 +6483,7 @@
         <v>1.23</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.75</v>
@@ -6558,7 +6558,7 @@
         <v>-1.05</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6633,7 +6633,7 @@
         <v>0.41</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>29.72</v>
@@ -6708,7 +6708,7 @@
         <v>2.41</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.75</v>
@@ -6783,7 +6783,7 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.75</v>
@@ -6858,7 +6858,7 @@
         <v>-1.57</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.72</v>
@@ -6933,7 +6933,7 @@
         <v>1.4</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>29.74</v>
@@ -7008,7 +7008,7 @@
         <v>-0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>29.74</v>
@@ -7083,7 +7083,7 @@
         <v>-0.83</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>29.75</v>
@@ -7158,7 +7158,7 @@
         <v>1.07</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>29.79</v>
@@ -7233,7 +7233,7 @@
         <v>-0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>29.82</v>
@@ -7308,7 +7308,7 @@
         <v>5.3</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>29.94</v>
@@ -7383,7 +7383,7 @@
         <v>-0.47</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>30.04</v>
@@ -7458,7 +7458,7 @@
         <v>-0.32</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>30.09</v>
@@ -7533,7 +7533,7 @@
         <v>3.54</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>30.24</v>
@@ -7608,7 +7608,7 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>30.4</v>
@@ -7683,7 +7683,7 @@
         <v>2.14</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>30.58</v>
@@ -7758,7 +7758,7 @@
         <v>-0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>30.76</v>
@@ -7833,7 +7833,7 @@
         <v>-0.84</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>30.91</v>
@@ -7908,7 +7908,7 @@
         <v>0.33</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>31.1</v>
@@ -7983,7 +7983,7 @@
         <v>-0.27</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>31.27</v>
@@ -8058,7 +8058,7 @@
         <v>0.18</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>31.46</v>
@@ -8133,7 +8133,7 @@
         <v>2.15</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>31.68</v>
@@ -8208,7 +8208,7 @@
         <v>-1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>31.83</v>
@@ -8283,7 +8283,7 @@
         <v>-1.65</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>31.94</v>
@@ -8358,7 +8358,7 @@
         <v>0.73</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>32.09</v>
@@ -8433,7 +8433,7 @@
         <v>-1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>32.2</v>
@@ -8508,7 +8508,7 @@
         <v>1.23</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>32.34</v>
@@ -8583,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>32.5</v>
@@ -8658,7 +8658,7 @@
         <v>-2.16</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>32.62</v>
@@ -8733,7 +8733,7 @@
         <v>0.58</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>32.76</v>
@@ -8808,7 +8808,7 @@
         <v>-0.24</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>32.82</v>
@@ -8887,7 +8887,7 @@
         <v>1.56</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>32.91</v>
@@ -8962,7 +8962,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.02</v>
@@ -9037,7 +9037,7 @@
         <v>-0.24</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.07</v>
@@ -9112,7 +9112,7 @@
         <v>-0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.1</v>
@@ -9187,7 +9187,7 @@
         <v>-0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>33.08</v>
@@ -9266,7 +9266,7 @@
         <v>2.27</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>33.1</v>
@@ -9341,7 +9341,7 @@
         <v>3.79</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>33.21</v>
@@ -9416,7 +9416,7 @@
         <v>-1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>33.28</v>
@@ -9491,7 +9491,7 @@
         <v>-1.07</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>33.35</v>
@@ -9566,7 +9566,7 @@
         <v>0.44</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>33.42</v>
@@ -9641,7 +9641,7 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>33.46</v>
@@ -9716,7 +9716,7 @@
         <v>-0.12</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>33.53</v>
@@ -9791,7 +9791,7 @@
         <v>2.14</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>33.66</v>
@@ -9866,7 +9866,7 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>33.8</v>
@@ -9941,7 +9941,7 @@
         <v>-0.08</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>33.95</v>
@@ -10016,7 +10016,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.08</v>
@@ -10091,7 +10091,7 @@
         <v>-2.34</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.14</v>
@@ -10166,7 +10166,7 @@
         <v>-0.06</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.24</v>
@@ -10241,7 +10241,7 @@
         <v>0.06</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>34.34</v>
@@ -10316,7 +10316,7 @@
         <v>-3.32</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.38</v>
@@ -10395,7 +10395,7 @@
         <v>-0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.38</v>
@@ -10470,7 +10470,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.38</v>
@@ -10545,7 +10545,7 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.41</v>
@@ -10620,7 +10620,7 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.46</v>
@@ -10695,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.53</v>
@@ -10770,7 +10770,7 @@
         <v>1.19</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10845,7 +10845,7 @@
         <v>0.35</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.58</v>
@@ -10920,7 +10920,7 @@
         <v>-2.01</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.55</v>
@@ -10999,7 +10999,7 @@
         <v>0.67</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.56</v>
@@ -11074,7 +11074,7 @@
         <v>1.71</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.59</v>
@@ -11149,7 +11149,7 @@
         <v>-1.43</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.58</v>
@@ -11228,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.58</v>
@@ -11303,7 +11303,7 @@
         <v>0.14</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>34.54</v>
@@ -11378,7 +11378,7 @@
         <v>-1.97</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>34.44</v>
@@ -11457,7 +11457,7 @@
         <v>1.65</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>34.38</v>
@@ -11532,7 +11532,7 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>34.34</v>
@@ -11607,7 +11607,7 @@
         <v>2.11</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>34.37</v>
@@ -11682,7 +11682,7 @@
         <v>-0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>34.39</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>34.41</v>
@@ -11832,7 +11832,7 @@
         <v>-0.09</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>34.48</v>
@@ -11907,7 +11907,7 @@
         <v>1.51</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>34.59</v>
@@ -11982,7 +11982,7 @@
         <v>1.89</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>34.72</v>
@@ -12057,7 +12057,7 @@
         <v>2.65</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>34.88</v>
@@ -12132,7 +12132,7 @@
         <v>0.51</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>35.03</v>
@@ -12207,7 +12207,7 @@
         <v>-1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>35.16</v>
@@ -12282,7 +12282,7 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>35.28</v>
@@ -12357,7 +12357,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>35.41</v>
@@ -12432,7 +12432,7 @@
         <v>-0.88</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>35.56</v>
@@ -12507,7 +12507,7 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>35.71</v>
@@ -12582,7 +12582,7 @@
         <v>1.02</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>35.85</v>
@@ -12657,7 +12657,7 @@
         <v>1.46</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>36.04</v>
@@ -12732,7 +12732,7 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>36.26</v>
@@ -12807,7 +12807,7 @@
         <v>-0.41</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>36.46</v>
@@ -12882,7 +12882,7 @@
         <v>-2.1</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>36.66</v>
@@ -12957,7 +12957,7 @@
         <v>0.53</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>36.83</v>
@@ -13032,7 +13032,7 @@
         <v>2.76</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>37.06</v>
@@ -13107,7 +13107,7 @@
         <v>2.56</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>37.29</v>
@@ -13182,7 +13182,7 @@
         <v>-0.2</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>37.54</v>
@@ -13257,7 +13257,7 @@
         <v>-0.35</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>37.78</v>
@@ -13332,7 +13332,7 @@
         <v>3.04</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>38.08</v>
@@ -13407,7 +13407,7 @@
         <v>2.02</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>38.4</v>
@@ -13482,7 +13482,7 @@
         <v>1.53</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>38.71</v>
@@ -13557,7 +13557,7 @@
         <v>-0.31</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>38.97</v>
@@ -13632,7 +13632,7 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>39.25</v>
@@ -13707,7 +13707,7 @@
         <v>-0.89</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>39.53</v>
@@ -13782,7 +13782,7 @@
         <v>2.33</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>39.85</v>
@@ -13857,7 +13857,7 @@
         <v>1.24</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>40.17</v>
@@ -13932,7 +13932,7 @@
         <v>-1.52</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>40.49</v>
@@ -14007,7 +14007,7 @@
         <v>2.7</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>40.84</v>
@@ -14082,7 +14082,7 @@
         <v>0.34</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>41.19</v>
@@ -14157,7 +14157,7 @@
         <v>1.61</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>41.54</v>
@@ -14232,7 +14232,7 @@
         <v>4.03</v>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>41.97</v>
@@ -14307,7 +14307,7 @@
         <v>-0.97</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>42.38</v>
@@ -14382,7 +14382,7 @@
         <v>3.27</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>42.91</v>
@@ -14457,7 +14457,7 @@
         <v>1.74</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>43.46</v>
@@ -14532,7 +14532,7 @@
         <v>-4.43</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>43.86</v>
@@ -14607,7 +14607,7 @@
         <v>1.55</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>44.25</v>
@@ -14682,7 +14682,7 @@
         <v>-8.24</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>44.44</v>
@@ -14761,7 +14761,7 @@
         <v>0.21</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>44.64</v>
@@ -14836,7 +14836,7 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>44.8</v>
@@ -14911,7 +14911,7 @@
         <v>-0.43</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>44.9</v>
@@ -14986,7 +14986,7 @@
         <v>-3.61</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>44.9</v>
@@ -15061,7 +15061,7 @@
         <v>0.71</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>44.92</v>
@@ -15136,7 +15136,7 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>44.93</v>
@@ -15211,7 +15211,7 @@
         <v>2.57</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>45.02</v>
@@ -15286,7 +15286,7 @@
         <v>-0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>45.05</v>
@@ -15361,7 +15361,7 @@
         <v>-0.57</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>45.03</v>
@@ -15436,7 +15436,7 @@
         <v>-2.33</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>45</v>
@@ -15511,7 +15511,7 @@
         <v>2.13</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.95</v>
@@ -15586,7 +15586,7 @@
         <v>-0.23</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.9</v>
@@ -15661,7 +15661,7 @@
         <v>0.85</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>44.82</v>
@@ -15736,7 +15736,7 @@
         <v>4.26</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>44.75</v>
@@ -15811,7 +15811,7 @@
         <v>1.44</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>44.73</v>
@@ -15886,7 +15886,7 @@
         <v>4.03</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>44.73</v>
@@ -15961,7 +15961,7 @@
         <v>-1.86</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>44.64</v>
@@ -16036,7 +16036,7 @@
         <v>-3.08</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>44.59</v>
@@ -16111,7 +16111,7 @@
         <v>-1.07</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>44.48</v>
@@ -16186,7 +16186,7 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>44.59</v>
@@ -16261,7 +16261,7 @@
         <v>0.76</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>44.72</v>
@@ -16336,7 +16336,7 @@
         <v>-1.44</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>44.8</v>
@@ -16415,7 +16415,7 @@
         <v>-1.05</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>44.87</v>
@@ -16490,7 +16490,7 @@
         <v>2.94</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>45.08</v>
@@ -16565,7 +16565,7 @@
         <v>0.09</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>45.28</v>
@@ -16640,7 +16640,7 @@
         <v>3.71</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>45.54</v>
@@ -16715,7 +16715,7 @@
         <v>5.81</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>45.88</v>
@@ -16790,7 +16790,7 @@
         <v>2.56</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>46.3</v>
@@ -16865,7 +16865,7 @@
         <v>1.16</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>46.77</v>
@@ -16940,7 +16940,7 @@
         <v>-0.11</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>47.29</v>
@@ -17015,7 +17015,7 @@
         <v>-2.47</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>47.7</v>
@@ -17090,7 +17090,7 @@
         <v>2.3</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>48.16</v>
@@ -17165,7 +17165,7 @@
         <v>-0.45</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>48.6</v>
@@ -17240,7 +17240,7 @@
         <v>4.67</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>49.07</v>
@@ -17315,7 +17315,7 @@
         <v>1.63</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>49.55</v>
@@ -17390,7 +17390,7 @@
         <v>2.76</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>50.02</v>
@@ -17465,7 +17465,7 @@
         <v>-2.64</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>50.45</v>
@@ -17540,7 +17540,7 @@
         <v>3.58</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>51.06</v>
@@ -17615,7 +17615,7 @@
         <v>-0.65</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>51.67</v>
@@ -17690,7 +17690,7 @@
         <v>4.38</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>52.38</v>
@@ -17765,7 +17765,7 @@
         <v>-1.56</v>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" t="n">
         <v>53.03</v>
@@ -17840,7 +17840,7 @@
         <v>2.71</v>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>53.78</v>
@@ -17915,7 +17915,7 @@
         <v>2.53</v>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" t="n">
         <v>54.64</v>
@@ -17990,7 +17990,7 @@
         <v>3.79</v>
       </c>
       <c r="I232" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" t="n">
         <v>55.55</v>
@@ -18065,7 +18065,7 @@
         <v>0.59</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>56.48</v>
@@ -18140,7 +18140,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>57.62</v>
@@ -18215,7 +18215,7 @@
         <v>-7.19</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" s="4" t="n">
         <v>58.36</v>
@@ -18290,7 +18290,7 @@
         <v>4.5</v>
       </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" t="n">
         <v>59.18</v>
@@ -18365,7 +18365,7 @@
         <v>-6.61</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>59.74</v>
@@ -18440,7 +18440,7 @@
         <v>2.06</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>60.38</v>
@@ -18515,7 +18515,7 @@
         <v>5.06</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>61.24</v>
@@ -18590,7 +18590,7 @@
         <v>6.7</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>62.28</v>
@@ -18665,7 +18665,7 @@
         <v>-3.73</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>63.19</v>
@@ -18740,7 +18740,7 @@
         <v>-1.76</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>63.92</v>
@@ -18815,7 +18815,7 @@
         <v>3.83</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>64.73999999999999</v>
@@ -18890,7 +18890,7 @@
         <v>6.7</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>65.72</v>
@@ -18965,7 +18965,7 @@
         <v>1.77</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>66.84</v>
@@ -19040,7 +19040,7 @@
         <v>7.58</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>68.16</v>
@@ -19115,7 +19115,7 @@
         <v>-1.47</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>69.44</v>
@@ -19190,7 +19190,7 @@
         <v>-2.76</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>70.48</v>
@@ -19265,7 +19265,7 @@
         <v>5.39</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>71.78</v>
@@ -19340,7 +19340,7 @@
         <v>-1.67</v>
       </c>
       <c r="I250" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" t="n">
         <v>72.94</v>
@@ -19415,7 +19415,7 @@
         <v>3.78</v>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" t="n">
         <v>74.17</v>
@@ -19490,7 +19490,7 @@
         <v>6.63</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>75.56999999999999</v>
@@ -19565,7 +19565,7 @@
         <v>5.84</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>77.23</v>
@@ -19640,7 +19640,7 @@
         <v>3.3</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>78.75</v>
@@ -19715,7 +19715,7 @@
         <v>3.95</v>
       </c>
       <c r="I255" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" t="n">
         <v>80.73</v>
@@ -19790,7 +19790,7 @@
         <v>-0.03</v>
       </c>
       <c r="I256" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" t="n">
         <v>82.56</v>
@@ -19865,7 +19865,7 @@
         <v>-28.54</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" s="4" t="n">
         <v>83.11</v>
@@ -19944,7 +19944,7 @@
         <v>-3.98</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>83.45</v>
@@ -20019,7 +20019,7 @@
         <v>6.24</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>83.84</v>
@@ -20094,7 +20094,7 @@
         <v>2.88</v>
       </c>
       <c r="I260" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" t="n">
         <v>84.11</v>
@@ -20169,7 +20169,7 @@
         <v>-15.77</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" s="4" t="n">
         <v>83.90000000000001</v>
@@ -20244,7 +20244,7 @@
         <v>5.25</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>83.92</v>
@@ -20319,7 +20319,7 @@
         <v>8.33</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>84.11</v>
@@ -20394,7 +20394,7 @@
         <v>-3.46</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>83.92</v>
@@ -20469,7 +20469,7 @@
         <v>4.29</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>83.81999999999999</v>
@@ -20544,7 +20544,7 @@
         <v>-11.53</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>82.97</v>
@@ -20619,7 +20619,7 @@
         <v>2.94</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>82.29000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>-4.8</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>81.56</v>
@@ -20773,7 +20773,7 @@
         <v>5.6</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>80.8</v>
@@ -20848,7 +20848,7 @@
         <v>1.31</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>80.15000000000001</v>
@@ -20923,7 +20923,7 @@
         <v>7.9</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>79.62</v>
@@ -20998,7 +20998,7 @@
         <v>5.16</v>
       </c>
       <c r="I272" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" t="n">
         <v>79.01000000000001</v>
@@ -21073,7 +21073,7 @@
         <v>-1.85</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>78.04000000000001</v>
@@ -21148,7 +21148,7 @@
         <v>1.21</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>76.97</v>
@@ -21223,7 +21223,7 @@
         <v>0.51</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>75.70999999999999</v>
@@ -21298,7 +21298,7 @@
         <v>5.64</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>74.68000000000001</v>
@@ -21373,7 +21373,7 @@
         <v>-4.02</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>74.98999999999999</v>
@@ -21448,7 +21448,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I278" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21527,7 +21527,7 @@
         <v>0.88</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>75.02</v>
@@ -21602,7 +21602,7 @@
         <v>-1.42</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>74.77</v>
@@ -21681,7 +21681,7 @@
         <v>2.25</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>75.23</v>
@@ -21760,7 +21760,7 @@
         <v>3.06</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>75.64</v>
@@ -21835,7 +21835,7 @@
         <v>2.34</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>75.84</v>
@@ -21910,7 +21910,7 @@
         <v>-2.72</v>
       </c>
       <c r="I284" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" t="n">
         <v>76.06</v>
@@ -21985,7 +21985,7 @@
         <v>-1.84</v>
       </c>
       <c r="I285" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" t="n">
         <v>76.06</v>
@@ -22054,7 +22054,7 @@
         <v>-4.96</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>76.31</v>
@@ -22137,7 +22137,7 @@
         <v>0.73</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>76.48</v>
@@ -22212,7 +22212,7 @@
         <v>-2.13</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>76.75</v>
@@ -22287,7 +22287,7 @@
         <v>-4.13</v>
       </c>
       <c r="I289" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" t="n">
         <v>76.68000000000001</v>
@@ -22362,7 +22362,7 @@
         <v>-4.4</v>
       </c>
       <c r="I290" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" t="n">
         <v>76.41</v>
@@ -22437,7 +22437,7 @@
         <v>-6.33</v>
       </c>
       <c r="I291" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" s="4" t="n">
         <v>75.66</v>
@@ -22520,7 +22520,7 @@
         <v>1.54</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>74.75</v>
@@ -22595,7 +22595,7 @@
         <v>0.77</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>73.95</v>
@@ -22670,7 +22670,7 @@
         <v>3.59</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>73.2</v>
@@ -22745,7 +22745,7 @@
         <v>-6.81</v>
       </c>
       <c r="I295" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" s="4" t="n">
         <v>72.22</v>
@@ -22824,7 +22824,7 @@
         <v>4.39</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>71.14</v>
@@ -22903,7 +22903,7 @@
         <v>0.13</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>70.23999999999999</v>
@@ -22978,7 +22978,7 @@
         <v>7.27</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>69.91</v>
@@ -23053,7 +23053,7 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>69.55</v>
@@ -23128,7 +23128,7 @@
         <v>-3.45</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>69.13</v>
@@ -23203,7 +23203,7 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>68.64</v>
@@ -23278,7 +23278,7 @@
         <v>-0.23</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>68.02</v>
@@ -23357,7 +23357,7 @@
         <v>2.32</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>67.39</v>
@@ -23432,7 +23432,7 @@
         <v>1.36</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>66.91</v>
@@ -23507,7 +23507,7 @@
         <v>1.01</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>66.54000000000001</v>
@@ -23582,7 +23582,7 @@
         <v>-1.16</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>66.31999999999999</v>
@@ -23657,7 +23657,7 @@
         <v>5.51</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>66.26000000000001</v>
@@ -23732,7 +23732,7 @@
         <v>-0.28</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>66.27</v>
@@ -23807,7 +23807,7 @@
         <v>-0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>66.40000000000001</v>
@@ -23882,7 +23882,7 @@
         <v>3.35</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>66.8</v>
@@ -23957,7 +23957,7 @@
         <v>-2.01</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>67.33</v>
@@ -24032,7 +24032,7 @@
         <v>-5.07</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>67.63</v>
@@ -24107,7 +24107,7 @@
         <v>2.74</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>68</v>
@@ -24182,7 +24182,7 @@
         <v>-2.83</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>68.16</v>
@@ -24257,7 +24257,7 @@
         <v>0.6</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>68.56</v>
@@ -24332,7 +24332,7 @@
         <v>-0.67</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>68.8</v>
@@ -24411,7 +24411,7 @@
         <v>-3.12</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>68.94</v>
@@ -24490,7 +24490,7 @@
         <v>-2.05</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>68.77</v>
@@ -24565,7 +24565,7 @@
         <v>2.81</v>
       </c>
       <c r="I319" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" t="n">
         <v>68.7</v>
@@ -24640,7 +24640,7 @@
         <v>2.45</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>68.81999999999999</v>
@@ -24715,7 +24715,7 @@
         <v>-3.44</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>68.81999999999999</v>
@@ -24794,7 +24794,7 @@
         <v>-0.05</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>68.81999999999999</v>
@@ -24869,7 +24869,7 @@
         <v>6.4</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>68.95</v>
@@ -24944,7 +24944,7 @@
         <v>2.1</v>
       </c>
       <c r="I324" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" t="n">
         <v>69.11</v>
@@ -25019,7 +25019,7 @@
         <v>1.97</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>69.31</v>
@@ -25094,7 +25094,7 @@
         <v>6.83</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>69.79000000000001</v>
@@ -25169,7 +25169,7 @@
         <v>0.71</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.12</v>
@@ -25244,7 +25244,7 @@
         <v>1.02</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.48999999999999</v>
@@ -25319,7 +25319,7 @@
         <v>-4.84</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>70.70999999999999</v>
@@ -25394,7 +25394,7 @@
         <v>-8.57</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>70.48</v>
@@ -25473,7 +25473,7 @@
         <v>1.3</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.37</v>
@@ -25548,7 +25548,7 @@
         <v>-4.35</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.29000000000001</v>
@@ -25623,7 +25623,7 @@
         <v>2.74</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>70.20999999999999</v>
@@ -25698,7 +25698,7 @@
         <v>1.05</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>70.26000000000001</v>
@@ -25773,7 +25773,7 @@
         <v>-1.57</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>70.23999999999999</v>
@@ -25848,7 +25848,7 @@
         <v>1.99</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>70.31</v>
@@ -25923,7 +25923,7 @@
         <v>-3.18</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>70.37</v>
@@ -25998,7 +25998,7 @@
         <v>1.27</v>
       </c>
       <c r="I338" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" t="n">
         <v>70.55</v>
@@ -26073,7 +26073,7 @@
         <v>-0.04</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>70.63</v>
@@ -26148,7 +26148,7 @@
         <v>-0.97</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>70.59999999999999</v>
@@ -26223,7 +26223,7 @@
         <v>0.47</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>70.7</v>
@@ -26298,7 +26298,7 @@
         <v>-2.62</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>70.72</v>
@@ -26373,7 +26373,7 @@
         <v>1.16</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>70.56</v>
@@ -26448,7 +26448,7 @@
         <v>-8.08</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>70.06</v>
@@ -26523,7 +26523,7 @@
         <v>0.02</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>69.48999999999999</v>
@@ -26598,7 +26598,7 @@
         <v>-4.17</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>68.54000000000001</v>
@@ -26677,7 +26677,7 @@
         <v>-2.29</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>67.48999999999999</v>
@@ -26756,7 +26756,7 @@
         <v>5.48</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>66.56999999999999</v>
@@ -26831,7 +26831,7 @@
         <v>0.77</v>
       </c>
       <c r="I349" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" t="n">
         <v>65.86</v>
@@ -26906,7 +26906,7 @@
         <v>3.56</v>
       </c>
       <c r="I350" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" t="n">
         <v>65.58</v>
@@ -26981,7 +26981,7 @@
         <v>-0.13</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>65.25</v>
@@ -27056,7 +27056,7 @@
         <v>-4.39</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>64.94</v>
@@ -27131,7 +27131,7 @@
         <v>-1.81</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>64.47</v>
@@ -27206,7 +27206,7 @@
         <v>-1.01</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>63.95</v>
@@ -27281,7 +27281,7 @@
         <v>-5.4</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>63.32</v>
@@ -27360,7 +27360,7 @@
         <v>-7.09</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>62.42</v>
@@ -27439,7 +27439,7 @@
         <v>1.12</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>61.66</v>
@@ -27518,7 +27518,7 @@
         <v>1.76</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>60.91</v>
@@ -27593,7 +27593,7 @@
         <v>-1.13</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>60.12</v>
@@ -27668,7 +27668,7 @@
         <v>1.5</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>59.42</v>
@@ -27743,7 +27743,7 @@
         <v>0.21</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>58.69</v>
@@ -27818,7 +27818,7 @@
         <v>2.69</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>58.14</v>
@@ -27893,7 +27893,7 @@
         <v>1.98</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>57.59</v>
@@ -27968,7 +27968,7 @@
         <v>-2.94</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>57.24</v>
@@ -28047,7 +28047,7 @@
         <v>-2.99</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>56.8</v>
@@ -28126,7 +28126,7 @@
         <v>2.48</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>56.55</v>
@@ -28201,7 +28201,7 @@
         <v>-0.35</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>56.37</v>
@@ -28276,7 +28276,7 @@
         <v>-3.32</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>55.94</v>
@@ -28351,7 +28351,7 @@
         <v>1.94</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>55.53</v>
@@ -28426,7 +28426,7 @@
         <v>-1.81</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>54.97</v>
@@ -28501,7 +28501,7 @@
         <v>-3.49</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>54.32</v>
@@ -28576,7 +28576,7 @@
         <v>0.77</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>53.83</v>
@@ -28651,7 +28651,7 @@
         <v>0.39</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>53.4</v>
@@ -28724,7 +28724,7 @@
         <v>4.12</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>53.11</v>
@@ -28797,7 +28797,7 @@
         <v>1.58</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>53.02</v>
@@ -28870,7 +28870,7 @@
         <v>-3.45</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>53.03</v>
@@ -28947,7 +28947,7 @@
         <v>1.02</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>53.04</v>
@@ -29020,7 +29020,7 @@
         <v>0.65</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>53.03</v>
@@ -29093,7 +29093,7 @@
         <v>-2.32</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>52.98</v>
@@ -29166,7 +29166,7 @@
         <v>0.14</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>52.89</v>
@@ -29239,7 +29239,7 @@
         <v>3.34</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>52.89</v>
@@ -29312,7 +29312,7 @@
         <v>-2.13</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>52.75</v>
@@ -29389,7 +29389,7 @@
         <v>0.19</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>52.57</v>
@@ -29462,7 +29462,7 @@
         <v>2.63</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>52.54</v>
@@ -29535,7 +29535,7 @@
         <v>4.14</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>52.7</v>
@@ -29608,7 +29608,7 @@
         <v>-0.39</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>52.79</v>
@@ -29681,7 +29681,7 @@
         <v>2.95</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>52.97</v>
@@ -29754,7 +29754,7 @@
         <v>3.32</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>53.33</v>
@@ -29827,7 +29827,7 @@
         <v>-1.45</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>53.6</v>
@@ -29900,7 +29900,7 @@
         <v>0.87</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>53.94</v>
@@ -29973,7 +29973,7 @@
         <v>-1.52</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>54.33</v>
@@ -30046,7 +30046,7 @@
         <v>0.55</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>54.71</v>
@@ -30119,7 +30119,7 @@
         <v>1.86</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>55.14</v>
@@ -30192,7 +30192,7 @@
         <v>-3.58</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>55.36</v>
@@ -30269,7 +30269,7 @@
         <v>4.47</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>55.67</v>
@@ -30342,7 +30342,7 @@
         <v>2.75</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>56.15</v>
@@ -30415,7 +30415,7 @@
         <v>1.72</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>56.65</v>
@@ -30488,7 +30488,7 @@
         <v>-0.83</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>57.12</v>
@@ -30561,7 +30561,7 @@
         <v>0.19</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>57.65</v>
@@ -30634,7 +30634,7 @@
         <v>-1.17</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>58.14</v>
@@ -30707,7 +30707,7 @@
         <v>1.92</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>58.6</v>
@@ -30780,7 +30780,7 @@
         <v>-4.38</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>58.98</v>
@@ -30853,7 +30853,7 @@
         <v>0.18</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>59.37</v>
@@ -30926,7 +30926,7 @@
         <v>-3.68</v>
       </c>
       <c r="I404" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" t="n">
         <v>59.57</v>
@@ -31003,7 +31003,7 @@
         <v>1.99</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>59.72</v>
@@ -31076,7 +31076,7 @@
         <v>2.51</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>59.96</v>
@@ -31149,7 +31149,7 @@
         <v>-1.21</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>60.07</v>
@@ -31226,7 +31226,7 @@
         <v>-0.75</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>60.07</v>
@@ -31299,7 +31299,7 @@
         <v>2.27</v>
       </c>
       <c r="I409" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" t="n">
         <v>60.18</v>
@@ -31372,7 +31372,7 @@
         <v>-5.3</v>
       </c>
       <c r="I410" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>60.1</v>
@@ -31449,7 +31449,7 @@
         <v>1.08</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>60.1</v>
@@ -31522,7 +31522,7 @@
         <v>-2.2</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>60.02</v>
@@ -31540,7 +31540,7 @@
         <v>34.58</v>
       </c>
       <c r="O412" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31565,6 +31565,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="D413" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="E413" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="F413" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="G413" t="n">
+        <v>7955051</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>27.34</v>
@@ -645,9 +645,7 @@
       <c r="T2" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="3" t="n">
         <v>173.2</v>
@@ -683,7 +681,7 @@
         <v>-1.61</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>27.36</v>
@@ -724,9 +722,7 @@
       <c r="T3" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="3" t="n">
         <v>168.6</v>
@@ -762,7 +758,7 @@
         <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.38</v>
@@ -799,9 +795,7 @@
       <c r="T4" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
         <v>163.6</v>
@@ -837,7 +831,7 @@
         <v>1.34</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>27.44</v>
@@ -874,9 +868,7 @@
       <c r="T5" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
         <v>157.4</v>
@@ -912,7 +904,7 @@
         <v>2.57</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>27.56</v>
@@ -949,9 +941,7 @@
       <c r="T6" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
         <v>156.7</v>
@@ -987,7 +977,7 @@
         <v>-0.73</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>27.67</v>
@@ -1024,9 +1014,7 @@
       <c r="T7" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
         <v>158.5</v>
@@ -1062,7 +1050,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>27.75</v>
@@ -1099,9 +1087,7 @@
       <c r="T8" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
         <v>155.4</v>
@@ -1137,7 +1123,7 @@
         <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>27.87</v>
@@ -1174,9 +1160,7 @@
       <c r="T9" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
         <v>159.4</v>
@@ -1212,7 +1196,7 @@
         <v>0.44</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>27.97</v>
@@ -1249,9 +1233,7 @@
       <c r="T10" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="3" t="n">
         <v>162.6</v>
@@ -1287,7 +1269,7 @@
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>28.07</v>
@@ -1324,9 +1306,7 @@
       <c r="T11" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="3" t="n">
         <v>163.6</v>
@@ -1362,7 +1342,7 @@
         <v>-1.19</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>28.16</v>
@@ -1399,9 +1379,7 @@
       <c r="T12" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="3" t="n">
         <v>166.5</v>
@@ -1437,7 +1415,7 @@
         <v>0.59</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>28.24</v>
@@ -1474,9 +1452,7 @@
       <c r="T13" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="3" t="n">
         <v>166.9</v>
@@ -1512,7 +1488,7 @@
         <v>-0.68</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>28.34</v>
@@ -1549,9 +1525,7 @@
       <c r="T14" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="3" t="n">
         <v>168.8</v>
@@ -1587,7 +1561,7 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>28.44</v>
@@ -1624,9 +1598,7 @@
       <c r="T15" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="3" t="n">
         <v>166.1</v>
@@ -1662,7 +1634,7 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>28.52</v>
@@ -1699,9 +1671,7 @@
       <c r="T16" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="3" t="n">
         <v>163.4</v>
@@ -1737,7 +1707,7 @@
         <v>-0.51</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>28.58</v>
@@ -1774,9 +1744,7 @@
       <c r="T17" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="3" t="n">
         <v>168</v>
@@ -1812,7 +1780,7 @@
         <v>2.05</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>28.7</v>
@@ -1849,9 +1817,7 @@
       <c r="T18" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="3" t="n">
         <v>183.1</v>
@@ -1887,7 +1853,7 @@
         <v>-0.33</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>28.79</v>
@@ -1924,9 +1890,7 @@
       <c r="T19" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="3" t="n">
         <v>175.8</v>
@@ -1962,7 +1926,7 @@
         <v>0.47</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>28.88</v>
@@ -1999,9 +1963,7 @@
       <c r="T20" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="3" t="n">
         <v>178.6</v>
@@ -2037,7 +1999,7 @@
         <v>-1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>28.97</v>
@@ -2074,9 +2036,7 @@
       <c r="T21" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="3" t="n">
         <v>165</v>
@@ -2112,7 +2072,7 @@
         <v>-0.51</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>29.05</v>
@@ -2149,9 +2109,7 @@
       <c r="T22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="3" t="n">
         <v>156.9</v>
@@ -2187,7 +2145,7 @@
         <v>-2.07</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>29.12</v>
@@ -2228,9 +2186,7 @@
       <c r="T23" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="3" t="n">
         <v>157.6</v>
@@ -2266,7 +2222,7 @@
         <v>0.38</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>29.18</v>
@@ -2303,9 +2259,7 @@
       <c r="T24" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>153.4</v>
@@ -2341,7 +2295,7 @@
         <v>-1.87</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>29.2</v>
@@ -2378,9 +2332,7 @@
       <c r="T25" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="2" t="n">
         <v>149.3</v>
@@ -2416,7 +2368,7 @@
         <v>-0.32</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>29.18</v>
@@ -2457,9 +2409,7 @@
       <c r="T26" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="3" t="n">
         <v>157.9</v>
@@ -2495,7 +2445,7 @@
         <v>1.55</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>29.19</v>
@@ -2532,9 +2482,7 @@
       <c r="T27" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>154.3</v>
@@ -2570,7 +2518,7 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>29.21</v>
@@ -2607,9 +2555,7 @@
       <c r="T28" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="2" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>151.4</v>
@@ -2645,7 +2591,7 @@
         <v>2.66</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.24</v>
@@ -2682,9 +2628,7 @@
       <c r="T29" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>138.9</v>
@@ -2720,7 +2664,7 @@
         <v>-0.27</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.26</v>
@@ -2757,9 +2701,7 @@
       <c r="T30" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>137.6</v>
@@ -2795,7 +2737,7 @@
         <v>-0.34</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.27</v>
@@ -2832,9 +2774,7 @@
       <c r="T31" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="2" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>139.9</v>
@@ -2870,7 +2810,7 @@
         <v>-1.62</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.27</v>
@@ -2911,14 +2851,8 @@
       <c r="T32" s="1" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="1" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" s="2" t="n">
         <v>146</v>
       </c>
@@ -2953,7 +2887,7 @@
         <v>2.92</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.31</v>
@@ -2990,14 +2924,8 @@
       <c r="T33" s="1" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="1" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -3032,13 +2960,13 @@
         <v>0.87</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.37</v>
       </c>
       <c r="K34" t="n">
-        <v>28.29</v>
+        <v>28.28</v>
       </c>
       <c r="L34" t="n">
         <v>28.58</v>
@@ -3069,9 +2997,7 @@
       <c r="T34" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.7</v>
@@ -3107,7 +3033,7 @@
         <v>1.72</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.44</v>
@@ -3144,9 +3070,7 @@
       <c r="T35" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="2" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>128.9</v>
@@ -3182,7 +3106,7 @@
         <v>-0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.5</v>
@@ -3219,9 +3143,7 @@
       <c r="T36" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>130.3</v>
@@ -3257,7 +3179,7 @@
         <v>0.33</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.58</v>
@@ -3294,9 +3216,7 @@
       <c r="T37" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>133.9</v>
@@ -3332,7 +3252,7 @@
         <v>0.13</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.62</v>
@@ -3369,9 +3289,7 @@
       <c r="T38" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.8</v>
@@ -3407,7 +3325,7 @@
         <v>-0.32</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>29.67</v>
@@ -3444,9 +3362,7 @@
       <c r="T39" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>136.4</v>
@@ -3482,7 +3398,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>29.7</v>
@@ -3519,9 +3435,7 @@
       <c r="T40" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>140.8</v>
@@ -3557,7 +3471,7 @@
         <v>-1.57</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>29.72</v>
@@ -3594,9 +3508,7 @@
       <c r="T41" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>141.7</v>
@@ -3632,7 +3544,7 @@
         <v>-0.2</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>29.75</v>
@@ -3669,9 +3581,7 @@
       <c r="T42" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>144</v>
@@ -3707,7 +3617,7 @@
         <v>2.07</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>29.83</v>
@@ -3744,9 +3654,7 @@
       <c r="T43" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>148.7</v>
@@ -3782,7 +3690,7 @@
         <v>-0.16</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>29.91</v>
@@ -3819,9 +3727,7 @@
       <c r="T44" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>144.8</v>
@@ -3857,7 +3763,7 @@
         <v>2.59</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>30.06</v>
@@ -3894,9 +3800,7 @@
       <c r="T45" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>140.9</v>
@@ -3932,7 +3836,7 @@
         <v>-1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>30.19</v>
@@ -3969,9 +3873,7 @@
       <c r="T46" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="1" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>139</v>
@@ -4007,7 +3909,7 @@
         <v>-0.03</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>30.3</v>
@@ -4044,9 +3946,7 @@
       <c r="T47" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>148.6</v>
@@ -4082,7 +3982,7 @@
         <v>-1.16</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>30.39</v>
@@ -4119,9 +4019,7 @@
       <c r="T48" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="2" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>143</v>
@@ -4157,7 +4055,7 @@
         <v>0.42</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>30.44</v>
@@ -4194,9 +4092,7 @@
       <c r="T49" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="1" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>144.3</v>
@@ -4232,7 +4128,7 @@
         <v>-6.08</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>30.4</v>
@@ -4273,14 +4169,8 @@
       <c r="T50" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="7" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="4" t="inlineStr"/>
       <c r="W50" s="6" t="n">
         <v>139.2</v>
       </c>
@@ -4315,7 +4205,7 @@
         <v>-6.27</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>30.27</v>
@@ -4356,14 +4246,8 @@
       <c r="T51" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="7" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="4" t="inlineStr"/>
       <c r="W51" s="6" t="n">
         <v>136.5</v>
       </c>
@@ -4398,7 +4282,7 @@
         <v>0.22</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>30.17</v>
@@ -4439,14 +4323,8 @@
       <c r="T52" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="1" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4481,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>30.03</v>
@@ -4522,14 +4400,8 @@
       <c r="T53" s="1" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="1" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4564,7 +4436,7 @@
         <v>3.39</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.92</v>
@@ -4601,14 +4473,8 @@
       <c r="T54" s="1" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="1" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4643,7 +4509,7 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.8</v>
@@ -4680,14 +4546,8 @@
       <c r="T55" s="1" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="1" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" s="2" t="n">
         <v>127.5</v>
       </c>
@@ -4722,7 +4582,7 @@
         <v>3.22</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.72</v>
@@ -4759,14 +4619,8 @@
       <c r="T56" s="1" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="1" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4801,7 +4655,7 @@
         <v>0.65</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.65</v>
@@ -4838,9 +4692,7 @@
       <c r="T57" s="1" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.7</v>
@@ -4876,7 +4728,7 @@
         <v>0.1</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.58</v>
@@ -4913,9 +4765,7 @@
       <c r="T58" s="1" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="1" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>135.8</v>
@@ -4951,7 +4801,7 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.53</v>
@@ -4988,14 +4838,8 @@
       <c r="T59" s="1" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -5030,7 +4874,7 @@
         <v>-0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.48</v>
@@ -5067,14 +4911,8 @@
       <c r="T60" s="1" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="1" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="2" t="n">
         <v>130</v>
       </c>
@@ -5109,7 +4947,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.47</v>
@@ -5146,9 +4984,7 @@
       <c r="T61" s="1" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="1" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="1" t="n">
         <v>125.8</v>
@@ -5184,7 +5020,7 @@
         <v>-0.97</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.45</v>
@@ -5221,9 +5057,7 @@
       <c r="T62" s="1" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="1" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="1" t="n">
         <v>125.9</v>
@@ -5259,7 +5093,7 @@
         <v>3.59</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.45</v>
@@ -5296,14 +5130,8 @@
       <c r="T63" s="1" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="1" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="1" t="n">
         <v>126.7</v>
       </c>
@@ -5338,13 +5166,13 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.45</v>
       </c>
       <c r="K64" t="n">
-        <v>29.52</v>
+        <v>29.51</v>
       </c>
       <c r="L64" t="n">
         <v>28.72</v>
@@ -5375,9 +5203,7 @@
       <c r="T64" s="1" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="1" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>129</v>
@@ -5413,7 +5239,7 @@
         <v>-1.67</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.39</v>
@@ -5450,9 +5276,7 @@
       <c r="T65" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="2" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>132.4</v>
@@ -5488,7 +5312,7 @@
         <v>0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>29.35</v>
@@ -5525,9 +5349,7 @@
       <c r="T66" s="1" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>131.3</v>
@@ -5563,7 +5385,7 @@
         <v>-1.19</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>29.29</v>
@@ -5600,9 +5422,7 @@
       <c r="T67" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>134.3</v>
@@ -5638,7 +5458,7 @@
         <v>-0.77</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>29.24</v>
@@ -5679,9 +5499,7 @@
       <c r="T68" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="2" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>132.7</v>
@@ -5717,7 +5535,7 @@
         <v>-0.71</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>29.17</v>
@@ -5754,9 +5572,7 @@
       <c r="T69" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="1" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.1</v>
@@ -5792,7 +5608,7 @@
         <v>-0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>29.18</v>
@@ -5833,9 +5649,7 @@
       <c r="T70" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.8</v>
@@ -5871,7 +5685,7 @@
         <v>1.24</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>29.3</v>
@@ -5908,9 +5722,7 @@
       <c r="T71" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>134.1</v>
@@ -5946,7 +5758,7 @@
         <v>2.51</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>29.45</v>
@@ -5983,9 +5795,7 @@
       <c r="T72" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>133.2</v>
@@ -6021,7 +5831,7 @@
         <v>-2.42</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>29.57</v>
@@ -6062,9 +5872,7 @@
       <c r="T73" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="2" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>132.2</v>
@@ -6100,7 +5908,7 @@
         <v>-0.1</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>29.64</v>
@@ -6137,9 +5945,7 @@
       <c r="T74" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>131.5</v>
@@ -6175,7 +5981,7 @@
         <v>1.15</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6212,9 +6018,7 @@
       <c r="T75" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="1" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>128.4</v>
@@ -6250,7 +6054,7 @@
         <v>-0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>29.74</v>
@@ -6291,9 +6095,7 @@
       <c r="T76" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>137.7</v>
@@ -6329,13 +6131,13 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>29.77</v>
       </c>
       <c r="K77" t="n">
-        <v>29.66</v>
+        <v>29.67</v>
       </c>
       <c r="L77" t="n">
         <v>28.82</v>
@@ -6366,9 +6168,7 @@
       <c r="T77" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>140.5</v>
@@ -6404,7 +6204,7 @@
         <v>-2.27</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>29.76</v>
@@ -6445,9 +6245,7 @@
       <c r="T78" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>138.9</v>
@@ -6483,7 +6281,7 @@
         <v>1.23</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>29.75</v>
@@ -6520,9 +6318,7 @@
       <c r="T79" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>140.9</v>
@@ -6558,7 +6354,7 @@
         <v>-1.05</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6595,9 +6391,7 @@
       <c r="T80" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>136</v>
@@ -6633,7 +6427,7 @@
         <v>0.41</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>29.72</v>
@@ -6670,9 +6464,7 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>135.9</v>
@@ -6708,7 +6500,7 @@
         <v>2.41</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>29.75</v>
@@ -6745,9 +6537,7 @@
       <c r="T82" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6783,7 +6573,7 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>29.75</v>
@@ -6820,9 +6610,7 @@
       <c r="T83" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>137.3</v>
@@ -6858,7 +6646,7 @@
         <v>-1.57</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>29.72</v>
@@ -6895,9 +6683,7 @@
       <c r="T84" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139</v>
@@ -6933,7 +6719,7 @@
         <v>1.4</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>29.74</v>
@@ -6970,9 +6756,7 @@
       <c r="T85" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>139.3</v>
@@ -7008,7 +6792,7 @@
         <v>-0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>29.74</v>
@@ -7045,9 +6829,7 @@
       <c r="T86" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>140.9</v>
@@ -7083,7 +6865,7 @@
         <v>-0.83</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>29.75</v>
@@ -7120,9 +6902,7 @@
       <c r="T87" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.6</v>
@@ -7158,7 +6938,7 @@
         <v>1.07</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>29.79</v>
@@ -7195,9 +6975,7 @@
       <c r="T88" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>137.3</v>
@@ -7233,7 +7011,7 @@
         <v>-0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>29.82</v>
@@ -7270,9 +7048,7 @@
       <c r="T89" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>138.2</v>
@@ -7308,7 +7084,7 @@
         <v>5.3</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>29.94</v>
@@ -7345,9 +7121,7 @@
       <c r="T90" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141</v>
@@ -7383,7 +7157,7 @@
         <v>-0.47</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>30.04</v>
@@ -7420,9 +7194,7 @@
       <c r="T91" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>141.6</v>
@@ -7458,7 +7230,7 @@
         <v>-0.32</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>30.09</v>
@@ -7495,9 +7267,7 @@
       <c r="T92" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>137.5</v>
@@ -7533,7 +7303,7 @@
         <v>3.54</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>30.24</v>
@@ -7570,9 +7340,7 @@
       <c r="T93" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>140.1</v>
@@ -7608,7 +7376,7 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>30.4</v>
@@ -7645,9 +7413,7 @@
       <c r="T94" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>138.9</v>
@@ -7683,7 +7449,7 @@
         <v>2.14</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>30.58</v>
@@ -7720,9 +7486,7 @@
       <c r="T95" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>139.2</v>
@@ -7758,7 +7522,7 @@
         <v>-0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>30.76</v>
@@ -7795,9 +7559,7 @@
       <c r="T96" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.2</v>
@@ -7833,7 +7595,7 @@
         <v>-0.84</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>30.91</v>
@@ -7870,9 +7632,7 @@
       <c r="T97" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>141.4</v>
@@ -7908,7 +7668,7 @@
         <v>0.33</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>31.1</v>
@@ -7945,9 +7705,7 @@
       <c r="T98" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>145.6</v>
@@ -7983,7 +7741,7 @@
         <v>-0.27</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>31.27</v>
@@ -8020,9 +7778,7 @@
       <c r="T99" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="2" t="n">
         <v>149.6</v>
@@ -8058,7 +7814,7 @@
         <v>0.18</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>31.46</v>
@@ -8095,9 +7851,7 @@
       <c r="T100" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="3" t="n">
         <v>156.6</v>
@@ -8133,7 +7887,7 @@
         <v>2.15</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>31.68</v>
@@ -8170,9 +7924,7 @@
       <c r="T101" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="2" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>154.4</v>
@@ -8208,7 +7960,7 @@
         <v>-1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>31.83</v>
@@ -8245,9 +7997,7 @@
       <c r="T102" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>148.4</v>
@@ -8283,7 +8033,7 @@
         <v>-1.65</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>31.94</v>
@@ -8320,9 +8070,7 @@
       <c r="T103" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="2" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>149.2</v>
@@ -8358,7 +8106,7 @@
         <v>0.73</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>32.09</v>
@@ -8395,9 +8143,7 @@
       <c r="T104" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="2" t="n">
         <v>154.8</v>
@@ -8433,7 +8179,7 @@
         <v>-1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>32.2</v>
@@ -8470,9 +8216,7 @@
       <c r="T105" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="3" t="n">
         <v>155</v>
@@ -8508,7 +8252,7 @@
         <v>1.23</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>32.34</v>
@@ -8545,9 +8289,7 @@
       <c r="T106" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>152.2</v>
@@ -8583,7 +8325,7 @@
         <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>32.5</v>
@@ -8620,9 +8362,7 @@
       <c r="T107" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>147.5</v>
@@ -8658,7 +8398,7 @@
         <v>-2.16</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>32.62</v>
@@ -8695,9 +8435,7 @@
       <c r="T108" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>143.4</v>
@@ -8733,7 +8471,7 @@
         <v>0.58</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>32.76</v>
@@ -8770,9 +8508,7 @@
       <c r="T109" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>139.6</v>
@@ -8808,7 +8544,7 @@
         <v>-0.24</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>32.82</v>
@@ -8849,9 +8585,7 @@
       <c r="T110" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>140.1</v>
@@ -8887,7 +8621,7 @@
         <v>1.56</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>32.91</v>
@@ -8924,9 +8658,7 @@
       <c r="T111" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>139.3</v>
@@ -8962,7 +8694,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>33.02</v>
@@ -8999,9 +8731,7 @@
       <c r="T112" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>141.4</v>
@@ -9037,7 +8767,7 @@
         <v>-0.24</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>33.07</v>
@@ -9074,9 +8804,7 @@
       <c r="T113" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>138</v>
@@ -9112,7 +8840,7 @@
         <v>-0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>33.1</v>
@@ -9149,9 +8877,7 @@
       <c r="T114" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>140.8</v>
@@ -9187,7 +8913,7 @@
         <v>-0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>33.08</v>
@@ -9228,9 +8954,7 @@
       <c r="T115" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>141.8</v>
@@ -9266,7 +8990,7 @@
         <v>2.27</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>33.1</v>
@@ -9303,9 +9027,7 @@
       <c r="T116" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>143.3</v>
@@ -9341,7 +9063,7 @@
         <v>3.79</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>33.21</v>
@@ -9378,9 +9100,7 @@
       <c r="T117" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>145</v>
@@ -9416,7 +9136,7 @@
         <v>-1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>33.28</v>
@@ -9453,9 +9173,7 @@
       <c r="T118" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>147</v>
@@ -9491,7 +9209,7 @@
         <v>-1.07</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>33.35</v>
@@ -9528,9 +9246,7 @@
       <c r="T119" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>143.7</v>
@@ -9566,7 +9282,7 @@
         <v>0.44</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>33.42</v>
@@ -9603,9 +9319,7 @@
       <c r="T120" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>146.7</v>
@@ -9641,7 +9355,7 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>33.46</v>
@@ -9678,9 +9392,7 @@
       <c r="T121" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>151.1</v>
@@ -9716,7 +9428,7 @@
         <v>-0.12</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>33.53</v>
@@ -9753,9 +9465,7 @@
       <c r="T122" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>150.4</v>
@@ -9791,7 +9501,7 @@
         <v>2.14</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>33.66</v>
@@ -9828,9 +9538,7 @@
       <c r="T123" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>154.8</v>
@@ -9866,7 +9574,7 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>33.8</v>
@@ -9903,9 +9611,7 @@
       <c r="T124" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="2" t="n">
         <v>153.4</v>
@@ -9941,7 +9647,7 @@
         <v>-0.08</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>33.95</v>
@@ -9978,9 +9684,7 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="3" t="n">
         <v>159.3</v>
@@ -10016,7 +9720,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.08</v>
@@ -10053,9 +9757,7 @@
       <c r="T126" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="3" t="n">
         <v>159.4</v>
@@ -10091,7 +9793,7 @@
         <v>-2.34</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.14</v>
@@ -10128,9 +9830,7 @@
       <c r="T127" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>145.6</v>
@@ -10166,7 +9866,7 @@
         <v>-0.06</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.24</v>
@@ -10203,9 +9903,7 @@
       <c r="T128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="2" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>147.6</v>
@@ -10241,7 +9939,7 @@
         <v>0.06</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>34.34</v>
@@ -10278,9 +9976,7 @@
       <c r="T129" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>149.1</v>
@@ -10316,7 +10012,7 @@
         <v>-3.32</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>34.38</v>
@@ -10357,9 +10053,7 @@
       <c r="T130" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>154.1</v>
@@ -10395,7 +10089,7 @@
         <v>-0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>34.38</v>
@@ -10432,9 +10126,7 @@
       <c r="T131" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="2" t="n">
         <v>152.3</v>
@@ -10470,7 +10162,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>34.38</v>
@@ -10507,9 +10199,7 @@
       <c r="T132" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="3" t="n">
         <v>155.5</v>
@@ -10545,7 +10235,7 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>34.41</v>
@@ -10582,9 +10272,7 @@
       <c r="T133" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="3" t="n">
         <v>159.3</v>
@@ -10620,7 +10308,7 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>34.46</v>
@@ -10657,9 +10345,7 @@
       <c r="T134" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.9</v>
@@ -10695,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>34.53</v>
@@ -10732,9 +10418,7 @@
       <c r="T135" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>149.7</v>
@@ -10770,7 +10454,7 @@
         <v>1.19</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10807,9 +10491,7 @@
       <c r="T136" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147</v>
@@ -10845,7 +10527,7 @@
         <v>0.35</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>34.58</v>
@@ -10882,9 +10564,7 @@
       <c r="T137" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>147.5</v>
@@ -10920,7 +10600,7 @@
         <v>-2.01</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>34.55</v>
@@ -10961,9 +10641,7 @@
       <c r="T138" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>148.6</v>
@@ -10999,7 +10677,7 @@
         <v>0.67</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>34.56</v>
@@ -11036,9 +10714,7 @@
       <c r="T139" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>151.4</v>
@@ -11074,7 +10750,7 @@
         <v>1.71</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>34.59</v>
@@ -11111,9 +10787,7 @@
       <c r="T140" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>153.1</v>
@@ -11149,7 +10823,7 @@
         <v>-1.43</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>34.58</v>
@@ -11190,9 +10864,7 @@
       <c r="T141" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>150.6</v>
@@ -11228,7 +10900,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>34.58</v>
@@ -11265,9 +10937,7 @@
       <c r="T142" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.8</v>
@@ -11303,7 +10973,7 @@
         <v>0.14</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>34.54</v>
@@ -11340,9 +11010,7 @@
       <c r="T143" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.9</v>
@@ -11378,7 +11046,7 @@
         <v>-1.97</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>34.44</v>
@@ -11419,9 +11087,7 @@
       <c r="T144" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>153.2</v>
@@ -11457,7 +11123,7 @@
         <v>1.65</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>34.38</v>
@@ -11494,9 +11160,7 @@
       <c r="T145" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.6</v>
@@ -11532,7 +11196,7 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>34.34</v>
@@ -11569,9 +11233,7 @@
       <c r="T146" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>144.3</v>
@@ -11607,7 +11269,7 @@
         <v>2.11</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>34.37</v>
@@ -11644,9 +11306,7 @@
       <c r="T147" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>146.4</v>
@@ -11682,7 +11342,7 @@
         <v>-0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>34.39</v>
@@ -11719,9 +11379,7 @@
       <c r="T148" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="2" t="n">
         <v>150</v>
@@ -11757,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>34.41</v>
@@ -11794,9 +11452,7 @@
       <c r="T149" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="3" t="n">
         <v>156.5</v>
@@ -11832,7 +11488,7 @@
         <v>-0.09</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>34.48</v>
@@ -11869,9 +11525,7 @@
       <c r="T150" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>150.9</v>
@@ -11907,7 +11561,7 @@
         <v>1.51</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>34.59</v>
@@ -11944,9 +11598,7 @@
       <c r="T151" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.5</v>
@@ -11982,7 +11634,7 @@
         <v>1.89</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>34.72</v>
@@ -12019,9 +11671,7 @@
       <c r="T152" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>152.1</v>
@@ -12057,7 +11707,7 @@
         <v>2.65</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>34.88</v>
@@ -12094,9 +11744,7 @@
       <c r="T153" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>151.5</v>
@@ -12132,7 +11780,7 @@
         <v>0.51</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>35.03</v>
@@ -12169,9 +11817,7 @@
       <c r="T154" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>150.2</v>
@@ -12207,7 +11853,7 @@
         <v>-1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>35.16</v>
@@ -12244,9 +11890,7 @@
       <c r="T155" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>154</v>
@@ -12282,7 +11926,7 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>35.28</v>
@@ -12319,9 +11963,7 @@
       <c r="T156" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.2</v>
@@ -12357,7 +11999,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>35.41</v>
@@ -12394,9 +12036,7 @@
       <c r="T157" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>148.8</v>
@@ -12432,7 +12072,7 @@
         <v>-0.88</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>35.56</v>
@@ -12469,9 +12109,7 @@
       <c r="T158" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>150.9</v>
@@ -12507,7 +12145,7 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>35.71</v>
@@ -12544,9 +12182,7 @@
       <c r="T159" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>151.9</v>
@@ -12582,7 +12218,7 @@
         <v>1.02</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>35.85</v>
@@ -12619,9 +12255,7 @@
       <c r="T160" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>147.6</v>
@@ -12657,7 +12291,7 @@
         <v>1.46</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>36.04</v>
@@ -12694,9 +12328,7 @@
       <c r="T161" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>149.5</v>
@@ -12732,7 +12364,7 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>36.26</v>
@@ -12769,9 +12401,7 @@
       <c r="T162" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>152.1</v>
@@ -12807,7 +12437,7 @@
         <v>-0.41</v>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>36.46</v>
@@ -12844,9 +12474,7 @@
       <c r="T163" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>148.2</v>
@@ -12882,7 +12510,7 @@
         <v>-2.1</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>36.66</v>
@@ -12919,9 +12547,7 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>146.4</v>
@@ -12957,7 +12583,7 @@
         <v>0.53</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>36.83</v>
@@ -12994,9 +12620,7 @@
       <c r="T165" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>148.2</v>
@@ -13032,7 +12656,7 @@
         <v>2.76</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>37.06</v>
@@ -13069,9 +12693,7 @@
       <c r="T166" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>147</v>
@@ -13107,7 +12729,7 @@
         <v>2.56</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>37.29</v>
@@ -13144,9 +12766,7 @@
       <c r="T167" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="2" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>145.5</v>
@@ -13182,7 +12802,7 @@
         <v>-0.2</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>37.54</v>
@@ -13219,9 +12839,7 @@
       <c r="T168" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>146.5</v>
@@ -13257,7 +12875,7 @@
         <v>-0.35</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>37.78</v>
@@ -13294,9 +12912,7 @@
       <c r="T169" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13332,7 +12948,7 @@
         <v>3.04</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>38.08</v>
@@ -13369,9 +12985,7 @@
       <c r="T170" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>145.9</v>
@@ -13407,7 +13021,7 @@
         <v>2.02</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>38.4</v>
@@ -13444,9 +13058,7 @@
       <c r="T171" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>141.5</v>
@@ -13482,7 +13094,7 @@
         <v>1.53</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>38.71</v>
@@ -13519,9 +13131,7 @@
       <c r="T172" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143</v>
@@ -13557,7 +13167,7 @@
         <v>-0.31</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>38.97</v>
@@ -13594,9 +13204,7 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.4</v>
@@ -13632,7 +13240,7 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>39.25</v>
@@ -13669,9 +13277,7 @@
       <c r="T174" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>143.7</v>
@@ -13707,7 +13313,7 @@
         <v>-0.89</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>39.53</v>
@@ -13744,9 +13350,7 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>145.9</v>
@@ -13782,7 +13386,7 @@
         <v>2.33</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>39.85</v>
@@ -13819,9 +13423,7 @@
       <c r="T176" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>144.6</v>
@@ -13857,7 +13459,7 @@
         <v>1.24</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>40.17</v>
@@ -13894,9 +13496,7 @@
       <c r="T177" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="2" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>142.5</v>
@@ -13932,7 +13532,7 @@
         <v>-1.52</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>40.49</v>
@@ -13969,9 +13569,7 @@
       <c r="T178" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.2</v>
@@ -14007,7 +13605,7 @@
         <v>2.7</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>40.84</v>
@@ -14044,9 +13642,7 @@
       <c r="T179" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.8</v>
@@ -14082,7 +13678,7 @@
         <v>0.34</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>41.19</v>
@@ -14119,9 +13715,7 @@
       <c r="T180" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>145.3</v>
@@ -14157,7 +13751,7 @@
         <v>1.61</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>41.54</v>
@@ -14194,9 +13788,7 @@
       <c r="T181" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="1" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="2" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>138.9</v>
@@ -14232,7 +13824,7 @@
         <v>4.03</v>
       </c>
       <c r="I182" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>41.97</v>
@@ -14269,9 +13861,7 @@
       <c r="T182" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>142.8</v>
@@ -14307,7 +13897,7 @@
         <v>-0.97</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>42.38</v>
@@ -14344,9 +13934,7 @@
       <c r="T183" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>146.5</v>
@@ -14382,7 +13970,7 @@
         <v>3.27</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>42.91</v>
@@ -14419,9 +14007,7 @@
       <c r="T184" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>145</v>
@@ -14457,7 +14043,7 @@
         <v>1.74</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>43.46</v>
@@ -14494,9 +14080,7 @@
       <c r="T185" s="1" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="2" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.1</v>
@@ -14532,7 +14116,7 @@
         <v>-4.43</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>43.86</v>
@@ -14569,9 +14153,7 @@
       <c r="T186" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="2" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>147.6</v>
@@ -14607,7 +14189,7 @@
         <v>1.55</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>44.25</v>
@@ -14644,9 +14226,7 @@
       <c r="T187" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>151.3</v>
@@ -14682,7 +14262,7 @@
         <v>-8.24</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>44.44</v>
@@ -14723,9 +14303,7 @@
       <c r="T188" s="6" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="6" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="6" t="inlineStr"/>
       <c r="V188" s="4" t="inlineStr"/>
       <c r="W188" s="6" t="n">
         <v>149.9</v>
@@ -14761,7 +14339,7 @@
         <v>0.21</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>44.64</v>
@@ -14798,9 +14376,7 @@
       <c r="T189" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>152.9</v>
@@ -14836,7 +14412,7 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>44.8</v>
@@ -14873,9 +14449,7 @@
       <c r="T190" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>154.3</v>
@@ -14911,7 +14485,7 @@
         <v>-0.43</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>44.9</v>
@@ -14948,9 +14522,7 @@
       <c r="T191" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>153.5</v>
@@ -14986,7 +14558,7 @@
         <v>-3.61</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>44.9</v>
@@ -15023,9 +14595,7 @@
       <c r="T192" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>148.5</v>
@@ -15061,7 +14631,7 @@
         <v>0.71</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>44.92</v>
@@ -15098,9 +14668,7 @@
       <c r="T193" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>140.4</v>
@@ -15136,7 +14704,7 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>44.93</v>
@@ -15173,9 +14741,7 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>139.4</v>
@@ -15211,7 +14777,7 @@
         <v>2.57</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>45.02</v>
@@ -15248,9 +14814,7 @@
       <c r="T195" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="2" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>141.1</v>
@@ -15286,7 +14850,7 @@
         <v>-0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>45.05</v>
@@ -15323,9 +14887,7 @@
       <c r="T196" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="2" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142.8</v>
@@ -15361,7 +14923,7 @@
         <v>-0.57</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>45.03</v>
@@ -15398,9 +14960,7 @@
       <c r="T197" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>142</v>
@@ -15436,7 +14996,7 @@
         <v>-2.33</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>45</v>
@@ -15473,9 +15033,7 @@
       <c r="T198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>144</v>
@@ -15511,7 +15069,7 @@
         <v>2.13</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>44.95</v>
@@ -15548,9 +15106,7 @@
       <c r="T199" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="2" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.6</v>
@@ -15586,7 +15142,7 @@
         <v>-0.23</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>44.9</v>
@@ -15623,9 +15179,7 @@
       <c r="T200" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="2" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>143.5</v>
@@ -15661,7 +15215,7 @@
         <v>0.85</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>44.82</v>
@@ -15698,9 +15252,7 @@
       <c r="T201" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="2" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>141.3</v>
@@ -15736,7 +15288,7 @@
         <v>4.26</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>44.75</v>
@@ -15773,9 +15325,7 @@
       <c r="T202" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="2" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>142.9</v>
@@ -15811,7 +15361,7 @@
         <v>1.44</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>44.73</v>
@@ -15848,9 +15398,7 @@
       <c r="T203" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>143.4</v>
@@ -15886,7 +15434,7 @@
         <v>4.03</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>44.73</v>
@@ -15923,9 +15471,7 @@
       <c r="T204" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>138.6</v>
@@ -15961,7 +15507,7 @@
         <v>-1.86</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>44.64</v>
@@ -15998,9 +15544,7 @@
       <c r="T205" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="2" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>142.5</v>
@@ -16036,7 +15580,7 @@
         <v>-3.08</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>44.59</v>
@@ -16073,9 +15617,7 @@
       <c r="T206" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="2" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>137.9</v>
@@ -16111,7 +15653,7 @@
         <v>-1.07</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>44.48</v>
@@ -16148,9 +15690,7 @@
       <c r="T207" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="2" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>140.9</v>
@@ -16186,7 +15726,7 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>44.59</v>
@@ -16223,9 +15763,7 @@
       <c r="T208" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="2" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143</v>
@@ -16261,7 +15799,7 @@
         <v>0.76</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>44.72</v>
@@ -16298,9 +15836,7 @@
       <c r="T209" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="1" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="2" t="n">
         <v>143.1</v>
@@ -16336,7 +15872,7 @@
         <v>-1.44</v>
       </c>
       <c r="I210" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>44.8</v>
@@ -16373,14 +15909,8 @@
       <c r="T210" s="1" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="1" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>145</v>
       </c>
@@ -16415,7 +15945,7 @@
         <v>-1.05</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>44.87</v>
@@ -16452,9 +15982,7 @@
       <c r="T211" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="2" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.3</v>
@@ -16490,7 +16018,7 @@
         <v>2.94</v>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>45.08</v>
@@ -16527,9 +16055,7 @@
       <c r="T212" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>148.6</v>
@@ -16565,7 +16091,7 @@
         <v>0.09</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>45.28</v>
@@ -16602,9 +16128,7 @@
       <c r="T213" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>151.7</v>
@@ -16640,7 +16164,7 @@
         <v>3.71</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>45.54</v>
@@ -16677,9 +16201,7 @@
       <c r="T214" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>145</v>
@@ -16715,7 +16237,7 @@
         <v>5.81</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>45.88</v>
@@ -16752,9 +16274,7 @@
       <c r="T215" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>143</v>
@@ -16790,7 +16310,7 @@
         <v>2.56</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>46.3</v>
@@ -16827,9 +16347,7 @@
       <c r="T216" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16865,7 +16383,7 @@
         <v>1.16</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>46.77</v>
@@ -16902,9 +16420,7 @@
       <c r="T217" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>144.9</v>
@@ -16940,7 +16456,7 @@
         <v>-0.11</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>47.29</v>
@@ -16977,9 +16493,7 @@
       <c r="T218" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="2" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>149.2</v>
@@ -17015,7 +16529,7 @@
         <v>-2.47</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>47.7</v>
@@ -17052,9 +16566,7 @@
       <c r="T219" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.9</v>
@@ -17090,7 +16602,7 @@
         <v>2.3</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>48.16</v>
@@ -17127,9 +16639,7 @@
       <c r="T220" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>148.8</v>
@@ -17165,7 +16675,7 @@
         <v>-0.45</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>48.6</v>
@@ -17202,9 +16712,7 @@
       <c r="T221" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.6</v>
@@ -17240,7 +16748,7 @@
         <v>4.67</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>49.07</v>
@@ -17277,9 +16785,7 @@
       <c r="T222" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>150.3</v>
@@ -17315,7 +16821,7 @@
         <v>1.63</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>49.55</v>
@@ -17352,9 +16858,7 @@
       <c r="T223" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>147.6</v>
@@ -17390,7 +16894,7 @@
         <v>2.76</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>50.02</v>
@@ -17427,9 +16931,7 @@
       <c r="T224" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>148.3</v>
@@ -17465,7 +16967,7 @@
         <v>-2.64</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>50.45</v>
@@ -17502,9 +17004,7 @@
       <c r="T225" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="2" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="2" t="n">
         <v>153.6</v>
@@ -17540,7 +17040,7 @@
         <v>3.58</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>51.06</v>
@@ -17577,9 +17077,7 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="2" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="3" t="n">
         <v>161.9</v>
@@ -17615,7 +17113,7 @@
         <v>-0.65</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>51.67</v>
@@ -17652,9 +17150,7 @@
       <c r="T227" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="2" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="3" t="n">
         <v>157</v>
@@ -17690,7 +17186,7 @@
         <v>4.38</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>52.38</v>
@@ -17727,9 +17223,7 @@
       <c r="T228" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="2" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="2" t="n">
         <v>153.5</v>
@@ -17765,7 +17259,7 @@
         <v>-1.56</v>
       </c>
       <c r="I229" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>53.03</v>
@@ -17802,9 +17296,7 @@
       <c r="T229" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="3" t="n">
         <v>155.4</v>
@@ -17840,7 +17332,7 @@
         <v>2.71</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>53.78</v>
@@ -17877,9 +17369,7 @@
       <c r="T230" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="3" t="n">
         <v>155.9</v>
@@ -17915,7 +17405,7 @@
         <v>2.53</v>
       </c>
       <c r="I231" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>54.64</v>
@@ -17952,9 +17442,7 @@
       <c r="T231" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="2" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="3" t="n">
         <v>159.9</v>
@@ -17990,7 +17478,7 @@
         <v>3.79</v>
       </c>
       <c r="I232" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>55.55</v>
@@ -18027,9 +17515,7 @@
       <c r="T232" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="2" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="3" t="n">
         <v>160.5</v>
@@ -18065,7 +17551,7 @@
         <v>0.59</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>56.48</v>
@@ -18102,9 +17588,7 @@
       <c r="T233" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="2" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="2" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="3" t="n">
         <v>160.5</v>
@@ -18140,7 +17624,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>57.62</v>
@@ -18177,9 +17661,7 @@
       <c r="T234" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>151.4</v>
@@ -18215,7 +17697,7 @@
         <v>-7.19</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" s="4" t="n">
         <v>58.36</v>
@@ -18252,9 +17734,7 @@
       <c r="T235" s="6" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="6" t="inlineStr"/>
       <c r="V235" s="4" t="inlineStr"/>
       <c r="W235" s="6" t="n">
         <v>150.5</v>
@@ -18290,7 +17770,7 @@
         <v>4.5</v>
       </c>
       <c r="I236" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>59.18</v>
@@ -18327,9 +17807,7 @@
       <c r="T236" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.3</v>
@@ -18365,7 +17843,7 @@
         <v>-6.61</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>59.74</v>
@@ -18402,9 +17880,7 @@
       <c r="T237" s="6" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="6" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="6" t="inlineStr"/>
       <c r="V237" s="4" t="inlineStr"/>
       <c r="W237" s="6" t="n">
         <v>148.7</v>
@@ -18440,7 +17916,7 @@
         <v>2.06</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>60.38</v>
@@ -18477,9 +17953,7 @@
       <c r="T238" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>141.9</v>
@@ -18515,7 +17989,7 @@
         <v>5.06</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>61.24</v>
@@ -18552,9 +18026,7 @@
       <c r="T239" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>142.4</v>
@@ -18590,7 +18062,7 @@
         <v>6.7</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>62.28</v>
@@ -18627,9 +18099,7 @@
       <c r="T240" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="2" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>146.2</v>
@@ -18665,7 +18135,7 @@
         <v>-3.73</v>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>63.19</v>
@@ -18702,9 +18172,7 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="2" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>143.6</v>
@@ -18740,7 +18208,7 @@
         <v>-1.76</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>63.92</v>
@@ -18777,9 +18245,7 @@
       <c r="T242" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>147.1</v>
@@ -18815,7 +18281,7 @@
         <v>3.83</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>64.73999999999999</v>
@@ -18852,9 +18318,7 @@
       <c r="T243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="2" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="2" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>146</v>
@@ -18890,7 +18354,7 @@
         <v>6.7</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>65.72</v>
@@ -18927,9 +18391,7 @@
       <c r="T244" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>149.8</v>
@@ -18965,7 +18427,7 @@
         <v>1.77</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>66.84</v>
@@ -19002,9 +18464,7 @@
       <c r="T245" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="2" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>151.6</v>
@@ -19040,7 +18500,7 @@
         <v>7.58</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>68.16</v>
@@ -19077,9 +18537,7 @@
       <c r="T246" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="2" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>152.5</v>
@@ -19115,7 +18573,7 @@
         <v>-1.47</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>69.44</v>
@@ -19152,9 +18610,7 @@
       <c r="T247" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="2" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>151.6</v>
@@ -19190,7 +18646,7 @@
         <v>-2.76</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>70.48</v>
@@ -19227,9 +18683,7 @@
       <c r="T248" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="2" t="n">
         <v>153.6</v>
@@ -19265,7 +18719,7 @@
         <v>5.39</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>71.78</v>
@@ -19302,9 +18756,7 @@
       <c r="T249" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="3" t="n">
         <v>155</v>
@@ -19340,7 +18792,7 @@
         <v>-1.67</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>72.94</v>
@@ -19377,9 +18829,7 @@
       <c r="T250" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>144.4</v>
@@ -19415,7 +18865,7 @@
         <v>3.78</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>74.17</v>
@@ -19452,9 +18902,7 @@
       <c r="T251" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>141.3</v>
@@ -19490,7 +18938,7 @@
         <v>6.63</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>75.56999999999999</v>
@@ -19527,9 +18975,7 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>144</v>
@@ -19565,7 +19011,7 @@
         <v>5.84</v>
       </c>
       <c r="I253" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>77.23</v>
@@ -19602,9 +19048,7 @@
       <c r="T253" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>148.1</v>
@@ -19640,7 +19084,7 @@
         <v>3.3</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>78.75</v>
@@ -19677,9 +19121,7 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>147.2</v>
@@ -19715,7 +19157,7 @@
         <v>3.95</v>
       </c>
       <c r="I255" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>80.73</v>
@@ -19752,9 +19194,7 @@
       <c r="T255" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>145</v>
@@ -19790,7 +19230,7 @@
         <v>-0.03</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>82.56</v>
@@ -19827,9 +19267,7 @@
       <c r="T256" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="2" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.7</v>
@@ -19865,7 +19303,7 @@
         <v>-28.54</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" s="4" t="n">
         <v>83.11</v>
@@ -19906,9 +19344,7 @@
       <c r="T257" s="6" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="6" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="6" t="inlineStr"/>
       <c r="V257" s="4" t="inlineStr"/>
       <c r="W257" s="6" t="n">
         <v>143.6</v>
@@ -19944,7 +19380,7 @@
         <v>-3.98</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>83.45</v>
@@ -19981,9 +19417,7 @@
       <c r="T258" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>146.6</v>
@@ -20019,7 +19453,7 @@
         <v>6.24</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>83.84</v>
@@ -20056,9 +19490,7 @@
       <c r="T259" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.9</v>
@@ -20094,7 +19526,7 @@
         <v>2.88</v>
       </c>
       <c r="I260" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>84.11</v>
@@ -20131,9 +19563,7 @@
       <c r="T260" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>143.2</v>
@@ -20169,7 +19599,7 @@
         <v>-15.77</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" s="4" t="n">
         <v>83.90000000000001</v>
@@ -20206,9 +19636,7 @@
       <c r="T261" s="6" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="6" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="6" t="inlineStr"/>
       <c r="V261" s="4" t="inlineStr"/>
       <c r="W261" s="6" t="n">
         <v>137.2</v>
@@ -20244,7 +19672,7 @@
         <v>5.25</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>83.92</v>
@@ -20281,9 +19709,7 @@
       <c r="T262" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="2" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>140.3</v>
@@ -20319,7 +19745,7 @@
         <v>8.33</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>84.11</v>
@@ -20356,9 +19782,7 @@
       <c r="T263" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="2" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.2</v>
@@ -20394,7 +19818,7 @@
         <v>-3.46</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>83.92</v>
@@ -20431,9 +19855,7 @@
       <c r="T264" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>145.7</v>
@@ -20469,7 +19891,7 @@
         <v>4.29</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>83.81999999999999</v>
@@ -20506,9 +19928,7 @@
       <c r="T265" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="2" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>143.8</v>
@@ -20544,7 +19964,7 @@
         <v>-11.53</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>82.97</v>
@@ -20581,9 +20001,7 @@
       <c r="T266" s="6" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="6" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="6" t="inlineStr"/>
       <c r="V266" s="4" t="inlineStr"/>
       <c r="W266" s="6" t="n">
         <v>142.5</v>
@@ -20619,7 +20037,7 @@
         <v>2.94</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>82.29000000000001</v>
@@ -20656,9 +20074,7 @@
       <c r="T267" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="2" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>139.4</v>
@@ -20694,7 +20110,7 @@
         <v>-4.8</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>81.56</v>
@@ -20735,9 +20151,7 @@
       <c r="T268" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>140.3</v>
@@ -20773,7 +20187,7 @@
         <v>5.6</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>80.8</v>
@@ -20810,9 +20224,7 @@
       <c r="T269" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="2" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>139.2</v>
@@ -20848,7 +20260,7 @@
         <v>1.31</v>
       </c>
       <c r="I270" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>80.15000000000001</v>
@@ -20885,9 +20297,7 @@
       <c r="T270" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>141.2</v>
@@ -20923,7 +20333,7 @@
         <v>7.9</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>79.62</v>
@@ -20960,9 +20370,7 @@
       <c r="T271" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>145.5</v>
@@ -20998,7 +20406,7 @@
         <v>5.16</v>
       </c>
       <c r="I272" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>79.01000000000001</v>
@@ -21035,9 +20443,7 @@
       <c r="T272" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.4</v>
@@ -21073,7 +20479,7 @@
         <v>-1.85</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>78.04000000000001</v>
@@ -21110,9 +20516,7 @@
       <c r="T273" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>141.9</v>
@@ -21148,7 +20552,7 @@
         <v>1.21</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>76.97</v>
@@ -21185,9 +20589,7 @@
       <c r="T274" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.1</v>
@@ -21223,7 +20625,7 @@
         <v>0.51</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>75.70999999999999</v>
@@ -21260,9 +20662,7 @@
       <c r="T275" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.6</v>
@@ -21298,7 +20698,7 @@
         <v>5.64</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>74.68000000000001</v>
@@ -21335,9 +20735,7 @@
       <c r="T276" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="2" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>146.7</v>
@@ -21373,7 +20771,7 @@
         <v>-4.02</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>74.98999999999999</v>
@@ -21410,9 +20808,7 @@
       <c r="T277" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="2" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="2" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>151.8</v>
@@ -21448,7 +20844,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I278" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21489,9 +20885,7 @@
       <c r="T278" s="6" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="6" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="6" t="inlineStr"/>
       <c r="V278" s="4" t="inlineStr"/>
       <c r="W278" s="6" t="n">
         <v>152.8</v>
@@ -21527,7 +20921,7 @@
         <v>0.88</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>75.02</v>
@@ -21564,9 +20958,7 @@
       <c r="T279" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="2" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>152.9</v>
@@ -21602,7 +20994,7 @@
         <v>-1.42</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>74.77</v>
@@ -21643,9 +21035,7 @@
       <c r="T280" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="2" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="2" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="2" t="n">
         <v>153.9</v>
@@ -21681,7 +21071,7 @@
         <v>2.25</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>75.23</v>
@@ -21718,14 +21108,8 @@
       <c r="T281" s="1" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="1" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21760,7 +21144,7 @@
         <v>3.06</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>75.64</v>
@@ -21797,9 +21181,7 @@
       <c r="T282" s="1" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="3" t="n">
         <v>158</v>
@@ -21835,7 +21217,7 @@
         <v>2.34</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>75.84</v>
@@ -21872,9 +21254,7 @@
       <c r="T283" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="2" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>154.5</v>
@@ -21910,7 +21290,7 @@
         <v>-2.72</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>76.06</v>
@@ -21947,9 +21327,7 @@
       <c r="T284" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="2" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>152.4</v>
@@ -21985,7 +21363,7 @@
         <v>-1.84</v>
       </c>
       <c r="I285" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>76.06</v>
@@ -22016,9 +21394,7 @@
       <c r="T285" s="1" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="2" t="n">
         <v>139.9</v>
@@ -22054,7 +21430,7 @@
         <v>-4.96</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>76.31</v>
@@ -22095,14 +21471,8 @@
       <c r="T286" s="1" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="1" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -22137,7 +21507,7 @@
         <v>0.73</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>76.48</v>
@@ -22174,9 +21544,7 @@
       <c r="T287" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>141.5</v>
@@ -22212,7 +21580,7 @@
         <v>-2.13</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>76.75</v>
@@ -22249,9 +21617,7 @@
       <c r="T288" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>145</v>
@@ -22287,7 +21653,7 @@
         <v>-4.13</v>
       </c>
       <c r="I289" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>76.68000000000001</v>
@@ -22324,9 +21690,7 @@
       <c r="T289" s="1" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>136.5</v>
@@ -22362,7 +21726,7 @@
         <v>-4.4</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>76.41</v>
@@ -22399,9 +21763,7 @@
       <c r="T290" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="2" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="2" t="n">
         <v>138.3</v>
@@ -22437,7 +21799,7 @@
         <v>-6.33</v>
       </c>
       <c r="I291" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" s="4" t="n">
         <v>75.66</v>
@@ -22478,14 +21840,8 @@
       <c r="T291" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="7" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="6" t="inlineStr"/>
+      <c r="V291" s="4" t="inlineStr"/>
       <c r="W291" s="6" t="n">
         <v>139.1</v>
       </c>
@@ -22520,7 +21876,7 @@
         <v>1.54</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>74.75</v>
@@ -22557,9 +21913,7 @@
       <c r="T292" s="1" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142</v>
@@ -22595,7 +21949,7 @@
         <v>0.77</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>73.95</v>
@@ -22632,9 +21986,7 @@
       <c r="T293" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="2" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>142.6</v>
@@ -22670,7 +22022,7 @@
         <v>3.59</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>73.2</v>
@@ -22707,9 +22059,7 @@
       <c r="T294" s="1" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>140.9</v>
@@ -22745,7 +22095,7 @@
         <v>-6.81</v>
       </c>
       <c r="I295" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" s="4" t="n">
         <v>72.22</v>
@@ -22786,9 +22136,7 @@
       <c r="T295" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="6" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="6" t="inlineStr"/>
       <c r="V295" s="4" t="inlineStr"/>
       <c r="W295" s="6" t="n">
         <v>144</v>
@@ -22824,7 +22172,7 @@
         <v>4.39</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>71.14</v>
@@ -22861,14 +22209,8 @@
       <c r="T296" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="1" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>139</v>
       </c>
@@ -22903,7 +22245,7 @@
         <v>0.13</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>70.23999999999999</v>
@@ -22940,9 +22282,7 @@
       <c r="T297" s="1" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>142.2</v>
@@ -22978,7 +22318,7 @@
         <v>7.27</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>69.91</v>
@@ -23015,9 +22355,7 @@
       <c r="T298" s="1" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>145.4</v>
@@ -23053,7 +22391,7 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>69.55</v>
@@ -23090,9 +22428,7 @@
       <c r="T299" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>143.8</v>
@@ -23128,7 +22464,7 @@
         <v>-3.45</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>69.13</v>
@@ -23165,9 +22501,7 @@
       <c r="T300" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="1" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>146.9</v>
@@ -23203,7 +22537,7 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>68.64</v>
@@ -23240,9 +22574,7 @@
       <c r="T301" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="2" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="2" t="n">
         <v>147.6</v>
@@ -23278,7 +22610,7 @@
         <v>-0.23</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>68.02</v>
@@ -23315,14 +22647,8 @@
       <c r="T302" s="1" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="1" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -23357,7 +22683,7 @@
         <v>2.32</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>67.39</v>
@@ -23394,9 +22720,7 @@
       <c r="T303" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>150.4</v>
@@ -23432,7 +22756,7 @@
         <v>1.36</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>66.91</v>
@@ -23469,9 +22793,7 @@
       <c r="T304" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>143.3</v>
@@ -23507,7 +22829,7 @@
         <v>1.01</v>
       </c>
       <c r="I305" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>66.54000000000001</v>
@@ -23544,9 +22866,7 @@
       <c r="T305" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="2" t="n">
         <v>144.2</v>
@@ -23582,7 +22902,7 @@
         <v>-1.16</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>66.31999999999999</v>
@@ -23619,9 +22939,7 @@
       <c r="T306" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="3" t="n">
         <v>156.9</v>
@@ -23657,7 +22975,7 @@
         <v>5.51</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>66.26000000000001</v>
@@ -23694,9 +23012,7 @@
       <c r="T307" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>149.9</v>
@@ -23732,7 +23048,7 @@
         <v>-0.28</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>66.27</v>
@@ -23769,9 +23085,7 @@
       <c r="T308" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="2" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>139.2</v>
@@ -23807,7 +23121,7 @@
         <v>-0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>66.40000000000001</v>
@@ -23844,9 +23158,7 @@
       <c r="T309" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>140.7</v>
@@ -23882,7 +23194,7 @@
         <v>3.35</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>66.8</v>
@@ -23919,9 +23231,7 @@
       <c r="T310" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.8</v>
@@ -23957,7 +23267,7 @@
         <v>-2.01</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>67.33</v>
@@ -23994,9 +23304,7 @@
       <c r="T311" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>141.9</v>
@@ -24032,7 +23340,7 @@
         <v>-5.07</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>67.63</v>
@@ -24069,9 +23377,7 @@
       <c r="T312" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.9</v>
@@ -24107,7 +23413,7 @@
         <v>2.74</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>68</v>
@@ -24144,9 +23450,7 @@
       <c r="T313" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>140.8</v>
@@ -24182,7 +23486,7 @@
         <v>-2.83</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>68.16</v>
@@ -24219,9 +23523,7 @@
       <c r="T314" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.6</v>
@@ -24257,7 +23559,7 @@
         <v>0.6</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>68.56</v>
@@ -24294,9 +23596,7 @@
       <c r="T315" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.1</v>
@@ -24332,7 +23632,7 @@
         <v>-0.67</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>68.8</v>
@@ -24373,9 +23673,7 @@
       <c r="T316" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>139.6</v>
@@ -24411,7 +23709,7 @@
         <v>-3.12</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>68.94</v>
@@ -24452,9 +23750,7 @@
       <c r="T317" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="2" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>138.2</v>
@@ -24490,7 +23786,7 @@
         <v>-2.05</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>68.77</v>
@@ -24527,9 +23823,7 @@
       <c r="T318" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="2" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>141.9</v>
@@ -24565,7 +23859,7 @@
         <v>2.81</v>
       </c>
       <c r="I319" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>68.7</v>
@@ -24602,9 +23896,7 @@
       <c r="T319" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>143.3</v>
@@ -24640,7 +23932,7 @@
         <v>2.45</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>68.81999999999999</v>
@@ -24677,9 +23969,7 @@
       <c r="T320" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.4</v>
@@ -24715,7 +24005,7 @@
         <v>-3.44</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>68.81999999999999</v>
@@ -24756,9 +24046,7 @@
       <c r="T321" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="2" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>141.7</v>
@@ -24794,7 +24082,7 @@
         <v>-0.05</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>68.81999999999999</v>
@@ -24831,9 +24119,7 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="2" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>138.7</v>
@@ -24869,7 +24155,7 @@
         <v>6.4</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>68.95</v>
@@ -24906,9 +24192,7 @@
       <c r="T323" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>135.4</v>
@@ -24944,7 +24228,7 @@
         <v>2.1</v>
       </c>
       <c r="I324" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>69.11</v>
@@ -24981,9 +24265,7 @@
       <c r="T324" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>136.1</v>
@@ -25019,7 +24301,7 @@
         <v>1.97</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>69.31</v>
@@ -25056,9 +24338,7 @@
       <c r="T325" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>138.2</v>
@@ -25094,7 +24374,7 @@
         <v>6.83</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>69.79000000000001</v>
@@ -25131,9 +24411,7 @@
       <c r="T326" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>140.2</v>
@@ -25169,7 +24447,7 @@
         <v>0.71</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>70.12</v>
@@ -25206,9 +24484,7 @@
       <c r="T327" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="2" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>139.4</v>
@@ -25244,7 +24520,7 @@
         <v>1.02</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>70.48999999999999</v>
@@ -25281,9 +24557,7 @@
       <c r="T328" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>141.5</v>
@@ -25319,7 +24593,7 @@
         <v>-4.84</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>70.70999999999999</v>
@@ -25356,9 +24630,7 @@
       <c r="T329" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>139.3</v>
@@ -25394,7 +24666,7 @@
         <v>-8.57</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>70.48</v>
@@ -25435,9 +24707,7 @@
       <c r="T330" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="6" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="6" t="inlineStr"/>
       <c r="V330" s="4" t="inlineStr"/>
       <c r="W330" s="6" t="n">
         <v>145.8</v>
@@ -25473,7 +24743,7 @@
         <v>1.3</v>
       </c>
       <c r="I331" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" t="n">
         <v>70.37</v>
@@ -25510,9 +24780,7 @@
       <c r="T331" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>138.4</v>
@@ -25548,7 +24816,7 @@
         <v>-4.35</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>70.29000000000001</v>
@@ -25585,9 +24853,7 @@
       <c r="T332" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>135.5</v>
@@ -25623,7 +24889,7 @@
         <v>2.74</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>70.20999999999999</v>
@@ -25660,9 +24926,7 @@
       <c r="T333" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>132.3</v>
@@ -25698,7 +24962,7 @@
         <v>1.05</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>70.26000000000001</v>
@@ -25735,9 +24999,7 @@
       <c r="T334" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="2" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137</v>
@@ -25773,7 +25035,7 @@
         <v>-1.57</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>70.23999999999999</v>
@@ -25810,9 +25072,7 @@
       <c r="T335" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>137.4</v>
@@ -25848,7 +25108,7 @@
         <v>1.99</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>70.31</v>
@@ -25885,9 +25145,7 @@
       <c r="T336" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="2" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>139</v>
@@ -25923,7 +25181,7 @@
         <v>-3.18</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>70.37</v>
@@ -25960,9 +25218,7 @@
       <c r="T337" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="2" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>138.6</v>
@@ -25998,7 +25254,7 @@
         <v>1.27</v>
       </c>
       <c r="I338" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>70.55</v>
@@ -26035,9 +25291,7 @@
       <c r="T338" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>139.5</v>
@@ -26073,7 +25327,7 @@
         <v>-0.04</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>70.63</v>
@@ -26110,9 +25364,7 @@
       <c r="T339" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="2" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>144.2</v>
@@ -26148,7 +25400,7 @@
         <v>-0.97</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>70.59999999999999</v>
@@ -26185,9 +25437,7 @@
       <c r="T340" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="2" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>142.5</v>
@@ -26223,7 +25473,7 @@
         <v>0.47</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>70.7</v>
@@ -26260,9 +25510,7 @@
       <c r="T341" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="2" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>143.2</v>
@@ -26298,7 +25546,7 @@
         <v>-2.62</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>70.72</v>
@@ -26335,9 +25583,7 @@
       <c r="T342" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>136.9</v>
@@ -26373,7 +25619,7 @@
         <v>1.16</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>70.56</v>
@@ -26410,9 +25656,7 @@
       <c r="T343" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>142.1</v>
@@ -26448,7 +25692,7 @@
         <v>-8.08</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>70.06</v>
@@ -26485,9 +25729,7 @@
       <c r="T344" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="6" t="inlineStr"/>
       <c r="V344" s="4" t="inlineStr"/>
       <c r="W344" s="6" t="n">
         <v>152.2</v>
@@ -26523,7 +25765,7 @@
         <v>0.02</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>69.48999999999999</v>
@@ -26560,9 +25802,7 @@
       <c r="T345" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="2" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>145</v>
@@ -26598,7 +25838,7 @@
         <v>-4.17</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>68.54000000000001</v>
@@ -26639,9 +25879,7 @@
       <c r="T346" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>142</v>
@@ -26677,7 +25915,7 @@
         <v>-2.29</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>67.48999999999999</v>
@@ -26718,9 +25956,7 @@
       <c r="T347" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="2" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143.1</v>
@@ -26756,7 +25992,7 @@
         <v>5.48</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>66.56999999999999</v>
@@ -26793,9 +26029,7 @@
       <c r="T348" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="2" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="2" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>143</v>
@@ -26831,7 +26065,7 @@
         <v>0.77</v>
       </c>
       <c r="I349" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>65.86</v>
@@ -26868,9 +26102,7 @@
       <c r="T349" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="2" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>142.6</v>
@@ -26906,7 +26138,7 @@
         <v>3.56</v>
       </c>
       <c r="I350" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>65.58</v>
@@ -26943,9 +26175,7 @@
       <c r="T350" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>144.3</v>
@@ -26981,7 +26211,7 @@
         <v>-0.13</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>65.25</v>
@@ -27018,9 +26248,7 @@
       <c r="T351" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="2" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.7</v>
@@ -27056,7 +26284,7 @@
         <v>-4.39</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>64.94</v>
@@ -27093,9 +26321,7 @@
       <c r="T352" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="2" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>142.6</v>
@@ -27131,7 +26357,7 @@
         <v>-1.81</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>64.47</v>
@@ -27168,9 +26394,7 @@
       <c r="T353" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="2" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>146.7</v>
@@ -27206,7 +26430,7 @@
         <v>-1.01</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>63.95</v>
@@ -27243,9 +26467,7 @@
       <c r="T354" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>141.9</v>
@@ -27281,7 +26503,7 @@
         <v>-5.4</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>63.32</v>
@@ -27322,9 +26544,7 @@
       <c r="T355" s="6" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="6" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="6" t="inlineStr"/>
       <c r="V355" s="4" t="inlineStr"/>
       <c r="W355" s="6" t="n">
         <v>143.1</v>
@@ -27360,7 +26580,7 @@
         <v>-7.09</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>62.42</v>
@@ -27401,9 +26621,7 @@
       <c r="T356" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="6" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="6" t="inlineStr"/>
       <c r="V356" s="4" t="inlineStr"/>
       <c r="W356" s="6" t="n">
         <v>145.3</v>
@@ -27439,7 +26657,7 @@
         <v>1.12</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>61.66</v>
@@ -27480,9 +26698,7 @@
       <c r="T357" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.9</v>
@@ -27518,7 +26734,7 @@
         <v>1.76</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>60.91</v>
@@ -27555,9 +26771,7 @@
       <c r="T358" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="2" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="2" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>139.4</v>
@@ -27593,7 +26807,7 @@
         <v>-1.13</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>60.12</v>
@@ -27630,9 +26844,7 @@
       <c r="T359" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="2" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>144.5</v>
@@ -27668,7 +26880,7 @@
         <v>1.5</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>59.42</v>
@@ -27705,9 +26917,7 @@
       <c r="T360" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>149.6</v>
@@ -27743,7 +26953,7 @@
         <v>0.21</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>58.69</v>
@@ -27780,9 +26990,7 @@
       <c r="T361" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="2" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>154.8</v>
@@ -27818,7 +27026,7 @@
         <v>2.69</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>58.14</v>
@@ -27855,9 +27063,7 @@
       <c r="T362" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="2" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>150</v>
@@ -27893,7 +27099,7 @@
         <v>1.98</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>57.59</v>
@@ -27930,9 +27136,7 @@
       <c r="T363" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="2" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.4</v>
@@ -27968,7 +27172,7 @@
         <v>-2.94</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>57.24</v>
@@ -28009,9 +27213,7 @@
       <c r="T364" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="2" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>145.7</v>
@@ -28047,7 +27249,7 @@
         <v>-2.99</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>56.8</v>
@@ -28088,9 +27290,7 @@
       <c r="T365" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>149.8</v>
@@ -28126,7 +27326,7 @@
         <v>2.48</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>56.55</v>
@@ -28163,9 +27363,7 @@
       <c r="T366" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.7</v>
@@ -28201,7 +27399,7 @@
         <v>-0.35</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>56.37</v>
@@ -28238,9 +27436,7 @@
       <c r="T367" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>144.3</v>
@@ -28276,7 +27472,7 @@
         <v>-3.32</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>55.94</v>
@@ -28313,9 +27509,7 @@
       <c r="T368" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="2" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.7</v>
@@ -28351,7 +27545,7 @@
         <v>1.94</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>55.53</v>
@@ -28388,9 +27582,7 @@
       <c r="T369" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="2" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>145.1</v>
@@ -28426,7 +27618,7 @@
         <v>-1.81</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>54.97</v>
@@ -28463,9 +27655,7 @@
       <c r="T370" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="2" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>148.5</v>
@@ -28501,7 +27691,7 @@
         <v>-3.49</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>54.32</v>
@@ -28538,9 +27728,7 @@
       <c r="T371" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>145.7</v>
@@ -28576,7 +27764,7 @@
         <v>0.77</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>53.83</v>
@@ -28613,9 +27801,7 @@
       <c r="T372" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="2" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>147.3</v>
@@ -28651,7 +27837,7 @@
         <v>0.39</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>53.4</v>
@@ -28724,7 +27910,7 @@
         <v>4.12</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>53.11</v>
@@ -28797,7 +27983,7 @@
         <v>1.58</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>53.02</v>
@@ -28870,7 +28056,7 @@
         <v>-3.45</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>53.03</v>
@@ -28947,7 +28133,7 @@
         <v>1.02</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>53.04</v>
@@ -29020,7 +28206,7 @@
         <v>0.65</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>53.03</v>
@@ -29093,7 +28279,7 @@
         <v>-2.32</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>52.98</v>
@@ -29166,7 +28352,7 @@
         <v>0.14</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>52.89</v>
@@ -29239,7 +28425,7 @@
         <v>3.34</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>52.89</v>
@@ -29312,7 +28498,7 @@
         <v>-2.13</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>52.75</v>
@@ -29389,7 +28575,7 @@
         <v>0.19</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>52.57</v>
@@ -29462,7 +28648,7 @@
         <v>2.63</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>52.54</v>
@@ -29535,7 +28721,7 @@
         <v>4.14</v>
       </c>
       <c r="I385" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>52.7</v>
@@ -29608,7 +28794,7 @@
         <v>-0.39</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>52.79</v>
@@ -29681,7 +28867,7 @@
         <v>2.95</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>52.97</v>
@@ -29754,7 +28940,7 @@
         <v>3.32</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>53.33</v>
@@ -29827,7 +29013,7 @@
         <v>-1.45</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>53.6</v>
@@ -29900,7 +29086,7 @@
         <v>0.87</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>53.94</v>
@@ -29973,7 +29159,7 @@
         <v>-1.52</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>54.33</v>
@@ -30046,7 +29232,7 @@
         <v>0.55</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>54.71</v>
@@ -30119,7 +29305,7 @@
         <v>1.86</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>55.14</v>
@@ -30192,7 +29378,7 @@
         <v>-3.58</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>55.36</v>
@@ -30269,7 +29455,7 @@
         <v>4.47</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>55.67</v>
@@ -30342,7 +29528,7 @@
         <v>2.75</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>56.15</v>
@@ -30415,7 +29601,7 @@
         <v>1.72</v>
       </c>
       <c r="I397" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>56.65</v>
@@ -30488,7 +29674,7 @@
         <v>-0.83</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>57.12</v>
@@ -30561,7 +29747,7 @@
         <v>0.19</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>57.65</v>
@@ -30634,7 +29820,7 @@
         <v>-1.17</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>58.14</v>
@@ -30707,7 +29893,7 @@
         <v>1.92</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>58.6</v>
@@ -30780,7 +29966,7 @@
         <v>-4.38</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>58.98</v>
@@ -30853,7 +30039,7 @@
         <v>0.18</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>59.37</v>
@@ -30926,7 +30112,7 @@
         <v>-3.68</v>
       </c>
       <c r="I404" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>59.57</v>
@@ -31003,7 +30189,7 @@
         <v>1.99</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>59.72</v>
@@ -31076,7 +30262,7 @@
         <v>2.51</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>59.96</v>
@@ -31149,7 +30335,7 @@
         <v>-1.21</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>60.07</v>
@@ -31226,7 +30412,7 @@
         <v>-0.75</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>60.07</v>
@@ -31299,7 +30485,7 @@
         <v>2.27</v>
       </c>
       <c r="I409" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" t="n">
         <v>60.18</v>
@@ -31372,7 +30558,7 @@
         <v>-5.3</v>
       </c>
       <c r="I410" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>60.1</v>
@@ -31449,7 +30635,7 @@
         <v>1.08</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>60.1</v>
@@ -31516,13 +30702,13 @@
         <v>56.84</v>
       </c>
       <c r="G412" t="n">
-        <v>14116900</v>
+        <v>14182100</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-2.2</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>60.02</v>
@@ -31580,37 +30766,37 @@
         <v>57.48</v>
       </c>
       <c r="D413" t="n">
-        <v>57.73</v>
+        <v>57.75</v>
       </c>
       <c r="E413" t="n">
         <v>56.95</v>
       </c>
       <c r="F413" t="n">
-        <v>57.33</v>
+        <v>57.53</v>
       </c>
       <c r="G413" t="n">
-        <v>7955051</v>
+        <v>11722514</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.86</v>
+        <v>1.21</v>
       </c>
       <c r="I413" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>59.91</v>
+        <v>59.92</v>
       </c>
       <c r="K413" t="n">
         <v>56.15</v>
       </c>
       <c r="L413" t="n">
-        <v>61.85</v>
+        <v>61.86</v>
       </c>
       <c r="M413" t="n">
         <v>65.68000000000001</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>35.94</v>
+        <v>36.66</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31627,16 +30813,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -30689,28 +30689,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="D412" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="E412" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="F412" t="n">
+        <v>57.53</v>
+      </c>
       <c r="G412" t="n">
-        <v>11722514</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>11759600</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>1.21</v>
       </c>
       <c r="I412" t="n">
         <v>5.2</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="K412" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="L412" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="M412" t="n">
+        <v>65.68000000000001</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>34.13</v>
+        <v>36.66</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>-1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>27.36</v>
@@ -685,7 +685,7 @@
         <v>0.62</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>27.38</v>
@@ -758,7 +758,7 @@
         <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>27.44</v>
@@ -831,7 +831,7 @@
         <v>2.57</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>27.56</v>
@@ -904,7 +904,7 @@
         <v>-0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>27.67</v>
@@ -977,7 +977,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>27.75</v>
@@ -1050,7 +1050,7 @@
         <v>1.92</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>27.87</v>
@@ -1123,7 +1123,7 @@
         <v>0.44</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>27.97</v>
@@ -1196,7 +1196,7 @@
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>28.07</v>
@@ -1269,7 +1269,7 @@
         <v>-1.19</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>28.16</v>
@@ -1342,7 +1342,7 @@
         <v>0.59</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>28.24</v>
@@ -1415,7 +1415,7 @@
         <v>-0.68</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>28.34</v>
@@ -1488,7 +1488,7 @@
         <v>1.17</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>28.44</v>
@@ -1561,7 +1561,7 @@
         <v>0.41</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>28.52</v>
@@ -1634,7 +1634,7 @@
         <v>-0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>28.58</v>
@@ -1707,7 +1707,7 @@
         <v>2.05</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>28.7</v>
@@ -1780,7 +1780,7 @@
         <v>-0.33</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>28.79</v>
@@ -1853,7 +1853,7 @@
         <v>0.47</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>28.88</v>
@@ -1926,7 +1926,7 @@
         <v>-1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>28.97</v>
@@ -1999,7 +1999,7 @@
         <v>-0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>29.05</v>
@@ -2072,7 +2072,7 @@
         <v>-2.07</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.12</v>
@@ -2149,7 +2149,7 @@
         <v>0.38</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.18</v>
@@ -2222,7 +2222,7 @@
         <v>-1.87</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.2</v>
@@ -2295,7 +2295,7 @@
         <v>-0.32</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.18</v>
@@ -2372,7 +2372,7 @@
         <v>1.55</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.19</v>
@@ -2445,7 +2445,7 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.21</v>
@@ -2518,7 +2518,7 @@
         <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.24</v>
@@ -2591,7 +2591,7 @@
         <v>-0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.26</v>
@@ -2664,7 +2664,7 @@
         <v>-0.34</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.27</v>
@@ -2737,7 +2737,7 @@
         <v>-1.62</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.27</v>
@@ -2814,7 +2814,7 @@
         <v>2.92</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.31</v>
@@ -2887,7 +2887,7 @@
         <v>0.87</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.37</v>
@@ -2960,7 +2960,7 @@
         <v>1.72</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.44</v>
@@ -3033,7 +3033,7 @@
         <v>-0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.5</v>
@@ -3106,7 +3106,7 @@
         <v>0.33</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.58</v>
@@ -3179,7 +3179,7 @@
         <v>0.13</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.62</v>
@@ -3252,7 +3252,7 @@
         <v>-0.32</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>29.67</v>
@@ -3325,7 +3325,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>29.7</v>
@@ -3398,7 +3398,7 @@
         <v>-1.57</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>29.72</v>
@@ -3471,7 +3471,7 @@
         <v>-0.2</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>29.75</v>
@@ -3544,7 +3544,7 @@
         <v>2.07</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>29.83</v>
@@ -3617,7 +3617,7 @@
         <v>-0.16</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>29.91</v>
@@ -3690,7 +3690,7 @@
         <v>2.59</v>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>30.06</v>
@@ -3763,7 +3763,7 @@
         <v>-1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>30.19</v>
@@ -3836,7 +3836,7 @@
         <v>-0.03</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>30.3</v>
@@ -3909,7 +3909,7 @@
         <v>-1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>30.39</v>
@@ -3982,7 +3982,7 @@
         <v>0.42</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>30.44</v>
@@ -4055,7 +4055,7 @@
         <v>-6.08</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>30.4</v>
@@ -4132,7 +4132,7 @@
         <v>-6.27</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>30.27</v>
@@ -4209,7 +4209,7 @@
         <v>0.22</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>30.17</v>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>30.03</v>
@@ -4363,7 +4363,7 @@
         <v>3.39</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.92</v>
@@ -4436,7 +4436,7 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.8</v>
@@ -4509,7 +4509,7 @@
         <v>3.22</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.72</v>
@@ -4582,7 +4582,7 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.65</v>
@@ -4655,7 +4655,7 @@
         <v>0.1</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.58</v>
@@ -4728,7 +4728,7 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.53</v>
@@ -4801,7 +4801,7 @@
         <v>-0.71</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.48</v>
@@ -4874,7 +4874,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.47</v>
@@ -4947,7 +4947,7 @@
         <v>-0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.45</v>
@@ -5020,7 +5020,7 @@
         <v>3.59</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.45</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.45</v>
@@ -5166,7 +5166,7 @@
         <v>-1.67</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.39</v>
@@ -5239,7 +5239,7 @@
         <v>0.47</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.35</v>
@@ -5312,7 +5312,7 @@
         <v>-1.19</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.29</v>
@@ -5385,7 +5385,7 @@
         <v>-0.77</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.24</v>
@@ -5462,7 +5462,7 @@
         <v>-0.71</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.17</v>
@@ -5535,7 +5535,7 @@
         <v>-0.92</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.18</v>
@@ -5612,7 +5612,7 @@
         <v>1.24</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.3</v>
@@ -5685,7 +5685,7 @@
         <v>2.51</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.45</v>
@@ -5758,7 +5758,7 @@
         <v>-2.42</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.57</v>
@@ -5835,7 +5835,7 @@
         <v>-0.1</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.64</v>
@@ -5908,7 +5908,7 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.72</v>
@@ -5981,7 +5981,7 @@
         <v>-0.57</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.74</v>
@@ -6058,7 +6058,7 @@
         <v>1.01</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.77</v>
@@ -6131,7 +6131,7 @@
         <v>-2.27</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.76</v>
@@ -6208,7 +6208,7 @@
         <v>1.23</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.75</v>
@@ -6281,7 +6281,7 @@
         <v>-1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6354,7 +6354,7 @@
         <v>0.41</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>29.72</v>
@@ -6427,7 +6427,7 @@
         <v>2.41</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>29.75</v>
@@ -6500,7 +6500,7 @@
         <v>1.26</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.75</v>
@@ -6573,7 +6573,7 @@
         <v>-1.57</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.72</v>
@@ -6646,7 +6646,7 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.74</v>
@@ -6719,7 +6719,7 @@
         <v>-0.72</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>29.74</v>
@@ -6792,7 +6792,7 @@
         <v>-0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>29.75</v>
@@ -6865,7 +6865,7 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>29.79</v>
@@ -6938,7 +6938,7 @@
         <v>-0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>29.82</v>
@@ -7011,7 +7011,7 @@
         <v>5.3</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>29.94</v>
@@ -7084,7 +7084,7 @@
         <v>-0.47</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>30.04</v>
@@ -7157,7 +7157,7 @@
         <v>-0.32</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>30.09</v>
@@ -7230,7 +7230,7 @@
         <v>3.54</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>30.24</v>
@@ -7303,7 +7303,7 @@
         <v>0.74</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>30.4</v>
@@ -7376,7 +7376,7 @@
         <v>2.14</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>30.58</v>
@@ -7449,7 +7449,7 @@
         <v>-0.48</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>30.76</v>
@@ -7522,7 +7522,7 @@
         <v>-0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>30.91</v>
@@ -7595,7 +7595,7 @@
         <v>0.33</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>31.1</v>
@@ -7668,7 +7668,7 @@
         <v>-0.27</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>31.27</v>
@@ -7741,7 +7741,7 @@
         <v>0.18</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>31.46</v>
@@ -7814,7 +7814,7 @@
         <v>2.15</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>31.68</v>
@@ -7887,7 +7887,7 @@
         <v>-1.39</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>31.83</v>
@@ -7960,7 +7960,7 @@
         <v>-1.65</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>31.94</v>
@@ -8033,7 +8033,7 @@
         <v>0.73</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>32.09</v>
@@ -8106,7 +8106,7 @@
         <v>-1.06</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>32.2</v>
@@ -8179,7 +8179,7 @@
         <v>1.23</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>32.34</v>
@@ -8252,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>32.5</v>
@@ -8325,7 +8325,7 @@
         <v>-2.16</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>32.62</v>
@@ -8398,7 +8398,7 @@
         <v>0.58</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>32.76</v>
@@ -8471,7 +8471,7 @@
         <v>-0.24</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>32.82</v>
@@ -8548,7 +8548,7 @@
         <v>1.56</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>32.91</v>
@@ -8621,7 +8621,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>33.02</v>
@@ -8694,7 +8694,7 @@
         <v>-0.24</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.07</v>
@@ -8767,7 +8767,7 @@
         <v>-0.42</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.1</v>
@@ -8840,7 +8840,7 @@
         <v>-0.87</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.08</v>
@@ -8917,7 +8917,7 @@
         <v>2.27</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>33.1</v>
@@ -8990,7 +8990,7 @@
         <v>3.79</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>33.21</v>
@@ -9063,7 +9063,7 @@
         <v>-1.14</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>33.28</v>
@@ -9136,7 +9136,7 @@
         <v>-1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>33.35</v>
@@ -9209,7 +9209,7 @@
         <v>0.44</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>33.42</v>
@@ -9282,7 +9282,7 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>33.46</v>
@@ -9355,7 +9355,7 @@
         <v>-0.12</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>33.53</v>
@@ -9428,7 +9428,7 @@
         <v>2.14</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>33.66</v>
@@ -9501,7 +9501,7 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>33.8</v>
@@ -9574,7 +9574,7 @@
         <v>-0.08</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>33.95</v>
@@ -9647,7 +9647,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.08</v>
@@ -9720,7 +9720,7 @@
         <v>-2.34</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.14</v>
@@ -9793,7 +9793,7 @@
         <v>-0.06</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.24</v>
@@ -9866,7 +9866,7 @@
         <v>0.06</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.34</v>
@@ -9939,7 +9939,7 @@
         <v>-3.32</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>-0.57</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.38</v>
@@ -10089,7 +10089,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.38</v>
@@ -10162,7 +10162,7 @@
         <v>1.16</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.41</v>
@@ -10235,7 +10235,7 @@
         <v>1.09</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.46</v>
@@ -10308,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.53</v>
@@ -10381,7 +10381,7 @@
         <v>1.19</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10454,7 +10454,7 @@
         <v>0.35</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10527,7 +10527,7 @@
         <v>-2.01</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.55</v>
@@ -10604,7 +10604,7 @@
         <v>0.67</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.56</v>
@@ -10677,7 +10677,7 @@
         <v>1.71</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.59</v>
@@ -10750,7 +10750,7 @@
         <v>-1.43</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.58</v>
@@ -10827,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.58</v>
@@ -10900,7 +10900,7 @@
         <v>0.14</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.54</v>
@@ -10973,7 +10973,7 @@
         <v>-1.97</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>34.44</v>
@@ -11050,7 +11050,7 @@
         <v>1.65</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>34.38</v>
@@ -11123,7 +11123,7 @@
         <v>0.52</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>34.34</v>
@@ -11196,7 +11196,7 @@
         <v>2.11</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>34.37</v>
@@ -11269,7 +11269,7 @@
         <v>-0.91</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>34.39</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>34.41</v>
@@ -11415,7 +11415,7 @@
         <v>-0.09</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>34.48</v>
@@ -11488,7 +11488,7 @@
         <v>1.51</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>34.59</v>
@@ -11561,7 +11561,7 @@
         <v>1.89</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>34.72</v>
@@ -11634,7 +11634,7 @@
         <v>2.65</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>34.88</v>
@@ -11707,7 +11707,7 @@
         <v>0.51</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>35.03</v>
@@ -11780,7 +11780,7 @@
         <v>-1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>35.16</v>
@@ -11853,7 +11853,7 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>35.28</v>
@@ -11926,7 +11926,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>35.41</v>
@@ -11999,7 +11999,7 @@
         <v>-0.88</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>35.56</v>
@@ -12072,7 +12072,7 @@
         <v>0.62</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>35.71</v>
@@ -12145,7 +12145,7 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>35.85</v>
@@ -12218,7 +12218,7 @@
         <v>1.46</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>36.04</v>
@@ -12291,7 +12291,7 @@
         <v>1.1</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>36.26</v>
@@ -12364,7 +12364,7 @@
         <v>-0.41</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>36.46</v>
@@ -12437,7 +12437,7 @@
         <v>-2.1</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>36.66</v>
@@ -12510,7 +12510,7 @@
         <v>0.53</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>36.83</v>
@@ -12583,7 +12583,7 @@
         <v>2.76</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>37.06</v>
@@ -12656,7 +12656,7 @@
         <v>2.56</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>37.29</v>
@@ -12729,7 +12729,7 @@
         <v>-0.2</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>37.54</v>
@@ -12802,7 +12802,7 @@
         <v>-0.35</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>37.78</v>
@@ -12875,7 +12875,7 @@
         <v>3.04</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>38.08</v>
@@ -12948,7 +12948,7 @@
         <v>2.02</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>38.4</v>
@@ -13021,7 +13021,7 @@
         <v>1.53</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>38.71</v>
@@ -13094,7 +13094,7 @@
         <v>-0.31</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>38.97</v>
@@ -13167,7 +13167,7 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>39.25</v>
@@ -13240,7 +13240,7 @@
         <v>-0.89</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>39.53</v>
@@ -13313,7 +13313,7 @@
         <v>2.33</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>39.85</v>
@@ -13386,7 +13386,7 @@
         <v>1.24</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>40.17</v>
@@ -13459,7 +13459,7 @@
         <v>-1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>40.49</v>
@@ -13532,7 +13532,7 @@
         <v>2.7</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>40.84</v>
@@ -13605,7 +13605,7 @@
         <v>0.34</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>41.19</v>
@@ -13678,7 +13678,7 @@
         <v>1.61</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>41.54</v>
@@ -13751,7 +13751,7 @@
         <v>4.03</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>41.97</v>
@@ -13824,7 +13824,7 @@
         <v>-0.97</v>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>42.38</v>
@@ -13897,7 +13897,7 @@
         <v>3.27</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>42.91</v>
@@ -13970,7 +13970,7 @@
         <v>1.74</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>43.46</v>
@@ -14043,7 +14043,7 @@
         <v>-4.43</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>43.86</v>
@@ -14116,7 +14116,7 @@
         <v>1.55</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>44.25</v>
@@ -14189,7 +14189,7 @@
         <v>-8.24</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>44.44</v>
@@ -14266,7 +14266,7 @@
         <v>0.21</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>44.64</v>
@@ -14339,7 +14339,7 @@
         <v>0.68</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>44.8</v>
@@ -14412,7 +14412,7 @@
         <v>-0.43</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>44.9</v>
@@ -14485,7 +14485,7 @@
         <v>-3.61</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>44.9</v>
@@ -14558,7 +14558,7 @@
         <v>0.71</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>44.92</v>
@@ -14631,7 +14631,7 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>44.93</v>
@@ -14704,7 +14704,7 @@
         <v>2.57</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>45.02</v>
@@ -14777,7 +14777,7 @@
         <v>-0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>45.05</v>
@@ -14850,7 +14850,7 @@
         <v>-0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>45.03</v>
@@ -14923,7 +14923,7 @@
         <v>-2.33</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>45</v>
@@ -14996,7 +14996,7 @@
         <v>2.13</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>44.95</v>
@@ -15069,7 +15069,7 @@
         <v>-0.23</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.9</v>
@@ -15142,7 +15142,7 @@
         <v>0.85</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.82</v>
@@ -15215,7 +15215,7 @@
         <v>4.26</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>44.75</v>
@@ -15288,7 +15288,7 @@
         <v>1.44</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>44.73</v>
@@ -15361,7 +15361,7 @@
         <v>4.03</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>44.73</v>
@@ -15434,7 +15434,7 @@
         <v>-1.86</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>44.64</v>
@@ -15507,7 +15507,7 @@
         <v>-3.08</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>44.59</v>
@@ -15580,7 +15580,7 @@
         <v>-1.07</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>44.48</v>
@@ -15653,7 +15653,7 @@
         <v>1.39</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>44.59</v>
@@ -15726,7 +15726,7 @@
         <v>0.76</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>44.72</v>
@@ -15799,7 +15799,7 @@
         <v>-1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>44.8</v>
@@ -15872,7 +15872,7 @@
         <v>-1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>44.87</v>
@@ -15945,7 +15945,7 @@
         <v>2.94</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>45.08</v>
@@ -16018,7 +16018,7 @@
         <v>0.09</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>45.28</v>
@@ -16091,7 +16091,7 @@
         <v>3.71</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>45.54</v>
@@ -16164,7 +16164,7 @@
         <v>5.81</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>45.88</v>
@@ -16237,7 +16237,7 @@
         <v>2.56</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>46.3</v>
@@ -16310,7 +16310,7 @@
         <v>1.16</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>46.77</v>
@@ -16383,7 +16383,7 @@
         <v>-0.11</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>47.29</v>
@@ -16456,7 +16456,7 @@
         <v>-2.47</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>47.7</v>
@@ -16529,7 +16529,7 @@
         <v>2.3</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>48.16</v>
@@ -16602,7 +16602,7 @@
         <v>-0.45</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>48.6</v>
@@ -16675,7 +16675,7 @@
         <v>4.67</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>49.07</v>
@@ -16748,7 +16748,7 @@
         <v>1.63</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>49.55</v>
@@ -16821,7 +16821,7 @@
         <v>2.76</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>50.02</v>
@@ -16894,7 +16894,7 @@
         <v>-2.64</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>50.45</v>
@@ -16967,7 +16967,7 @@
         <v>3.58</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>51.06</v>
@@ -17040,7 +17040,7 @@
         <v>-0.65</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>51.67</v>
@@ -17113,7 +17113,7 @@
         <v>4.38</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>52.38</v>
@@ -17186,7 +17186,7 @@
         <v>-1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>53.03</v>
@@ -17259,7 +17259,7 @@
         <v>2.71</v>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" t="n">
         <v>53.78</v>
@@ -17332,7 +17332,7 @@
         <v>2.53</v>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>54.64</v>
@@ -17405,7 +17405,7 @@
         <v>3.79</v>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" t="n">
         <v>55.55</v>
@@ -17478,7 +17478,7 @@
         <v>0.59</v>
       </c>
       <c r="I232" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" t="n">
         <v>56.48</v>
@@ -17551,7 +17551,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>57.62</v>
@@ -17624,7 +17624,7 @@
         <v>-7.19</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>58.36</v>
@@ -17697,7 +17697,7 @@
         <v>4.5</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>59.18</v>
@@ -17770,7 +17770,7 @@
         <v>-6.61</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>59.74</v>
@@ -17843,7 +17843,7 @@
         <v>2.06</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>60.38</v>
@@ -17916,7 +17916,7 @@
         <v>5.06</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>61.24</v>
@@ -17989,7 +17989,7 @@
         <v>6.7</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>62.28</v>
@@ -18062,7 +18062,7 @@
         <v>-3.73</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>63.19</v>
@@ -18135,7 +18135,7 @@
         <v>-1.76</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>63.92</v>
@@ -18208,7 +18208,7 @@
         <v>3.83</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>64.73999999999999</v>
@@ -18281,7 +18281,7 @@
         <v>6.7</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>65.72</v>
@@ -18354,7 +18354,7 @@
         <v>1.77</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>66.84</v>
@@ -18427,7 +18427,7 @@
         <v>7.58</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>68.16</v>
@@ -18500,7 +18500,7 @@
         <v>-1.47</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>69.44</v>
@@ -18573,7 +18573,7 @@
         <v>-2.76</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>70.48</v>
@@ -18646,7 +18646,7 @@
         <v>5.39</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>71.78</v>
@@ -18719,7 +18719,7 @@
         <v>-1.67</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>72.94</v>
@@ -18792,7 +18792,7 @@
         <v>3.78</v>
       </c>
       <c r="I250" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" t="n">
         <v>74.17</v>
@@ -18865,7 +18865,7 @@
         <v>6.63</v>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" t="n">
         <v>75.56999999999999</v>
@@ -18938,7 +18938,7 @@
         <v>5.84</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>77.23</v>
@@ -19011,7 +19011,7 @@
         <v>3.3</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>78.75</v>
@@ -19084,7 +19084,7 @@
         <v>3.95</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>80.73</v>
@@ -19157,7 +19157,7 @@
         <v>-0.03</v>
       </c>
       <c r="I255" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" t="n">
         <v>82.56</v>
@@ -19230,7 +19230,7 @@
         <v>-28.54</v>
       </c>
       <c r="I256" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" s="4" t="n">
         <v>83.11</v>
@@ -19307,7 +19307,7 @@
         <v>-3.98</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>83.45</v>
@@ -19380,7 +19380,7 @@
         <v>6.24</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>83.84</v>
@@ -19453,7 +19453,7 @@
         <v>2.88</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>84.11</v>
@@ -19526,7 +19526,7 @@
         <v>-15.77</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19599,7 +19599,7 @@
         <v>5.25</v>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" t="n">
         <v>83.92</v>
@@ -19672,7 +19672,7 @@
         <v>8.33</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>84.11</v>
@@ -19745,7 +19745,7 @@
         <v>-3.46</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>83.92</v>
@@ -19818,7 +19818,7 @@
         <v>4.29</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>83.81999999999999</v>
@@ -19891,7 +19891,7 @@
         <v>-11.53</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>82.97</v>
@@ -19964,7 +19964,7 @@
         <v>2.94</v>
       </c>
       <c r="I266" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>82.29000000000001</v>
@@ -20037,7 +20037,7 @@
         <v>-4.8</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>81.56</v>
@@ -20114,7 +20114,7 @@
         <v>5.6</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>80.8</v>
@@ -20187,7 +20187,7 @@
         <v>1.31</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>80.15000000000001</v>
@@ -20260,7 +20260,7 @@
         <v>7.9</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>79.62</v>
@@ -20333,7 +20333,7 @@
         <v>5.16</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>79.01000000000001</v>
@@ -20406,7 +20406,7 @@
         <v>-1.85</v>
       </c>
       <c r="I272" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" t="n">
         <v>78.04000000000001</v>
@@ -20479,7 +20479,7 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>76.97</v>
@@ -20552,7 +20552,7 @@
         <v>0.51</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>75.70999999999999</v>
@@ -20625,7 +20625,7 @@
         <v>5.64</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>74.68000000000001</v>
@@ -20698,7 +20698,7 @@
         <v>-4.02</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>74.98999999999999</v>
@@ -20771,7 +20771,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I277" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>75.09999999999999</v>
@@ -20848,7 +20848,7 @@
         <v>0.88</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>75.02</v>
@@ -20921,7 +20921,7 @@
         <v>-1.42</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>74.77</v>
@@ -20998,7 +20998,7 @@
         <v>2.25</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>75.23</v>
@@ -21071,7 +21071,7 @@
         <v>3.06</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>75.64</v>
@@ -21144,7 +21144,7 @@
         <v>2.34</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>75.84</v>
@@ -21217,7 +21217,7 @@
         <v>-2.72</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>76.06</v>
@@ -21290,7 +21290,7 @@
         <v>-1.84</v>
       </c>
       <c r="I284" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" t="n">
         <v>76.06</v>
@@ -21357,7 +21357,7 @@
         <v>-4.96</v>
       </c>
       <c r="I285" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" t="n">
         <v>76.31</v>
@@ -21434,7 +21434,7 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>76.48</v>
@@ -21507,7 +21507,7 @@
         <v>-2.13</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>76.75</v>
@@ -21580,7 +21580,7 @@
         <v>-4.13</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>76.68000000000001</v>
@@ -21653,7 +21653,7 @@
         <v>-4.4</v>
       </c>
       <c r="I289" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" t="n">
         <v>76.41</v>
@@ -21726,7 +21726,7 @@
         <v>-6.33</v>
       </c>
       <c r="I290" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>75.66</v>
@@ -21803,7 +21803,7 @@
         <v>1.54</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>74.75</v>
@@ -21876,7 +21876,7 @@
         <v>0.77</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>73.95</v>
@@ -21949,7 +21949,7 @@
         <v>3.59</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>73.2</v>
@@ -22022,7 +22022,7 @@
         <v>-6.81</v>
       </c>
       <c r="I294" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" s="4" t="n">
         <v>72.22</v>
@@ -22099,7 +22099,7 @@
         <v>4.39</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>71.14</v>
@@ -22172,7 +22172,7 @@
         <v>0.13</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>70.23999999999999</v>
@@ -22245,7 +22245,7 @@
         <v>7.27</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>69.91</v>
@@ -22318,7 +22318,7 @@
         <v>0</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>69.55</v>
@@ -22391,7 +22391,7 @@
         <v>-3.45</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>69.13</v>
@@ -22464,7 +22464,7 @@
         <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>68.64</v>
@@ -22537,7 +22537,7 @@
         <v>-0.23</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>68.02</v>
@@ -22610,7 +22610,7 @@
         <v>2.32</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>67.39</v>
@@ -22683,7 +22683,7 @@
         <v>1.36</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>66.91</v>
@@ -22756,7 +22756,7 @@
         <v>1.01</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>66.54000000000001</v>
@@ -22829,7 +22829,7 @@
         <v>-1.16</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>66.31999999999999</v>
@@ -22902,7 +22902,7 @@
         <v>5.51</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>66.26000000000001</v>
@@ -22975,7 +22975,7 @@
         <v>-0.28</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>66.27</v>
@@ -23048,7 +23048,7 @@
         <v>-0.84</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>66.40000000000001</v>
@@ -23121,7 +23121,7 @@
         <v>3.35</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>66.8</v>
@@ -23194,7 +23194,7 @@
         <v>-2.01</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>67.33</v>
@@ -23267,7 +23267,7 @@
         <v>-5.07</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>67.63</v>
@@ -23340,7 +23340,7 @@
         <v>2.74</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>68</v>
@@ -23413,7 +23413,7 @@
         <v>-2.83</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>68.16</v>
@@ -23486,7 +23486,7 @@
         <v>0.6</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>68.56</v>
@@ -23559,7 +23559,7 @@
         <v>-0.67</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>68.8</v>
@@ -23636,7 +23636,7 @@
         <v>-3.12</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>68.94</v>
@@ -23713,7 +23713,7 @@
         <v>-2.05</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>68.77</v>
@@ -23786,7 +23786,7 @@
         <v>2.81</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>68.7</v>
@@ -23859,7 +23859,7 @@
         <v>2.45</v>
       </c>
       <c r="I319" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" t="n">
         <v>68.81999999999999</v>
@@ -23932,7 +23932,7 @@
         <v>-3.44</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>68.81999999999999</v>
@@ -24009,7 +24009,7 @@
         <v>-0.05</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>68.81999999999999</v>
@@ -24082,7 +24082,7 @@
         <v>6.4</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>68.95</v>
@@ -24155,7 +24155,7 @@
         <v>2.1</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>69.11</v>
@@ -24228,7 +24228,7 @@
         <v>1.97</v>
       </c>
       <c r="I324" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" t="n">
         <v>69.31</v>
@@ -24301,7 +24301,7 @@
         <v>6.83</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>69.79000000000001</v>
@@ -24374,7 +24374,7 @@
         <v>0.71</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>70.12</v>
@@ -24447,7 +24447,7 @@
         <v>1.02</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.48999999999999</v>
@@ -24520,7 +24520,7 @@
         <v>-4.84</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.70999999999999</v>
@@ -24593,7 +24593,7 @@
         <v>-8.57</v>
       </c>
       <c r="I329" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" s="4" t="n">
         <v>70.48</v>
@@ -24670,7 +24670,7 @@
         <v>1.3</v>
       </c>
       <c r="I330" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" t="n">
         <v>70.37</v>
@@ -24743,7 +24743,7 @@
         <v>-4.35</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.29000000000001</v>
@@ -24816,7 +24816,7 @@
         <v>2.74</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.20999999999999</v>
@@ -24889,7 +24889,7 @@
         <v>1.05</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>70.26000000000001</v>
@@ -24962,7 +24962,7 @@
         <v>-1.57</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>70.23999999999999</v>
@@ -25035,7 +25035,7 @@
         <v>1.99</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>70.31</v>
@@ -25108,7 +25108,7 @@
         <v>-3.18</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>70.37</v>
@@ -25181,7 +25181,7 @@
         <v>1.27</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>70.55</v>
@@ -25254,7 +25254,7 @@
         <v>-0.04</v>
       </c>
       <c r="I338" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" t="n">
         <v>70.63</v>
@@ -25327,7 +25327,7 @@
         <v>-0.97</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>70.59999999999999</v>
@@ -25400,7 +25400,7 @@
         <v>0.47</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>70.7</v>
@@ -25473,7 +25473,7 @@
         <v>-2.62</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>70.72</v>
@@ -25546,7 +25546,7 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>70.56</v>
@@ -25619,7 +25619,7 @@
         <v>-8.08</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>70.06</v>
@@ -25692,7 +25692,7 @@
         <v>0.02</v>
       </c>
       <c r="I344" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" t="n">
         <v>69.48999999999999</v>
@@ -25765,7 +25765,7 @@
         <v>-4.17</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>68.54000000000001</v>
@@ -25842,7 +25842,7 @@
         <v>-2.29</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>67.48999999999999</v>
@@ -25919,7 +25919,7 @@
         <v>5.48</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>66.56999999999999</v>
@@ -25992,7 +25992,7 @@
         <v>0.77</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>65.86</v>
@@ -26065,7 +26065,7 @@
         <v>3.56</v>
       </c>
       <c r="I349" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" t="n">
         <v>65.58</v>
@@ -26138,7 +26138,7 @@
         <v>-0.13</v>
       </c>
       <c r="I350" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" t="n">
         <v>65.25</v>
@@ -26211,7 +26211,7 @@
         <v>-4.39</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>64.94</v>
@@ -26284,7 +26284,7 @@
         <v>-1.81</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>64.47</v>
@@ -26357,7 +26357,7 @@
         <v>-1.01</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>63.95</v>
@@ -26430,7 +26430,7 @@
         <v>-5.4</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>63.32</v>
@@ -26507,7 +26507,7 @@
         <v>-7.09</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>62.42</v>
@@ -26584,7 +26584,7 @@
         <v>1.12</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>61.66</v>
@@ -26661,7 +26661,7 @@
         <v>1.76</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>60.91</v>
@@ -26734,7 +26734,7 @@
         <v>-1.13</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>60.12</v>
@@ -26807,7 +26807,7 @@
         <v>1.5</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>59.42</v>
@@ -26880,7 +26880,7 @@
         <v>0.21</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>58.69</v>
@@ -26953,7 +26953,7 @@
         <v>2.69</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>58.14</v>
@@ -27026,7 +27026,7 @@
         <v>1.98</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>57.59</v>
@@ -27099,7 +27099,7 @@
         <v>-2.94</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>57.24</v>
@@ -27176,7 +27176,7 @@
         <v>-2.99</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>56.8</v>
@@ -27253,7 +27253,7 @@
         <v>2.48</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>56.55</v>
@@ -27326,7 +27326,7 @@
         <v>-0.35</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>56.37</v>
@@ -27399,7 +27399,7 @@
         <v>-3.32</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>55.94</v>
@@ -27472,7 +27472,7 @@
         <v>1.94</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>55.53</v>
@@ -27545,7 +27545,7 @@
         <v>-1.81</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>54.97</v>
@@ -27618,7 +27618,7 @@
         <v>-3.49</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>54.32</v>
@@ -27691,7 +27691,7 @@
         <v>0.77</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>53.83</v>
@@ -27764,7 +27764,7 @@
         <v>0.39</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>53.4</v>
@@ -27837,7 +27837,7 @@
         <v>4.12</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>53.11</v>
@@ -27910,7 +27910,7 @@
         <v>1.58</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>53.02</v>
@@ -27983,7 +27983,7 @@
         <v>-3.45</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>53.03</v>
@@ -28060,7 +28060,7 @@
         <v>1.02</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>53.04</v>
@@ -28133,7 +28133,7 @@
         <v>0.65</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>53.03</v>
@@ -28206,7 +28206,7 @@
         <v>-2.32</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>52.98</v>
@@ -28279,7 +28279,7 @@
         <v>0.14</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>52.89</v>
@@ -28352,7 +28352,7 @@
         <v>3.34</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>52.89</v>
@@ -28425,7 +28425,7 @@
         <v>-2.13</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>52.75</v>
@@ -28502,7 +28502,7 @@
         <v>0.19</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>52.57</v>
@@ -28575,7 +28575,7 @@
         <v>2.63</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>52.54</v>
@@ -28648,7 +28648,7 @@
         <v>4.14</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>52.7</v>
@@ -28721,7 +28721,7 @@
         <v>-0.39</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>52.79</v>
@@ -28794,7 +28794,7 @@
         <v>2.95</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>52.97</v>
@@ -28867,7 +28867,7 @@
         <v>3.32</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>53.33</v>
@@ -28940,7 +28940,7 @@
         <v>-1.45</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>53.6</v>
@@ -29013,7 +29013,7 @@
         <v>0.87</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>53.94</v>
@@ -29086,7 +29086,7 @@
         <v>-1.52</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>54.33</v>
@@ -29159,7 +29159,7 @@
         <v>0.55</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>54.71</v>
@@ -29232,7 +29232,7 @@
         <v>1.86</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>55.14</v>
@@ -29305,7 +29305,7 @@
         <v>-3.58</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>55.36</v>
@@ -29382,7 +29382,7 @@
         <v>4.47</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>55.67</v>
@@ -29455,7 +29455,7 @@
         <v>2.75</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>56.15</v>
@@ -29528,7 +29528,7 @@
         <v>1.72</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>56.65</v>
@@ -29601,7 +29601,7 @@
         <v>-0.83</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>57.12</v>
@@ -29674,7 +29674,7 @@
         <v>0.19</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>57.65</v>
@@ -29747,7 +29747,7 @@
         <v>-1.17</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>58.14</v>
@@ -29820,7 +29820,7 @@
         <v>1.92</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>58.6</v>
@@ -29893,7 +29893,7 @@
         <v>-4.38</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>58.98</v>
@@ -29966,7 +29966,7 @@
         <v>0.18</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>59.37</v>
@@ -30039,7 +30039,7 @@
         <v>-3.68</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>59.57</v>
@@ -30116,7 +30116,7 @@
         <v>1.99</v>
       </c>
       <c r="I404" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" t="n">
         <v>59.72</v>
@@ -30189,7 +30189,7 @@
         <v>2.51</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>59.96</v>
@@ -30262,7 +30262,7 @@
         <v>-1.21</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>60.07</v>
@@ -30339,7 +30339,7 @@
         <v>-0.75</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>60.07</v>
@@ -30412,7 +30412,7 @@
         <v>2.27</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>60.18</v>
@@ -30485,7 +30485,7 @@
         <v>-5.3</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>60.1</v>
@@ -30562,7 +30562,7 @@
         <v>1.08</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>60.1</v>
@@ -30635,7 +30635,7 @@
         <v>-2.2</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>60.02</v>
@@ -30708,7 +30708,7 @@
         <v>1.21</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>59.92</v>
@@ -30745,13 +30745,84 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="D413" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="E413" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="F413" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="G413" t="n">
+        <v>5357664</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.73</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -30702,7 +30702,7 @@
         <v>57.53</v>
       </c>
       <c r="G412" t="n">
-        <v>11759600</v>
+        <v>11807700</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>1.21</v>
@@ -30766,40 +30766,40 @@
         <v>58.35</v>
       </c>
       <c r="D413" t="n">
-        <v>58.59</v>
+        <v>58.63</v>
       </c>
       <c r="E413" t="n">
-        <v>57.88</v>
+        <v>56.28</v>
       </c>
       <c r="F413" t="n">
-        <v>58.32</v>
+        <v>56.95</v>
       </c>
       <c r="G413" t="n">
-        <v>5357664</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>1.37</v>
+        <v>19561380</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.01</v>
       </c>
       <c r="I413" t="n">
         <v>5.1</v>
       </c>
       <c r="J413" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="K413" t="n">
-        <v>56.14</v>
+        <v>56.12</v>
       </c>
       <c r="L413" t="n">
-        <v>61.8</v>
+        <v>61.79</v>
       </c>
       <c r="M413" t="n">
         <v>65.73</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>40.92</v>
+        <v>36.97</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30813,13 +30813,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>-1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>27.36</v>
@@ -685,7 +685,7 @@
         <v>0.62</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>27.38</v>
@@ -758,7 +758,7 @@
         <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.44</v>
@@ -831,7 +831,7 @@
         <v>2.57</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>27.56</v>
@@ -904,7 +904,7 @@
         <v>-0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>27.67</v>
@@ -977,7 +977,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>27.75</v>
@@ -1050,7 +1050,7 @@
         <v>1.92</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>27.87</v>
@@ -1123,7 +1123,7 @@
         <v>0.44</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>27.97</v>
@@ -1196,7 +1196,7 @@
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>28.07</v>
@@ -1269,7 +1269,7 @@
         <v>-1.19</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>28.16</v>
@@ -1342,7 +1342,7 @@
         <v>0.59</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>28.24</v>
@@ -1415,7 +1415,7 @@
         <v>-0.68</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>28.34</v>
@@ -1488,7 +1488,7 @@
         <v>1.17</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>28.44</v>
@@ -1561,7 +1561,7 @@
         <v>0.41</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>28.52</v>
@@ -1634,7 +1634,7 @@
         <v>-0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>28.58</v>
@@ -1707,7 +1707,7 @@
         <v>2.05</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>28.7</v>
@@ -1780,7 +1780,7 @@
         <v>-0.33</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>28.79</v>
@@ -1853,7 +1853,7 @@
         <v>0.47</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>28.88</v>
@@ -1926,7 +1926,7 @@
         <v>-1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>28.97</v>
@@ -1999,7 +1999,7 @@
         <v>-0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>29.05</v>
@@ -2072,7 +2072,7 @@
         <v>-2.07</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>29.12</v>
@@ -2149,7 +2149,7 @@
         <v>0.38</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>29.18</v>
@@ -2222,7 +2222,7 @@
         <v>-1.87</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>29.2</v>
@@ -2295,7 +2295,7 @@
         <v>-0.32</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>29.18</v>
@@ -2372,7 +2372,7 @@
         <v>1.55</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>29.19</v>
@@ -2445,7 +2445,7 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>29.21</v>
@@ -2518,7 +2518,7 @@
         <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>29.24</v>
@@ -2591,7 +2591,7 @@
         <v>-0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.26</v>
@@ -2664,7 +2664,7 @@
         <v>-0.34</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.27</v>
@@ -2737,7 +2737,7 @@
         <v>-1.62</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.27</v>
@@ -2814,7 +2814,7 @@
         <v>2.92</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.31</v>
@@ -2887,7 +2887,7 @@
         <v>0.87</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.37</v>
@@ -2960,7 +2960,7 @@
         <v>1.72</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.44</v>
@@ -3033,7 +3033,7 @@
         <v>-0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.5</v>
@@ -3106,7 +3106,7 @@
         <v>0.33</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.58</v>
@@ -3179,7 +3179,7 @@
         <v>0.13</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.62</v>
@@ -3252,7 +3252,7 @@
         <v>-0.32</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.67</v>
@@ -3325,7 +3325,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>29.7</v>
@@ -3398,7 +3398,7 @@
         <v>-1.57</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>29.72</v>
@@ -3471,7 +3471,7 @@
         <v>-0.2</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>29.75</v>
@@ -3544,7 +3544,7 @@
         <v>2.07</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>29.83</v>
@@ -3617,7 +3617,7 @@
         <v>-0.16</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>29.91</v>
@@ -3690,7 +3690,7 @@
         <v>2.59</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>30.06</v>
@@ -3763,7 +3763,7 @@
         <v>-1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>30.19</v>
@@ -3836,7 +3836,7 @@
         <v>-0.03</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>30.3</v>
@@ -3909,7 +3909,7 @@
         <v>-1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>30.39</v>
@@ -3982,7 +3982,7 @@
         <v>0.42</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>30.44</v>
@@ -4055,7 +4055,7 @@
         <v>-6.08</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>30.4</v>
@@ -4132,7 +4132,7 @@
         <v>-6.27</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>30.27</v>
@@ -4209,7 +4209,7 @@
         <v>0.22</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>30.17</v>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>30.03</v>
@@ -4363,7 +4363,7 @@
         <v>3.39</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>29.92</v>
@@ -4436,7 +4436,7 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.8</v>
@@ -4509,7 +4509,7 @@
         <v>3.22</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.72</v>
@@ -4582,7 +4582,7 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.65</v>
@@ -4655,7 +4655,7 @@
         <v>0.1</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.58</v>
@@ -4728,7 +4728,7 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.53</v>
@@ -4801,7 +4801,7 @@
         <v>-0.71</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.48</v>
@@ -4874,7 +4874,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.47</v>
@@ -4947,7 +4947,7 @@
         <v>-0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.45</v>
@@ -5020,7 +5020,7 @@
         <v>3.59</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.45</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.45</v>
@@ -5166,7 +5166,7 @@
         <v>-1.67</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.39</v>
@@ -5239,7 +5239,7 @@
         <v>0.47</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.35</v>
@@ -5312,7 +5312,7 @@
         <v>-1.19</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>29.29</v>
@@ -5385,7 +5385,7 @@
         <v>-0.77</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>29.24</v>
@@ -5462,7 +5462,7 @@
         <v>-0.71</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>29.17</v>
@@ -5535,7 +5535,7 @@
         <v>-0.92</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>29.18</v>
@@ -5612,7 +5612,7 @@
         <v>1.24</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>29.3</v>
@@ -5685,7 +5685,7 @@
         <v>2.51</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>29.45</v>
@@ -5758,7 +5758,7 @@
         <v>-2.42</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>29.57</v>
@@ -5835,7 +5835,7 @@
         <v>-0.1</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>29.64</v>
@@ -5908,7 +5908,7 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>29.72</v>
@@ -5981,7 +5981,7 @@
         <v>-0.57</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>29.74</v>
@@ -6058,7 +6058,7 @@
         <v>1.01</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>29.77</v>
@@ -6131,7 +6131,7 @@
         <v>-2.27</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>29.76</v>
@@ -6208,7 +6208,7 @@
         <v>1.23</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>29.75</v>
@@ -6281,7 +6281,7 @@
         <v>-1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6354,7 +6354,7 @@
         <v>0.41</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>29.72</v>
@@ -6427,7 +6427,7 @@
         <v>2.41</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>29.75</v>
@@ -6500,7 +6500,7 @@
         <v>1.26</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>29.75</v>
@@ -6573,7 +6573,7 @@
         <v>-1.57</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>29.72</v>
@@ -6646,7 +6646,7 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>29.74</v>
@@ -6719,7 +6719,7 @@
         <v>-0.72</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>29.74</v>
@@ -6792,7 +6792,7 @@
         <v>-0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>29.75</v>
@@ -6865,7 +6865,7 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>29.79</v>
@@ -6938,7 +6938,7 @@
         <v>-0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>29.82</v>
@@ -7011,7 +7011,7 @@
         <v>5.3</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>29.94</v>
@@ -7084,7 +7084,7 @@
         <v>-0.47</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>30.04</v>
@@ -7157,7 +7157,7 @@
         <v>-0.32</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>30.09</v>
@@ -7230,7 +7230,7 @@
         <v>3.54</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>30.24</v>
@@ -7303,7 +7303,7 @@
         <v>0.74</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>30.4</v>
@@ -7376,7 +7376,7 @@
         <v>2.14</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>30.58</v>
@@ -7449,7 +7449,7 @@
         <v>-0.48</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>30.76</v>
@@ -7522,7 +7522,7 @@
         <v>-0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>30.91</v>
@@ -7595,7 +7595,7 @@
         <v>0.33</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>31.1</v>
@@ -7668,7 +7668,7 @@
         <v>-0.27</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>31.27</v>
@@ -7741,7 +7741,7 @@
         <v>0.18</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>31.46</v>
@@ -7814,7 +7814,7 @@
         <v>2.15</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>31.68</v>
@@ -7887,7 +7887,7 @@
         <v>-1.39</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>31.83</v>
@@ -7960,7 +7960,7 @@
         <v>-1.65</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>31.94</v>
@@ -8033,7 +8033,7 @@
         <v>0.73</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>32.09</v>
@@ -8106,7 +8106,7 @@
         <v>-1.06</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>32.2</v>
@@ -8179,7 +8179,7 @@
         <v>1.23</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>32.34</v>
@@ -8252,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>32.5</v>
@@ -8325,7 +8325,7 @@
         <v>-2.16</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>32.62</v>
@@ -8398,7 +8398,7 @@
         <v>0.58</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>32.76</v>
@@ -8471,7 +8471,7 @@
         <v>-0.24</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>32.82</v>
@@ -8548,7 +8548,7 @@
         <v>1.56</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>32.91</v>
@@ -8621,7 +8621,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>33.02</v>
@@ -8694,7 +8694,7 @@
         <v>-0.24</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>33.07</v>
@@ -8767,7 +8767,7 @@
         <v>-0.42</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>33.1</v>
@@ -8840,7 +8840,7 @@
         <v>-0.87</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>33.08</v>
@@ -8917,7 +8917,7 @@
         <v>2.27</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>33.1</v>
@@ -8990,7 +8990,7 @@
         <v>3.79</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>33.21</v>
@@ -9063,7 +9063,7 @@
         <v>-1.14</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>33.28</v>
@@ -9136,7 +9136,7 @@
         <v>-1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>33.35</v>
@@ -9209,7 +9209,7 @@
         <v>0.44</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>33.42</v>
@@ -9282,7 +9282,7 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>33.46</v>
@@ -9355,7 +9355,7 @@
         <v>-0.12</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>33.53</v>
@@ -9428,7 +9428,7 @@
         <v>2.14</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>33.66</v>
@@ -9501,7 +9501,7 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>33.8</v>
@@ -9574,7 +9574,7 @@
         <v>-0.08</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>33.95</v>
@@ -9647,7 +9647,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>34.08</v>
@@ -9720,7 +9720,7 @@
         <v>-2.34</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.14</v>
@@ -9793,10 +9793,10 @@
         <v>-0.06</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="K127" t="n">
         <v>32.22</v>
@@ -9866,7 +9866,7 @@
         <v>0.06</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.34</v>
@@ -9939,7 +9939,7 @@
         <v>-3.32</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>-0.57</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>34.38</v>
@@ -10089,7 +10089,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>34.38</v>
@@ -10162,7 +10162,7 @@
         <v>1.16</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>34.41</v>
@@ -10235,10 +10235,10 @@
         <v>1.09</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
-        <v>34.46</v>
+        <v>34.47</v>
       </c>
       <c r="K133" t="n">
         <v>32.65</v>
@@ -10308,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>34.53</v>
@@ -10381,7 +10381,7 @@
         <v>1.19</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10454,7 +10454,7 @@
         <v>0.35</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10527,7 +10527,7 @@
         <v>-2.01</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>34.55</v>
@@ -10604,7 +10604,7 @@
         <v>0.67</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>34.56</v>
@@ -10677,7 +10677,7 @@
         <v>1.71</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>34.59</v>
@@ -10750,7 +10750,7 @@
         <v>-1.43</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>34.58</v>
@@ -10827,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>34.58</v>
@@ -10900,7 +10900,7 @@
         <v>0.14</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>34.54</v>
@@ -10973,7 +10973,7 @@
         <v>-1.97</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>34.44</v>
@@ -11050,7 +11050,7 @@
         <v>1.65</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>34.38</v>
@@ -11123,7 +11123,7 @@
         <v>0.52</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>34.34</v>
@@ -11196,7 +11196,7 @@
         <v>2.11</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>34.37</v>
@@ -11269,7 +11269,7 @@
         <v>-0.91</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>34.39</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>34.41</v>
@@ -11415,7 +11415,7 @@
         <v>-0.09</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>34.48</v>
@@ -11488,7 +11488,7 @@
         <v>1.51</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>34.59</v>
@@ -11561,7 +11561,7 @@
         <v>1.89</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>34.72</v>
@@ -11634,7 +11634,7 @@
         <v>2.65</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>34.88</v>
@@ -11707,7 +11707,7 @@
         <v>0.51</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>35.03</v>
@@ -11780,7 +11780,7 @@
         <v>-1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>35.16</v>
@@ -11853,7 +11853,7 @@
         <v>0.76</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>35.28</v>
@@ -11926,7 +11926,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>35.41</v>
@@ -11999,7 +11999,7 @@
         <v>-0.88</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>35.56</v>
@@ -12072,7 +12072,7 @@
         <v>0.62</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>35.71</v>
@@ -12145,7 +12145,7 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>35.85</v>
@@ -12218,7 +12218,7 @@
         <v>1.46</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>36.04</v>
@@ -12291,7 +12291,7 @@
         <v>1.1</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>36.26</v>
@@ -12364,7 +12364,7 @@
         <v>-0.41</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>36.46</v>
@@ -12437,7 +12437,7 @@
         <v>-2.1</v>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>36.66</v>
@@ -12510,7 +12510,7 @@
         <v>0.53</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>36.83</v>
@@ -12583,7 +12583,7 @@
         <v>2.76</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>37.06</v>
@@ -12656,7 +12656,7 @@
         <v>2.56</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>37.29</v>
@@ -12729,7 +12729,7 @@
         <v>-0.2</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>37.54</v>
@@ -12802,7 +12802,7 @@
         <v>-0.35</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>37.78</v>
@@ -12875,7 +12875,7 @@
         <v>3.04</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>38.08</v>
@@ -12948,7 +12948,7 @@
         <v>2.02</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>38.4</v>
@@ -13021,7 +13021,7 @@
         <v>1.53</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>38.71</v>
@@ -13094,7 +13094,7 @@
         <v>-0.31</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>38.97</v>
@@ -13167,7 +13167,7 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>39.25</v>
@@ -13240,7 +13240,7 @@
         <v>-0.89</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>39.53</v>
@@ -13313,7 +13313,7 @@
         <v>2.33</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>39.85</v>
@@ -13386,7 +13386,7 @@
         <v>1.24</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>40.17</v>
@@ -13459,7 +13459,7 @@
         <v>-1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>40.49</v>
@@ -13532,7 +13532,7 @@
         <v>2.7</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>40.84</v>
@@ -13605,7 +13605,7 @@
         <v>0.34</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>41.19</v>
@@ -13678,7 +13678,7 @@
         <v>1.61</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>41.54</v>
@@ -13751,7 +13751,7 @@
         <v>4.03</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>41.97</v>
@@ -13824,7 +13824,7 @@
         <v>-0.97</v>
       </c>
       <c r="I182" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>42.38</v>
@@ -13897,7 +13897,7 @@
         <v>3.27</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>42.91</v>
@@ -13970,7 +13970,7 @@
         <v>1.74</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>43.46</v>
@@ -14043,7 +14043,7 @@
         <v>-4.43</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>43.86</v>
@@ -14116,7 +14116,7 @@
         <v>1.55</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>44.25</v>
@@ -14189,7 +14189,7 @@
         <v>-8.24</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>44.44</v>
@@ -14266,7 +14266,7 @@
         <v>0.21</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>44.64</v>
@@ -14339,7 +14339,7 @@
         <v>0.68</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>44.8</v>
@@ -14412,7 +14412,7 @@
         <v>-0.43</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>44.9</v>
@@ -14485,7 +14485,7 @@
         <v>-3.61</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>44.9</v>
@@ -14558,7 +14558,7 @@
         <v>0.71</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>44.92</v>
@@ -14631,7 +14631,7 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>44.93</v>
@@ -14704,7 +14704,7 @@
         <v>2.57</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>45.02</v>
@@ -14777,7 +14777,7 @@
         <v>-0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>45.05</v>
@@ -14850,7 +14850,7 @@
         <v>-0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>45.03</v>
@@ -14923,7 +14923,7 @@
         <v>-2.33</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>45</v>
@@ -14996,7 +14996,7 @@
         <v>2.13</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>44.95</v>
@@ -15069,7 +15069,7 @@
         <v>-0.23</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>44.9</v>
@@ -15142,7 +15142,7 @@
         <v>0.85</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>44.82</v>
@@ -15215,7 +15215,7 @@
         <v>4.26</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>44.75</v>
@@ -15288,7 +15288,7 @@
         <v>1.44</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>44.73</v>
@@ -15361,7 +15361,7 @@
         <v>4.03</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>44.73</v>
@@ -15434,7 +15434,7 @@
         <v>-1.86</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>44.64</v>
@@ -15507,7 +15507,7 @@
         <v>-3.08</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>44.59</v>
@@ -15580,7 +15580,7 @@
         <v>-1.07</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>44.48</v>
@@ -15653,7 +15653,7 @@
         <v>1.39</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>44.59</v>
@@ -15726,7 +15726,7 @@
         <v>0.76</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>44.72</v>
@@ -15799,7 +15799,7 @@
         <v>-1.44</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>44.8</v>
@@ -15872,7 +15872,7 @@
         <v>-1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>44.87</v>
@@ -15945,7 +15945,7 @@
         <v>2.94</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>45.08</v>
@@ -16018,7 +16018,7 @@
         <v>0.09</v>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>45.28</v>
@@ -16091,7 +16091,7 @@
         <v>3.71</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>45.54</v>
@@ -16164,7 +16164,7 @@
         <v>5.81</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>45.88</v>
@@ -16237,7 +16237,7 @@
         <v>2.56</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>46.3</v>
@@ -16310,7 +16310,7 @@
         <v>1.16</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>46.77</v>
@@ -16383,7 +16383,7 @@
         <v>-0.11</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>47.29</v>
@@ -16456,7 +16456,7 @@
         <v>-2.47</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>47.7</v>
@@ -16529,7 +16529,7 @@
         <v>2.3</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>48.16</v>
@@ -16602,7 +16602,7 @@
         <v>-0.45</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>48.6</v>
@@ -16675,7 +16675,7 @@
         <v>4.67</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>49.07</v>
@@ -16748,7 +16748,7 @@
         <v>1.63</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>49.55</v>
@@ -16821,7 +16821,7 @@
         <v>2.76</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>50.02</v>
@@ -16894,7 +16894,7 @@
         <v>-2.64</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>50.45</v>
@@ -16967,7 +16967,7 @@
         <v>3.58</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>51.06</v>
@@ -17040,7 +17040,7 @@
         <v>-0.65</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>51.67</v>
@@ -17113,7 +17113,7 @@
         <v>4.38</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>52.38</v>
@@ -17186,7 +17186,7 @@
         <v>-1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>53.03</v>
@@ -17259,7 +17259,7 @@
         <v>2.71</v>
       </c>
       <c r="I229" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>53.78</v>
@@ -17332,7 +17332,7 @@
         <v>2.53</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>54.64</v>
@@ -17405,7 +17405,7 @@
         <v>3.79</v>
       </c>
       <c r="I231" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>55.55</v>
@@ -17478,7 +17478,7 @@
         <v>0.59</v>
       </c>
       <c r="I232" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>56.48</v>
@@ -17551,7 +17551,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>57.62</v>
@@ -17624,7 +17624,7 @@
         <v>-7.19</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>58.36</v>
@@ -17697,7 +17697,7 @@
         <v>4.5</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>59.18</v>
@@ -17770,7 +17770,7 @@
         <v>-6.61</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>59.74</v>
@@ -17843,7 +17843,7 @@
         <v>2.06</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>60.38</v>
@@ -17916,7 +17916,7 @@
         <v>5.06</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>61.24</v>
@@ -17989,7 +17989,7 @@
         <v>6.7</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>62.28</v>
@@ -18062,7 +18062,7 @@
         <v>-3.73</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>63.19</v>
@@ -18135,7 +18135,7 @@
         <v>-1.76</v>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>63.92</v>
@@ -18208,7 +18208,7 @@
         <v>3.83</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>64.73999999999999</v>
@@ -18281,7 +18281,7 @@
         <v>6.7</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>65.72</v>
@@ -18354,7 +18354,7 @@
         <v>1.77</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>66.84</v>
@@ -18427,7 +18427,7 @@
         <v>7.58</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>68.16</v>
@@ -18500,7 +18500,7 @@
         <v>-1.47</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>69.44</v>
@@ -18573,7 +18573,7 @@
         <v>-2.76</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>70.48</v>
@@ -18646,7 +18646,7 @@
         <v>5.39</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>71.78</v>
@@ -18719,7 +18719,7 @@
         <v>-1.67</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>72.94</v>
@@ -18792,7 +18792,7 @@
         <v>3.78</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>74.17</v>
@@ -18865,7 +18865,7 @@
         <v>6.63</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>75.56999999999999</v>
@@ -18938,7 +18938,7 @@
         <v>5.84</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>77.23</v>
@@ -19011,7 +19011,7 @@
         <v>3.3</v>
       </c>
       <c r="I253" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>78.75</v>
@@ -19084,7 +19084,7 @@
         <v>3.95</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>80.73</v>
@@ -19157,7 +19157,7 @@
         <v>-0.03</v>
       </c>
       <c r="I255" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>82.56</v>
@@ -19230,7 +19230,7 @@
         <v>-28.54</v>
       </c>
       <c r="I256" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" s="4" t="n">
         <v>83.11</v>
@@ -19307,7 +19307,7 @@
         <v>-3.98</v>
       </c>
       <c r="I257" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>83.45</v>
@@ -19380,7 +19380,7 @@
         <v>6.24</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>83.84</v>
@@ -19453,7 +19453,7 @@
         <v>2.88</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>84.11</v>
@@ -19526,7 +19526,7 @@
         <v>-15.77</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19599,7 +19599,7 @@
         <v>5.25</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>83.92</v>
@@ -19672,7 +19672,7 @@
         <v>8.33</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>84.11</v>
@@ -19745,7 +19745,7 @@
         <v>-3.46</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>83.92</v>
@@ -19818,7 +19818,7 @@
         <v>4.29</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>83.81999999999999</v>
@@ -19891,7 +19891,7 @@
         <v>-11.53</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>82.97</v>
@@ -19964,7 +19964,7 @@
         <v>2.94</v>
       </c>
       <c r="I266" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" t="n">
         <v>82.29000000000001</v>
@@ -20037,7 +20037,7 @@
         <v>-4.8</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>81.56</v>
@@ -20114,7 +20114,7 @@
         <v>5.6</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>80.8</v>
@@ -20187,7 +20187,7 @@
         <v>1.31</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>80.15000000000001</v>
@@ -20260,7 +20260,7 @@
         <v>7.9</v>
       </c>
       <c r="I270" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>79.62</v>
@@ -20333,7 +20333,7 @@
         <v>5.16</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>79.01000000000001</v>
@@ -20406,7 +20406,7 @@
         <v>-1.85</v>
       </c>
       <c r="I272" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>78.04000000000001</v>
@@ -20479,7 +20479,7 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>76.97</v>
@@ -20552,7 +20552,7 @@
         <v>0.51</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>75.70999999999999</v>
@@ -20625,7 +20625,7 @@
         <v>5.64</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>74.68000000000001</v>
@@ -20698,7 +20698,7 @@
         <v>-4.02</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>74.98999999999999</v>
@@ -20771,7 +20771,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I277" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>75.09999999999999</v>
@@ -20848,7 +20848,7 @@
         <v>0.88</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>75.02</v>
@@ -20921,7 +20921,7 @@
         <v>-1.42</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>74.77</v>
@@ -20998,7 +20998,7 @@
         <v>2.25</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>75.23</v>
@@ -21071,7 +21071,7 @@
         <v>3.06</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>75.64</v>
@@ -21144,7 +21144,7 @@
         <v>2.34</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>75.84</v>
@@ -21217,7 +21217,7 @@
         <v>-2.72</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>76.06</v>
@@ -21290,7 +21290,7 @@
         <v>-1.84</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>76.06</v>
@@ -21357,7 +21357,7 @@
         <v>-4.96</v>
       </c>
       <c r="I285" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>76.31</v>
@@ -21434,7 +21434,7 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>76.48</v>
@@ -21507,7 +21507,7 @@
         <v>-2.13</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>76.75</v>
@@ -21580,7 +21580,7 @@
         <v>-4.13</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>76.68000000000001</v>
@@ -21653,7 +21653,7 @@
         <v>-4.4</v>
       </c>
       <c r="I289" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>76.41</v>
@@ -21726,7 +21726,7 @@
         <v>-6.33</v>
       </c>
       <c r="I290" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>75.66</v>
@@ -21803,7 +21803,7 @@
         <v>1.54</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>74.75</v>
@@ -21876,7 +21876,7 @@
         <v>0.77</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>73.95</v>
@@ -21949,7 +21949,7 @@
         <v>3.59</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>73.2</v>
@@ -22022,7 +22022,7 @@
         <v>-6.81</v>
       </c>
       <c r="I294" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" s="4" t="n">
         <v>72.22</v>
@@ -22099,7 +22099,7 @@
         <v>4.39</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>71.14</v>
@@ -22172,7 +22172,7 @@
         <v>0.13</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>70.23999999999999</v>
@@ -22245,7 +22245,7 @@
         <v>7.27</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>69.91</v>
@@ -22318,7 +22318,7 @@
         <v>0</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>69.55</v>
@@ -22391,7 +22391,7 @@
         <v>-3.45</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>69.13</v>
@@ -22464,7 +22464,7 @@
         <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>68.64</v>
@@ -22537,7 +22537,7 @@
         <v>-0.23</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>68.02</v>
@@ -22610,7 +22610,7 @@
         <v>2.32</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>67.39</v>
@@ -22683,7 +22683,7 @@
         <v>1.36</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>66.91</v>
@@ -22756,7 +22756,7 @@
         <v>1.01</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>66.54000000000001</v>
@@ -22829,7 +22829,7 @@
         <v>-1.16</v>
       </c>
       <c r="I305" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>66.31999999999999</v>
@@ -22902,7 +22902,7 @@
         <v>5.51</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>66.26000000000001</v>
@@ -22975,7 +22975,7 @@
         <v>-0.28</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>66.27</v>
@@ -23048,7 +23048,7 @@
         <v>-0.84</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>66.40000000000001</v>
@@ -23121,7 +23121,7 @@
         <v>3.35</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>66.8</v>
@@ -23194,7 +23194,7 @@
         <v>-2.01</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>67.33</v>
@@ -23267,7 +23267,7 @@
         <v>-5.07</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>67.63</v>
@@ -23340,7 +23340,7 @@
         <v>2.74</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>68</v>
@@ -23413,7 +23413,7 @@
         <v>-2.83</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>68.16</v>
@@ -23486,7 +23486,7 @@
         <v>0.6</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>68.56</v>
@@ -23559,7 +23559,7 @@
         <v>-0.67</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>68.8</v>
@@ -23636,7 +23636,7 @@
         <v>-3.12</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>68.94</v>
@@ -23713,7 +23713,7 @@
         <v>-2.05</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>68.77</v>
@@ -23786,7 +23786,7 @@
         <v>2.81</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>68.7</v>
@@ -23859,7 +23859,7 @@
         <v>2.45</v>
       </c>
       <c r="I319" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>68.81999999999999</v>
@@ -23932,7 +23932,7 @@
         <v>-3.44</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>68.81999999999999</v>
@@ -24009,7 +24009,7 @@
         <v>-0.05</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>68.81999999999999</v>
@@ -24082,7 +24082,7 @@
         <v>6.4</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>68.95</v>
@@ -24155,7 +24155,7 @@
         <v>2.1</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>69.11</v>
@@ -24228,7 +24228,7 @@
         <v>1.97</v>
       </c>
       <c r="I324" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>69.31</v>
@@ -24301,7 +24301,7 @@
         <v>6.83</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>69.79000000000001</v>
@@ -24374,7 +24374,7 @@
         <v>0.71</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>70.12</v>
@@ -24447,7 +24447,7 @@
         <v>1.02</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>70.48999999999999</v>
@@ -24520,7 +24520,7 @@
         <v>-4.84</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>70.70999999999999</v>
@@ -24593,7 +24593,7 @@
         <v>-8.57</v>
       </c>
       <c r="I329" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" s="4" t="n">
         <v>70.48</v>
@@ -24670,7 +24670,7 @@
         <v>1.3</v>
       </c>
       <c r="I330" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" t="n">
         <v>70.37</v>
@@ -24743,7 +24743,7 @@
         <v>-4.35</v>
       </c>
       <c r="I331" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" t="n">
         <v>70.29000000000001</v>
@@ -24816,7 +24816,7 @@
         <v>2.74</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>70.20999999999999</v>
@@ -24889,7 +24889,7 @@
         <v>1.05</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>70.26000000000001</v>
@@ -24962,7 +24962,7 @@
         <v>-1.57</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>70.23999999999999</v>
@@ -25035,7 +25035,7 @@
         <v>1.99</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>70.31</v>
@@ -25108,7 +25108,7 @@
         <v>-3.18</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>70.37</v>
@@ -25181,7 +25181,7 @@
         <v>1.27</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>70.55</v>
@@ -25254,7 +25254,7 @@
         <v>-0.04</v>
       </c>
       <c r="I338" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>70.63</v>
@@ -25327,7 +25327,7 @@
         <v>-0.97</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>70.59999999999999</v>
@@ -25400,7 +25400,7 @@
         <v>0.47</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>70.7</v>
@@ -25473,7 +25473,7 @@
         <v>-2.62</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>70.72</v>
@@ -25546,7 +25546,7 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>70.56</v>
@@ -25619,7 +25619,7 @@
         <v>-8.08</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>70.06</v>
@@ -25692,7 +25692,7 @@
         <v>0.02</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>69.48999999999999</v>
@@ -25765,7 +25765,7 @@
         <v>-4.17</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>68.54000000000001</v>
@@ -25842,7 +25842,7 @@
         <v>-2.29</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>67.48999999999999</v>
@@ -25919,7 +25919,7 @@
         <v>5.48</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>66.56999999999999</v>
@@ -25992,7 +25992,7 @@
         <v>0.77</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>65.86</v>
@@ -26065,7 +26065,7 @@
         <v>3.56</v>
       </c>
       <c r="I349" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>65.58</v>
@@ -26138,7 +26138,7 @@
         <v>-0.13</v>
       </c>
       <c r="I350" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>65.25</v>
@@ -26211,10 +26211,10 @@
         <v>-4.39</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
-        <v>64.94</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K351" t="n">
         <v>67.62</v>
@@ -26284,7 +26284,7 @@
         <v>-1.81</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>64.47</v>
@@ -26357,7 +26357,7 @@
         <v>-1.01</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>63.95</v>
@@ -26430,7 +26430,7 @@
         <v>-5.4</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>63.32</v>
@@ -26507,7 +26507,7 @@
         <v>-7.09</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>62.42</v>
@@ -26584,7 +26584,7 @@
         <v>1.12</v>
       </c>
       <c r="I356" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>61.66</v>
@@ -26661,7 +26661,7 @@
         <v>1.76</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>60.91</v>
@@ -26734,7 +26734,7 @@
         <v>-1.13</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>60.12</v>
@@ -26807,7 +26807,7 @@
         <v>1.5</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>59.42</v>
@@ -26880,7 +26880,7 @@
         <v>0.21</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>58.69</v>
@@ -26953,7 +26953,7 @@
         <v>2.69</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>58.14</v>
@@ -27026,7 +27026,7 @@
         <v>1.98</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>57.59</v>
@@ -27099,7 +27099,7 @@
         <v>-2.94</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>57.24</v>
@@ -27176,7 +27176,7 @@
         <v>-2.99</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>56.8</v>
@@ -27253,10 +27253,10 @@
         <v>2.48</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="K365" t="n">
         <v>64.95999999999999</v>
@@ -27326,7 +27326,7 @@
         <v>-0.35</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>56.37</v>
@@ -27399,7 +27399,7 @@
         <v>-3.32</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>55.94</v>
@@ -27472,7 +27472,7 @@
         <v>1.94</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>55.53</v>
@@ -27545,7 +27545,7 @@
         <v>-1.81</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>54.97</v>
@@ -27618,7 +27618,7 @@
         <v>-3.49</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>54.32</v>
@@ -27691,7 +27691,7 @@
         <v>0.77</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>53.83</v>
@@ -27764,7 +27764,7 @@
         <v>0.39</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>53.4</v>
@@ -27837,7 +27837,7 @@
         <v>4.12</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>53.11</v>
@@ -27910,7 +27910,7 @@
         <v>1.58</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>53.02</v>
@@ -27983,7 +27983,7 @@
         <v>-3.45</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>53.03</v>
@@ -28060,7 +28060,7 @@
         <v>1.02</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>53.04</v>
@@ -28133,7 +28133,7 @@
         <v>0.65</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>53.03</v>
@@ -28206,7 +28206,7 @@
         <v>-2.32</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>52.98</v>
@@ -28279,7 +28279,7 @@
         <v>0.14</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>52.89</v>
@@ -28352,7 +28352,7 @@
         <v>3.34</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>52.89</v>
@@ -28425,7 +28425,7 @@
         <v>-2.13</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>52.75</v>
@@ -28502,7 +28502,7 @@
         <v>0.19</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>52.57</v>
@@ -28575,7 +28575,7 @@
         <v>2.63</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>52.54</v>
@@ -28648,7 +28648,7 @@
         <v>4.14</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>52.7</v>
@@ -28721,7 +28721,7 @@
         <v>-0.39</v>
       </c>
       <c r="I385" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>52.79</v>
@@ -28794,7 +28794,7 @@
         <v>2.95</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>52.97</v>
@@ -28867,7 +28867,7 @@
         <v>3.32</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>53.33</v>
@@ -28940,7 +28940,7 @@
         <v>-1.45</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>53.6</v>
@@ -29013,7 +29013,7 @@
         <v>0.87</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>53.94</v>
@@ -29086,7 +29086,7 @@
         <v>-1.52</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>54.33</v>
@@ -29159,7 +29159,7 @@
         <v>0.55</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>54.71</v>
@@ -29232,7 +29232,7 @@
         <v>1.86</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>55.14</v>
@@ -29305,7 +29305,7 @@
         <v>-3.58</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>55.36</v>
@@ -29382,7 +29382,7 @@
         <v>4.47</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>55.67</v>
@@ -29455,7 +29455,7 @@
         <v>2.75</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>56.15</v>
@@ -29528,7 +29528,7 @@
         <v>1.72</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>56.65</v>
@@ -29601,7 +29601,7 @@
         <v>-0.83</v>
       </c>
       <c r="I397" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>57.12</v>
@@ -29674,7 +29674,7 @@
         <v>0.19</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>57.65</v>
@@ -29747,7 +29747,7 @@
         <v>-1.17</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>58.14</v>
@@ -29820,7 +29820,7 @@
         <v>1.92</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>58.6</v>
@@ -29893,7 +29893,7 @@
         <v>-4.38</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>58.98</v>
@@ -29966,7 +29966,7 @@
         <v>0.18</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>59.37</v>
@@ -30039,7 +30039,7 @@
         <v>-3.68</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>59.57</v>
@@ -30116,7 +30116,7 @@
         <v>1.99</v>
       </c>
       <c r="I404" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>59.72</v>
@@ -30189,7 +30189,7 @@
         <v>2.51</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>59.96</v>
@@ -30262,7 +30262,7 @@
         <v>-1.21</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>60.07</v>
@@ -30339,7 +30339,7 @@
         <v>-0.75</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>60.07</v>
@@ -30412,7 +30412,7 @@
         <v>2.27</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>60.18</v>
@@ -30485,7 +30485,7 @@
         <v>-5.3</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>60.1</v>
@@ -30562,7 +30562,7 @@
         <v>1.08</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>60.1</v>
@@ -30635,7 +30635,7 @@
         <v>-2.2</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>60.02</v>
@@ -30708,7 +30708,7 @@
         <v>1.21</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>59.92</v>
@@ -30772,19 +30772,19 @@
         <v>56.28</v>
       </c>
       <c r="F413" t="n">
-        <v>56.95</v>
+        <v>57.05</v>
       </c>
       <c r="G413" t="n">
-        <v>19561380</v>
+        <v>20751920</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.01</v>
+        <v>-0.83</v>
       </c>
       <c r="I413" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>59.89</v>
+        <v>59.9</v>
       </c>
       <c r="K413" t="n">
         <v>56.12</v>
@@ -30796,7 +30796,7 @@
         <v>65.73</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>36.97</v>
+        <v>37.18</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30816,13 +30816,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -30775,7 +30775,7 @@
         <v>57.05</v>
       </c>
       <c r="G413" t="n">
-        <v>20751920</v>
+        <v>20752000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.83</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30799,7 +30799,7 @@
         <v>37.18</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30818,13 +30818,84 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="2" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D414" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="E414" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="F414" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="G414" t="n">
+        <v>10613217</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -30775,7 +30775,7 @@
         <v>57.05</v>
       </c>
       <c r="G413" t="n">
-        <v>20752000</v>
+        <v>20877500</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.83</v>
@@ -30842,34 +30842,34 @@
         <v>59.74</v>
       </c>
       <c r="E414" t="n">
-        <v>58.94</v>
+        <v>58.89</v>
       </c>
       <c r="F414" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="G414" t="n">
-        <v>10613217</v>
+        <v>13908829</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>3.82</v>
+        <v>3.37</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>59.86</v>
+        <v>59.84</v>
       </c>
       <c r="K414" t="n">
         <v>56.18</v>
       </c>
       <c r="L414" t="n">
-        <v>61.78</v>
+        <v>61.77</v>
       </c>
       <c r="M414" t="n">
         <v>65.77</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>40.53</v>
+        <v>39.7</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30889,13 +30889,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -30835,41 +30835,25 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>59.04</v>
-      </c>
-      <c r="D414" t="n">
-        <v>59.74</v>
-      </c>
-      <c r="E414" t="n">
-        <v>58.89</v>
-      </c>
-      <c r="F414" t="n">
-        <v>58.97</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>13908829</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>3.37</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="n">
-        <v>59.84</v>
-      </c>
-      <c r="K414" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="L414" t="n">
-        <v>61.77</v>
-      </c>
-      <c r="M414" t="n">
-        <v>65.77</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>39.7</v>
+        <v>32.69</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -30835,25 +30835,41 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D414" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="E414" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="F414" t="n">
+        <v>58.97</v>
+      </c>
       <c r="G414" t="n">
-        <v>13908829</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>14039400</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>3.37</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.77</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>32.69</v>
+        <v>39.7</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30872,7 +30872,7 @@
         <v>39.7</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30891,13 +30891,84 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="D415" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="E415" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="F415" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G415" t="n">
+        <v>5055876</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="K415" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L415" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -649,7 +649,9 @@
       <c r="T2" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>168.6</v>
@@ -722,7 +724,9 @@
       <c r="T3" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>163.6</v>
@@ -795,7 +799,9 @@
       <c r="T4" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>157.4</v>
@@ -868,7 +874,9 @@
       <c r="T5" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>156.7</v>
@@ -941,7 +949,9 @@
       <c r="T6" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>158.5</v>
@@ -1014,7 +1024,9 @@
       <c r="T7" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>155.4</v>
@@ -1087,7 +1099,9 @@
       <c r="T8" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>159.4</v>
@@ -1160,7 +1174,9 @@
       <c r="T9" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>162.6</v>
@@ -1233,7 +1249,9 @@
       <c r="T10" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>163.6</v>
@@ -1306,7 +1324,9 @@
       <c r="T11" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>166.5</v>
@@ -1379,7 +1399,9 @@
       <c r="T12" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.9</v>
@@ -1452,7 +1474,9 @@
       <c r="T13" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>168.8</v>
@@ -1525,7 +1549,9 @@
       <c r="T14" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>166.1</v>
@@ -1598,7 +1624,9 @@
       <c r="T15" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>163.4</v>
@@ -1671,7 +1699,9 @@
       <c r="T16" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>168</v>
@@ -1744,7 +1774,9 @@
       <c r="T17" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>183.1</v>
@@ -1817,7 +1849,9 @@
       <c r="T18" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>175.8</v>
@@ -1890,7 +1924,9 @@
       <c r="T19" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>178.6</v>
@@ -1963,7 +1999,9 @@
       <c r="T20" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>165</v>
@@ -2036,7 +2074,9 @@
       <c r="T21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>156.9</v>
@@ -2113,7 +2153,9 @@
       <c r="T22" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>157.6</v>
@@ -2186,7 +2228,9 @@
       <c r="T23" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>153.4</v>
@@ -2259,7 +2303,9 @@
       <c r="T24" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>149.3</v>
@@ -2336,7 +2382,9 @@
       <c r="T25" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>157.9</v>
@@ -2409,7 +2457,9 @@
       <c r="T26" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>154.3</v>
@@ -2482,7 +2532,9 @@
       <c r="T27" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>151.4</v>
@@ -2555,7 +2607,9 @@
       <c r="T28" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>138.9</v>
@@ -2628,7 +2682,9 @@
       <c r="T29" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>137.6</v>
@@ -2701,7 +2757,9 @@
       <c r="T30" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>139.9</v>
@@ -2778,8 +2836,14 @@
       <c r="T31" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="2" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="n">
         <v>146</v>
       </c>
@@ -2851,8 +2915,14 @@
       <c r="T32" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -2924,7 +2994,9 @@
       <c r="T33" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>128.7</v>
@@ -2997,7 +3069,9 @@
       <c r="T34" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.9</v>
@@ -3070,7 +3144,9 @@
       <c r="T35" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>130.3</v>
@@ -3143,7 +3219,9 @@
       <c r="T36" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>133.9</v>
@@ -3216,7 +3294,9 @@
       <c r="T37" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>136.8</v>
@@ -3289,7 +3369,9 @@
       <c r="T38" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.4</v>
@@ -3362,7 +3444,9 @@
       <c r="T39" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>140.8</v>
@@ -3435,7 +3519,9 @@
       <c r="T40" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>141.7</v>
@@ -3508,7 +3594,9 @@
       <c r="T41" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>144</v>
@@ -3581,7 +3669,9 @@
       <c r="T42" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>148.7</v>
@@ -3654,7 +3744,9 @@
       <c r="T43" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>144.8</v>
@@ -3727,7 +3819,9 @@
       <c r="T44" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>140.9</v>
@@ -3800,7 +3894,9 @@
       <c r="T45" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>139</v>
@@ -3873,7 +3969,9 @@
       <c r="T46" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>148.6</v>
@@ -3946,7 +4044,9 @@
       <c r="T47" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>143</v>
@@ -4019,7 +4119,9 @@
       <c r="T48" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
+      <c r="U48" s="3" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>144.3</v>
@@ -4096,8 +4198,14 @@
       <c r="T49" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="4" t="inlineStr"/>
+      <c r="U49" s="7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="6" t="n">
         <v>139.2</v>
       </c>
@@ -4173,8 +4281,14 @@
       <c r="T50" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr"/>
+      <c r="U50" s="7" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="6" t="n">
         <v>136.5</v>
       </c>
@@ -4250,8 +4364,14 @@
       <c r="T51" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4327,8 +4447,14 @@
       <c r="T52" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4400,8 +4526,14 @@
       <c r="T53" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4473,8 +4605,14 @@
       <c r="T54" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="U54" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="n">
         <v>127.5</v>
       </c>
@@ -4546,8 +4684,14 @@
       <c r="T55" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4619,7 +4763,9 @@
       <c r="T56" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="U56" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>135.7</v>
@@ -4692,7 +4838,9 @@
       <c r="T57" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.8</v>
@@ -4765,8 +4913,14 @@
       <c r="T58" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="2" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="U58" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -4838,8 +4992,14 @@
       <c r="T59" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="n">
         <v>130</v>
       </c>
@@ -4911,7 +5071,9 @@
       <c r="T60" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="2" t="inlineStr"/>
+      <c r="U60" s="3" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="3" t="n">
         <v>125.8</v>
@@ -4984,7 +5146,9 @@
       <c r="T61" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="3" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="3" t="n">
         <v>125.9</v>
@@ -5057,8 +5221,14 @@
       <c r="T62" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5130,7 +5300,9 @@
       <c r="T63" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>129</v>
@@ -5203,7 +5375,9 @@
       <c r="T64" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>132.4</v>
@@ -5276,7 +5450,9 @@
       <c r="T65" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>131.3</v>
@@ -5349,7 +5525,9 @@
       <c r="T66" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>134.3</v>
@@ -5426,7 +5604,9 @@
       <c r="T67" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>132.7</v>
@@ -5499,7 +5679,9 @@
       <c r="T68" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
+      <c r="U68" s="3" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>134.1</v>
@@ -5576,7 +5758,9 @@
       <c r="T69" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.8</v>
@@ -5649,7 +5833,9 @@
       <c r="T70" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.1</v>
@@ -5722,7 +5908,9 @@
       <c r="T71" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>133.2</v>
@@ -5799,7 +5987,9 @@
       <c r="T72" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>132.2</v>
@@ -5872,7 +6062,9 @@
       <c r="T73" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>131.5</v>
@@ -5945,7 +6137,9 @@
       <c r="T74" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>128.4</v>
@@ -6022,7 +6216,9 @@
       <c r="T75" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>137.7</v>
@@ -6095,7 +6291,9 @@
       <c r="T76" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>140.5</v>
@@ -6172,7 +6370,9 @@
       <c r="T77" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>138.9</v>
@@ -6245,7 +6445,9 @@
       <c r="T78" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>140.9</v>
@@ -6318,7 +6520,9 @@
       <c r="T79" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>136</v>
@@ -6391,7 +6595,9 @@
       <c r="T80" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>135.9</v>
@@ -6464,7 +6670,9 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>137.3</v>
@@ -6537,7 +6745,9 @@
       <c r="T82" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6610,7 +6820,9 @@
       <c r="T83" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>139</v>
@@ -6683,7 +6895,9 @@
       <c r="T84" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139.3</v>
@@ -6756,7 +6970,9 @@
       <c r="T85" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>140.9</v>
@@ -6829,7 +7045,9 @@
       <c r="T86" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>137.6</v>
@@ -6902,7 +7120,9 @@
       <c r="T87" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.3</v>
@@ -6975,7 +7195,9 @@
       <c r="T88" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>138.2</v>
@@ -7048,7 +7270,9 @@
       <c r="T89" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>141</v>
@@ -7121,7 +7345,9 @@
       <c r="T90" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141.6</v>
@@ -7194,7 +7420,9 @@
       <c r="T91" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>137.5</v>
@@ -7267,7 +7495,9 @@
       <c r="T92" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>140.1</v>
@@ -7340,7 +7570,9 @@
       <c r="T93" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>138.9</v>
@@ -7413,7 +7645,9 @@
       <c r="T94" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>139.2</v>
@@ -7486,7 +7720,9 @@
       <c r="T95" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>141.2</v>
@@ -7559,7 +7795,9 @@
       <c r="T96" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.4</v>
@@ -7632,7 +7870,9 @@
       <c r="T97" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>145.6</v>
@@ -7705,7 +7945,9 @@
       <c r="T98" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>149.6</v>
@@ -7778,7 +8020,9 @@
       <c r="T99" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="1" t="n">
         <v>156.6</v>
@@ -7851,7 +8095,9 @@
       <c r="T100" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>154.4</v>
@@ -7924,7 +8170,9 @@
       <c r="T101" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>148.4</v>
@@ -7997,7 +8245,9 @@
       <c r="T102" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>149.2</v>
@@ -8070,7 +8320,9 @@
       <c r="T103" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>154.8</v>
@@ -8143,7 +8395,9 @@
       <c r="T104" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>155</v>
@@ -8216,7 +8470,9 @@
       <c r="T105" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>152.2</v>
@@ -8289,7 +8545,9 @@
       <c r="T106" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>147.5</v>
@@ -8362,7 +8620,9 @@
       <c r="T107" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>143.4</v>
@@ -8435,7 +8695,9 @@
       <c r="T108" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>139.6</v>
@@ -8512,7 +8774,9 @@
       <c r="T109" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>140.1</v>
@@ -8585,7 +8849,9 @@
       <c r="T110" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>139.3</v>
@@ -8658,7 +8924,9 @@
       <c r="T111" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>141.4</v>
@@ -8731,7 +8999,9 @@
       <c r="T112" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>138</v>
@@ -8804,7 +9074,9 @@
       <c r="T113" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>140.8</v>
@@ -8881,7 +9153,9 @@
       <c r="T114" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>141.8</v>
@@ -8954,7 +9228,9 @@
       <c r="T115" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>143.3</v>
@@ -9027,7 +9303,9 @@
       <c r="T116" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>145</v>
@@ -9100,7 +9378,9 @@
       <c r="T117" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>147</v>
@@ -9173,7 +9453,9 @@
       <c r="T118" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>143.7</v>
@@ -9246,7 +9528,9 @@
       <c r="T119" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>146.7</v>
@@ -9319,7 +9603,9 @@
       <c r="T120" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>151.1</v>
@@ -9392,7 +9678,9 @@
       <c r="T121" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>150.4</v>
@@ -9465,7 +9753,9 @@
       <c r="T122" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>154.8</v>
@@ -9538,7 +9828,9 @@
       <c r="T123" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>153.4</v>
@@ -9611,7 +9903,9 @@
       <c r="T124" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>159.3</v>
@@ -9684,7 +9978,9 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.4</v>
@@ -9757,7 +10053,9 @@
       <c r="T126" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>145.6</v>
@@ -9830,7 +10128,9 @@
       <c r="T127" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>147.6</v>
@@ -9903,7 +10203,9 @@
       <c r="T128" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>149.1</v>
@@ -9980,7 +10282,9 @@
       <c r="T129" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>154.1</v>
@@ -10053,7 +10357,9 @@
       <c r="T130" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>152.3</v>
@@ -10126,7 +10432,9 @@
       <c r="T131" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>155.5</v>
@@ -10199,7 +10507,9 @@
       <c r="T132" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>159.3</v>
@@ -10272,7 +10582,9 @@
       <c r="T133" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>149.9</v>
@@ -10345,7 +10657,9 @@
       <c r="T134" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.7</v>
@@ -10418,7 +10732,9 @@
       <c r="T135" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>147</v>
@@ -10491,7 +10807,9 @@
       <c r="T136" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147.5</v>
@@ -10568,7 +10886,9 @@
       <c r="T137" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>148.6</v>
@@ -10641,7 +10961,9 @@
       <c r="T138" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>151.4</v>
@@ -10714,7 +11036,9 @@
       <c r="T139" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>153.1</v>
@@ -10791,7 +11115,9 @@
       <c r="T140" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>150.6</v>
@@ -10864,7 +11190,9 @@
       <c r="T141" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>153.8</v>
@@ -10937,7 +11265,9 @@
       <c r="T142" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.9</v>
@@ -11014,7 +11344,9 @@
       <c r="T143" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.2</v>
@@ -11087,7 +11419,9 @@
       <c r="T144" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>144.6</v>
@@ -11160,7 +11494,9 @@
       <c r="T145" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.3</v>
@@ -11233,7 +11569,9 @@
       <c r="T146" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>146.4</v>
@@ -11306,7 +11644,9 @@
       <c r="T147" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>150</v>
@@ -11379,7 +11719,9 @@
       <c r="T148" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>156.5</v>
@@ -11452,7 +11794,9 @@
       <c r="T149" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>150.9</v>
@@ -11525,7 +11869,9 @@
       <c r="T150" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>152.5</v>
@@ -11598,7 +11944,9 @@
       <c r="T151" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.1</v>
@@ -11671,7 +12019,9 @@
       <c r="T152" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>151.5</v>
@@ -11744,7 +12094,9 @@
       <c r="T153" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>150.2</v>
@@ -11817,7 +12169,9 @@
       <c r="T154" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>154</v>
@@ -11890,7 +12244,9 @@
       <c r="T155" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>148.2</v>
@@ -11963,7 +12319,9 @@
       <c r="T156" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.8</v>
@@ -12036,7 +12394,9 @@
       <c r="T157" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>150.9</v>
@@ -12109,7 +12469,9 @@
       <c r="T158" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>151.9</v>
@@ -12182,7 +12544,9 @@
       <c r="T159" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>147.6</v>
@@ -12255,7 +12619,9 @@
       <c r="T160" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>149.5</v>
@@ -12328,7 +12694,9 @@
       <c r="T161" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>152.1</v>
@@ -12401,7 +12769,9 @@
       <c r="T162" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>148.2</v>
@@ -12474,7 +12844,9 @@
       <c r="T163" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>146.4</v>
@@ -12547,7 +12919,9 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>148.2</v>
@@ -12620,7 +12994,9 @@
       <c r="T165" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>147</v>
@@ -12693,7 +13069,9 @@
       <c r="T166" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>145.5</v>
@@ -12766,7 +13144,9 @@
       <c r="T167" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>146.5</v>
@@ -12839,7 +13219,9 @@
       <c r="T168" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>145.9</v>
@@ -12912,7 +13294,9 @@
       <c r="T169" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -12985,7 +13369,9 @@
       <c r="T170" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>141.5</v>
@@ -13058,7 +13444,9 @@
       <c r="T171" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>143</v>
@@ -13131,7 +13519,9 @@
       <c r="T172" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143.4</v>
@@ -13204,7 +13594,9 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.7</v>
@@ -13277,7 +13669,9 @@
       <c r="T174" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>145.9</v>
@@ -13350,7 +13744,9 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>144.6</v>
@@ -13423,7 +13819,9 @@
       <c r="T176" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>142.5</v>
@@ -13496,7 +13894,9 @@
       <c r="T177" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>145.2</v>
@@ -13569,7 +13969,9 @@
       <c r="T178" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.8</v>
@@ -13642,7 +14044,9 @@
       <c r="T179" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.3</v>
@@ -13715,7 +14119,9 @@
       <c r="T180" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="2" t="inlineStr"/>
+      <c r="U180" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>138.9</v>
@@ -13788,7 +14194,9 @@
       <c r="T181" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>142.8</v>
@@ -13861,7 +14269,9 @@
       <c r="T182" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>146.5</v>
@@ -13934,7 +14344,9 @@
       <c r="T183" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>145</v>
@@ -14007,7 +14419,9 @@
       <c r="T184" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>147.1</v>
@@ -14080,7 +14494,9 @@
       <c r="T185" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.6</v>
@@ -14153,7 +14569,9 @@
       <c r="T186" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>151.3</v>
@@ -14230,7 +14648,9 @@
       <c r="T187" s="6" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="6" t="inlineStr"/>
+      <c r="U187" s="6" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" s="4" t="inlineStr"/>
       <c r="W187" s="6" t="n">
         <v>149.9</v>
@@ -14303,7 +14723,9 @@
       <c r="T188" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>152.9</v>
@@ -14376,7 +14798,9 @@
       <c r="T189" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>154.3</v>
@@ -14449,7 +14873,9 @@
       <c r="T190" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>153.5</v>
@@ -14522,7 +14948,9 @@
       <c r="T191" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>148.5</v>
@@ -14595,7 +15023,9 @@
       <c r="T192" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>140.4</v>
@@ -14668,7 +15098,9 @@
       <c r="T193" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>139.4</v>
@@ -14741,7 +15173,9 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>141.1</v>
@@ -14814,7 +15248,9 @@
       <c r="T195" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>142.8</v>
@@ -14887,7 +15323,9 @@
       <c r="T196" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142</v>
@@ -14960,7 +15398,9 @@
       <c r="T197" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>144</v>
@@ -15033,7 +15473,9 @@
       <c r="T198" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>143.6</v>
@@ -15106,7 +15548,9 @@
       <c r="T199" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.5</v>
@@ -15179,7 +15623,9 @@
       <c r="T200" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>141.3</v>
@@ -15252,7 +15698,9 @@
       <c r="T201" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>142.9</v>
@@ -15325,7 +15773,9 @@
       <c r="T202" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>143.4</v>
@@ -15398,7 +15848,9 @@
       <c r="T203" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>138.6</v>
@@ -15471,7 +15923,9 @@
       <c r="T204" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>142.5</v>
@@ -15544,7 +15998,9 @@
       <c r="T205" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>137.9</v>
@@ -15617,7 +16073,9 @@
       <c r="T206" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>140.9</v>
@@ -15690,7 +16148,9 @@
       <c r="T207" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>143</v>
@@ -15763,7 +16223,9 @@
       <c r="T208" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="2" t="inlineStr"/>
+      <c r="U208" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143.1</v>
@@ -15836,8 +16298,14 @@
       <c r="T209" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="2" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="2" t="n">
         <v>145</v>
       </c>
@@ -15909,7 +16377,9 @@
       <c r="T210" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>148.3</v>
@@ -15982,7 +16452,9 @@
       <c r="T211" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.6</v>
@@ -16055,7 +16527,9 @@
       <c r="T212" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>151.7</v>
@@ -16128,7 +16602,9 @@
       <c r="T213" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>145</v>
@@ -16201,7 +16677,9 @@
       <c r="T214" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>143</v>
@@ -16274,7 +16752,9 @@
       <c r="T215" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>144.9</v>
@@ -16347,7 +16827,9 @@
       <c r="T216" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16420,7 +16902,9 @@
       <c r="T217" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>149.2</v>
@@ -16493,7 +16977,9 @@
       <c r="T218" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>148.9</v>
@@ -16566,7 +17052,9 @@
       <c r="T219" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.8</v>
@@ -16639,7 +17127,9 @@
       <c r="T220" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>150.6</v>
@@ -16712,7 +17202,9 @@
       <c r="T221" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.3</v>
@@ -16785,7 +17277,9 @@
       <c r="T222" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>147.6</v>
@@ -16858,7 +17352,9 @@
       <c r="T223" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>148.3</v>
@@ -16931,7 +17427,9 @@
       <c r="T224" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>153.6</v>
@@ -17004,7 +17502,9 @@
       <c r="T225" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>161.9</v>
@@ -17077,7 +17577,9 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>157</v>
@@ -17150,7 +17652,9 @@
       <c r="T227" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>153.5</v>
@@ -17223,7 +17727,9 @@
       <c r="T228" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>155.4</v>
@@ -17296,7 +17802,9 @@
       <c r="T229" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.9</v>
@@ -17369,7 +17877,9 @@
       <c r="T230" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>159.9</v>
@@ -17442,7 +17952,9 @@
       <c r="T231" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>160.5</v>
@@ -17515,7 +18027,9 @@
       <c r="T232" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -17588,7 +18102,9 @@
       <c r="T233" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>151.4</v>
@@ -17661,7 +18177,9 @@
       <c r="T234" s="6" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="6" t="inlineStr"/>
+      <c r="U234" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" s="4" t="inlineStr"/>
       <c r="W234" s="6" t="n">
         <v>150.5</v>
@@ -17734,7 +18252,9 @@
       <c r="T235" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>148.3</v>
@@ -17807,7 +18327,9 @@
       <c r="T236" s="6" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="6" t="inlineStr"/>
+      <c r="U236" s="6" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" s="4" t="inlineStr"/>
       <c r="W236" s="6" t="n">
         <v>148.7</v>
@@ -17880,7 +18402,9 @@
       <c r="T237" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>141.9</v>
@@ -17953,7 +18477,9 @@
       <c r="T238" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>142.4</v>
@@ -18026,7 +18552,9 @@
       <c r="T239" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>146.2</v>
@@ -18099,7 +18627,9 @@
       <c r="T240" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>143.6</v>
@@ -18172,7 +18702,9 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>147.1</v>
@@ -18245,7 +18777,9 @@
       <c r="T242" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>146</v>
@@ -18318,7 +18852,9 @@
       <c r="T243" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>149.8</v>
@@ -18391,7 +18927,9 @@
       <c r="T244" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>151.6</v>
@@ -18464,7 +19002,9 @@
       <c r="T245" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>152.5</v>
@@ -18537,7 +19077,9 @@
       <c r="T246" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>151.6</v>
@@ -18610,7 +19152,9 @@
       <c r="T247" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>153.6</v>
@@ -18683,7 +19227,9 @@
       <c r="T248" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="2" t="inlineStr"/>
+      <c r="U248" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="1" t="n">
         <v>155</v>
@@ -18756,7 +19302,9 @@
       <c r="T249" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>144.4</v>
@@ -18829,7 +19377,9 @@
       <c r="T250" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>141.3</v>
@@ -18902,7 +19452,9 @@
       <c r="T251" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>144</v>
@@ -18975,7 +19527,9 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>148.1</v>
@@ -19048,7 +19602,9 @@
       <c r="T253" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>147.2</v>
@@ -19121,7 +19677,9 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>145</v>
@@ -19194,7 +19752,9 @@
       <c r="T255" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>143.7</v>
@@ -19271,7 +19831,9 @@
       <c r="T256" s="6" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="6" t="inlineStr"/>
+      <c r="U256" s="6" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" s="4" t="inlineStr"/>
       <c r="W256" s="6" t="n">
         <v>143.6</v>
@@ -19344,7 +19906,9 @@
       <c r="T257" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>146.6</v>
@@ -19417,7 +19981,9 @@
       <c r="T258" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>143.9</v>
@@ -19490,7 +20056,9 @@
       <c r="T259" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.2</v>
@@ -19563,7 +20131,9 @@
       <c r="T260" s="6" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="6" t="inlineStr"/>
+      <c r="U260" s="6" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" s="4" t="inlineStr"/>
       <c r="W260" s="6" t="n">
         <v>137.2</v>
@@ -19636,7 +20206,9 @@
       <c r="T261" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>140.3</v>
@@ -19709,7 +20281,9 @@
       <c r="T262" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>145.2</v>
@@ -19782,7 +20356,9 @@
       <c r="T263" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.7</v>
@@ -19855,7 +20431,9 @@
       <c r="T264" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>143.8</v>
@@ -19928,7 +20506,9 @@
       <c r="T265" s="6" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="6" t="inlineStr"/>
+      <c r="U265" s="6" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" s="4" t="inlineStr"/>
       <c r="W265" s="6" t="n">
         <v>142.5</v>
@@ -20001,7 +20581,9 @@
       <c r="T266" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>139.4</v>
@@ -20078,7 +20660,9 @@
       <c r="T267" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>140.3</v>
@@ -20151,7 +20735,9 @@
       <c r="T268" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>139.2</v>
@@ -20224,7 +20810,9 @@
       <c r="T269" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>141.2</v>
@@ -20297,7 +20885,9 @@
       <c r="T270" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>145.5</v>
@@ -20370,7 +20960,9 @@
       <c r="T271" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>141.4</v>
@@ -20443,7 +21035,9 @@
       <c r="T272" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.9</v>
@@ -20516,7 +21110,9 @@
       <c r="T273" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>146.1</v>
@@ -20589,7 +21185,9 @@
       <c r="T274" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.6</v>
@@ -20662,7 +21260,9 @@
       <c r="T275" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.7</v>
@@ -20735,7 +21335,9 @@
       <c r="T276" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>151.8</v>
@@ -20812,7 +21414,9 @@
       <c r="T277" s="6" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="6" t="inlineStr"/>
+      <c r="U277" s="6" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" s="4" t="inlineStr"/>
       <c r="W277" s="6" t="n">
         <v>152.8</v>
@@ -20885,7 +21489,9 @@
       <c r="T278" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.9</v>
@@ -20962,7 +21568,9 @@
       <c r="T279" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>153.9</v>
@@ -21035,8 +21643,14 @@
       <c r="T280" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="2" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21108,7 +21722,9 @@
       <c r="T281" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>158</v>
@@ -21181,7 +21797,9 @@
       <c r="T282" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>154.5</v>
@@ -21254,7 +21872,9 @@
       <c r="T283" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>152.4</v>
@@ -21321,7 +21941,9 @@
       <c r="T284" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="2" t="inlineStr"/>
+      <c r="U284" s="2" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>139.9</v>
@@ -21398,8 +22020,14 @@
       <c r="T285" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="2" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -21471,7 +22099,9 @@
       <c r="T286" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>141.5</v>
@@ -21544,7 +22174,9 @@
       <c r="T287" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>145</v>
@@ -21617,7 +22249,9 @@
       <c r="T288" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>136.5</v>
@@ -21690,7 +22324,9 @@
       <c r="T289" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>138.3</v>
@@ -21767,8 +22403,14 @@
       <c r="T290" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="6" t="inlineStr"/>
-      <c r="V290" s="4" t="inlineStr"/>
+      <c r="U290" s="7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="6" t="n">
         <v>139.1</v>
       </c>
@@ -21840,7 +22482,9 @@
       <c r="T291" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>142</v>
@@ -21913,7 +22557,9 @@
       <c r="T292" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142.6</v>
@@ -21986,7 +22632,9 @@
       <c r="T293" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>140.9</v>
@@ -22063,7 +22711,9 @@
       <c r="T294" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="6" t="inlineStr"/>
+      <c r="U294" s="6" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" s="4" t="inlineStr"/>
       <c r="W294" s="6" t="n">
         <v>144</v>
@@ -22136,8 +22786,14 @@
       <c r="T295" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="2" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="2" t="n">
         <v>139</v>
       </c>
@@ -22209,7 +22865,9 @@
       <c r="T296" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>142.2</v>
@@ -22282,7 +22940,9 @@
       <c r="T297" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>145.4</v>
@@ -22355,7 +23015,9 @@
       <c r="T298" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>143.8</v>
@@ -22428,7 +23090,9 @@
       <c r="T299" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="2" t="inlineStr"/>
+      <c r="U299" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>146.9</v>
@@ -22501,7 +23165,9 @@
       <c r="T300" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>147.6</v>
@@ -22574,8 +23240,14 @@
       <c r="T301" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="2" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -22647,7 +23319,9 @@
       <c r="T302" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>150.4</v>
@@ -22720,7 +23394,9 @@
       <c r="T303" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>143.3</v>
@@ -22793,7 +23469,9 @@
       <c r="T304" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>144.2</v>
@@ -22866,7 +23544,9 @@
       <c r="T305" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>156.9</v>
@@ -22939,7 +23619,9 @@
       <c r="T306" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>149.9</v>
@@ -23012,7 +23694,9 @@
       <c r="T307" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>139.2</v>
@@ -23085,7 +23769,9 @@
       <c r="T308" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>140.7</v>
@@ -23158,7 +23844,9 @@
       <c r="T309" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>141.8</v>
@@ -23231,7 +23919,9 @@
       <c r="T310" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.9</v>
@@ -23304,7 +23994,9 @@
       <c r="T311" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>140.9</v>
@@ -23377,7 +24069,9 @@
       <c r="T312" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.8</v>
@@ -23450,7 +24144,9 @@
       <c r="T313" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>139.6</v>
@@ -23523,7 +24219,9 @@
       <c r="T314" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.1</v>
@@ -23600,7 +24298,9 @@
       <c r="T315" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.6</v>
@@ -23677,7 +24377,9 @@
       <c r="T316" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>138.2</v>
@@ -23750,7 +24452,9 @@
       <c r="T317" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>141.9</v>
@@ -23823,7 +24527,9 @@
       <c r="T318" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>143.3</v>
@@ -23896,7 +24602,9 @@
       <c r="T319" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>141.4</v>
@@ -23973,7 +24681,9 @@
       <c r="T320" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.7</v>
@@ -24046,7 +24756,9 @@
       <c r="T321" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>138.7</v>
@@ -24119,7 +24831,9 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>135.4</v>
@@ -24192,7 +24906,9 @@
       <c r="T323" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>136.1</v>
@@ -24265,7 +24981,9 @@
       <c r="T324" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>138.2</v>
@@ -24338,7 +25056,9 @@
       <c r="T325" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>140.2</v>
@@ -24411,7 +25131,9 @@
       <c r="T326" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>139.4</v>
@@ -24484,7 +25206,9 @@
       <c r="T327" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>141.5</v>
@@ -24557,7 +25281,9 @@
       <c r="T328" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>139.3</v>
@@ -24634,7 +25360,9 @@
       <c r="T329" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="6" t="inlineStr"/>
+      <c r="U329" s="6" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" s="4" t="inlineStr"/>
       <c r="W329" s="6" t="n">
         <v>145.8</v>
@@ -24707,7 +25435,9 @@
       <c r="T330" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>138.4</v>
@@ -24780,7 +25510,9 @@
       <c r="T331" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>135.5</v>
@@ -24853,7 +25585,9 @@
       <c r="T332" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>132.3</v>
@@ -24926,7 +25660,9 @@
       <c r="T333" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>137</v>
@@ -24999,7 +25735,9 @@
       <c r="T334" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137.4</v>
@@ -25072,7 +25810,9 @@
       <c r="T335" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>139</v>
@@ -25145,7 +25885,9 @@
       <c r="T336" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>138.6</v>
@@ -25218,7 +25960,9 @@
       <c r="T337" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>139.5</v>
@@ -25291,7 +26035,9 @@
       <c r="T338" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>144.2</v>
@@ -25364,7 +26110,9 @@
       <c r="T339" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>142.5</v>
@@ -25437,7 +26185,9 @@
       <c r="T340" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>143.2</v>
@@ -25510,7 +26260,9 @@
       <c r="T341" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>136.9</v>
@@ -25583,7 +26335,9 @@
       <c r="T342" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>142.1</v>
@@ -25656,7 +26410,9 @@
       <c r="T343" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="6" t="inlineStr"/>
+      <c r="U343" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="4" t="inlineStr"/>
       <c r="W343" s="6" t="n">
         <v>152.2</v>
@@ -25729,7 +26485,9 @@
       <c r="T344" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="2" t="n">
         <v>145</v>
@@ -25806,7 +26564,9 @@
       <c r="T345" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>142</v>
@@ -25883,7 +26643,9 @@
       <c r="T346" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>143.1</v>
@@ -25956,7 +26718,9 @@
       <c r="T347" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143</v>
@@ -26029,7 +26793,9 @@
       <c r="T348" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>142.6</v>
@@ -26102,7 +26868,9 @@
       <c r="T349" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>144.3</v>
@@ -26175,7 +26943,9 @@
       <c r="T350" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>142.7</v>
@@ -26248,7 +27018,9 @@
       <c r="T351" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.6</v>
@@ -26321,7 +27093,9 @@
       <c r="T352" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>146.7</v>
@@ -26394,7 +27168,9 @@
       <c r="T353" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>141.9</v>
@@ -26471,7 +27247,9 @@
       <c r="T354" s="6" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="6" t="inlineStr"/>
+      <c r="U354" s="6" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" s="4" t="inlineStr"/>
       <c r="W354" s="6" t="n">
         <v>143.1</v>
@@ -26548,7 +27326,9 @@
       <c r="T355" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="6" t="inlineStr"/>
+      <c r="U355" s="6" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" s="4" t="inlineStr"/>
       <c r="W355" s="6" t="n">
         <v>145.3</v>
@@ -26625,7 +27405,9 @@
       <c r="T356" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>139.9</v>
@@ -26698,7 +27480,9 @@
       <c r="T357" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.4</v>
@@ -26771,7 +27555,9 @@
       <c r="T358" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>144.5</v>
@@ -26844,7 +27630,9 @@
       <c r="T359" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>149.6</v>
@@ -26917,7 +27705,9 @@
       <c r="T360" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>154.8</v>
@@ -26990,7 +27780,9 @@
       <c r="T361" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>150</v>
@@ -27063,7 +27855,9 @@
       <c r="T362" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>145.4</v>
@@ -27140,7 +27934,9 @@
       <c r="T363" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.7</v>
@@ -27217,7 +28013,9 @@
       <c r="T364" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>149.8</v>
@@ -27290,7 +28088,9 @@
       <c r="T365" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>144.7</v>
@@ -27363,7 +28163,9 @@
       <c r="T366" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.3</v>
@@ -27436,7 +28238,9 @@
       <c r="T367" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>145.7</v>
@@ -27509,7 +28313,9 @@
       <c r="T368" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.1</v>
@@ -27582,7 +28388,9 @@
       <c r="T369" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>148.5</v>
@@ -27655,7 +28463,9 @@
       <c r="T370" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>145.7</v>
@@ -27728,7 +28538,9 @@
       <c r="T371" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>147.3</v>
@@ -27801,7 +28613,9 @@
       <c r="T372" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>146.1</v>
@@ -27874,7 +28688,9 @@
       <c r="T373" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>151.7</v>
@@ -27947,7 +28763,9 @@
       <c r="T374" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="2" t="n">
         <v>150.2</v>
@@ -28024,7 +28842,9 @@
       <c r="T375" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="2" t="n">
         <v>145.9</v>
@@ -28097,7 +28917,9 @@
       <c r="T376" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="2" t="n">
         <v>147.3</v>
@@ -28170,7 +28992,9 @@
       <c r="T377" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="2" t="n">
         <v>146.6</v>
@@ -28243,7 +29067,9 @@
       <c r="T378" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="2" t="n">
         <v>143</v>
@@ -28316,7 +29142,9 @@
       <c r="T379" s="2" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="2" t="n">
         <v>139.6</v>
@@ -28389,7 +29217,9 @@
       <c r="T380" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="2" t="n">
         <v>139.9</v>
@@ -28466,7 +29296,9 @@
       <c r="T381" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="2" t="n">
         <v>141.2</v>
@@ -28539,7 +29371,9 @@
       <c r="T382" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="2" t="n">
         <v>140</v>
@@ -28612,7 +29446,9 @@
       <c r="T383" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="3" t="n">
         <v>126.4</v>
@@ -28685,7 +29521,9 @@
       <c r="T384" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="2" t="n">
         <v>133.3</v>
@@ -28758,7 +29596,9 @@
       <c r="T385" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="2" t="n">
         <v>134.7</v>
@@ -28831,7 +29671,9 @@
       <c r="T386" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="2" t="n">
         <v>132.6</v>
@@ -28904,7 +29746,9 @@
       <c r="T387" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="2" t="n">
         <v>137.1</v>
@@ -28977,7 +29821,9 @@
       <c r="T388" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="2" t="n">
         <v>135.6</v>
@@ -29050,7 +29896,9 @@
       <c r="T389" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="2" t="n">
         <v>136.5</v>
@@ -29123,7 +29971,9 @@
       <c r="T390" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="2" t="n">
         <v>134.4</v>
@@ -29196,7 +30046,9 @@
       <c r="T391" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="2" t="n">
         <v>138.4</v>
@@ -29269,7 +30121,9 @@
       <c r="T392" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="2" t="n">
         <v>142.9</v>
@@ -29346,7 +30200,9 @@
       <c r="T393" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="2" t="n">
         <v>143.6</v>
@@ -29419,7 +30275,9 @@
       <c r="T394" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="2" t="n">
         <v>142.9</v>
@@ -29492,7 +30350,9 @@
       <c r="T395" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="2" t="n">
         <v>143.2</v>
@@ -29565,7 +30425,9 @@
       <c r="T396" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="2" t="n">
         <v>143.9</v>
@@ -29638,7 +30500,9 @@
       <c r="T397" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="2" t="n">
         <v>145.6</v>
@@ -29711,7 +30575,9 @@
       <c r="T398" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="2" t="n">
         <v>143.3</v>
@@ -29784,7 +30650,9 @@
       <c r="T399" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="2" t="n">
         <v>143</v>
@@ -29857,7 +30725,9 @@
       <c r="T400" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="2" t="n">
         <v>144.1</v>
@@ -29930,7 +30800,9 @@
       <c r="T401" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="2" t="n">
         <v>149.8</v>
@@ -30003,7 +30875,9 @@
       <c r="T402" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="2" t="n">
         <v>148.5</v>
@@ -30080,7 +30954,9 @@
       <c r="T403" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="2" t="n">
         <v>149.2</v>
@@ -30153,7 +31029,9 @@
       <c r="T404" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="2" t="n">
         <v>144.1</v>
@@ -30226,7 +31104,9 @@
       <c r="T405" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="2" t="n">
         <v>150.6</v>
@@ -30303,7 +31183,9 @@
       <c r="T406" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="2" t="n">
         <v>151.6</v>
@@ -30376,7 +31258,9 @@
       <c r="T407" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="2" t="n">
         <v>148.9</v>
@@ -30449,7 +31333,9 @@
       <c r="T408" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="2" t="n">
         <v>149.2</v>
@@ -30526,7 +31412,9 @@
       <c r="T409" s="6" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="6" t="inlineStr"/>
+      <c r="U409" s="6" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" s="4" t="inlineStr"/>
       <c r="W409" s="6" t="n">
         <v>147</v>
@@ -30599,7 +31487,9 @@
       <c r="T410" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="2" t="n">
         <v>154.5</v>
@@ -30672,7 +31562,9 @@
       <c r="T411" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" t="inlineStr"/>
       <c r="W411" s="2" t="n">
         <v>152.1</v>
@@ -30745,7 +31637,9 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
@@ -30818,7 +31712,9 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
@@ -30891,7 +31787,9 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
@@ -30912,37 +31810,37 @@
         <v>60.08</v>
       </c>
       <c r="D415" t="n">
-        <v>60.11</v>
+        <v>60.35</v>
       </c>
       <c r="E415" t="n">
-        <v>59.76</v>
+        <v>59.58</v>
       </c>
       <c r="F415" t="n">
-        <v>59.9</v>
+        <v>60.24</v>
       </c>
       <c r="G415" t="n">
-        <v>5055876</v>
+        <v>10951735</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>59.76</v>
+        <v>59.77</v>
       </c>
       <c r="K415" t="n">
-        <v>56.31</v>
+        <v>56.32</v>
       </c>
       <c r="L415" t="n">
-        <v>61.74</v>
+        <v>61.75</v>
       </c>
       <c r="M415" t="n">
         <v>65.8</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>49.64</v>
+        <v>50.65</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -30962,10 +31860,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31744,7 +31744,7 @@
         <v>58.97</v>
       </c>
       <c r="G414" t="n">
-        <v>14039400</v>
+        <v>14094000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>3.37</v>
@@ -31810,37 +31810,37 @@
         <v>60.08</v>
       </c>
       <c r="D415" t="n">
-        <v>60.35</v>
+        <v>60.37</v>
       </c>
       <c r="E415" t="n">
         <v>59.58</v>
       </c>
       <c r="F415" t="n">
-        <v>60.24</v>
+        <v>59.93</v>
       </c>
       <c r="G415" t="n">
-        <v>10951735</v>
+        <v>15497177</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>59.77</v>
+        <v>59.76</v>
       </c>
       <c r="K415" t="n">
-        <v>56.32</v>
+        <v>56.31</v>
       </c>
       <c r="L415" t="n">
-        <v>61.75</v>
+        <v>61.74</v>
       </c>
       <c r="M415" t="n">
         <v>65.8</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>50.65</v>
+        <v>49.73</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31860,13 +31860,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2734,7 +2734,7 @@
         <v>29.37</v>
       </c>
       <c r="K30" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="L30" t="n">
         <v>28.58</v>
@@ -9865,7 +9865,7 @@
         <v>5.2</v>
       </c>
       <c r="J124" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="K124" t="n">
         <v>32.22</v>
@@ -10319,7 +10319,7 @@
         <v>5.2</v>
       </c>
       <c r="J130" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="K130" t="n">
         <v>32.65</v>
@@ -24871,7 +24871,7 @@
         <v>70.12</v>
       </c>
       <c r="K323" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="L323" t="n">
         <v>69.38</v>
@@ -26755,7 +26755,7 @@
         <v>5.2</v>
       </c>
       <c r="J348" t="n">
-        <v>64.93000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K348" t="n">
         <v>67.62</v>
@@ -27825,7 +27825,7 @@
         <v>5.2</v>
       </c>
       <c r="J362" t="n">
-        <v>56.56</v>
+        <v>56.55</v>
       </c>
       <c r="K362" t="n">
         <v>64.95999999999999</v>
@@ -31614,7 +31614,7 @@
         <v>49.73</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31640,6 +31640,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="D413" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="E413" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="F413" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="G413" t="n">
+        <v>7164692</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -2734,7 +2734,7 @@
         <v>29.37</v>
       </c>
       <c r="K30" t="n">
-        <v>28.29</v>
+        <v>28.28</v>
       </c>
       <c r="L30" t="n">
         <v>28.58</v>
@@ -5040,7 +5040,7 @@
         <v>29.45</v>
       </c>
       <c r="K60" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
       <c r="L60" t="n">
         <v>28.72</v>
@@ -24871,7 +24871,7 @@
         <v>70.12</v>
       </c>
       <c r="K323" t="n">
-        <v>70.95</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="L323" t="n">
         <v>69.38</v>
@@ -31659,16 +31659,16 @@
         <v>60.15</v>
       </c>
       <c r="E413" t="n">
-        <v>59.43</v>
+        <v>59.35</v>
       </c>
       <c r="F413" t="n">
-        <v>59.62</v>
+        <v>59.63</v>
       </c>
       <c r="G413" t="n">
-        <v>7164692</v>
+        <v>10540411</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
@@ -31683,10 +31683,10 @@
         <v>61.71</v>
       </c>
       <c r="M413" t="n">
-        <v>65.83</v>
+        <v>65.84</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>48.49</v>
+        <v>48.52</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31703,13 +31703,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31665,7 +31665,7 @@
         <v>59.63</v>
       </c>
       <c r="G413" t="n">
-        <v>10540411</v>
+        <v>10566486</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.5</v>
@@ -31712,7 +31712,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31641,6 +31641,83 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="D413" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="E413" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="F413" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3920079</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31656,40 +31656,40 @@
         <v>59.31</v>
       </c>
       <c r="D413" t="n">
-        <v>59.67</v>
+        <v>60.61</v>
       </c>
       <c r="E413" t="n">
-        <v>59.26</v>
+        <v>59.05</v>
       </c>
       <c r="F413" t="n">
-        <v>59.29</v>
+        <v>60.38</v>
       </c>
       <c r="G413" t="n">
-        <v>3920079</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.57</v>
+        <v>9603923</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>1.26</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>59.46</v>
+        <v>59.51</v>
       </c>
       <c r="K413" t="n">
-        <v>56.53</v>
+        <v>56.55</v>
       </c>
       <c r="L413" t="n">
-        <v>61.64</v>
+        <v>61.65</v>
       </c>
       <c r="M413" t="n">
         <v>65.87</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>54.58</v>
+        <v>58</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31701,19 +31701,15 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>-0.73</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>27.67</v>
@@ -683,7 +683,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>27.75</v>
@@ -758,7 +758,7 @@
         <v>1.92</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>27.87</v>
@@ -833,7 +833,7 @@
         <v>0.44</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>27.97</v>
@@ -908,7 +908,7 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>28.07</v>
@@ -983,7 +983,7 @@
         <v>-1.19</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>28.16</v>
@@ -1058,7 +1058,7 @@
         <v>0.59</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>28.24</v>
@@ -1133,7 +1133,7 @@
         <v>-0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>28.34</v>
@@ -1208,7 +1208,7 @@
         <v>1.17</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>28.44</v>
@@ -1283,7 +1283,7 @@
         <v>0.41</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>28.52</v>
@@ -1358,7 +1358,7 @@
         <v>-0.51</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>28.58</v>
@@ -1433,7 +1433,7 @@
         <v>2.05</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>28.7</v>
@@ -1508,7 +1508,7 @@
         <v>-0.33</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>28.79</v>
@@ -1583,7 +1583,7 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>28.88</v>
@@ -1658,7 +1658,7 @@
         <v>-1.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>28.97</v>
@@ -1733,7 +1733,7 @@
         <v>-0.51</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>29.05</v>
@@ -1808,7 +1808,7 @@
         <v>-2.07</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>29.12</v>
@@ -1887,7 +1887,7 @@
         <v>0.38</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>29.18</v>
@@ -1962,7 +1962,7 @@
         <v>-1.87</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>29.2</v>
@@ -2037,7 +2037,7 @@
         <v>-0.32</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>29.18</v>
@@ -2116,7 +2116,7 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.19</v>
@@ -2191,7 +2191,7 @@
         <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.21</v>
@@ -2266,7 +2266,7 @@
         <v>2.66</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.24</v>
@@ -2341,7 +2341,7 @@
         <v>-0.27</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.26</v>
@@ -2416,7 +2416,7 @@
         <v>-0.34</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.27</v>
@@ -2491,7 +2491,7 @@
         <v>-1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.27</v>
@@ -2574,7 +2574,7 @@
         <v>2.92</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.31</v>
@@ -2653,7 +2653,7 @@
         <v>0.87</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.37</v>
@@ -2728,7 +2728,7 @@
         <v>1.72</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.44</v>
@@ -2803,7 +2803,7 @@
         <v>-0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.5</v>
@@ -2878,7 +2878,7 @@
         <v>0.33</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.58</v>
@@ -2953,7 +2953,7 @@
         <v>0.13</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.62</v>
@@ -3028,7 +3028,7 @@
         <v>-0.32</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.67</v>
@@ -3103,7 +3103,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.7</v>
@@ -3178,7 +3178,7 @@
         <v>-1.57</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.72</v>
@@ -3253,7 +3253,7 @@
         <v>-0.2</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.75</v>
@@ -3328,7 +3328,7 @@
         <v>2.07</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>29.83</v>
@@ -3403,7 +3403,7 @@
         <v>-0.16</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>29.91</v>
@@ -3478,7 +3478,7 @@
         <v>2.59</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>30.06</v>
@@ -3553,7 +3553,7 @@
         <v>-1.02</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>30.19</v>
@@ -3628,7 +3628,7 @@
         <v>-0.03</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>30.3</v>
@@ -3703,7 +3703,7 @@
         <v>-1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>30.39</v>
@@ -3778,7 +3778,7 @@
         <v>0.42</v>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>30.44</v>
@@ -3853,7 +3853,7 @@
         <v>-6.08</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30.4</v>
@@ -3936,7 +3936,7 @@
         <v>-6.27</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>30.27</v>
@@ -4019,7 +4019,7 @@
         <v>0.22</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>30.17</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>30.03</v>
@@ -4185,7 +4185,7 @@
         <v>3.39</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>29.92</v>
@@ -4264,7 +4264,7 @@
         <v>0.78</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>29.8</v>
@@ -4343,7 +4343,7 @@
         <v>3.22</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>29.72</v>
@@ -4422,7 +4422,7 @@
         <v>0.65</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>29.65</v>
@@ -4497,7 +4497,7 @@
         <v>0.1</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.58</v>
@@ -4572,7 +4572,7 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.53</v>
@@ -4651,7 +4651,7 @@
         <v>-0.71</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.48</v>
@@ -4730,7 +4730,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.47</v>
@@ -4805,7 +4805,7 @@
         <v>-0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.45</v>
@@ -4880,7 +4880,7 @@
         <v>3.59</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.45</v>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.45</v>
@@ -5034,7 +5034,7 @@
         <v>-1.67</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.39</v>
@@ -5109,7 +5109,7 @@
         <v>0.47</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.35</v>
@@ -5184,7 +5184,7 @@
         <v>-1.19</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.29</v>
@@ -5259,7 +5259,7 @@
         <v>-0.77</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.24</v>
@@ -5338,7 +5338,7 @@
         <v>-0.71</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.17</v>
@@ -5413,7 +5413,7 @@
         <v>-0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.18</v>
@@ -5492,7 +5492,7 @@
         <v>1.24</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.3</v>
@@ -5567,7 +5567,7 @@
         <v>2.51</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.45</v>
@@ -5642,7 +5642,7 @@
         <v>-2.42</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.57</v>
@@ -5721,7 +5721,7 @@
         <v>-0.1</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.64</v>
@@ -5796,7 +5796,7 @@
         <v>1.15</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.72</v>
@@ -5871,7 +5871,7 @@
         <v>-0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.74</v>
@@ -5950,13 +5950,13 @@
         <v>1.01</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.77</v>
       </c>
       <c r="K72" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="L72" t="n">
         <v>28.82</v>
@@ -6025,7 +6025,7 @@
         <v>-2.27</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.76</v>
@@ -6104,7 +6104,7 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.75</v>
@@ -6179,7 +6179,7 @@
         <v>-1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.74</v>
@@ -6254,7 +6254,7 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.72</v>
@@ -6329,7 +6329,7 @@
         <v>2.41</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.75</v>
@@ -6404,7 +6404,7 @@
         <v>1.26</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.75</v>
@@ -6479,7 +6479,7 @@
         <v>-1.57</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.72</v>
@@ -6554,7 +6554,7 @@
         <v>1.4</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6629,7 +6629,7 @@
         <v>-0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>29.74</v>
@@ -6704,7 +6704,7 @@
         <v>-0.83</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.75</v>
@@ -6779,7 +6779,7 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.79</v>
@@ -6854,7 +6854,7 @@
         <v>-0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.82</v>
@@ -6929,7 +6929,7 @@
         <v>5.3</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>29.94</v>
@@ -7004,7 +7004,7 @@
         <v>-0.47</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>30.04</v>
@@ -7079,7 +7079,7 @@
         <v>-0.32</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>30.09</v>
@@ -7154,7 +7154,7 @@
         <v>3.54</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>30.24</v>
@@ -7229,7 +7229,7 @@
         <v>0.74</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>30.4</v>
@@ -7304,7 +7304,7 @@
         <v>2.14</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>30.58</v>
@@ -7379,7 +7379,7 @@
         <v>-0.48</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>30.76</v>
@@ -7454,7 +7454,7 @@
         <v>-0.84</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>30.91</v>
@@ -7529,7 +7529,7 @@
         <v>0.33</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>31.1</v>
@@ -7604,7 +7604,7 @@
         <v>-0.27</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>31.27</v>
@@ -7679,7 +7679,7 @@
         <v>0.18</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>31.46</v>
@@ -7754,7 +7754,7 @@
         <v>2.15</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>31.68</v>
@@ -7829,7 +7829,7 @@
         <v>-1.39</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>31.83</v>
@@ -7904,7 +7904,7 @@
         <v>-1.65</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>31.94</v>
@@ -7979,7 +7979,7 @@
         <v>0.73</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>32.09</v>
@@ -8054,7 +8054,7 @@
         <v>-1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>32.2</v>
@@ -8129,7 +8129,7 @@
         <v>1.23</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>32.34</v>
@@ -8204,7 +8204,7 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>32.5</v>
@@ -8279,7 +8279,7 @@
         <v>-2.16</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>32.62</v>
@@ -8354,7 +8354,7 @@
         <v>0.58</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>32.76</v>
@@ -8429,7 +8429,7 @@
         <v>-0.24</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>32.82</v>
@@ -8508,7 +8508,7 @@
         <v>1.56</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>32.91</v>
@@ -8583,7 +8583,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>33.02</v>
@@ -8658,7 +8658,7 @@
         <v>-0.24</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>33.07</v>
@@ -8733,7 +8733,7 @@
         <v>-0.42</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>33.1</v>
@@ -8808,7 +8808,7 @@
         <v>-0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>33.08</v>
@@ -8887,7 +8887,7 @@
         <v>2.27</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>33.1</v>
@@ -8962,7 +8962,7 @@
         <v>3.79</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.21</v>
@@ -9037,7 +9037,7 @@
         <v>-1.14</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.28</v>
@@ -9112,7 +9112,7 @@
         <v>-1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.35</v>
@@ -9187,7 +9187,7 @@
         <v>0.44</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>33.42</v>
@@ -9262,7 +9262,7 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>33.46</v>
@@ -9337,7 +9337,7 @@
         <v>-0.12</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>33.53</v>
@@ -9412,7 +9412,7 @@
         <v>2.14</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>33.66</v>
@@ -9487,7 +9487,7 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>33.8</v>
@@ -9562,7 +9562,7 @@
         <v>-0.08</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>33.95</v>
@@ -9637,7 +9637,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>34.08</v>
@@ -9712,7 +9712,7 @@
         <v>-2.34</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>34.14</v>
@@ -9787,10 +9787,10 @@
         <v>-0.06</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="K123" t="n">
         <v>32.22</v>
@@ -9862,7 +9862,7 @@
         <v>0.06</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>34.34</v>
@@ -9937,7 +9937,7 @@
         <v>-3.32</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>-0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.38</v>
@@ -10091,7 +10091,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.38</v>
@@ -10166,7 +10166,7 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.41</v>
@@ -10241,10 +10241,10 @@
         <v>1.09</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
-        <v>34.46</v>
+        <v>34.47</v>
       </c>
       <c r="K129" t="n">
         <v>32.65</v>
@@ -10316,7 +10316,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.53</v>
@@ -10391,7 +10391,7 @@
         <v>1.19</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.58</v>
@@ -10466,7 +10466,7 @@
         <v>0.35</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.58</v>
@@ -10541,7 +10541,7 @@
         <v>-2.01</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.55</v>
@@ -10620,7 +10620,7 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.56</v>
@@ -10695,7 +10695,7 @@
         <v>1.71</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.59</v>
@@ -10770,7 +10770,7 @@
         <v>-1.43</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10849,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.58</v>
@@ -10924,7 +10924,7 @@
         <v>0.14</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.54</v>
@@ -10999,7 +10999,7 @@
         <v>-1.97</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.44</v>
@@ -11078,7 +11078,7 @@
         <v>1.65</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.38</v>
@@ -11153,7 +11153,7 @@
         <v>0.52</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.34</v>
@@ -11228,7 +11228,7 @@
         <v>2.11</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.37</v>
@@ -11303,7 +11303,7 @@
         <v>-0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>34.39</v>
@@ -11378,7 +11378,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>34.41</v>
@@ -11453,7 +11453,7 @@
         <v>-0.09</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>34.48</v>
@@ -11528,7 +11528,7 @@
         <v>1.51</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>34.59</v>
@@ -11603,7 +11603,7 @@
         <v>1.89</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>34.72</v>
@@ -11678,7 +11678,7 @@
         <v>2.65</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>34.88</v>
@@ -11753,7 +11753,7 @@
         <v>0.51</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>35.03</v>
@@ -11828,7 +11828,7 @@
         <v>-1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>35.16</v>
@@ -11903,7 +11903,7 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>35.28</v>
@@ -11978,7 +11978,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>35.41</v>
@@ -12053,7 +12053,7 @@
         <v>-0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>35.56</v>
@@ -12128,7 +12128,7 @@
         <v>0.62</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>35.71</v>
@@ -12203,7 +12203,7 @@
         <v>1.02</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>35.85</v>
@@ -12278,7 +12278,7 @@
         <v>1.46</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>36.04</v>
@@ -12353,7 +12353,7 @@
         <v>1.1</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>36.26</v>
@@ -12428,7 +12428,7 @@
         <v>-0.41</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>36.46</v>
@@ -12503,7 +12503,7 @@
         <v>-2.1</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>36.66</v>
@@ -12578,7 +12578,7 @@
         <v>0.53</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>36.83</v>
@@ -12653,7 +12653,7 @@
         <v>2.76</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>37.06</v>
@@ -12728,7 +12728,7 @@
         <v>2.56</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>37.29</v>
@@ -12803,7 +12803,7 @@
         <v>-0.2</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>37.54</v>
@@ -12878,7 +12878,7 @@
         <v>-0.35</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>37.78</v>
@@ -12953,7 +12953,7 @@
         <v>3.04</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>38.08</v>
@@ -13028,7 +13028,7 @@
         <v>2.02</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>38.4</v>
@@ -13103,7 +13103,7 @@
         <v>1.53</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>38.71</v>
@@ -13178,7 +13178,7 @@
         <v>-0.31</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>38.97</v>
@@ -13253,7 +13253,7 @@
         <v>1.27</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>39.25</v>
@@ -13328,7 +13328,7 @@
         <v>-0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>39.53</v>
@@ -13403,7 +13403,7 @@
         <v>2.33</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>39.85</v>
@@ -13478,7 +13478,7 @@
         <v>1.24</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>40.17</v>
@@ -13553,7 +13553,7 @@
         <v>-1.52</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>40.49</v>
@@ -13628,7 +13628,7 @@
         <v>2.7</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>40.84</v>
@@ -13703,7 +13703,7 @@
         <v>0.34</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>41.19</v>
@@ -13778,7 +13778,7 @@
         <v>1.61</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>41.54</v>
@@ -13853,7 +13853,7 @@
         <v>4.03</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>41.97</v>
@@ -13928,7 +13928,7 @@
         <v>-0.97</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>42.38</v>
@@ -14003,7 +14003,7 @@
         <v>3.27</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>42.91</v>
@@ -14078,7 +14078,7 @@
         <v>1.74</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>43.46</v>
@@ -14153,7 +14153,7 @@
         <v>-4.43</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>43.86</v>
@@ -14228,7 +14228,7 @@
         <v>1.55</v>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>44.25</v>
@@ -14303,7 +14303,7 @@
         <v>-8.24</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>44.44</v>
@@ -14382,7 +14382,7 @@
         <v>0.21</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>44.64</v>
@@ -14457,7 +14457,7 @@
         <v>0.68</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>44.8</v>
@@ -14532,7 +14532,7 @@
         <v>-0.43</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>44.9</v>
@@ -14607,7 +14607,7 @@
         <v>-3.61</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>44.9</v>
@@ -14682,7 +14682,7 @@
         <v>0.71</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>44.92</v>
@@ -14757,7 +14757,7 @@
         <v>1.24</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>44.93</v>
@@ -14832,7 +14832,7 @@
         <v>2.57</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>45.02</v>
@@ -14907,7 +14907,7 @@
         <v>-0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>45.05</v>
@@ -14982,7 +14982,7 @@
         <v>-0.57</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>45.03</v>
@@ -15057,7 +15057,7 @@
         <v>-2.33</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>45</v>
@@ -15132,7 +15132,7 @@
         <v>2.13</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>44.95</v>
@@ -15207,7 +15207,7 @@
         <v>-0.23</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>44.9</v>
@@ -15282,7 +15282,7 @@
         <v>0.85</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>44.82</v>
@@ -15357,7 +15357,7 @@
         <v>4.26</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>44.75</v>
@@ -15432,7 +15432,7 @@
         <v>1.44</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>44.73</v>
@@ -15507,7 +15507,7 @@
         <v>4.03</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.73</v>
@@ -15582,7 +15582,7 @@
         <v>-1.86</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.64</v>
@@ -15657,7 +15657,7 @@
         <v>-3.08</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>44.59</v>
@@ -15732,7 +15732,7 @@
         <v>-1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>44.48</v>
@@ -15807,7 +15807,7 @@
         <v>1.39</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>44.59</v>
@@ -15882,7 +15882,7 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>44.72</v>
@@ -15957,7 +15957,7 @@
         <v>-1.44</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>44.8</v>
@@ -16036,7 +16036,7 @@
         <v>-1.05</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>44.87</v>
@@ -16111,7 +16111,7 @@
         <v>2.94</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>45.08</v>
@@ -16186,7 +16186,7 @@
         <v>0.09</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>45.28</v>
@@ -16261,7 +16261,7 @@
         <v>3.71</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>45.54</v>
@@ -16336,7 +16336,7 @@
         <v>5.81</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>45.88</v>
@@ -16411,7 +16411,7 @@
         <v>2.56</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>46.3</v>
@@ -16486,7 +16486,7 @@
         <v>1.16</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>46.77</v>
@@ -16561,7 +16561,7 @@
         <v>-0.11</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>47.29</v>
@@ -16636,7 +16636,7 @@
         <v>-2.47</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>47.7</v>
@@ -16711,7 +16711,7 @@
         <v>2.3</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>48.16</v>
@@ -16786,7 +16786,7 @@
         <v>-0.45</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>48.6</v>
@@ -16861,7 +16861,7 @@
         <v>4.67</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>49.07</v>
@@ -16936,7 +16936,7 @@
         <v>1.63</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>49.55</v>
@@ -17011,7 +17011,7 @@
         <v>2.76</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>50.02</v>
@@ -17086,7 +17086,7 @@
         <v>-2.64</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>50.45</v>
@@ -17161,7 +17161,7 @@
         <v>3.58</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>51.06</v>
@@ -17236,7 +17236,7 @@
         <v>-0.65</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>51.67</v>
@@ -17311,7 +17311,7 @@
         <v>4.38</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>52.38</v>
@@ -17386,7 +17386,7 @@
         <v>-1.56</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>53.03</v>
@@ -17461,7 +17461,7 @@
         <v>2.71</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>53.78</v>
@@ -17536,7 +17536,7 @@
         <v>2.53</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>54.64</v>
@@ -17611,7 +17611,7 @@
         <v>3.79</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>55.55</v>
@@ -17686,7 +17686,7 @@
         <v>0.59</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>56.48</v>
@@ -17761,7 +17761,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" t="n">
         <v>57.62</v>
@@ -17836,7 +17836,7 @@
         <v>-7.19</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>58.36</v>
@@ -17911,7 +17911,7 @@
         <v>4.5</v>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" t="n">
         <v>59.18</v>
@@ -17986,7 +17986,7 @@
         <v>-6.61</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>59.74</v>
@@ -18061,7 +18061,7 @@
         <v>2.06</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>60.38</v>
@@ -18136,7 +18136,7 @@
         <v>5.06</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>61.24</v>
@@ -18211,7 +18211,7 @@
         <v>6.7</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>62.28</v>
@@ -18286,7 +18286,7 @@
         <v>-3.73</v>
       </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" t="n">
         <v>63.19</v>
@@ -18361,7 +18361,7 @@
         <v>-1.76</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>63.92</v>
@@ -18436,7 +18436,7 @@
         <v>3.83</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>64.73999999999999</v>
@@ -18511,7 +18511,7 @@
         <v>6.7</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>65.72</v>
@@ -18586,7 +18586,7 @@
         <v>1.77</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>66.84</v>
@@ -18661,7 +18661,7 @@
         <v>7.58</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>68.16</v>
@@ -18736,7 +18736,7 @@
         <v>-1.47</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>69.44</v>
@@ -18811,7 +18811,7 @@
         <v>-2.76</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>70.48</v>
@@ -18886,7 +18886,7 @@
         <v>5.39</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>71.78</v>
@@ -18961,7 +18961,7 @@
         <v>-1.67</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>72.94</v>
@@ -19036,7 +19036,7 @@
         <v>3.78</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>74.17</v>
@@ -19111,7 +19111,7 @@
         <v>6.63</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>75.56999999999999</v>
@@ -19186,7 +19186,7 @@
         <v>5.84</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>77.23</v>
@@ -19261,7 +19261,7 @@
         <v>3.3</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>78.75</v>
@@ -19336,7 +19336,7 @@
         <v>3.95</v>
       </c>
       <c r="I250" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" t="n">
         <v>80.73</v>
@@ -19411,7 +19411,7 @@
         <v>-0.03</v>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" t="n">
         <v>82.56</v>
@@ -19486,7 +19486,7 @@
         <v>-28.54</v>
       </c>
       <c r="I252" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>83.11</v>
@@ -19565,7 +19565,7 @@
         <v>-3.98</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>83.45</v>
@@ -19640,7 +19640,7 @@
         <v>6.24</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>83.84</v>
@@ -19715,7 +19715,7 @@
         <v>2.88</v>
       </c>
       <c r="I255" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" t="n">
         <v>84.11</v>
@@ -19790,7 +19790,7 @@
         <v>-15.77</v>
       </c>
       <c r="I256" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19865,7 +19865,7 @@
         <v>5.25</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>83.92</v>
@@ -19940,7 +19940,7 @@
         <v>8.33</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>84.11</v>
@@ -20015,7 +20015,7 @@
         <v>-3.46</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>83.92</v>
@@ -20090,7 +20090,7 @@
         <v>4.29</v>
       </c>
       <c r="I260" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" t="n">
         <v>83.81999999999999</v>
@@ -20165,7 +20165,7 @@
         <v>-11.53</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" s="4" t="n">
         <v>82.97</v>
@@ -20240,7 +20240,7 @@
         <v>2.94</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>82.29000000000001</v>
@@ -20315,7 +20315,7 @@
         <v>-4.8</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>81.56</v>
@@ -20394,7 +20394,7 @@
         <v>5.6</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>80.8</v>
@@ -20469,7 +20469,7 @@
         <v>1.31</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>80.15000000000001</v>
@@ -20544,7 +20544,7 @@
         <v>7.9</v>
       </c>
       <c r="I266" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>79.62</v>
@@ -20619,7 +20619,7 @@
         <v>5.16</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>79.01000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>-1.85</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>78.04000000000001</v>
@@ -20769,7 +20769,7 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>76.97</v>
@@ -20844,7 +20844,7 @@
         <v>0.51</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>75.70999999999999</v>
@@ -20919,7 +20919,7 @@
         <v>5.64</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>74.68000000000001</v>
@@ -20994,7 +20994,7 @@
         <v>-4.02</v>
       </c>
       <c r="I272" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" t="n">
         <v>74.98999999999999</v>
@@ -21069,7 +21069,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I273" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21148,7 +21148,7 @@
         <v>0.88</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>75.02</v>
@@ -21223,7 +21223,7 @@
         <v>-1.42</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>74.77</v>
@@ -21302,7 +21302,7 @@
         <v>2.25</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>75.23</v>
@@ -21381,7 +21381,7 @@
         <v>3.06</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>75.64</v>
@@ -21456,7 +21456,7 @@
         <v>2.34</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>75.84</v>
@@ -21531,7 +21531,7 @@
         <v>-2.72</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>76.06</v>
@@ -21606,7 +21606,7 @@
         <v>-1.84</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>76.06</v>
@@ -21675,7 +21675,7 @@
         <v>-4.96</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>76.31</v>
@@ -21758,7 +21758,7 @@
         <v>0.73</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>76.48</v>
@@ -21833,7 +21833,7 @@
         <v>-2.13</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>76.75</v>
@@ -21908,7 +21908,7 @@
         <v>-4.13</v>
       </c>
       <c r="I284" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" t="n">
         <v>76.68000000000001</v>
@@ -21983,7 +21983,7 @@
         <v>-4.4</v>
       </c>
       <c r="I285" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" t="n">
         <v>76.41</v>
@@ -22058,7 +22058,7 @@
         <v>-6.33</v>
       </c>
       <c r="I286" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" s="4" t="n">
         <v>75.66</v>
@@ -22141,7 +22141,7 @@
         <v>1.54</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>74.75</v>
@@ -22216,7 +22216,7 @@
         <v>0.77</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>73.95</v>
@@ -22291,7 +22291,7 @@
         <v>3.59</v>
       </c>
       <c r="I289" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" t="n">
         <v>73.2</v>
@@ -22366,7 +22366,7 @@
         <v>-6.81</v>
       </c>
       <c r="I290" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>72.22</v>
@@ -22445,7 +22445,7 @@
         <v>4.39</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>71.14</v>
@@ -22524,7 +22524,7 @@
         <v>0.13</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>70.23999999999999</v>
@@ -22599,7 +22599,7 @@
         <v>7.27</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>69.91</v>
@@ -22674,7 +22674,7 @@
         <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>69.55</v>
@@ -22749,7 +22749,7 @@
         <v>-3.45</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>69.13</v>
@@ -22824,7 +22824,7 @@
         <v>0.46</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>68.64</v>
@@ -22899,7 +22899,7 @@
         <v>-0.23</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>68.02</v>
@@ -22978,7 +22978,7 @@
         <v>2.32</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>67.39</v>
@@ -23053,7 +23053,7 @@
         <v>1.36</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>66.91</v>
@@ -23128,7 +23128,7 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>66.54000000000001</v>
@@ -23203,7 +23203,7 @@
         <v>-1.16</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>66.31999999999999</v>
@@ -23278,7 +23278,7 @@
         <v>5.51</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>66.26000000000001</v>
@@ -23353,7 +23353,7 @@
         <v>-0.28</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>66.27</v>
@@ -23428,7 +23428,7 @@
         <v>-0.84</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>66.40000000000001</v>
@@ -23503,7 +23503,7 @@
         <v>3.35</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>66.8</v>
@@ -23578,7 +23578,7 @@
         <v>-2.01</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>67.33</v>
@@ -23653,7 +23653,7 @@
         <v>-5.07</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>67.63</v>
@@ -23728,7 +23728,7 @@
         <v>2.74</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>68</v>
@@ -23803,7 +23803,7 @@
         <v>-2.83</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>68.16</v>
@@ -23878,7 +23878,7 @@
         <v>0.6</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>68.56</v>
@@ -23953,7 +23953,7 @@
         <v>-0.67</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>68.8</v>
@@ -24032,7 +24032,7 @@
         <v>-3.12</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>68.94</v>
@@ -24111,7 +24111,7 @@
         <v>-2.05</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>68.77</v>
@@ -24186,7 +24186,7 @@
         <v>2.81</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>68.7</v>
@@ -24261,7 +24261,7 @@
         <v>2.45</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>68.81999999999999</v>
@@ -24336,7 +24336,7 @@
         <v>-3.44</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>68.81999999999999</v>
@@ -24415,7 +24415,7 @@
         <v>-0.05</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>68.81999999999999</v>
@@ -24490,7 +24490,7 @@
         <v>6.4</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>68.95</v>
@@ -24565,7 +24565,7 @@
         <v>2.1</v>
       </c>
       <c r="I319" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" t="n">
         <v>69.11</v>
@@ -24640,7 +24640,7 @@
         <v>1.97</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>69.31</v>
@@ -24715,7 +24715,7 @@
         <v>6.83</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>69.79000000000001</v>
@@ -24790,7 +24790,7 @@
         <v>0.71</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>70.12</v>
@@ -24865,7 +24865,7 @@
         <v>1.02</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>70.48999999999999</v>
@@ -24940,7 +24940,7 @@
         <v>-4.84</v>
       </c>
       <c r="I324" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" t="n">
         <v>70.70999999999999</v>
@@ -25015,7 +25015,7 @@
         <v>-8.57</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>70.48</v>
@@ -25094,7 +25094,7 @@
         <v>1.3</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>70.37</v>
@@ -25169,7 +25169,7 @@
         <v>-4.35</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.29000000000001</v>
@@ -25244,7 +25244,7 @@
         <v>2.74</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.20999999999999</v>
@@ -25319,7 +25319,7 @@
         <v>1.05</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>70.26000000000001</v>
@@ -25394,7 +25394,7 @@
         <v>-1.57</v>
       </c>
       <c r="I330" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" t="n">
         <v>70.23999999999999</v>
@@ -25469,7 +25469,7 @@
         <v>1.99</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.31</v>
@@ -25544,7 +25544,7 @@
         <v>-3.18</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.37</v>
@@ -25619,7 +25619,7 @@
         <v>1.27</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>70.55</v>
@@ -25694,7 +25694,7 @@
         <v>-0.04</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>70.63</v>
@@ -25769,7 +25769,7 @@
         <v>-0.97</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>70.59999999999999</v>
@@ -25844,7 +25844,7 @@
         <v>0.47</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>70.7</v>
@@ -25919,7 +25919,7 @@
         <v>-2.62</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>70.72</v>
@@ -25994,7 +25994,7 @@
         <v>1.16</v>
       </c>
       <c r="I338" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" t="n">
         <v>70.56</v>
@@ -26069,7 +26069,7 @@
         <v>-8.08</v>
       </c>
       <c r="I339" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>70.06</v>
@@ -26144,7 +26144,7 @@
         <v>0.02</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>69.48999999999999</v>
@@ -26219,7 +26219,7 @@
         <v>-4.17</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>68.54000000000001</v>
@@ -26298,7 +26298,7 @@
         <v>-2.29</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>67.48999999999999</v>
@@ -26377,7 +26377,7 @@
         <v>5.48</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>66.56999999999999</v>
@@ -26452,7 +26452,7 @@
         <v>0.77</v>
       </c>
       <c r="I344" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" t="n">
         <v>65.86</v>
@@ -26527,7 +26527,7 @@
         <v>3.56</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>65.58</v>
@@ -26602,7 +26602,7 @@
         <v>-0.13</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>65.25</v>
@@ -26677,10 +26677,10 @@
         <v>-4.39</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
-        <v>64.94</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K347" t="n">
         <v>67.62</v>
@@ -26752,7 +26752,7 @@
         <v>-1.81</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>64.47</v>
@@ -26827,7 +26827,7 @@
         <v>-1.01</v>
       </c>
       <c r="I349" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" t="n">
         <v>63.95</v>
@@ -26902,7 +26902,7 @@
         <v>-5.4</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>63.32</v>
@@ -26981,7 +26981,7 @@
         <v>-7.09</v>
       </c>
       <c r="I351" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" s="4" t="n">
         <v>62.42</v>
@@ -27060,7 +27060,7 @@
         <v>1.12</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>61.66</v>
@@ -27139,7 +27139,7 @@
         <v>1.76</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>60.91</v>
@@ -27214,7 +27214,7 @@
         <v>-1.13</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>60.12</v>
@@ -27289,7 +27289,7 @@
         <v>1.5</v>
       </c>
       <c r="I355" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" t="n">
         <v>59.42</v>
@@ -27364,7 +27364,7 @@
         <v>0.21</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>58.69</v>
@@ -27439,7 +27439,7 @@
         <v>2.69</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>58.14</v>
@@ -27514,7 +27514,7 @@
         <v>1.98</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>57.59</v>
@@ -27589,7 +27589,7 @@
         <v>-2.94</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>57.24</v>
@@ -27668,7 +27668,7 @@
         <v>-2.99</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>56.8</v>
@@ -27747,10 +27747,10 @@
         <v>2.48</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="K361" t="n">
         <v>64.95999999999999</v>
@@ -27822,7 +27822,7 @@
         <v>-0.35</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>56.37</v>
@@ -27897,7 +27897,7 @@
         <v>-3.32</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>55.94</v>
@@ -27972,7 +27972,7 @@
         <v>1.94</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>55.53</v>
@@ -28047,7 +28047,7 @@
         <v>-1.81</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>54.97</v>
@@ -28122,7 +28122,7 @@
         <v>-3.49</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>54.32</v>
@@ -28197,7 +28197,7 @@
         <v>0.77</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>53.83</v>
@@ -28272,7 +28272,7 @@
         <v>0.39</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>53.4</v>
@@ -28347,7 +28347,7 @@
         <v>4.12</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>53.11</v>
@@ -28422,7 +28422,7 @@
         <v>1.58</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>53.02</v>
@@ -28497,7 +28497,7 @@
         <v>-3.45</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>53.03</v>
@@ -28576,7 +28576,7 @@
         <v>1.02</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>53.04</v>
@@ -28651,7 +28651,7 @@
         <v>0.65</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>53.03</v>
@@ -28726,7 +28726,7 @@
         <v>-2.32</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>52.98</v>
@@ -28801,7 +28801,7 @@
         <v>0.14</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>52.89</v>
@@ -28876,7 +28876,7 @@
         <v>3.34</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>52.89</v>
@@ -28951,7 +28951,7 @@
         <v>-2.13</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>52.75</v>
@@ -29030,7 +29030,7 @@
         <v>0.19</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>52.57</v>
@@ -29105,7 +29105,7 @@
         <v>2.63</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>52.54</v>
@@ -29180,7 +29180,7 @@
         <v>4.14</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>52.7</v>
@@ -29255,7 +29255,7 @@
         <v>-0.39</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>52.79</v>
@@ -29330,7 +29330,7 @@
         <v>2.95</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>52.97</v>
@@ -29405,7 +29405,7 @@
         <v>3.32</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>53.33</v>
@@ -29480,7 +29480,7 @@
         <v>-1.45</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>53.6</v>
@@ -29555,7 +29555,7 @@
         <v>0.87</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>53.94</v>
@@ -29630,7 +29630,7 @@
         <v>-1.52</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>54.33</v>
@@ -29705,7 +29705,7 @@
         <v>0.55</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>54.71</v>
@@ -29780,7 +29780,7 @@
         <v>1.86</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>55.14</v>
@@ -29855,7 +29855,7 @@
         <v>-3.58</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>55.36</v>
@@ -29934,7 +29934,7 @@
         <v>4.47</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>55.67</v>
@@ -30009,7 +30009,7 @@
         <v>2.75</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>56.15</v>
@@ -30084,7 +30084,7 @@
         <v>1.72</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>56.65</v>
@@ -30159,7 +30159,7 @@
         <v>-0.83</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>57.12</v>
@@ -30234,7 +30234,7 @@
         <v>0.19</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>57.65</v>
@@ -30309,7 +30309,7 @@
         <v>-1.17</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>58.14</v>
@@ -30384,7 +30384,7 @@
         <v>1.92</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>58.6</v>
@@ -30459,7 +30459,7 @@
         <v>-4.38</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>58.98</v>
@@ -30534,7 +30534,7 @@
         <v>0.18</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>59.37</v>
@@ -30609,7 +30609,7 @@
         <v>-3.68</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>59.57</v>
@@ -30688,7 +30688,7 @@
         <v>1.99</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>59.72</v>
@@ -30763,7 +30763,7 @@
         <v>2.51</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>59.96</v>
@@ -30838,7 +30838,7 @@
         <v>-1.21</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>60.07</v>
@@ -30917,7 +30917,7 @@
         <v>-0.75</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>60.07</v>
@@ -30992,7 +30992,7 @@
         <v>2.27</v>
       </c>
       <c r="I404" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" t="n">
         <v>60.18</v>
@@ -31067,7 +31067,7 @@
         <v>-5.3</v>
       </c>
       <c r="I405" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>60.1</v>
@@ -31146,7 +31146,7 @@
         <v>1.08</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>60.1</v>
@@ -31221,7 +31221,7 @@
         <v>-2.2</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>60.02</v>
@@ -31296,7 +31296,7 @@
         <v>1.21</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>59.92</v>
@@ -31371,7 +31371,7 @@
         <v>-0.83</v>
       </c>
       <c r="I409" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" t="n">
         <v>59.9</v>
@@ -31446,7 +31446,7 @@
         <v>3.37</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>59.84</v>
@@ -31521,7 +31521,7 @@
         <v>1.63</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>59.76</v>
@@ -31590,13 +31590,13 @@
         <v>59.63</v>
       </c>
       <c r="G412" t="n">
-        <v>10657000</v>
+        <v>10799200</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.5</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>59.6</v>
@@ -31656,28 +31656,28 @@
         <v>59.31</v>
       </c>
       <c r="D413" t="n">
-        <v>60.61</v>
+        <v>61</v>
       </c>
       <c r="E413" t="n">
         <v>59.05</v>
       </c>
       <c r="F413" t="n">
-        <v>60.38</v>
+        <v>60.73</v>
       </c>
       <c r="G413" t="n">
-        <v>9603923</v>
+        <v>15323871</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>1.26</v>
+        <v>1.84</v>
       </c>
       <c r="I413" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J413" t="n">
-        <v>59.51</v>
+        <v>59.53</v>
       </c>
       <c r="K413" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="L413" t="n">
         <v>61.65</v>
@@ -31686,10 +31686,10 @@
         <v>65.87</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>58</v>
+        <v>58.93</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31703,16 +31703,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31611,19 +31611,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31574,31 +31574,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>59</v>
+      </c>
+      <c r="D412" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="E412" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="F412" t="n">
+        <v>58.32</v>
+      </c>
       <c r="G412" t="n">
-        <v>15323871</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>9112108</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>-2.2</v>
       </c>
       <c r="I412" t="n">
         <v>5.1</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>59.41</v>
+      </c>
+      <c r="K412" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="L412" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="M412" t="n">
+        <v>65.86</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>55.84</v>
+        <v>51.25</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31610,10 +31626,20 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>27.75</v>
@@ -683,7 +683,7 @@
         <v>1.92</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>27.87</v>
@@ -758,7 +758,7 @@
         <v>0.44</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.97</v>
@@ -833,7 +833,7 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>28.07</v>
@@ -908,7 +908,7 @@
         <v>-1.19</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>28.16</v>
@@ -983,7 +983,7 @@
         <v>0.59</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>28.24</v>
@@ -1058,7 +1058,7 @@
         <v>-0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>28.34</v>
@@ -1133,7 +1133,7 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>28.44</v>
@@ -1208,7 +1208,7 @@
         <v>0.41</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>28.52</v>
@@ -1283,7 +1283,7 @@
         <v>-0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>28.58</v>
@@ -1358,7 +1358,7 @@
         <v>2.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>28.7</v>
@@ -1433,7 +1433,7 @@
         <v>-0.33</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>28.79</v>
@@ -1508,7 +1508,7 @@
         <v>0.47</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>28.88</v>
@@ -1583,7 +1583,7 @@
         <v>-1.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>28.97</v>
@@ -1658,7 +1658,7 @@
         <v>-0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>29.05</v>
@@ -1733,7 +1733,7 @@
         <v>-2.07</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>29.12</v>
@@ -1812,7 +1812,7 @@
         <v>0.38</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>29.18</v>
@@ -1887,7 +1887,7 @@
         <v>-1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>29.2</v>
@@ -1962,7 +1962,7 @@
         <v>-0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>29.18</v>
@@ -2041,7 +2041,7 @@
         <v>1.55</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>29.19</v>
@@ -2116,7 +2116,7 @@
         <v>0.87</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>29.21</v>
@@ -2191,7 +2191,7 @@
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>29.24</v>
@@ -2266,7 +2266,7 @@
         <v>-0.27</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>29.26</v>
@@ -2341,7 +2341,7 @@
         <v>-0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>29.27</v>
@@ -2416,7 +2416,7 @@
         <v>-1.62</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>29.27</v>
@@ -2499,7 +2499,7 @@
         <v>2.92</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>29.31</v>
@@ -2578,7 +2578,7 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>29.37</v>
@@ -2653,7 +2653,7 @@
         <v>1.72</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.44</v>
@@ -2728,7 +2728,7 @@
         <v>-0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.5</v>
@@ -2803,7 +2803,7 @@
         <v>0.33</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.58</v>
@@ -2878,7 +2878,7 @@
         <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.62</v>
@@ -2953,7 +2953,7 @@
         <v>-0.32</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.67</v>
@@ -3028,7 +3028,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.7</v>
@@ -3103,7 +3103,7 @@
         <v>-1.57</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.72</v>
@@ -3178,7 +3178,7 @@
         <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.75</v>
@@ -3253,7 +3253,7 @@
         <v>2.07</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.83</v>
@@ -3328,7 +3328,7 @@
         <v>-0.16</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.91</v>
@@ -3403,7 +3403,7 @@
         <v>2.59</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>30.06</v>
@@ -3478,7 +3478,7 @@
         <v>-1.02</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>30.19</v>
@@ -3553,7 +3553,7 @@
         <v>-0.03</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>30.3</v>
@@ -3628,7 +3628,7 @@
         <v>-1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>30.39</v>
@@ -3703,7 +3703,7 @@
         <v>0.42</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>30.44</v>
@@ -3778,7 +3778,7 @@
         <v>-6.08</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30.4</v>
@@ -3861,7 +3861,7 @@
         <v>-6.27</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30.27</v>
@@ -3944,7 +3944,7 @@
         <v>0.22</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>30.17</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>30.03</v>
@@ -4110,7 +4110,7 @@
         <v>3.39</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>29.92</v>
@@ -4189,7 +4189,7 @@
         <v>0.78</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>29.8</v>
@@ -4268,7 +4268,7 @@
         <v>3.22</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4347,7 +4347,7 @@
         <v>0.65</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>29.65</v>
@@ -4422,7 +4422,7 @@
         <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>29.58</v>
@@ -4497,7 +4497,7 @@
         <v>1.19</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>29.53</v>
@@ -4576,7 +4576,7 @@
         <v>-0.71</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.48</v>
@@ -4655,7 +4655,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.47</v>
@@ -4730,7 +4730,7 @@
         <v>-0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.45</v>
@@ -4805,7 +4805,7 @@
         <v>3.59</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.45</v>
@@ -4884,13 +4884,13 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.45</v>
       </c>
       <c r="K58" t="n">
-        <v>29.52</v>
+        <v>29.51</v>
       </c>
       <c r="L58" t="n">
         <v>28.72</v>
@@ -4959,7 +4959,7 @@
         <v>-1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.39</v>
@@ -5034,7 +5034,7 @@
         <v>0.47</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.35</v>
@@ -5109,7 +5109,7 @@
         <v>-1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.29</v>
@@ -5184,7 +5184,7 @@
         <v>-0.77</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.24</v>
@@ -5263,7 +5263,7 @@
         <v>-0.71</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.17</v>
@@ -5338,7 +5338,7 @@
         <v>-0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.18</v>
@@ -5417,7 +5417,7 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.3</v>
@@ -5492,7 +5492,7 @@
         <v>2.51</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>29.45</v>
@@ -5567,7 +5567,7 @@
         <v>-2.42</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>29.57</v>
@@ -5646,7 +5646,7 @@
         <v>-0.1</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>29.64</v>
@@ -5721,7 +5721,7 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>29.72</v>
@@ -5796,7 +5796,7 @@
         <v>-0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>29.74</v>
@@ -5875,13 +5875,13 @@
         <v>1.01</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>29.77</v>
       </c>
       <c r="K71" t="n">
-        <v>29.66</v>
+        <v>29.67</v>
       </c>
       <c r="L71" t="n">
         <v>28.82</v>
@@ -5950,7 +5950,7 @@
         <v>-2.27</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>29.76</v>
@@ -6029,7 +6029,7 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>29.75</v>
@@ -6104,7 +6104,7 @@
         <v>-1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>29.74</v>
@@ -6179,7 +6179,7 @@
         <v>0.41</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6254,7 +6254,7 @@
         <v>2.41</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>29.75</v>
@@ -6329,7 +6329,7 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>29.75</v>
@@ -6404,7 +6404,7 @@
         <v>-1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>29.72</v>
@@ -6479,7 +6479,7 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6554,7 +6554,7 @@
         <v>-0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6629,7 +6629,7 @@
         <v>-0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>29.75</v>
@@ -6704,7 +6704,7 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>29.79</v>
@@ -6779,7 +6779,7 @@
         <v>-0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>29.82</v>
@@ -6854,7 +6854,7 @@
         <v>5.3</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>29.94</v>
@@ -6929,7 +6929,7 @@
         <v>-0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>30.04</v>
@@ -7004,7 +7004,7 @@
         <v>-0.32</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>30.09</v>
@@ -7079,7 +7079,7 @@
         <v>3.54</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>30.24</v>
@@ -7154,7 +7154,7 @@
         <v>0.74</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>30.4</v>
@@ -7229,7 +7229,7 @@
         <v>2.14</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>30.58</v>
@@ -7304,7 +7304,7 @@
         <v>-0.48</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>30.76</v>
@@ -7379,7 +7379,7 @@
         <v>-0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>30.91</v>
@@ -7454,7 +7454,7 @@
         <v>0.33</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>31.1</v>
@@ -7529,7 +7529,7 @@
         <v>-0.27</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>31.27</v>
@@ -7604,7 +7604,7 @@
         <v>0.18</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>31.46</v>
@@ -7679,7 +7679,7 @@
         <v>2.15</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>31.68</v>
@@ -7754,7 +7754,7 @@
         <v>-1.39</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>31.83</v>
@@ -7829,7 +7829,7 @@
         <v>-1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>31.94</v>
@@ -7904,7 +7904,7 @@
         <v>0.73</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>32.09</v>
@@ -7979,7 +7979,7 @@
         <v>-1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>32.2</v>
@@ -8054,7 +8054,7 @@
         <v>1.23</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>32.34</v>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>32.5</v>
@@ -8204,7 +8204,7 @@
         <v>-2.16</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>32.62</v>
@@ -8279,7 +8279,7 @@
         <v>0.58</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>32.76</v>
@@ -8354,7 +8354,7 @@
         <v>-0.24</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>32.82</v>
@@ -8433,7 +8433,7 @@
         <v>1.56</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>32.91</v>
@@ -8508,7 +8508,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>33.02</v>
@@ -8583,7 +8583,7 @@
         <v>-0.24</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>33.07</v>
@@ -8658,7 +8658,7 @@
         <v>-0.42</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>33.1</v>
@@ -8733,7 +8733,7 @@
         <v>-0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>33.08</v>
@@ -8812,7 +8812,7 @@
         <v>2.27</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>33.1</v>
@@ -8887,7 +8887,7 @@
         <v>3.79</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>33.21</v>
@@ -8962,7 +8962,7 @@
         <v>-1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>33.28</v>
@@ -9037,7 +9037,7 @@
         <v>-1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>33.35</v>
@@ -9112,7 +9112,7 @@
         <v>0.44</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>33.42</v>
@@ -9187,7 +9187,7 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>33.46</v>
@@ -9262,7 +9262,7 @@
         <v>-0.12</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>33.53</v>
@@ -9337,7 +9337,7 @@
         <v>2.14</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>33.66</v>
@@ -9412,7 +9412,7 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>33.8</v>
@@ -9487,7 +9487,7 @@
         <v>-0.08</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>33.95</v>
@@ -9562,7 +9562,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>34.08</v>
@@ -9637,7 +9637,7 @@
         <v>-2.34</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>34.14</v>
@@ -9712,10 +9712,10 @@
         <v>-0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="K122" t="n">
         <v>32.22</v>
@@ -9787,7 +9787,7 @@
         <v>0.06</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>34.34</v>
@@ -9862,7 +9862,7 @@
         <v>-3.32</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>34.38</v>
@@ -9941,7 +9941,7 @@
         <v>-0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.38</v>
@@ -10091,7 +10091,7 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.41</v>
@@ -10166,10 +10166,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="K128" t="n">
         <v>32.65</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>34.53</v>
@@ -10316,7 +10316,7 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>34.58</v>
@@ -10391,7 +10391,7 @@
         <v>0.35</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>34.58</v>
@@ -10466,7 +10466,7 @@
         <v>-2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>34.55</v>
@@ -10545,7 +10545,7 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>34.56</v>
@@ -10620,7 +10620,7 @@
         <v>1.71</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>34.59</v>
@@ -10695,7 +10695,7 @@
         <v>-1.43</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10849,7 +10849,7 @@
         <v>0.14</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>34.54</v>
@@ -10924,7 +10924,7 @@
         <v>-1.97</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>34.44</v>
@@ -11003,7 +11003,7 @@
         <v>1.65</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>34.38</v>
@@ -11078,7 +11078,7 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>34.34</v>
@@ -11153,7 +11153,7 @@
         <v>2.11</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>34.37</v>
@@ -11228,7 +11228,7 @@
         <v>-0.91</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>34.39</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>34.41</v>
@@ -11378,7 +11378,7 @@
         <v>-0.09</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>34.48</v>
@@ -11453,7 +11453,7 @@
         <v>1.51</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>34.59</v>
@@ -11528,7 +11528,7 @@
         <v>1.89</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>34.72</v>
@@ -11603,7 +11603,7 @@
         <v>2.65</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>34.88</v>
@@ -11678,7 +11678,7 @@
         <v>0.51</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>35.03</v>
@@ -11753,7 +11753,7 @@
         <v>-1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>35.16</v>
@@ -11828,7 +11828,7 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>35.28</v>
@@ -11903,7 +11903,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>35.41</v>
@@ -11978,7 +11978,7 @@
         <v>-0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>35.56</v>
@@ -12053,7 +12053,7 @@
         <v>0.62</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>35.71</v>
@@ -12128,7 +12128,7 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>35.85</v>
@@ -12203,7 +12203,7 @@
         <v>1.46</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>36.04</v>
@@ -12278,7 +12278,7 @@
         <v>1.1</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>36.26</v>
@@ -12353,7 +12353,7 @@
         <v>-0.41</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>36.46</v>
@@ -12428,7 +12428,7 @@
         <v>-2.1</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>36.66</v>
@@ -12503,7 +12503,7 @@
         <v>0.53</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>36.83</v>
@@ -12578,7 +12578,7 @@
         <v>2.76</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>37.06</v>
@@ -12653,7 +12653,7 @@
         <v>2.56</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>37.29</v>
@@ -12728,7 +12728,7 @@
         <v>-0.2</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>37.54</v>
@@ -12803,7 +12803,7 @@
         <v>-0.35</v>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>37.78</v>
@@ -12878,7 +12878,7 @@
         <v>3.04</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>38.08</v>
@@ -12953,7 +12953,7 @@
         <v>2.02</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>38.4</v>
@@ -13028,7 +13028,7 @@
         <v>1.53</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>38.71</v>
@@ -13103,7 +13103,7 @@
         <v>-0.31</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>38.97</v>
@@ -13178,7 +13178,7 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>39.25</v>
@@ -13253,7 +13253,7 @@
         <v>-0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>39.53</v>
@@ -13328,7 +13328,7 @@
         <v>2.33</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>39.85</v>
@@ -13403,7 +13403,7 @@
         <v>1.24</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>40.17</v>
@@ -13478,7 +13478,7 @@
         <v>-1.52</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>40.49</v>
@@ -13553,7 +13553,7 @@
         <v>2.7</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>40.84</v>
@@ -13628,7 +13628,7 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>41.19</v>
@@ -13703,7 +13703,7 @@
         <v>1.61</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>41.54</v>
@@ -13778,7 +13778,7 @@
         <v>4.03</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>41.97</v>
@@ -13853,7 +13853,7 @@
         <v>-0.97</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>42.38</v>
@@ -13928,7 +13928,7 @@
         <v>3.27</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>42.91</v>
@@ -14003,7 +14003,7 @@
         <v>1.74</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>43.46</v>
@@ -14078,7 +14078,7 @@
         <v>-4.43</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>43.86</v>
@@ -14153,7 +14153,7 @@
         <v>1.55</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>44.25</v>
@@ -14228,7 +14228,7 @@
         <v>-8.24</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>44.44</v>
@@ -14307,7 +14307,7 @@
         <v>0.21</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>44.64</v>
@@ -14382,7 +14382,7 @@
         <v>0.68</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>44.8</v>
@@ -14457,7 +14457,7 @@
         <v>-0.43</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>44.9</v>
@@ -14532,7 +14532,7 @@
         <v>-3.61</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>44.9</v>
@@ -14607,7 +14607,7 @@
         <v>0.71</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>44.92</v>
@@ -14682,7 +14682,7 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>44.93</v>
@@ -14757,7 +14757,7 @@
         <v>2.57</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>45.02</v>
@@ -14832,7 +14832,7 @@
         <v>-0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>45.05</v>
@@ -14907,7 +14907,7 @@
         <v>-0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>45.03</v>
@@ -14982,7 +14982,7 @@
         <v>-2.33</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>45</v>
@@ -15057,7 +15057,7 @@
         <v>2.13</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>44.95</v>
@@ -15132,7 +15132,7 @@
         <v>-0.23</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>44.9</v>
@@ -15207,7 +15207,7 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>44.82</v>
@@ -15282,7 +15282,7 @@
         <v>4.26</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>44.75</v>
@@ -15357,7 +15357,7 @@
         <v>1.44</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>44.73</v>
@@ -15432,7 +15432,7 @@
         <v>4.03</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>44.73</v>
@@ -15507,7 +15507,7 @@
         <v>-1.86</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>44.64</v>
@@ -15582,7 +15582,7 @@
         <v>-3.08</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>44.59</v>
@@ -15657,7 +15657,7 @@
         <v>-1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>44.48</v>
@@ -15732,7 +15732,7 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>44.59</v>
@@ -15807,7 +15807,7 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>44.72</v>
@@ -15882,7 +15882,7 @@
         <v>-1.44</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>44.8</v>
@@ -15961,7 +15961,7 @@
         <v>-1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>44.87</v>
@@ -16036,7 +16036,7 @@
         <v>2.94</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>45.08</v>
@@ -16111,7 +16111,7 @@
         <v>0.09</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>45.28</v>
@@ -16186,7 +16186,7 @@
         <v>3.71</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>45.54</v>
@@ -16261,7 +16261,7 @@
         <v>5.81</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>45.88</v>
@@ -16336,7 +16336,7 @@
         <v>2.56</v>
       </c>
       <c r="I210" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>46.3</v>
@@ -16411,7 +16411,7 @@
         <v>1.16</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>46.77</v>
@@ -16486,7 +16486,7 @@
         <v>-0.11</v>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>47.29</v>
@@ -16561,7 +16561,7 @@
         <v>-2.47</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>47.7</v>
@@ -16636,7 +16636,7 @@
         <v>2.3</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>48.16</v>
@@ -16711,7 +16711,7 @@
         <v>-0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>48.6</v>
@@ -16786,7 +16786,7 @@
         <v>4.67</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>49.07</v>
@@ -16861,7 +16861,7 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>49.55</v>
@@ -16936,7 +16936,7 @@
         <v>2.76</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>50.02</v>
@@ -17011,7 +17011,7 @@
         <v>-2.64</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>50.45</v>
@@ -17086,7 +17086,7 @@
         <v>3.58</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>51.06</v>
@@ -17161,7 +17161,7 @@
         <v>-0.65</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>51.67</v>
@@ -17236,7 +17236,7 @@
         <v>4.38</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>52.38</v>
@@ -17311,7 +17311,7 @@
         <v>-1.56</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>53.03</v>
@@ -17386,7 +17386,7 @@
         <v>2.71</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>53.78</v>
@@ -17461,7 +17461,7 @@
         <v>2.53</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>54.64</v>
@@ -17536,7 +17536,7 @@
         <v>3.79</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>55.55</v>
@@ -17611,7 +17611,7 @@
         <v>0.59</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>56.48</v>
@@ -17686,7 +17686,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>57.62</v>
@@ -17761,7 +17761,7 @@
         <v>-7.19</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>58.36</v>
@@ -17836,7 +17836,7 @@
         <v>4.5</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>59.18</v>
@@ -17911,7 +17911,7 @@
         <v>-6.61</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>59.74</v>
@@ -17986,7 +17986,7 @@
         <v>2.06</v>
       </c>
       <c r="I232" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>60.38</v>
@@ -18061,7 +18061,7 @@
         <v>5.06</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>61.24</v>
@@ -18136,7 +18136,7 @@
         <v>6.7</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>62.28</v>
@@ -18211,7 +18211,7 @@
         <v>-3.73</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>63.19</v>
@@ -18286,7 +18286,7 @@
         <v>-1.76</v>
       </c>
       <c r="I236" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>63.92</v>
@@ -18361,7 +18361,7 @@
         <v>3.83</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>64.73999999999999</v>
@@ -18436,7 +18436,7 @@
         <v>6.7</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>65.72</v>
@@ -18511,7 +18511,7 @@
         <v>1.77</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>66.84</v>
@@ -18586,7 +18586,7 @@
         <v>7.58</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>68.16</v>
@@ -18661,7 +18661,7 @@
         <v>-1.47</v>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>69.44</v>
@@ -18736,7 +18736,7 @@
         <v>-2.76</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>70.48</v>
@@ -18811,7 +18811,7 @@
         <v>5.39</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>71.78</v>
@@ -18886,7 +18886,7 @@
         <v>-1.67</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>72.94</v>
@@ -18961,7 +18961,7 @@
         <v>3.78</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>74.17</v>
@@ -19036,7 +19036,7 @@
         <v>6.63</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>75.56999999999999</v>
@@ -19111,7 +19111,7 @@
         <v>5.84</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>77.23</v>
@@ -19186,7 +19186,7 @@
         <v>3.3</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>78.75</v>
@@ -19261,7 +19261,7 @@
         <v>3.95</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>80.73</v>
@@ -19336,7 +19336,7 @@
         <v>-0.03</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>82.56</v>
@@ -19411,7 +19411,7 @@
         <v>-28.54</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>83.11</v>
@@ -19490,7 +19490,7 @@
         <v>-3.98</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>83.45</v>
@@ -19565,7 +19565,7 @@
         <v>6.24</v>
       </c>
       <c r="I253" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>83.84</v>
@@ -19640,7 +19640,7 @@
         <v>2.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>84.11</v>
@@ -19715,7 +19715,7 @@
         <v>-15.77</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19790,7 +19790,7 @@
         <v>5.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>83.92</v>
@@ -19865,7 +19865,7 @@
         <v>8.33</v>
       </c>
       <c r="I257" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>84.11</v>
@@ -19940,7 +19940,7 @@
         <v>-3.46</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>83.92</v>
@@ -20015,7 +20015,7 @@
         <v>4.29</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>83.81999999999999</v>
@@ -20090,7 +20090,7 @@
         <v>-11.53</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>82.97</v>
@@ -20165,7 +20165,7 @@
         <v>2.94</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>82.29000000000001</v>
@@ -20240,7 +20240,7 @@
         <v>-4.8</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>81.56</v>
@@ -20319,7 +20319,7 @@
         <v>5.6</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>80.8</v>
@@ -20394,7 +20394,7 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>80.15000000000001</v>
@@ -20469,7 +20469,7 @@
         <v>7.9</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>79.62</v>
@@ -20544,7 +20544,7 @@
         <v>5.16</v>
       </c>
       <c r="I266" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" t="n">
         <v>79.01000000000001</v>
@@ -20619,7 +20619,7 @@
         <v>-1.85</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>78.04000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>76.97</v>
@@ -20769,7 +20769,7 @@
         <v>0.51</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>75.70999999999999</v>
@@ -20844,7 +20844,7 @@
         <v>5.64</v>
       </c>
       <c r="I270" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>74.68000000000001</v>
@@ -20919,7 +20919,7 @@
         <v>-4.02</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>74.98999999999999</v>
@@ -20994,7 +20994,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I272" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21073,7 +21073,7 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>75.02</v>
@@ -21148,7 +21148,7 @@
         <v>-1.42</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>74.77</v>
@@ -21227,7 +21227,7 @@
         <v>2.25</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>75.23</v>
@@ -21306,7 +21306,7 @@
         <v>3.06</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>75.64</v>
@@ -21381,7 +21381,7 @@
         <v>2.34</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>75.84</v>
@@ -21456,7 +21456,7 @@
         <v>-2.72</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>76.06</v>
@@ -21531,7 +21531,7 @@
         <v>-1.84</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>76.06</v>
@@ -21600,7 +21600,7 @@
         <v>-4.96</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>76.31</v>
@@ -21683,7 +21683,7 @@
         <v>0.73</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>76.48</v>
@@ -21758,7 +21758,7 @@
         <v>-2.13</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>76.75</v>
@@ -21833,7 +21833,7 @@
         <v>-4.13</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>76.68000000000001</v>
@@ -21908,7 +21908,7 @@
         <v>-4.4</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>76.41</v>
@@ -21983,7 +21983,7 @@
         <v>-6.33</v>
       </c>
       <c r="I285" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" s="4" t="n">
         <v>75.66</v>
@@ -22066,7 +22066,7 @@
         <v>1.54</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>74.75</v>
@@ -22141,7 +22141,7 @@
         <v>0.77</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>73.95</v>
@@ -22216,7 +22216,7 @@
         <v>3.59</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>73.2</v>
@@ -22291,7 +22291,7 @@
         <v>-6.81</v>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>72.22</v>
@@ -22370,7 +22370,7 @@
         <v>4.39</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>71.14</v>
@@ -22449,7 +22449,7 @@
         <v>0.13</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>70.23999999999999</v>
@@ -22524,7 +22524,7 @@
         <v>7.27</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>69.91</v>
@@ -22599,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>69.55</v>
@@ -22674,7 +22674,7 @@
         <v>-3.45</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>69.13</v>
@@ -22749,7 +22749,7 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>68.64</v>
@@ -22824,7 +22824,7 @@
         <v>-0.23</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>68.02</v>
@@ -22903,7 +22903,7 @@
         <v>2.32</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>67.39</v>
@@ -22978,7 +22978,7 @@
         <v>1.36</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>66.91</v>
@@ -23053,7 +23053,7 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>66.54000000000001</v>
@@ -23128,7 +23128,7 @@
         <v>-1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>66.31999999999999</v>
@@ -23203,7 +23203,7 @@
         <v>5.51</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>66.26000000000001</v>
@@ -23278,7 +23278,7 @@
         <v>-0.28</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>66.27</v>
@@ -23353,7 +23353,7 @@
         <v>-0.84</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>66.40000000000001</v>
@@ -23428,7 +23428,7 @@
         <v>3.35</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>66.8</v>
@@ -23503,7 +23503,7 @@
         <v>-2.01</v>
       </c>
       <c r="I305" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>67.33</v>
@@ -23578,7 +23578,7 @@
         <v>-5.07</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>67.63</v>
@@ -23653,7 +23653,7 @@
         <v>2.74</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>68</v>
@@ -23728,7 +23728,7 @@
         <v>-2.83</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>68.16</v>
@@ -23803,7 +23803,7 @@
         <v>0.6</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>68.56</v>
@@ -23878,7 +23878,7 @@
         <v>-0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>68.8</v>
@@ -23957,7 +23957,7 @@
         <v>-3.12</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>68.94</v>
@@ -24036,7 +24036,7 @@
         <v>-2.05</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>68.77</v>
@@ -24111,7 +24111,7 @@
         <v>2.81</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>68.7</v>
@@ -24186,7 +24186,7 @@
         <v>2.45</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>68.81999999999999</v>
@@ -24261,7 +24261,7 @@
         <v>-3.44</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>68.81999999999999</v>
@@ -24340,7 +24340,7 @@
         <v>-0.05</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>68.81999999999999</v>
@@ -24415,7 +24415,7 @@
         <v>6.4</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>68.95</v>
@@ -24490,7 +24490,7 @@
         <v>2.1</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>69.11</v>
@@ -24565,7 +24565,7 @@
         <v>1.97</v>
       </c>
       <c r="I319" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>69.31</v>
@@ -24640,7 +24640,7 @@
         <v>6.83</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>69.79000000000001</v>
@@ -24715,7 +24715,7 @@
         <v>0.71</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>70.12</v>
@@ -24790,7 +24790,7 @@
         <v>1.02</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>70.48999999999999</v>
@@ -24865,7 +24865,7 @@
         <v>-4.84</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>70.70999999999999</v>
@@ -24940,7 +24940,7 @@
         <v>-8.57</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>70.48</v>
@@ -25019,7 +25019,7 @@
         <v>1.3</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>70.37</v>
@@ -25094,7 +25094,7 @@
         <v>-4.35</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>70.29000000000001</v>
@@ -25169,7 +25169,7 @@
         <v>2.74</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>70.20999999999999</v>
@@ -25244,7 +25244,7 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>70.26000000000001</v>
@@ -25319,7 +25319,7 @@
         <v>-1.57</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>70.23999999999999</v>
@@ -25394,7 +25394,7 @@
         <v>1.99</v>
       </c>
       <c r="I330" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" t="n">
         <v>70.31</v>
@@ -25469,7 +25469,7 @@
         <v>-3.18</v>
       </c>
       <c r="I331" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" t="n">
         <v>70.37</v>
@@ -25544,7 +25544,7 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>70.55</v>
@@ -25619,7 +25619,7 @@
         <v>-0.04</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>70.63</v>
@@ -25694,7 +25694,7 @@
         <v>-0.97</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>70.59999999999999</v>
@@ -25769,7 +25769,7 @@
         <v>0.47</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>70.7</v>
@@ -25844,7 +25844,7 @@
         <v>-2.62</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>70.72</v>
@@ -25919,7 +25919,7 @@
         <v>1.16</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>70.56</v>
@@ -25994,7 +25994,7 @@
         <v>-8.08</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>70.06</v>
@@ -26069,7 +26069,7 @@
         <v>0.02</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>69.48999999999999</v>
@@ -26144,7 +26144,7 @@
         <v>-4.17</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>68.54000000000001</v>
@@ -26223,7 +26223,7 @@
         <v>-2.29</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>67.48999999999999</v>
@@ -26302,7 +26302,7 @@
         <v>5.48</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>66.56999999999999</v>
@@ -26377,7 +26377,7 @@
         <v>0.77</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>65.86</v>
@@ -26452,7 +26452,7 @@
         <v>3.56</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>65.58</v>
@@ -26527,7 +26527,7 @@
         <v>-0.13</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>65.25</v>
@@ -26602,10 +26602,10 @@
         <v>-4.39</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
-        <v>64.93000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K346" t="n">
         <v>67.62</v>
@@ -26677,7 +26677,7 @@
         <v>-1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>64.47</v>
@@ -26752,7 +26752,7 @@
         <v>-1.01</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>63.95</v>
@@ -26827,7 +26827,7 @@
         <v>-5.4</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>63.32</v>
@@ -26906,7 +26906,7 @@
         <v>-7.09</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>62.42</v>
@@ -26985,7 +26985,7 @@
         <v>1.12</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>61.66</v>
@@ -27064,7 +27064,7 @@
         <v>1.76</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>60.91</v>
@@ -27139,7 +27139,7 @@
         <v>-1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>60.12</v>
@@ -27214,7 +27214,7 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>59.42</v>
@@ -27289,7 +27289,7 @@
         <v>0.21</v>
       </c>
       <c r="I355" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>58.69</v>
@@ -27364,7 +27364,7 @@
         <v>2.69</v>
       </c>
       <c r="I356" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>58.14</v>
@@ -27439,7 +27439,7 @@
         <v>1.98</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>57.59</v>
@@ -27514,7 +27514,7 @@
         <v>-2.94</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>57.24</v>
@@ -27593,7 +27593,7 @@
         <v>-2.99</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>56.8</v>
@@ -27672,10 +27672,10 @@
         <v>2.48</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
-        <v>56.56</v>
+        <v>56.55</v>
       </c>
       <c r="K360" t="n">
         <v>64.95999999999999</v>
@@ -27747,7 +27747,7 @@
         <v>-0.35</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>56.37</v>
@@ -27822,7 +27822,7 @@
         <v>-3.32</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>55.94</v>
@@ -27897,7 +27897,7 @@
         <v>1.94</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>55.53</v>
@@ -27972,7 +27972,7 @@
         <v>-1.81</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>54.97</v>
@@ -28047,7 +28047,7 @@
         <v>-3.49</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>54.32</v>
@@ -28122,7 +28122,7 @@
         <v>0.77</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>53.83</v>
@@ -28197,7 +28197,7 @@
         <v>0.39</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>53.4</v>
@@ -28272,7 +28272,7 @@
         <v>4.12</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>53.11</v>
@@ -28347,7 +28347,7 @@
         <v>1.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>53.02</v>
@@ -28422,7 +28422,7 @@
         <v>-3.45</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>53.03</v>
@@ -28501,7 +28501,7 @@
         <v>1.02</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>53.04</v>
@@ -28576,7 +28576,7 @@
         <v>0.65</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>53.03</v>
@@ -28651,7 +28651,7 @@
         <v>-2.32</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>52.98</v>
@@ -28726,7 +28726,7 @@
         <v>0.14</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>52.89</v>
@@ -28801,7 +28801,7 @@
         <v>3.34</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>52.89</v>
@@ -28876,7 +28876,7 @@
         <v>-2.13</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>52.75</v>
@@ -28955,7 +28955,7 @@
         <v>0.19</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>52.57</v>
@@ -29030,7 +29030,7 @@
         <v>2.63</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>52.54</v>
@@ -29105,7 +29105,7 @@
         <v>4.14</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>52.7</v>
@@ -29180,7 +29180,7 @@
         <v>-0.39</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>52.79</v>
@@ -29255,7 +29255,7 @@
         <v>2.95</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>52.97</v>
@@ -29330,7 +29330,7 @@
         <v>3.32</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>53.33</v>
@@ -29405,7 +29405,7 @@
         <v>-1.45</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>53.6</v>
@@ -29480,7 +29480,7 @@
         <v>0.87</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>53.94</v>
@@ -29555,7 +29555,7 @@
         <v>-1.52</v>
       </c>
       <c r="I385" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>54.33</v>
@@ -29630,7 +29630,7 @@
         <v>0.55</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>54.71</v>
@@ -29705,7 +29705,7 @@
         <v>1.86</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>55.14</v>
@@ -29780,7 +29780,7 @@
         <v>-3.58</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>55.36</v>
@@ -29859,7 +29859,7 @@
         <v>4.47</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>55.67</v>
@@ -29934,7 +29934,7 @@
         <v>2.75</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>56.15</v>
@@ -30009,7 +30009,7 @@
         <v>1.72</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>56.65</v>
@@ -30084,7 +30084,7 @@
         <v>-0.83</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>57.12</v>
@@ -30159,7 +30159,7 @@
         <v>0.19</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>57.65</v>
@@ -30234,7 +30234,7 @@
         <v>-1.17</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>58.14</v>
@@ -30309,7 +30309,7 @@
         <v>1.92</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>58.6</v>
@@ -30384,7 +30384,7 @@
         <v>-4.38</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>58.98</v>
@@ -30459,7 +30459,7 @@
         <v>0.18</v>
       </c>
       <c r="I397" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>59.37</v>
@@ -30534,7 +30534,7 @@
         <v>-3.68</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>59.57</v>
@@ -30613,7 +30613,7 @@
         <v>1.99</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>59.72</v>
@@ -30688,7 +30688,7 @@
         <v>2.51</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>59.96</v>
@@ -30763,7 +30763,7 @@
         <v>-1.21</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>60.07</v>
@@ -30842,7 +30842,7 @@
         <v>-0.75</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>60.07</v>
@@ -30917,7 +30917,7 @@
         <v>2.27</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>60.18</v>
@@ -30992,7 +30992,7 @@
         <v>-5.3</v>
       </c>
       <c r="I404" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>60.1</v>
@@ -31071,7 +31071,7 @@
         <v>1.08</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>60.1</v>
@@ -31146,7 +31146,7 @@
         <v>-2.2</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>60.02</v>
@@ -31221,7 +31221,7 @@
         <v>1.21</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>59.92</v>
@@ -31296,7 +31296,7 @@
         <v>-0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>59.9</v>
@@ -31371,7 +31371,7 @@
         <v>3.37</v>
       </c>
       <c r="I409" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" t="n">
         <v>59.84</v>
@@ -31446,7 +31446,7 @@
         <v>1.63</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>59.76</v>
@@ -31521,7 +31521,7 @@
         <v>-0.5</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>59.6</v>
@@ -31574,47 +31574,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>59</v>
+        <v>59.31</v>
       </c>
       <c r="D412" t="n">
-        <v>59.03</v>
+        <v>61</v>
       </c>
       <c r="E412" t="n">
-        <v>58.12</v>
+        <v>59.05</v>
       </c>
       <c r="F412" t="n">
-        <v>58.32</v>
+        <v>60.73</v>
       </c>
       <c r="G412" t="n">
-        <v>9112108</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>-2.2</v>
+        <v>15574300</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>1.84</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
-        <v>59.41</v>
+        <v>59.53</v>
       </c>
       <c r="K412" t="n">
-        <v>56.52</v>
+        <v>56.56</v>
       </c>
       <c r="L412" t="n">
-        <v>61.63</v>
+        <v>61.65</v>
       </c>
       <c r="M412" t="n">
-        <v>65.86</v>
+        <v>65.87</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>51.25</v>
+        <v>58.93</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31626,22 +31626,89 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
-      <c r="S412" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>59</v>
+      </c>
+      <c r="D413" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="E413" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="F413" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="G413" t="n">
+        <v>14519532</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31657,7 +31657,7 @@
         <v>58.16</v>
       </c>
       <c r="G413" t="n">
-        <v>14519532</v>
+        <v>14859069</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-4.23</v>
@@ -31705,10 +31705,12 @@
         <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>27.75</v>
@@ -683,7 +683,7 @@
         <v>1.92</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>27.87</v>
@@ -758,7 +758,7 @@
         <v>0.44</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>27.97</v>
@@ -833,7 +833,7 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>28.07</v>
@@ -908,7 +908,7 @@
         <v>-1.19</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>28.16</v>
@@ -983,7 +983,7 @@
         <v>0.59</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>28.24</v>
@@ -1058,7 +1058,7 @@
         <v>-0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>28.34</v>
@@ -1133,7 +1133,7 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>28.44</v>
@@ -1208,7 +1208,7 @@
         <v>0.41</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>28.52</v>
@@ -1283,7 +1283,7 @@
         <v>-0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>28.58</v>
@@ -1358,7 +1358,7 @@
         <v>2.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>28.7</v>
@@ -1433,7 +1433,7 @@
         <v>-0.33</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>28.79</v>
@@ -1508,7 +1508,7 @@
         <v>0.47</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>28.88</v>
@@ -1583,7 +1583,7 @@
         <v>-1.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>28.97</v>
@@ -1658,7 +1658,7 @@
         <v>-0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>29.05</v>
@@ -1733,7 +1733,7 @@
         <v>-2.07</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>29.12</v>
@@ -1812,7 +1812,7 @@
         <v>0.38</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>29.18</v>
@@ -1887,7 +1887,7 @@
         <v>-1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>29.2</v>
@@ -1962,7 +1962,7 @@
         <v>-0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>29.18</v>
@@ -2041,7 +2041,7 @@
         <v>1.55</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>29.19</v>
@@ -2116,7 +2116,7 @@
         <v>0.87</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.21</v>
@@ -2191,7 +2191,7 @@
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.24</v>
@@ -2266,7 +2266,7 @@
         <v>-0.27</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.26</v>
@@ -2341,7 +2341,7 @@
         <v>-0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.27</v>
@@ -2416,7 +2416,7 @@
         <v>-1.62</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.27</v>
@@ -2499,7 +2499,7 @@
         <v>2.92</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.31</v>
@@ -2578,7 +2578,7 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.37</v>
@@ -2653,7 +2653,7 @@
         <v>1.72</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.44</v>
@@ -2728,7 +2728,7 @@
         <v>-0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.5</v>
@@ -2803,7 +2803,7 @@
         <v>0.33</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.58</v>
@@ -2878,7 +2878,7 @@
         <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.62</v>
@@ -2953,7 +2953,7 @@
         <v>-0.32</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.67</v>
@@ -3028,7 +3028,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.7</v>
@@ -3103,7 +3103,7 @@
         <v>-1.57</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.72</v>
@@ -3178,7 +3178,7 @@
         <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.75</v>
@@ -3253,7 +3253,7 @@
         <v>2.07</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.83</v>
@@ -3328,7 +3328,7 @@
         <v>-0.16</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>29.91</v>
@@ -3403,7 +3403,7 @@
         <v>2.59</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>30.06</v>
@@ -3478,7 +3478,7 @@
         <v>-1.02</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>30.19</v>
@@ -3553,7 +3553,7 @@
         <v>-0.03</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>30.3</v>
@@ -3628,7 +3628,7 @@
         <v>-1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>30.39</v>
@@ -3703,7 +3703,7 @@
         <v>0.42</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>30.44</v>
@@ -3778,7 +3778,7 @@
         <v>-6.08</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30.4</v>
@@ -3861,7 +3861,7 @@
         <v>-6.27</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30.27</v>
@@ -3944,7 +3944,7 @@
         <v>0.22</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>30.17</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>30.03</v>
@@ -4110,7 +4110,7 @@
         <v>3.39</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>29.92</v>
@@ -4189,7 +4189,7 @@
         <v>0.78</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>29.8</v>
@@ -4268,7 +4268,7 @@
         <v>3.22</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4347,7 +4347,7 @@
         <v>0.65</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>29.65</v>
@@ -4422,7 +4422,7 @@
         <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>29.58</v>
@@ -4497,7 +4497,7 @@
         <v>1.19</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.53</v>
@@ -4576,7 +4576,7 @@
         <v>-0.71</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.48</v>
@@ -4655,7 +4655,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.47</v>
@@ -4730,7 +4730,7 @@
         <v>-0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.45</v>
@@ -4805,7 +4805,7 @@
         <v>3.59</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.45</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.45</v>
@@ -4959,7 +4959,7 @@
         <v>-1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.39</v>
@@ -5034,7 +5034,7 @@
         <v>0.47</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.35</v>
@@ -5109,7 +5109,7 @@
         <v>-1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.29</v>
@@ -5184,7 +5184,7 @@
         <v>-0.77</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.24</v>
@@ -5263,7 +5263,7 @@
         <v>-0.71</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.17</v>
@@ -5338,7 +5338,7 @@
         <v>-0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.18</v>
@@ -5417,7 +5417,7 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.3</v>
@@ -5492,7 +5492,7 @@
         <v>2.51</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.45</v>
@@ -5567,7 +5567,7 @@
         <v>-2.42</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.57</v>
@@ -5646,7 +5646,7 @@
         <v>-0.1</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.64</v>
@@ -5721,7 +5721,7 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.72</v>
@@ -5796,7 +5796,7 @@
         <v>-0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.74</v>
@@ -5875,7 +5875,7 @@
         <v>1.01</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.77</v>
@@ -5950,7 +5950,7 @@
         <v>-2.27</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.76</v>
@@ -6029,7 +6029,7 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.75</v>
@@ -6104,7 +6104,7 @@
         <v>-1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.74</v>
@@ -6179,7 +6179,7 @@
         <v>0.41</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6254,7 +6254,7 @@
         <v>2.41</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.75</v>
@@ -6329,7 +6329,7 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.75</v>
@@ -6404,7 +6404,7 @@
         <v>-1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.72</v>
@@ -6479,7 +6479,7 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6554,7 +6554,7 @@
         <v>-0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6629,7 +6629,7 @@
         <v>-0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>29.75</v>
@@ -6704,7 +6704,7 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.79</v>
@@ -6779,7 +6779,7 @@
         <v>-0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.82</v>
@@ -6854,7 +6854,7 @@
         <v>5.3</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.94</v>
@@ -6929,7 +6929,7 @@
         <v>-0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>30.04</v>
@@ -7004,7 +7004,7 @@
         <v>-0.32</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>30.09</v>
@@ -7079,7 +7079,7 @@
         <v>3.54</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>30.24</v>
@@ -7154,7 +7154,7 @@
         <v>0.74</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>30.4</v>
@@ -7229,7 +7229,7 @@
         <v>2.14</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>30.58</v>
@@ -7304,7 +7304,7 @@
         <v>-0.48</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>30.76</v>
@@ -7379,7 +7379,7 @@
         <v>-0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>30.91</v>
@@ -7454,7 +7454,7 @@
         <v>0.33</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>31.1</v>
@@ -7529,7 +7529,7 @@
         <v>-0.27</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>31.27</v>
@@ -7604,7 +7604,7 @@
         <v>0.18</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>31.46</v>
@@ -7679,7 +7679,7 @@
         <v>2.15</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>31.68</v>
@@ -7754,7 +7754,7 @@
         <v>-1.39</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>31.83</v>
@@ -7829,7 +7829,7 @@
         <v>-1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>31.94</v>
@@ -7904,7 +7904,7 @@
         <v>0.73</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>32.09</v>
@@ -7979,7 +7979,7 @@
         <v>-1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>32.2</v>
@@ -8054,7 +8054,7 @@
         <v>1.23</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>32.34</v>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>32.5</v>
@@ -8204,7 +8204,7 @@
         <v>-2.16</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>32.62</v>
@@ -8279,7 +8279,7 @@
         <v>0.58</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>32.76</v>
@@ -8354,7 +8354,7 @@
         <v>-0.24</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>32.82</v>
@@ -8433,7 +8433,7 @@
         <v>1.56</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>32.91</v>
@@ -8508,7 +8508,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>33.02</v>
@@ -8583,7 +8583,7 @@
         <v>-0.24</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>33.07</v>
@@ -8658,7 +8658,7 @@
         <v>-0.42</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>33.1</v>
@@ -8733,7 +8733,7 @@
         <v>-0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>33.08</v>
@@ -8812,7 +8812,7 @@
         <v>2.27</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>33.1</v>
@@ -8887,7 +8887,7 @@
         <v>3.79</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>33.21</v>
@@ -8962,7 +8962,7 @@
         <v>-1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.28</v>
@@ -9037,7 +9037,7 @@
         <v>-1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.35</v>
@@ -9112,7 +9112,7 @@
         <v>0.44</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.42</v>
@@ -9187,7 +9187,7 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>33.46</v>
@@ -9262,7 +9262,7 @@
         <v>-0.12</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>33.53</v>
@@ -9337,7 +9337,7 @@
         <v>2.14</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>33.66</v>
@@ -9412,7 +9412,7 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>33.8</v>
@@ -9487,7 +9487,7 @@
         <v>-0.08</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>33.95</v>
@@ -9562,7 +9562,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>34.08</v>
@@ -9637,7 +9637,7 @@
         <v>-2.34</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>34.14</v>
@@ -9712,7 +9712,7 @@
         <v>-0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>34.24</v>
@@ -9787,7 +9787,7 @@
         <v>0.06</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>34.34</v>
@@ -9862,7 +9862,7 @@
         <v>-3.32</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>34.38</v>
@@ -9941,7 +9941,7 @@
         <v>-0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.38</v>
@@ -10091,7 +10091,7 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.41</v>
@@ -10166,7 +10166,7 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.46</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>34.53</v>
@@ -10316,7 +10316,7 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.58</v>
@@ -10391,7 +10391,7 @@
         <v>0.35</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.58</v>
@@ -10466,7 +10466,7 @@
         <v>-2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.55</v>
@@ -10545,7 +10545,7 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.56</v>
@@ -10620,7 +10620,7 @@
         <v>1.71</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.59</v>
@@ -10695,7 +10695,7 @@
         <v>-1.43</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10849,7 +10849,7 @@
         <v>0.14</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.54</v>
@@ -10924,7 +10924,7 @@
         <v>-1.97</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.44</v>
@@ -11003,7 +11003,7 @@
         <v>1.65</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.38</v>
@@ -11078,7 +11078,7 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.34</v>
@@ -11153,7 +11153,7 @@
         <v>2.11</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.37</v>
@@ -11228,7 +11228,7 @@
         <v>-0.91</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.39</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>34.41</v>
@@ -11378,7 +11378,7 @@
         <v>-0.09</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>34.48</v>
@@ -11453,7 +11453,7 @@
         <v>1.51</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>34.59</v>
@@ -11528,7 +11528,7 @@
         <v>1.89</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>34.72</v>
@@ -11603,7 +11603,7 @@
         <v>2.65</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>34.88</v>
@@ -11678,7 +11678,7 @@
         <v>0.51</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>35.03</v>
@@ -11753,7 +11753,7 @@
         <v>-1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>35.16</v>
@@ -11828,7 +11828,7 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>35.28</v>
@@ -11903,7 +11903,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>35.41</v>
@@ -11978,7 +11978,7 @@
         <v>-0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>35.56</v>
@@ -12053,7 +12053,7 @@
         <v>0.62</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>35.71</v>
@@ -12128,7 +12128,7 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>35.85</v>
@@ -12203,7 +12203,7 @@
         <v>1.46</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>36.04</v>
@@ -12278,7 +12278,7 @@
         <v>1.1</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>36.26</v>
@@ -12353,7 +12353,7 @@
         <v>-0.41</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>36.46</v>
@@ -12428,7 +12428,7 @@
         <v>-2.1</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>36.66</v>
@@ -12503,7 +12503,7 @@
         <v>0.53</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>36.83</v>
@@ -12578,7 +12578,7 @@
         <v>2.76</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>37.06</v>
@@ -12653,7 +12653,7 @@
         <v>2.56</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>37.29</v>
@@ -12728,7 +12728,7 @@
         <v>-0.2</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>37.54</v>
@@ -12803,7 +12803,7 @@
         <v>-0.35</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>37.78</v>
@@ -12878,7 +12878,7 @@
         <v>3.04</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>38.08</v>
@@ -12953,7 +12953,7 @@
         <v>2.02</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>38.4</v>
@@ -13028,7 +13028,7 @@
         <v>1.53</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>38.71</v>
@@ -13103,7 +13103,7 @@
         <v>-0.31</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>38.97</v>
@@ -13178,7 +13178,7 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>39.25</v>
@@ -13253,7 +13253,7 @@
         <v>-0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>39.53</v>
@@ -13328,7 +13328,7 @@
         <v>2.33</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>39.85</v>
@@ -13403,7 +13403,7 @@
         <v>1.24</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>40.17</v>
@@ -13478,7 +13478,7 @@
         <v>-1.52</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>40.49</v>
@@ -13553,7 +13553,7 @@
         <v>2.7</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>40.84</v>
@@ -13628,7 +13628,7 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>41.19</v>
@@ -13703,7 +13703,7 @@
         <v>1.61</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>41.54</v>
@@ -13778,7 +13778,7 @@
         <v>4.03</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>41.97</v>
@@ -13853,7 +13853,7 @@
         <v>-0.97</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>42.38</v>
@@ -13928,7 +13928,7 @@
         <v>3.27</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>42.91</v>
@@ -14003,7 +14003,7 @@
         <v>1.74</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>43.46</v>
@@ -14078,7 +14078,7 @@
         <v>-4.43</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>43.86</v>
@@ -14153,7 +14153,7 @@
         <v>1.55</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>44.25</v>
@@ -14228,7 +14228,7 @@
         <v>-8.24</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>44.44</v>
@@ -14307,7 +14307,7 @@
         <v>0.21</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>44.64</v>
@@ -14382,7 +14382,7 @@
         <v>0.68</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>44.8</v>
@@ -14457,7 +14457,7 @@
         <v>-0.43</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>44.9</v>
@@ -14532,7 +14532,7 @@
         <v>-3.61</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>44.9</v>
@@ -14607,7 +14607,7 @@
         <v>0.71</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>44.92</v>
@@ -14682,7 +14682,7 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>44.93</v>
@@ -14757,7 +14757,7 @@
         <v>2.57</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>45.02</v>
@@ -14832,7 +14832,7 @@
         <v>-0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>45.05</v>
@@ -14907,7 +14907,7 @@
         <v>-0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>45.03</v>
@@ -14982,7 +14982,7 @@
         <v>-2.33</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>45</v>
@@ -15057,7 +15057,7 @@
         <v>2.13</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>44.95</v>
@@ -15132,7 +15132,7 @@
         <v>-0.23</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>44.9</v>
@@ -15207,7 +15207,7 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>44.82</v>
@@ -15282,7 +15282,7 @@
         <v>4.26</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>44.75</v>
@@ -15357,7 +15357,7 @@
         <v>1.44</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>44.73</v>
@@ -15432,7 +15432,7 @@
         <v>4.03</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>44.73</v>
@@ -15507,7 +15507,7 @@
         <v>-1.86</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.64</v>
@@ -15582,7 +15582,7 @@
         <v>-3.08</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.59</v>
@@ -15657,7 +15657,7 @@
         <v>-1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>44.48</v>
@@ -15732,7 +15732,7 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>44.59</v>
@@ -15807,7 +15807,7 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>44.72</v>
@@ -15882,7 +15882,7 @@
         <v>-1.44</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>44.8</v>
@@ -15961,7 +15961,7 @@
         <v>-1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>44.87</v>
@@ -16036,7 +16036,7 @@
         <v>2.94</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>45.08</v>
@@ -16111,7 +16111,7 @@
         <v>0.09</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>45.28</v>
@@ -16186,7 +16186,7 @@
         <v>3.71</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>45.54</v>
@@ -16261,7 +16261,7 @@
         <v>5.81</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>45.88</v>
@@ -16336,7 +16336,7 @@
         <v>2.56</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>46.3</v>
@@ -16411,7 +16411,7 @@
         <v>1.16</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>46.77</v>
@@ -16486,7 +16486,7 @@
         <v>-0.11</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>47.29</v>
@@ -16561,7 +16561,7 @@
         <v>-2.47</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>47.7</v>
@@ -16636,7 +16636,7 @@
         <v>2.3</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>48.16</v>
@@ -16711,7 +16711,7 @@
         <v>-0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>48.6</v>
@@ -16786,7 +16786,7 @@
         <v>4.67</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>49.07</v>
@@ -16861,7 +16861,7 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>49.55</v>
@@ -16936,7 +16936,7 @@
         <v>2.76</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>50.02</v>
@@ -17011,7 +17011,7 @@
         <v>-2.64</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>50.45</v>
@@ -17086,7 +17086,7 @@
         <v>3.58</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>51.06</v>
@@ -17161,7 +17161,7 @@
         <v>-0.65</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>51.67</v>
@@ -17236,7 +17236,7 @@
         <v>4.38</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>52.38</v>
@@ -17311,7 +17311,7 @@
         <v>-1.56</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>53.03</v>
@@ -17386,7 +17386,7 @@
         <v>2.71</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>53.78</v>
@@ -17461,7 +17461,7 @@
         <v>2.53</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>54.64</v>
@@ -17536,7 +17536,7 @@
         <v>3.79</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>55.55</v>
@@ -17611,7 +17611,7 @@
         <v>0.59</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>56.48</v>
@@ -17686,7 +17686,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>57.62</v>
@@ -17761,7 +17761,7 @@
         <v>-7.19</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>58.36</v>
@@ -17836,7 +17836,7 @@
         <v>4.5</v>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>59.18</v>
@@ -17911,7 +17911,7 @@
         <v>-6.61</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>59.74</v>
@@ -17986,7 +17986,7 @@
         <v>2.06</v>
       </c>
       <c r="I232" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" t="n">
         <v>60.38</v>
@@ -18061,7 +18061,7 @@
         <v>5.06</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>61.24</v>
@@ -18136,7 +18136,7 @@
         <v>6.7</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>62.28</v>
@@ -18211,7 +18211,7 @@
         <v>-3.73</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>63.19</v>
@@ -18286,7 +18286,7 @@
         <v>-1.76</v>
       </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" t="n">
         <v>63.92</v>
@@ -18361,7 +18361,7 @@
         <v>3.83</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>64.73999999999999</v>
@@ -18436,7 +18436,7 @@
         <v>6.7</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>65.72</v>
@@ -18511,7 +18511,7 @@
         <v>1.77</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>66.84</v>
@@ -18586,7 +18586,7 @@
         <v>7.58</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>68.16</v>
@@ -18661,7 +18661,7 @@
         <v>-1.47</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>69.44</v>
@@ -18736,7 +18736,7 @@
         <v>-2.76</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>70.48</v>
@@ -18811,7 +18811,7 @@
         <v>5.39</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>71.78</v>
@@ -18886,7 +18886,7 @@
         <v>-1.67</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>72.94</v>
@@ -18961,7 +18961,7 @@
         <v>3.78</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>74.17</v>
@@ -19036,7 +19036,7 @@
         <v>6.63</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>75.56999999999999</v>
@@ -19111,7 +19111,7 @@
         <v>5.84</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>77.23</v>
@@ -19186,7 +19186,7 @@
         <v>3.3</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>78.75</v>
@@ -19261,7 +19261,7 @@
         <v>3.95</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>80.73</v>
@@ -19336,7 +19336,7 @@
         <v>-0.03</v>
       </c>
       <c r="I250" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" t="n">
         <v>82.56</v>
@@ -19411,7 +19411,7 @@
         <v>-28.54</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>83.11</v>
@@ -19490,7 +19490,7 @@
         <v>-3.98</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>83.45</v>
@@ -19565,7 +19565,7 @@
         <v>6.24</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>83.84</v>
@@ -19640,7 +19640,7 @@
         <v>2.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>84.11</v>
@@ -19715,7 +19715,7 @@
         <v>-15.77</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19790,7 +19790,7 @@
         <v>5.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" t="n">
         <v>83.92</v>
@@ -19865,7 +19865,7 @@
         <v>8.33</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>84.11</v>
@@ -19940,7 +19940,7 @@
         <v>-3.46</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>83.92</v>
@@ -20015,7 +20015,7 @@
         <v>4.29</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>83.81999999999999</v>
@@ -20090,7 +20090,7 @@
         <v>-11.53</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>82.97</v>
@@ -20165,7 +20165,7 @@
         <v>2.94</v>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" t="n">
         <v>82.29000000000001</v>
@@ -20240,7 +20240,7 @@
         <v>-4.8</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>81.56</v>
@@ -20319,7 +20319,7 @@
         <v>5.6</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>80.8</v>
@@ -20394,7 +20394,7 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>80.15000000000001</v>
@@ -20469,7 +20469,7 @@
         <v>7.9</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>79.62</v>
@@ -20544,7 +20544,7 @@
         <v>5.16</v>
       </c>
       <c r="I266" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>79.01000000000001</v>
@@ -20619,7 +20619,7 @@
         <v>-1.85</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>78.04000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>76.97</v>
@@ -20769,7 +20769,7 @@
         <v>0.51</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>75.70999999999999</v>
@@ -20844,7 +20844,7 @@
         <v>5.64</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>74.68000000000001</v>
@@ -20919,7 +20919,7 @@
         <v>-4.02</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>74.98999999999999</v>
@@ -20994,7 +20994,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I272" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21073,7 +21073,7 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>75.02</v>
@@ -21148,7 +21148,7 @@
         <v>-1.42</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>74.77</v>
@@ -21227,7 +21227,7 @@
         <v>2.25</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>75.23</v>
@@ -21306,7 +21306,7 @@
         <v>3.06</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>75.64</v>
@@ -21381,7 +21381,7 @@
         <v>2.34</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>75.84</v>
@@ -21456,7 +21456,7 @@
         <v>-2.72</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>76.06</v>
@@ -21531,7 +21531,7 @@
         <v>-1.84</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>76.06</v>
@@ -21600,7 +21600,7 @@
         <v>-4.96</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>76.31</v>
@@ -21683,7 +21683,7 @@
         <v>0.73</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>76.48</v>
@@ -21758,7 +21758,7 @@
         <v>-2.13</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>76.75</v>
@@ -21833,7 +21833,7 @@
         <v>-4.13</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>76.68000000000001</v>
@@ -21908,7 +21908,7 @@
         <v>-4.4</v>
       </c>
       <c r="I284" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" t="n">
         <v>76.41</v>
@@ -21983,7 +21983,7 @@
         <v>-6.33</v>
       </c>
       <c r="I285" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" s="4" t="n">
         <v>75.66</v>
@@ -22066,7 +22066,7 @@
         <v>1.54</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>74.75</v>
@@ -22141,7 +22141,7 @@
         <v>0.77</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>73.95</v>
@@ -22216,7 +22216,7 @@
         <v>3.59</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>73.2</v>
@@ -22291,7 +22291,7 @@
         <v>-6.81</v>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>72.22</v>
@@ -22370,7 +22370,7 @@
         <v>4.39</v>
       </c>
       <c r="I290" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" t="n">
         <v>71.14</v>
@@ -22449,7 +22449,7 @@
         <v>0.13</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>70.23999999999999</v>
@@ -22524,7 +22524,7 @@
         <v>7.27</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>69.91</v>
@@ -22599,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>69.55</v>
@@ -22674,7 +22674,7 @@
         <v>-3.45</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>69.13</v>
@@ -22749,7 +22749,7 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>68.64</v>
@@ -22824,7 +22824,7 @@
         <v>-0.23</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>68.02</v>
@@ -22903,7 +22903,7 @@
         <v>2.32</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>67.39</v>
@@ -22978,7 +22978,7 @@
         <v>1.36</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>66.91</v>
@@ -23053,7 +23053,7 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>66.54000000000001</v>
@@ -23128,7 +23128,7 @@
         <v>-1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>66.31999999999999</v>
@@ -23203,7 +23203,7 @@
         <v>5.51</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>66.26000000000001</v>
@@ -23278,7 +23278,7 @@
         <v>-0.28</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>66.27</v>
@@ -23353,7 +23353,7 @@
         <v>-0.84</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>66.40000000000001</v>
@@ -23428,7 +23428,7 @@
         <v>3.35</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>66.8</v>
@@ -23503,7 +23503,7 @@
         <v>-2.01</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>67.33</v>
@@ -23578,7 +23578,7 @@
         <v>-5.07</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>67.63</v>
@@ -23653,7 +23653,7 @@
         <v>2.74</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>68</v>
@@ -23728,7 +23728,7 @@
         <v>-2.83</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>68.16</v>
@@ -23803,7 +23803,7 @@
         <v>0.6</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>68.56</v>
@@ -23878,7 +23878,7 @@
         <v>-0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>68.8</v>
@@ -23957,7 +23957,7 @@
         <v>-3.12</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>68.94</v>
@@ -24036,7 +24036,7 @@
         <v>-2.05</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>68.77</v>
@@ -24111,7 +24111,7 @@
         <v>2.81</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>68.7</v>
@@ -24186,7 +24186,7 @@
         <v>2.45</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>68.81999999999999</v>
@@ -24261,7 +24261,7 @@
         <v>-3.44</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>68.81999999999999</v>
@@ -24340,7 +24340,7 @@
         <v>-0.05</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>68.81999999999999</v>
@@ -24415,7 +24415,7 @@
         <v>6.4</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>68.95</v>
@@ -24490,7 +24490,7 @@
         <v>2.1</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>69.11</v>
@@ -24565,7 +24565,7 @@
         <v>1.97</v>
       </c>
       <c r="I319" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" t="n">
         <v>69.31</v>
@@ -24640,7 +24640,7 @@
         <v>6.83</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>69.79000000000001</v>
@@ -24715,7 +24715,7 @@
         <v>0.71</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>70.12</v>
@@ -24790,7 +24790,7 @@
         <v>1.02</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>70.48999999999999</v>
@@ -24865,7 +24865,7 @@
         <v>-4.84</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>70.70999999999999</v>
@@ -24940,7 +24940,7 @@
         <v>-8.57</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>70.48</v>
@@ -25019,7 +25019,7 @@
         <v>1.3</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>70.37</v>
@@ -25094,7 +25094,7 @@
         <v>-4.35</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>70.29000000000001</v>
@@ -25169,7 +25169,7 @@
         <v>2.74</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.20999999999999</v>
@@ -25244,7 +25244,7 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.26000000000001</v>
@@ -25319,7 +25319,7 @@
         <v>-1.57</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>70.23999999999999</v>
@@ -25394,7 +25394,7 @@
         <v>1.99</v>
       </c>
       <c r="I330" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" t="n">
         <v>70.31</v>
@@ -25469,7 +25469,7 @@
         <v>-3.18</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.37</v>
@@ -25544,7 +25544,7 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.55</v>
@@ -25619,7 +25619,7 @@
         <v>-0.04</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>70.63</v>
@@ -25694,7 +25694,7 @@
         <v>-0.97</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>70.59999999999999</v>
@@ -25769,7 +25769,7 @@
         <v>0.47</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>70.7</v>
@@ -25844,7 +25844,7 @@
         <v>-2.62</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>70.72</v>
@@ -25919,7 +25919,7 @@
         <v>1.16</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>70.56</v>
@@ -25994,7 +25994,7 @@
         <v>-8.08</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>70.06</v>
@@ -26069,7 +26069,7 @@
         <v>0.02</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>69.48999999999999</v>
@@ -26144,7 +26144,7 @@
         <v>-4.17</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>68.54000000000001</v>
@@ -26223,7 +26223,7 @@
         <v>-2.29</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>67.48999999999999</v>
@@ -26302,7 +26302,7 @@
         <v>5.48</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>66.56999999999999</v>
@@ -26377,7 +26377,7 @@
         <v>0.77</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>65.86</v>
@@ -26452,7 +26452,7 @@
         <v>3.56</v>
       </c>
       <c r="I344" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" t="n">
         <v>65.58</v>
@@ -26527,7 +26527,7 @@
         <v>-0.13</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>65.25</v>
@@ -26602,7 +26602,7 @@
         <v>-4.39</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>64.94</v>
@@ -26677,7 +26677,7 @@
         <v>-1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>64.47</v>
@@ -26752,7 +26752,7 @@
         <v>-1.01</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>63.95</v>
@@ -26827,7 +26827,7 @@
         <v>-5.4</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>63.32</v>
@@ -26906,7 +26906,7 @@
         <v>-7.09</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>62.42</v>
@@ -26985,7 +26985,7 @@
         <v>1.12</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>61.66</v>
@@ -27064,7 +27064,7 @@
         <v>1.76</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>60.91</v>
@@ -27139,7 +27139,7 @@
         <v>-1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>60.12</v>
@@ -27214,7 +27214,7 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>59.42</v>
@@ -27289,7 +27289,7 @@
         <v>0.21</v>
       </c>
       <c r="I355" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" t="n">
         <v>58.69</v>
@@ -27364,7 +27364,7 @@
         <v>2.69</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>58.14</v>
@@ -27439,7 +27439,7 @@
         <v>1.98</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>57.59</v>
@@ -27514,7 +27514,7 @@
         <v>-2.94</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>57.24</v>
@@ -27593,7 +27593,7 @@
         <v>-2.99</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>56.8</v>
@@ -27672,7 +27672,7 @@
         <v>2.48</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>56.55</v>
@@ -27747,7 +27747,7 @@
         <v>-0.35</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>56.37</v>
@@ -27822,7 +27822,7 @@
         <v>-3.32</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>55.94</v>
@@ -27897,7 +27897,7 @@
         <v>1.94</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>55.53</v>
@@ -27972,7 +27972,7 @@
         <v>-1.81</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>54.97</v>
@@ -28047,7 +28047,7 @@
         <v>-3.49</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>54.32</v>
@@ -28122,7 +28122,7 @@
         <v>0.77</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>53.83</v>
@@ -28197,7 +28197,7 @@
         <v>0.39</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>53.4</v>
@@ -28272,7 +28272,7 @@
         <v>4.12</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>53.11</v>
@@ -28347,7 +28347,7 @@
         <v>1.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>53.02</v>
@@ -28422,7 +28422,7 @@
         <v>-3.45</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>53.03</v>
@@ -28501,7 +28501,7 @@
         <v>1.02</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>53.04</v>
@@ -28576,7 +28576,7 @@
         <v>0.65</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>53.03</v>
@@ -28651,7 +28651,7 @@
         <v>-2.32</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>52.98</v>
@@ -28726,7 +28726,7 @@
         <v>0.14</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>52.89</v>
@@ -28801,7 +28801,7 @@
         <v>3.34</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>52.89</v>
@@ -28876,7 +28876,7 @@
         <v>-2.13</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>52.75</v>
@@ -28955,7 +28955,7 @@
         <v>0.19</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>52.57</v>
@@ -29030,7 +29030,7 @@
         <v>2.63</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>52.54</v>
@@ -29105,7 +29105,7 @@
         <v>4.14</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>52.7</v>
@@ -29180,7 +29180,7 @@
         <v>-0.39</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>52.79</v>
@@ -29255,7 +29255,7 @@
         <v>2.95</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>52.97</v>
@@ -29330,7 +29330,7 @@
         <v>3.32</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>53.33</v>
@@ -29405,7 +29405,7 @@
         <v>-1.45</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>53.6</v>
@@ -29480,7 +29480,7 @@
         <v>0.87</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>53.94</v>
@@ -29555,7 +29555,7 @@
         <v>-1.52</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>54.33</v>
@@ -29630,7 +29630,7 @@
         <v>0.55</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>54.71</v>
@@ -29705,7 +29705,7 @@
         <v>1.86</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>55.14</v>
@@ -29780,7 +29780,7 @@
         <v>-3.58</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>55.36</v>
@@ -29859,7 +29859,7 @@
         <v>4.47</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>55.67</v>
@@ -29934,7 +29934,7 @@
         <v>2.75</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>56.15</v>
@@ -30009,7 +30009,7 @@
         <v>1.72</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>56.65</v>
@@ -30084,7 +30084,7 @@
         <v>-0.83</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>57.12</v>
@@ -30159,7 +30159,7 @@
         <v>0.19</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>57.65</v>
@@ -30234,7 +30234,7 @@
         <v>-1.17</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>58.14</v>
@@ -30309,7 +30309,7 @@
         <v>1.92</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>58.6</v>
@@ -30384,7 +30384,7 @@
         <v>-4.38</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>58.98</v>
@@ -30459,7 +30459,7 @@
         <v>0.18</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>59.37</v>
@@ -30534,7 +30534,7 @@
         <v>-3.68</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>59.57</v>
@@ -30613,7 +30613,7 @@
         <v>1.99</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>59.72</v>
@@ -30688,7 +30688,7 @@
         <v>2.51</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>59.96</v>
@@ -30763,7 +30763,7 @@
         <v>-1.21</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>60.07</v>
@@ -30842,7 +30842,7 @@
         <v>-0.75</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>60.07</v>
@@ -30917,7 +30917,7 @@
         <v>2.27</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>60.18</v>
@@ -30992,7 +30992,7 @@
         <v>-5.3</v>
       </c>
       <c r="I404" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>60.1</v>
@@ -31071,7 +31071,7 @@
         <v>1.08</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>60.1</v>
@@ -31146,7 +31146,7 @@
         <v>-2.2</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>60.02</v>
@@ -31221,7 +31221,7 @@
         <v>1.21</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>59.92</v>
@@ -31296,7 +31296,7 @@
         <v>-0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>59.9</v>
@@ -31371,7 +31371,7 @@
         <v>3.37</v>
       </c>
       <c r="I409" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" t="n">
         <v>59.84</v>
@@ -31446,7 +31446,7 @@
         <v>1.63</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>59.76</v>
@@ -31521,7 +31521,7 @@
         <v>-0.5</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>59.6</v>
@@ -31596,7 +31596,7 @@
         <v>1.84</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>59.53</v>
@@ -31644,41 +31644,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>59</v>
-      </c>
-      <c r="D413" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="E413" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="F413" t="n">
-        <v>58.16</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>14859069</v>
       </c>
-      <c r="H413" s="3" t="n">
-        <v>-4.23</v>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J413" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="K413" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="L413" t="n">
-        <v>61.57</v>
-      </c>
-      <c r="M413" t="n">
-        <v>65.91</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>47.35</v>
+        <v>55.69</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>
@@ -31693,11 +31677,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
         <v>5.11</v>
       </c>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>27.75</v>
@@ -683,7 +683,7 @@
         <v>1.92</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>27.87</v>
@@ -758,7 +758,7 @@
         <v>0.44</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.97</v>
@@ -833,7 +833,7 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>28.07</v>
@@ -908,7 +908,7 @@
         <v>-1.19</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>28.16</v>
@@ -983,7 +983,7 @@
         <v>0.59</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>28.24</v>
@@ -1058,7 +1058,7 @@
         <v>-0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>28.34</v>
@@ -1133,7 +1133,7 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>28.44</v>
@@ -1208,7 +1208,7 @@
         <v>0.41</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>28.52</v>
@@ -1283,7 +1283,7 @@
         <v>-0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>28.58</v>
@@ -1358,7 +1358,7 @@
         <v>2.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>28.7</v>
@@ -1433,7 +1433,7 @@
         <v>-0.33</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>28.79</v>
@@ -1508,7 +1508,7 @@
         <v>0.47</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>28.88</v>
@@ -1583,7 +1583,7 @@
         <v>-1.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>28.97</v>
@@ -1658,7 +1658,7 @@
         <v>-0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>29.05</v>
@@ -1733,7 +1733,7 @@
         <v>-2.07</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>29.12</v>
@@ -1812,7 +1812,7 @@
         <v>0.38</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>29.18</v>
@@ -1887,7 +1887,7 @@
         <v>-1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>29.2</v>
@@ -1962,7 +1962,7 @@
         <v>-0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>29.18</v>
@@ -2041,7 +2041,7 @@
         <v>1.55</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>29.19</v>
@@ -2116,7 +2116,7 @@
         <v>0.87</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>29.21</v>
@@ -2191,7 +2191,7 @@
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>29.24</v>
@@ -2266,7 +2266,7 @@
         <v>-0.27</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>29.26</v>
@@ -2341,7 +2341,7 @@
         <v>-0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>29.27</v>
@@ -2416,7 +2416,7 @@
         <v>-1.62</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>29.27</v>
@@ -2499,7 +2499,7 @@
         <v>2.92</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>29.31</v>
@@ -2578,7 +2578,7 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>29.37</v>
@@ -2653,7 +2653,7 @@
         <v>1.72</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.44</v>
@@ -2728,7 +2728,7 @@
         <v>-0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.5</v>
@@ -2803,7 +2803,7 @@
         <v>0.33</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.58</v>
@@ -2878,7 +2878,7 @@
         <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.62</v>
@@ -2953,7 +2953,7 @@
         <v>-0.32</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.67</v>
@@ -3028,7 +3028,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.7</v>
@@ -3103,7 +3103,7 @@
         <v>-1.57</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.72</v>
@@ -3178,7 +3178,7 @@
         <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.75</v>
@@ -3253,7 +3253,7 @@
         <v>2.07</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.83</v>
@@ -3328,7 +3328,7 @@
         <v>-0.16</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.91</v>
@@ -3403,7 +3403,7 @@
         <v>2.59</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>30.06</v>
@@ -3478,7 +3478,7 @@
         <v>-1.02</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>30.19</v>
@@ -3553,7 +3553,7 @@
         <v>-0.03</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>30.3</v>
@@ -3628,7 +3628,7 @@
         <v>-1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>30.39</v>
@@ -3703,7 +3703,7 @@
         <v>0.42</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>30.44</v>
@@ -3778,7 +3778,7 @@
         <v>-6.08</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30.4</v>
@@ -3861,7 +3861,7 @@
         <v>-6.27</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30.27</v>
@@ -3944,7 +3944,7 @@
         <v>0.22</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>30.17</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>30.03</v>
@@ -4110,7 +4110,7 @@
         <v>3.39</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>29.92</v>
@@ -4189,7 +4189,7 @@
         <v>0.78</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>29.8</v>
@@ -4268,7 +4268,7 @@
         <v>3.22</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4347,7 +4347,7 @@
         <v>0.65</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>29.65</v>
@@ -4422,7 +4422,7 @@
         <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>29.58</v>
@@ -4497,7 +4497,7 @@
         <v>1.19</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>29.53</v>
@@ -4576,7 +4576,7 @@
         <v>-0.71</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.48</v>
@@ -4655,7 +4655,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.47</v>
@@ -4730,7 +4730,7 @@
         <v>-0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.45</v>
@@ -4805,7 +4805,7 @@
         <v>3.59</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.45</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.45</v>
@@ -4959,7 +4959,7 @@
         <v>-1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.39</v>
@@ -5034,7 +5034,7 @@
         <v>0.47</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.35</v>
@@ -5109,7 +5109,7 @@
         <v>-1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.29</v>
@@ -5184,7 +5184,7 @@
         <v>-0.77</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.24</v>
@@ -5263,7 +5263,7 @@
         <v>-0.71</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.17</v>
@@ -5338,7 +5338,7 @@
         <v>-0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.18</v>
@@ -5417,7 +5417,7 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.3</v>
@@ -5492,7 +5492,7 @@
         <v>2.51</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>29.45</v>
@@ -5567,7 +5567,7 @@
         <v>-2.42</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>29.57</v>
@@ -5646,7 +5646,7 @@
         <v>-0.1</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>29.64</v>
@@ -5721,7 +5721,7 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>29.72</v>
@@ -5796,7 +5796,7 @@
         <v>-0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>29.74</v>
@@ -5875,7 +5875,7 @@
         <v>1.01</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>29.77</v>
@@ -5950,7 +5950,7 @@
         <v>-2.27</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>29.76</v>
@@ -6029,7 +6029,7 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>29.75</v>
@@ -6104,7 +6104,7 @@
         <v>-1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>29.74</v>
@@ -6179,7 +6179,7 @@
         <v>0.41</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6254,7 +6254,7 @@
         <v>2.41</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>29.75</v>
@@ -6329,7 +6329,7 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>29.75</v>
@@ -6404,7 +6404,7 @@
         <v>-1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>29.72</v>
@@ -6479,7 +6479,7 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6554,7 +6554,7 @@
         <v>-0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6629,7 +6629,7 @@
         <v>-0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>29.75</v>
@@ -6704,7 +6704,7 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>29.79</v>
@@ -6779,7 +6779,7 @@
         <v>-0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>29.82</v>
@@ -6854,7 +6854,7 @@
         <v>5.3</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>29.94</v>
@@ -6929,7 +6929,7 @@
         <v>-0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>30.04</v>
@@ -7004,7 +7004,7 @@
         <v>-0.32</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>30.09</v>
@@ -7079,7 +7079,7 @@
         <v>3.54</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>30.24</v>
@@ -7154,7 +7154,7 @@
         <v>0.74</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>30.4</v>
@@ -7229,7 +7229,7 @@
         <v>2.14</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>30.58</v>
@@ -7304,7 +7304,7 @@
         <v>-0.48</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>30.76</v>
@@ -7379,7 +7379,7 @@
         <v>-0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>30.91</v>
@@ -7454,7 +7454,7 @@
         <v>0.33</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>31.1</v>
@@ -7529,7 +7529,7 @@
         <v>-0.27</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>31.27</v>
@@ -7604,7 +7604,7 @@
         <v>0.18</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>31.46</v>
@@ -7679,7 +7679,7 @@
         <v>2.15</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>31.68</v>
@@ -7754,7 +7754,7 @@
         <v>-1.39</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>31.83</v>
@@ -7829,7 +7829,7 @@
         <v>-1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>31.94</v>
@@ -7904,7 +7904,7 @@
         <v>0.73</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>32.09</v>
@@ -7979,7 +7979,7 @@
         <v>-1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>32.2</v>
@@ -8054,7 +8054,7 @@
         <v>1.23</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>32.34</v>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>32.5</v>
@@ -8204,7 +8204,7 @@
         <v>-2.16</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>32.62</v>
@@ -8279,7 +8279,7 @@
         <v>0.58</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>32.76</v>
@@ -8354,7 +8354,7 @@
         <v>-0.24</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>32.82</v>
@@ -8433,7 +8433,7 @@
         <v>1.56</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>32.91</v>
@@ -8508,7 +8508,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>33.02</v>
@@ -8583,7 +8583,7 @@
         <v>-0.24</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>33.07</v>
@@ -8658,7 +8658,7 @@
         <v>-0.42</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>33.1</v>
@@ -8733,7 +8733,7 @@
         <v>-0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>33.08</v>
@@ -8812,7 +8812,7 @@
         <v>2.27</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>33.1</v>
@@ -8887,7 +8887,7 @@
         <v>3.79</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>33.21</v>
@@ -8962,7 +8962,7 @@
         <v>-1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>33.28</v>
@@ -9037,7 +9037,7 @@
         <v>-1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>33.35</v>
@@ -9112,7 +9112,7 @@
         <v>0.44</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>33.42</v>
@@ -9187,7 +9187,7 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>33.46</v>
@@ -9262,7 +9262,7 @@
         <v>-0.12</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>33.53</v>
@@ -9337,7 +9337,7 @@
         <v>2.14</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>33.66</v>
@@ -9412,7 +9412,7 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>33.8</v>
@@ -9487,7 +9487,7 @@
         <v>-0.08</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>33.95</v>
@@ -9562,7 +9562,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>34.08</v>
@@ -9637,7 +9637,7 @@
         <v>-2.34</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>34.14</v>
@@ -9712,7 +9712,7 @@
         <v>-0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>34.24</v>
@@ -9787,7 +9787,7 @@
         <v>0.06</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>34.34</v>
@@ -9862,7 +9862,7 @@
         <v>-3.32</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>34.38</v>
@@ -9941,7 +9941,7 @@
         <v>-0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.38</v>
@@ -10091,7 +10091,7 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.41</v>
@@ -10166,7 +10166,7 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.46</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>34.53</v>
@@ -10316,7 +10316,7 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>34.58</v>
@@ -10391,7 +10391,7 @@
         <v>0.35</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>34.58</v>
@@ -10466,7 +10466,7 @@
         <v>-2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>34.55</v>
@@ -10545,7 +10545,7 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>34.56</v>
@@ -10620,7 +10620,7 @@
         <v>1.71</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>34.59</v>
@@ -10695,7 +10695,7 @@
         <v>-1.43</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10849,7 +10849,7 @@
         <v>0.14</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>34.54</v>
@@ -10924,7 +10924,7 @@
         <v>-1.97</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>34.44</v>
@@ -11003,7 +11003,7 @@
         <v>1.65</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>34.38</v>
@@ -11078,7 +11078,7 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>34.34</v>
@@ -11153,7 +11153,7 @@
         <v>2.11</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>34.37</v>
@@ -11228,7 +11228,7 @@
         <v>-0.91</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>34.39</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>34.41</v>
@@ -11378,7 +11378,7 @@
         <v>-0.09</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>34.48</v>
@@ -11453,7 +11453,7 @@
         <v>1.51</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>34.59</v>
@@ -11528,7 +11528,7 @@
         <v>1.89</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>34.72</v>
@@ -11603,7 +11603,7 @@
         <v>2.65</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>34.88</v>
@@ -11678,7 +11678,7 @@
         <v>0.51</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>35.03</v>
@@ -11753,7 +11753,7 @@
         <v>-1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>35.16</v>
@@ -11828,7 +11828,7 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>35.28</v>
@@ -11903,7 +11903,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>35.41</v>
@@ -11978,7 +11978,7 @@
         <v>-0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>35.56</v>
@@ -12053,7 +12053,7 @@
         <v>0.62</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>35.71</v>
@@ -12128,7 +12128,7 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>35.85</v>
@@ -12203,7 +12203,7 @@
         <v>1.46</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>36.04</v>
@@ -12278,7 +12278,7 @@
         <v>1.1</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>36.26</v>
@@ -12353,7 +12353,7 @@
         <v>-0.41</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>36.46</v>
@@ -12428,7 +12428,7 @@
         <v>-2.1</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>36.66</v>
@@ -12503,7 +12503,7 @@
         <v>0.53</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>36.83</v>
@@ -12578,7 +12578,7 @@
         <v>2.76</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>37.06</v>
@@ -12653,7 +12653,7 @@
         <v>2.56</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>37.29</v>
@@ -12728,7 +12728,7 @@
         <v>-0.2</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>37.54</v>
@@ -12803,7 +12803,7 @@
         <v>-0.35</v>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>37.78</v>
@@ -12878,7 +12878,7 @@
         <v>3.04</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>38.08</v>
@@ -12953,7 +12953,7 @@
         <v>2.02</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>38.4</v>
@@ -13028,7 +13028,7 @@
         <v>1.53</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>38.71</v>
@@ -13103,7 +13103,7 @@
         <v>-0.31</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>38.97</v>
@@ -13178,7 +13178,7 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>39.25</v>
@@ -13253,7 +13253,7 @@
         <v>-0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>39.53</v>
@@ -13328,7 +13328,7 @@
         <v>2.33</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>39.85</v>
@@ -13403,7 +13403,7 @@
         <v>1.24</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>40.17</v>
@@ -13478,7 +13478,7 @@
         <v>-1.52</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>40.49</v>
@@ -13553,7 +13553,7 @@
         <v>2.7</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>40.84</v>
@@ -13628,7 +13628,7 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>41.19</v>
@@ -13703,7 +13703,7 @@
         <v>1.61</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>41.54</v>
@@ -13778,7 +13778,7 @@
         <v>4.03</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>41.97</v>
@@ -13853,7 +13853,7 @@
         <v>-0.97</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>42.38</v>
@@ -13928,7 +13928,7 @@
         <v>3.27</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>42.91</v>
@@ -14003,7 +14003,7 @@
         <v>1.74</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>43.46</v>
@@ -14078,7 +14078,7 @@
         <v>-4.43</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>43.86</v>
@@ -14153,7 +14153,7 @@
         <v>1.55</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>44.25</v>
@@ -14228,7 +14228,7 @@
         <v>-8.24</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>44.44</v>
@@ -14307,7 +14307,7 @@
         <v>0.21</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>44.64</v>
@@ -14382,7 +14382,7 @@
         <v>0.68</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>44.8</v>
@@ -14457,7 +14457,7 @@
         <v>-0.43</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>44.9</v>
@@ -14532,7 +14532,7 @@
         <v>-3.61</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>44.9</v>
@@ -14607,7 +14607,7 @@
         <v>0.71</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>44.92</v>
@@ -14682,7 +14682,7 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>44.93</v>
@@ -14757,7 +14757,7 @@
         <v>2.57</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>45.02</v>
@@ -14832,7 +14832,7 @@
         <v>-0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>45.05</v>
@@ -14907,7 +14907,7 @@
         <v>-0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>45.03</v>
@@ -14982,7 +14982,7 @@
         <v>-2.33</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>45</v>
@@ -15057,7 +15057,7 @@
         <v>2.13</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>44.95</v>
@@ -15132,7 +15132,7 @@
         <v>-0.23</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>44.9</v>
@@ -15207,7 +15207,7 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>44.82</v>
@@ -15282,7 +15282,7 @@
         <v>4.26</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>44.75</v>
@@ -15357,7 +15357,7 @@
         <v>1.44</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>44.73</v>
@@ -15432,7 +15432,7 @@
         <v>4.03</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>44.73</v>
@@ -15507,7 +15507,7 @@
         <v>-1.86</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>44.64</v>
@@ -15582,7 +15582,7 @@
         <v>-3.08</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>44.59</v>
@@ -15657,7 +15657,7 @@
         <v>-1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>44.48</v>
@@ -15732,7 +15732,7 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>44.59</v>
@@ -15807,7 +15807,7 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>44.72</v>
@@ -15882,7 +15882,7 @@
         <v>-1.44</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>44.8</v>
@@ -15961,7 +15961,7 @@
         <v>-1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>44.87</v>
@@ -16036,7 +16036,7 @@
         <v>2.94</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>45.08</v>
@@ -16111,7 +16111,7 @@
         <v>0.09</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>45.28</v>
@@ -16186,7 +16186,7 @@
         <v>3.71</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>45.54</v>
@@ -16261,7 +16261,7 @@
         <v>5.81</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>45.88</v>
@@ -16336,7 +16336,7 @@
         <v>2.56</v>
       </c>
       <c r="I210" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>46.3</v>
@@ -16411,7 +16411,7 @@
         <v>1.16</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>46.77</v>
@@ -16486,7 +16486,7 @@
         <v>-0.11</v>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>47.29</v>
@@ -16561,7 +16561,7 @@
         <v>-2.47</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>47.7</v>
@@ -16636,7 +16636,7 @@
         <v>2.3</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>48.16</v>
@@ -16711,7 +16711,7 @@
         <v>-0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>48.6</v>
@@ -16786,7 +16786,7 @@
         <v>4.67</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>49.07</v>
@@ -16861,7 +16861,7 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>49.55</v>
@@ -16936,7 +16936,7 @@
         <v>2.76</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>50.02</v>
@@ -17011,7 +17011,7 @@
         <v>-2.64</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>50.45</v>
@@ -17086,7 +17086,7 @@
         <v>3.58</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>51.06</v>
@@ -17161,7 +17161,7 @@
         <v>-0.65</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>51.67</v>
@@ -17236,7 +17236,7 @@
         <v>4.38</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>52.38</v>
@@ -17311,7 +17311,7 @@
         <v>-1.56</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>53.03</v>
@@ -17386,7 +17386,7 @@
         <v>2.71</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>53.78</v>
@@ -17461,7 +17461,7 @@
         <v>2.53</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>54.64</v>
@@ -17536,7 +17536,7 @@
         <v>3.79</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>55.55</v>
@@ -17611,7 +17611,7 @@
         <v>0.59</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>56.48</v>
@@ -17686,7 +17686,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>57.62</v>
@@ -17761,7 +17761,7 @@
         <v>-7.19</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>58.36</v>
@@ -17836,7 +17836,7 @@
         <v>4.5</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>59.18</v>
@@ -17911,7 +17911,7 @@
         <v>-6.61</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>59.74</v>
@@ -17986,7 +17986,7 @@
         <v>2.06</v>
       </c>
       <c r="I232" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>60.38</v>
@@ -18061,7 +18061,7 @@
         <v>5.06</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>61.24</v>
@@ -18136,7 +18136,7 @@
         <v>6.7</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>62.28</v>
@@ -18211,7 +18211,7 @@
         <v>-3.73</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>63.19</v>
@@ -18286,7 +18286,7 @@
         <v>-1.76</v>
       </c>
       <c r="I236" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>63.92</v>
@@ -18361,7 +18361,7 @@
         <v>3.83</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>64.73999999999999</v>
@@ -18436,7 +18436,7 @@
         <v>6.7</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>65.72</v>
@@ -18511,7 +18511,7 @@
         <v>1.77</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>66.84</v>
@@ -18586,7 +18586,7 @@
         <v>7.58</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>68.16</v>
@@ -18661,7 +18661,7 @@
         <v>-1.47</v>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>69.44</v>
@@ -18736,7 +18736,7 @@
         <v>-2.76</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>70.48</v>
@@ -18811,7 +18811,7 @@
         <v>5.39</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>71.78</v>
@@ -18886,7 +18886,7 @@
         <v>-1.67</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>72.94</v>
@@ -18961,7 +18961,7 @@
         <v>3.78</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>74.17</v>
@@ -19036,7 +19036,7 @@
         <v>6.63</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>75.56999999999999</v>
@@ -19111,7 +19111,7 @@
         <v>5.84</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>77.23</v>
@@ -19186,7 +19186,7 @@
         <v>3.3</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>78.75</v>
@@ -19261,7 +19261,7 @@
         <v>3.95</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>80.73</v>
@@ -19336,7 +19336,7 @@
         <v>-0.03</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>82.56</v>
@@ -19411,7 +19411,7 @@
         <v>-28.54</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>83.11</v>
@@ -19490,7 +19490,7 @@
         <v>-3.98</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>83.45</v>
@@ -19565,7 +19565,7 @@
         <v>6.24</v>
       </c>
       <c r="I253" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>83.84</v>
@@ -19640,7 +19640,7 @@
         <v>2.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>84.11</v>
@@ -19715,7 +19715,7 @@
         <v>-15.77</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19790,7 +19790,7 @@
         <v>5.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>83.92</v>
@@ -19865,7 +19865,7 @@
         <v>8.33</v>
       </c>
       <c r="I257" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>84.11</v>
@@ -19940,7 +19940,7 @@
         <v>-3.46</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>83.92</v>
@@ -20015,7 +20015,7 @@
         <v>4.29</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>83.81999999999999</v>
@@ -20090,7 +20090,7 @@
         <v>-11.53</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>82.97</v>
@@ -20165,7 +20165,7 @@
         <v>2.94</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>82.29000000000001</v>
@@ -20240,7 +20240,7 @@
         <v>-4.8</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>81.56</v>
@@ -20319,7 +20319,7 @@
         <v>5.6</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>80.8</v>
@@ -20394,7 +20394,7 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>80.15000000000001</v>
@@ -20469,7 +20469,7 @@
         <v>7.9</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>79.62</v>
@@ -20544,7 +20544,7 @@
         <v>5.16</v>
       </c>
       <c r="I266" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" t="n">
         <v>79.01000000000001</v>
@@ -20619,7 +20619,7 @@
         <v>-1.85</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>78.04000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>76.97</v>
@@ -20769,7 +20769,7 @@
         <v>0.51</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>75.70999999999999</v>
@@ -20844,7 +20844,7 @@
         <v>5.64</v>
       </c>
       <c r="I270" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>74.68000000000001</v>
@@ -20919,7 +20919,7 @@
         <v>-4.02</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>74.98999999999999</v>
@@ -20994,7 +20994,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I272" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21073,7 +21073,7 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>75.02</v>
@@ -21148,7 +21148,7 @@
         <v>-1.42</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>74.77</v>
@@ -21227,7 +21227,7 @@
         <v>2.25</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>75.23</v>
@@ -21306,7 +21306,7 @@
         <v>3.06</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>75.64</v>
@@ -21381,7 +21381,7 @@
         <v>2.34</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>75.84</v>
@@ -21456,7 +21456,7 @@
         <v>-2.72</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>76.06</v>
@@ -21531,7 +21531,7 @@
         <v>-1.84</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>76.06</v>
@@ -21600,7 +21600,7 @@
         <v>-4.96</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>76.31</v>
@@ -21683,7 +21683,7 @@
         <v>0.73</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>76.48</v>
@@ -21758,7 +21758,7 @@
         <v>-2.13</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>76.75</v>
@@ -21833,7 +21833,7 @@
         <v>-4.13</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>76.68000000000001</v>
@@ -21908,7 +21908,7 @@
         <v>-4.4</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>76.41</v>
@@ -21983,7 +21983,7 @@
         <v>-6.33</v>
       </c>
       <c r="I285" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" s="4" t="n">
         <v>75.66</v>
@@ -22066,7 +22066,7 @@
         <v>1.54</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>74.75</v>
@@ -22141,7 +22141,7 @@
         <v>0.77</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>73.95</v>
@@ -22216,7 +22216,7 @@
         <v>3.59</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>73.2</v>
@@ -22291,7 +22291,7 @@
         <v>-6.81</v>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>72.22</v>
@@ -22370,7 +22370,7 @@
         <v>4.39</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>71.14</v>
@@ -22449,7 +22449,7 @@
         <v>0.13</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>70.23999999999999</v>
@@ -22524,7 +22524,7 @@
         <v>7.27</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>69.91</v>
@@ -22599,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>69.55</v>
@@ -22674,7 +22674,7 @@
         <v>-3.45</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>69.13</v>
@@ -22749,7 +22749,7 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>68.64</v>
@@ -22824,7 +22824,7 @@
         <v>-0.23</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>68.02</v>
@@ -22903,7 +22903,7 @@
         <v>2.32</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>67.39</v>
@@ -22978,7 +22978,7 @@
         <v>1.36</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>66.91</v>
@@ -23053,7 +23053,7 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>66.54000000000001</v>
@@ -23128,7 +23128,7 @@
         <v>-1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>66.31999999999999</v>
@@ -23203,7 +23203,7 @@
         <v>5.51</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>66.26000000000001</v>
@@ -23278,7 +23278,7 @@
         <v>-0.28</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>66.27</v>
@@ -23353,7 +23353,7 @@
         <v>-0.84</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>66.40000000000001</v>
@@ -23428,7 +23428,7 @@
         <v>3.35</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>66.8</v>
@@ -23503,7 +23503,7 @@
         <v>-2.01</v>
       </c>
       <c r="I305" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>67.33</v>
@@ -23578,7 +23578,7 @@
         <v>-5.07</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>67.63</v>
@@ -23653,7 +23653,7 @@
         <v>2.74</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>68</v>
@@ -23728,7 +23728,7 @@
         <v>-2.83</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>68.16</v>
@@ -23803,7 +23803,7 @@
         <v>0.6</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>68.56</v>
@@ -23878,7 +23878,7 @@
         <v>-0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>68.8</v>
@@ -23957,7 +23957,7 @@
         <v>-3.12</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>68.94</v>
@@ -24036,7 +24036,7 @@
         <v>-2.05</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>68.77</v>
@@ -24111,7 +24111,7 @@
         <v>2.81</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>68.7</v>
@@ -24186,7 +24186,7 @@
         <v>2.45</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>68.81999999999999</v>
@@ -24261,7 +24261,7 @@
         <v>-3.44</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>68.81999999999999</v>
@@ -24340,7 +24340,7 @@
         <v>-0.05</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>68.81999999999999</v>
@@ -24415,7 +24415,7 @@
         <v>6.4</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>68.95</v>
@@ -24490,7 +24490,7 @@
         <v>2.1</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>69.11</v>
@@ -24565,7 +24565,7 @@
         <v>1.97</v>
       </c>
       <c r="I319" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>69.31</v>
@@ -24640,7 +24640,7 @@
         <v>6.83</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>69.79000000000001</v>
@@ -24715,7 +24715,7 @@
         <v>0.71</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>70.12</v>
@@ -24790,7 +24790,7 @@
         <v>1.02</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>70.48999999999999</v>
@@ -24865,7 +24865,7 @@
         <v>-4.84</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>70.70999999999999</v>
@@ -24940,7 +24940,7 @@
         <v>-8.57</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>70.48</v>
@@ -25019,7 +25019,7 @@
         <v>1.3</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>70.37</v>
@@ -25094,7 +25094,7 @@
         <v>-4.35</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>70.29000000000001</v>
@@ -25169,7 +25169,7 @@
         <v>2.74</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>70.20999999999999</v>
@@ -25244,7 +25244,7 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>70.26000000000001</v>
@@ -25319,7 +25319,7 @@
         <v>-1.57</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>70.23999999999999</v>
@@ -25394,7 +25394,7 @@
         <v>1.99</v>
       </c>
       <c r="I330" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" t="n">
         <v>70.31</v>
@@ -25469,7 +25469,7 @@
         <v>-3.18</v>
       </c>
       <c r="I331" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" t="n">
         <v>70.37</v>
@@ -25544,7 +25544,7 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>70.55</v>
@@ -25619,7 +25619,7 @@
         <v>-0.04</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>70.63</v>
@@ -25694,7 +25694,7 @@
         <v>-0.97</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>70.59999999999999</v>
@@ -25769,7 +25769,7 @@
         <v>0.47</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>70.7</v>
@@ -25844,7 +25844,7 @@
         <v>-2.62</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>70.72</v>
@@ -25919,7 +25919,7 @@
         <v>1.16</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>70.56</v>
@@ -25994,7 +25994,7 @@
         <v>-8.08</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>70.06</v>
@@ -26069,7 +26069,7 @@
         <v>0.02</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>69.48999999999999</v>
@@ -26144,7 +26144,7 @@
         <v>-4.17</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>68.54000000000001</v>
@@ -26223,7 +26223,7 @@
         <v>-2.29</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>67.48999999999999</v>
@@ -26302,7 +26302,7 @@
         <v>5.48</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>66.56999999999999</v>
@@ -26377,7 +26377,7 @@
         <v>0.77</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>65.86</v>
@@ -26452,7 +26452,7 @@
         <v>3.56</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>65.58</v>
@@ -26527,7 +26527,7 @@
         <v>-0.13</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>65.25</v>
@@ -26602,7 +26602,7 @@
         <v>-4.39</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>64.94</v>
@@ -26677,7 +26677,7 @@
         <v>-1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>64.47</v>
@@ -26752,7 +26752,7 @@
         <v>-1.01</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>63.95</v>
@@ -26827,7 +26827,7 @@
         <v>-5.4</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>63.32</v>
@@ -26906,7 +26906,7 @@
         <v>-7.09</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>62.42</v>
@@ -26985,7 +26985,7 @@
         <v>1.12</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>61.66</v>
@@ -27064,7 +27064,7 @@
         <v>1.76</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>60.91</v>
@@ -27139,7 +27139,7 @@
         <v>-1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>60.12</v>
@@ -27214,7 +27214,7 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>59.42</v>
@@ -27289,7 +27289,7 @@
         <v>0.21</v>
       </c>
       <c r="I355" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>58.69</v>
@@ -27364,7 +27364,7 @@
         <v>2.69</v>
       </c>
       <c r="I356" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>58.14</v>
@@ -27439,7 +27439,7 @@
         <v>1.98</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>57.59</v>
@@ -27514,7 +27514,7 @@
         <v>-2.94</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>57.24</v>
@@ -27593,7 +27593,7 @@
         <v>-2.99</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>56.8</v>
@@ -27672,7 +27672,7 @@
         <v>2.48</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>56.55</v>
@@ -27747,7 +27747,7 @@
         <v>-0.35</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>56.37</v>
@@ -27822,7 +27822,7 @@
         <v>-3.32</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>55.94</v>
@@ -27897,7 +27897,7 @@
         <v>1.94</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>55.53</v>
@@ -27972,7 +27972,7 @@
         <v>-1.81</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>54.97</v>
@@ -28047,7 +28047,7 @@
         <v>-3.49</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>54.32</v>
@@ -28122,7 +28122,7 @@
         <v>0.77</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>53.83</v>
@@ -28197,7 +28197,7 @@
         <v>0.39</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>53.4</v>
@@ -28272,7 +28272,7 @@
         <v>4.12</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>53.11</v>
@@ -28347,7 +28347,7 @@
         <v>1.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>53.02</v>
@@ -28422,7 +28422,7 @@
         <v>-3.45</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>53.03</v>
@@ -28501,7 +28501,7 @@
         <v>1.02</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>53.04</v>
@@ -28576,7 +28576,7 @@
         <v>0.65</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>53.03</v>
@@ -28651,7 +28651,7 @@
         <v>-2.32</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>52.98</v>
@@ -28726,7 +28726,7 @@
         <v>0.14</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>52.89</v>
@@ -28801,7 +28801,7 @@
         <v>3.34</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>52.89</v>
@@ -28876,7 +28876,7 @@
         <v>-2.13</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>52.75</v>
@@ -28955,7 +28955,7 @@
         <v>0.19</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>52.57</v>
@@ -29030,7 +29030,7 @@
         <v>2.63</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>52.54</v>
@@ -29105,7 +29105,7 @@
         <v>4.14</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>52.7</v>
@@ -29180,7 +29180,7 @@
         <v>-0.39</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>52.79</v>
@@ -29255,7 +29255,7 @@
         <v>2.95</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>52.97</v>
@@ -29330,7 +29330,7 @@
         <v>3.32</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>53.33</v>
@@ -29405,7 +29405,7 @@
         <v>-1.45</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>53.6</v>
@@ -29480,7 +29480,7 @@
         <v>0.87</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>53.94</v>
@@ -29555,7 +29555,7 @@
         <v>-1.52</v>
       </c>
       <c r="I385" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>54.33</v>
@@ -29630,7 +29630,7 @@
         <v>0.55</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>54.71</v>
@@ -29705,7 +29705,7 @@
         <v>1.86</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>55.14</v>
@@ -29780,7 +29780,7 @@
         <v>-3.58</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>55.36</v>
@@ -29859,7 +29859,7 @@
         <v>4.47</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>55.67</v>
@@ -29934,7 +29934,7 @@
         <v>2.75</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>56.15</v>
@@ -30009,7 +30009,7 @@
         <v>1.72</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>56.65</v>
@@ -30084,7 +30084,7 @@
         <v>-0.83</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>57.12</v>
@@ -30159,7 +30159,7 @@
         <v>0.19</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>57.65</v>
@@ -30234,7 +30234,7 @@
         <v>-1.17</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>58.14</v>
@@ -30309,7 +30309,7 @@
         <v>1.92</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>58.6</v>
@@ -30384,7 +30384,7 @@
         <v>-4.38</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>58.98</v>
@@ -30459,7 +30459,7 @@
         <v>0.18</v>
       </c>
       <c r="I397" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>59.37</v>
@@ -30534,7 +30534,7 @@
         <v>-3.68</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>59.57</v>
@@ -30613,7 +30613,7 @@
         <v>1.99</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>59.72</v>
@@ -30688,7 +30688,7 @@
         <v>2.51</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>59.96</v>
@@ -30763,7 +30763,7 @@
         <v>-1.21</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>60.07</v>
@@ -30842,7 +30842,7 @@
         <v>-0.75</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>60.07</v>
@@ -30917,7 +30917,7 @@
         <v>2.27</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>60.18</v>
@@ -30992,7 +30992,7 @@
         <v>-5.3</v>
       </c>
       <c r="I404" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>60.1</v>
@@ -31071,7 +31071,7 @@
         <v>1.08</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>60.1</v>
@@ -31146,7 +31146,7 @@
         <v>-2.2</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>60.02</v>
@@ -31221,7 +31221,7 @@
         <v>1.21</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>59.92</v>
@@ -31296,7 +31296,7 @@
         <v>-0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>59.9</v>
@@ -31371,7 +31371,7 @@
         <v>3.37</v>
       </c>
       <c r="I409" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" t="n">
         <v>59.84</v>
@@ -31446,7 +31446,7 @@
         <v>1.63</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>59.76</v>
@@ -31521,7 +31521,7 @@
         <v>-0.5</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>59.6</v>
@@ -31596,7 +31596,7 @@
         <v>1.84</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>59.53</v>
@@ -31644,25 +31644,41 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>59</v>
+      </c>
+      <c r="D413" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="E413" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="F413" t="n">
+        <v>58.16</v>
+      </c>
       <c r="G413" t="n">
-        <v>14859069</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>14949400</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-4.23</v>
       </c>
       <c r="I413" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.91</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>55.69</v>
+        <v>47.35</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>
@@ -31677,7 +31693,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>5.11</v>
       </c>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31681,7 +31681,7 @@
         <v>47.35</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31711,6 +31711,79 @@
       <c r="W413" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="D414" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="E414" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="F414" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="G414" t="n">
+        <v>12078484</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31657,7 +31657,7 @@
         <v>58.16</v>
       </c>
       <c r="G413" t="n">
-        <v>14949400</v>
+        <v>14987000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-4.23</v>
@@ -31733,13 +31733,13 @@
         <v>56.95</v>
       </c>
       <c r="F414" t="n">
-        <v>57.49</v>
+        <v>57.62</v>
       </c>
       <c r="G414" t="n">
-        <v>12078484</v>
+        <v>15730363</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.93</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
@@ -31757,10 +31757,10 @@
         <v>65.93000000000001</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>40.64</v>
+        <v>40.96</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31774,16 +31774,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31723,41 +31723,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>57.29</v>
-      </c>
-      <c r="D414" t="n">
-        <v>57.83</v>
-      </c>
-      <c r="E414" t="n">
-        <v>56.95</v>
-      </c>
-      <c r="F414" t="n">
-        <v>57.62</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>15730363</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>-0.93</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="K414" t="n">
-        <v>56.72</v>
-      </c>
-      <c r="L414" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="M414" t="n">
-        <v>65.93000000000001</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>40.96</v>
+        <v>42.37</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31723,25 +31723,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="D414" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="E414" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="F414" t="n">
+        <v>57.62</v>
+      </c>
       <c r="G414" t="n">
-        <v>15730363</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>15754400</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.93</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.93000000000001</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>42.37</v>
+        <v>40.96</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31627,11 +31627,19 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>27.75</v>
@@ -683,7 +683,7 @@
         <v>1.92</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>27.87</v>
@@ -758,7 +758,7 @@
         <v>0.44</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>27.97</v>
@@ -833,7 +833,7 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>28.07</v>
@@ -908,7 +908,7 @@
         <v>-1.19</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>28.16</v>
@@ -983,7 +983,7 @@
         <v>0.59</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>28.24</v>
@@ -1058,7 +1058,7 @@
         <v>-0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>28.34</v>
@@ -1133,7 +1133,7 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>28.44</v>
@@ -1208,7 +1208,7 @@
         <v>0.41</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>28.52</v>
@@ -1283,7 +1283,7 @@
         <v>-0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>28.58</v>
@@ -1358,7 +1358,7 @@
         <v>2.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>28.7</v>
@@ -1433,7 +1433,7 @@
         <v>-0.33</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>28.79</v>
@@ -1508,7 +1508,7 @@
         <v>0.47</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>28.88</v>
@@ -1583,7 +1583,7 @@
         <v>-1.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>28.97</v>
@@ -1658,7 +1658,7 @@
         <v>-0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>29.05</v>
@@ -1733,7 +1733,7 @@
         <v>-2.07</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>29.12</v>
@@ -1812,7 +1812,7 @@
         <v>0.38</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>29.18</v>
@@ -1887,7 +1887,7 @@
         <v>-1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>29.2</v>
@@ -1962,7 +1962,7 @@
         <v>-0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>29.18</v>
@@ -2041,7 +2041,7 @@
         <v>1.55</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>29.19</v>
@@ -2116,7 +2116,7 @@
         <v>0.87</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.21</v>
@@ -2191,7 +2191,7 @@
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.24</v>
@@ -2266,7 +2266,7 @@
         <v>-0.27</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.26</v>
@@ -2341,7 +2341,7 @@
         <v>-0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.27</v>
@@ -2416,7 +2416,7 @@
         <v>-1.62</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.27</v>
@@ -2499,7 +2499,7 @@
         <v>2.92</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.31</v>
@@ -2578,7 +2578,7 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.37</v>
@@ -2653,7 +2653,7 @@
         <v>1.72</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.44</v>
@@ -2728,7 +2728,7 @@
         <v>-0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.5</v>
@@ -2803,7 +2803,7 @@
         <v>0.33</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.58</v>
@@ -2878,7 +2878,7 @@
         <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.62</v>
@@ -2953,7 +2953,7 @@
         <v>-0.32</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.67</v>
@@ -3028,7 +3028,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.7</v>
@@ -3103,7 +3103,7 @@
         <v>-1.57</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.72</v>
@@ -3178,7 +3178,7 @@
         <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.75</v>
@@ -3253,7 +3253,7 @@
         <v>2.07</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.83</v>
@@ -3328,7 +3328,7 @@
         <v>-0.16</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>29.91</v>
@@ -3403,7 +3403,7 @@
         <v>2.59</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>30.06</v>
@@ -3478,7 +3478,7 @@
         <v>-1.02</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>30.19</v>
@@ -3553,7 +3553,7 @@
         <v>-0.03</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>30.3</v>
@@ -3628,7 +3628,7 @@
         <v>-1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>30.39</v>
@@ -3703,7 +3703,7 @@
         <v>0.42</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>30.44</v>
@@ -3778,7 +3778,7 @@
         <v>-6.08</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30.4</v>
@@ -3861,7 +3861,7 @@
         <v>-6.27</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30.27</v>
@@ -3944,7 +3944,7 @@
         <v>0.22</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>30.17</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>30.03</v>
@@ -4110,7 +4110,7 @@
         <v>3.39</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>29.92</v>
@@ -4189,7 +4189,7 @@
         <v>0.78</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>29.8</v>
@@ -4268,7 +4268,7 @@
         <v>3.22</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4347,7 +4347,7 @@
         <v>0.65</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>29.65</v>
@@ -4422,7 +4422,7 @@
         <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>29.58</v>
@@ -4497,7 +4497,7 @@
         <v>1.19</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.53</v>
@@ -4576,7 +4576,7 @@
         <v>-0.71</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.48</v>
@@ -4655,7 +4655,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.47</v>
@@ -4730,7 +4730,7 @@
         <v>-0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.45</v>
@@ -4805,7 +4805,7 @@
         <v>3.59</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.45</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.45</v>
@@ -4959,7 +4959,7 @@
         <v>-1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.39</v>
@@ -5034,7 +5034,7 @@
         <v>0.47</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.35</v>
@@ -5109,7 +5109,7 @@
         <v>-1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.29</v>
@@ -5184,7 +5184,7 @@
         <v>-0.77</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.24</v>
@@ -5263,7 +5263,7 @@
         <v>-0.71</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.17</v>
@@ -5338,7 +5338,7 @@
         <v>-0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.18</v>
@@ -5417,7 +5417,7 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.3</v>
@@ -5492,7 +5492,7 @@
         <v>2.51</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.45</v>
@@ -5567,7 +5567,7 @@
         <v>-2.42</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.57</v>
@@ -5646,7 +5646,7 @@
         <v>-0.1</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.64</v>
@@ -5721,7 +5721,7 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.72</v>
@@ -5796,7 +5796,7 @@
         <v>-0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.74</v>
@@ -5875,7 +5875,7 @@
         <v>1.01</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.77</v>
@@ -5950,7 +5950,7 @@
         <v>-2.27</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.76</v>
@@ -6029,7 +6029,7 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.75</v>
@@ -6104,7 +6104,7 @@
         <v>-1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.74</v>
@@ -6179,7 +6179,7 @@
         <v>0.41</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6254,7 +6254,7 @@
         <v>2.41</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.75</v>
@@ -6329,7 +6329,7 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.75</v>
@@ -6404,7 +6404,7 @@
         <v>-1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.72</v>
@@ -6479,7 +6479,7 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6554,7 +6554,7 @@
         <v>-0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>29.74</v>
@@ -6629,7 +6629,7 @@
         <v>-0.83</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>29.75</v>
@@ -6704,7 +6704,7 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.79</v>
@@ -6779,7 +6779,7 @@
         <v>-0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.82</v>
@@ -6854,7 +6854,7 @@
         <v>5.3</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>29.94</v>
@@ -6929,7 +6929,7 @@
         <v>-0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>30.04</v>
@@ -7004,7 +7004,7 @@
         <v>-0.32</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>30.09</v>
@@ -7079,7 +7079,7 @@
         <v>3.54</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>30.24</v>
@@ -7154,7 +7154,7 @@
         <v>0.74</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>30.4</v>
@@ -7229,7 +7229,7 @@
         <v>2.14</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>30.58</v>
@@ -7304,7 +7304,7 @@
         <v>-0.48</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>30.76</v>
@@ -7379,7 +7379,7 @@
         <v>-0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>30.91</v>
@@ -7454,7 +7454,7 @@
         <v>0.33</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>31.1</v>
@@ -7529,7 +7529,7 @@
         <v>-0.27</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>31.27</v>
@@ -7604,7 +7604,7 @@
         <v>0.18</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>31.46</v>
@@ -7679,7 +7679,7 @@
         <v>2.15</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>31.68</v>
@@ -7754,7 +7754,7 @@
         <v>-1.39</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>31.83</v>
@@ -7829,7 +7829,7 @@
         <v>-1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>31.94</v>
@@ -7904,7 +7904,7 @@
         <v>0.73</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>32.09</v>
@@ -7979,7 +7979,7 @@
         <v>-1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>32.2</v>
@@ -8054,7 +8054,7 @@
         <v>1.23</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>32.34</v>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>32.5</v>
@@ -8204,7 +8204,7 @@
         <v>-2.16</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>32.62</v>
@@ -8279,7 +8279,7 @@
         <v>0.58</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>32.76</v>
@@ -8354,7 +8354,7 @@
         <v>-0.24</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>32.82</v>
@@ -8433,7 +8433,7 @@
         <v>1.56</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>32.91</v>
@@ -8508,7 +8508,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>33.02</v>
@@ -8583,7 +8583,7 @@
         <v>-0.24</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>33.07</v>
@@ -8658,7 +8658,7 @@
         <v>-0.42</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>33.1</v>
@@ -8733,7 +8733,7 @@
         <v>-0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>33.08</v>
@@ -8812,7 +8812,7 @@
         <v>2.27</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>33.1</v>
@@ -8887,7 +8887,7 @@
         <v>3.79</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>33.21</v>
@@ -8962,7 +8962,7 @@
         <v>-1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.28</v>
@@ -9037,7 +9037,7 @@
         <v>-1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.35</v>
@@ -9112,7 +9112,7 @@
         <v>0.44</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.42</v>
@@ -9187,7 +9187,7 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>33.46</v>
@@ -9262,7 +9262,7 @@
         <v>-0.12</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>33.53</v>
@@ -9337,7 +9337,7 @@
         <v>2.14</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>33.66</v>
@@ -9412,7 +9412,7 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>33.8</v>
@@ -9487,7 +9487,7 @@
         <v>-0.08</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>33.95</v>
@@ -9562,7 +9562,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>34.08</v>
@@ -9637,7 +9637,7 @@
         <v>-2.34</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>34.14</v>
@@ -9712,7 +9712,7 @@
         <v>-0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>34.24</v>
@@ -9787,7 +9787,7 @@
         <v>0.06</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>34.34</v>
@@ -9862,7 +9862,7 @@
         <v>-3.32</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>34.38</v>
@@ -9941,7 +9941,7 @@
         <v>-0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.38</v>
@@ -10091,7 +10091,7 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.41</v>
@@ -10166,7 +10166,7 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.46</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>34.53</v>
@@ -10316,7 +10316,7 @@
         <v>1.19</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.58</v>
@@ -10391,7 +10391,7 @@
         <v>0.35</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.58</v>
@@ -10466,7 +10466,7 @@
         <v>-2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.55</v>
@@ -10545,7 +10545,7 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.56</v>
@@ -10620,7 +10620,7 @@
         <v>1.71</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.59</v>
@@ -10695,7 +10695,7 @@
         <v>-1.43</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.58</v>
@@ -10849,7 +10849,7 @@
         <v>0.14</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.54</v>
@@ -10924,7 +10924,7 @@
         <v>-1.97</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.44</v>
@@ -11003,7 +11003,7 @@
         <v>1.65</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.38</v>
@@ -11078,7 +11078,7 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.34</v>
@@ -11153,7 +11153,7 @@
         <v>2.11</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.37</v>
@@ -11228,7 +11228,7 @@
         <v>-0.91</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.39</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>34.41</v>
@@ -11378,7 +11378,7 @@
         <v>-0.09</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>34.48</v>
@@ -11453,7 +11453,7 @@
         <v>1.51</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>34.59</v>
@@ -11528,7 +11528,7 @@
         <v>1.89</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>34.72</v>
@@ -11603,7 +11603,7 @@
         <v>2.65</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>34.88</v>
@@ -11678,7 +11678,7 @@
         <v>0.51</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>35.03</v>
@@ -11753,7 +11753,7 @@
         <v>-1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>35.16</v>
@@ -11828,7 +11828,7 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>35.28</v>
@@ -11903,7 +11903,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>35.41</v>
@@ -11978,7 +11978,7 @@
         <v>-0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>35.56</v>
@@ -12053,7 +12053,7 @@
         <v>0.62</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>35.71</v>
@@ -12128,7 +12128,7 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>35.85</v>
@@ -12203,7 +12203,7 @@
         <v>1.46</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>36.04</v>
@@ -12278,7 +12278,7 @@
         <v>1.1</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>36.26</v>
@@ -12353,7 +12353,7 @@
         <v>-0.41</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>36.46</v>
@@ -12428,7 +12428,7 @@
         <v>-2.1</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>36.66</v>
@@ -12503,7 +12503,7 @@
         <v>0.53</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>36.83</v>
@@ -12578,7 +12578,7 @@
         <v>2.76</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>37.06</v>
@@ -12653,7 +12653,7 @@
         <v>2.56</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>37.29</v>
@@ -12728,7 +12728,7 @@
         <v>-0.2</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>37.54</v>
@@ -12803,7 +12803,7 @@
         <v>-0.35</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>37.78</v>
@@ -12878,7 +12878,7 @@
         <v>3.04</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>38.08</v>
@@ -12953,7 +12953,7 @@
         <v>2.02</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>38.4</v>
@@ -13028,7 +13028,7 @@
         <v>1.53</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>38.71</v>
@@ -13103,7 +13103,7 @@
         <v>-0.31</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>38.97</v>
@@ -13178,7 +13178,7 @@
         <v>1.27</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>39.25</v>
@@ -13253,7 +13253,7 @@
         <v>-0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>39.53</v>
@@ -13328,7 +13328,7 @@
         <v>2.33</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>39.85</v>
@@ -13403,7 +13403,7 @@
         <v>1.24</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>40.17</v>
@@ -13478,7 +13478,7 @@
         <v>-1.52</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>40.49</v>
@@ -13553,7 +13553,7 @@
         <v>2.7</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>40.84</v>
@@ -13628,7 +13628,7 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>41.19</v>
@@ -13703,7 +13703,7 @@
         <v>1.61</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>41.54</v>
@@ -13778,7 +13778,7 @@
         <v>4.03</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>41.97</v>
@@ -13853,7 +13853,7 @@
         <v>-0.97</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>42.38</v>
@@ -13928,7 +13928,7 @@
         <v>3.27</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>42.91</v>
@@ -14003,7 +14003,7 @@
         <v>1.74</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>43.46</v>
@@ -14078,7 +14078,7 @@
         <v>-4.43</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>43.86</v>
@@ -14153,7 +14153,7 @@
         <v>1.55</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>44.25</v>
@@ -14228,7 +14228,7 @@
         <v>-8.24</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>44.44</v>
@@ -14307,7 +14307,7 @@
         <v>0.21</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>44.64</v>
@@ -14382,7 +14382,7 @@
         <v>0.68</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>44.8</v>
@@ -14457,7 +14457,7 @@
         <v>-0.43</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>44.9</v>
@@ -14532,7 +14532,7 @@
         <v>-3.61</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>44.9</v>
@@ -14607,7 +14607,7 @@
         <v>0.71</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>44.92</v>
@@ -14682,7 +14682,7 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>44.93</v>
@@ -14757,7 +14757,7 @@
         <v>2.57</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>45.02</v>
@@ -14832,7 +14832,7 @@
         <v>-0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>45.05</v>
@@ -14907,7 +14907,7 @@
         <v>-0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>45.03</v>
@@ -14982,7 +14982,7 @@
         <v>-2.33</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>45</v>
@@ -15057,7 +15057,7 @@
         <v>2.13</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>44.95</v>
@@ -15132,7 +15132,7 @@
         <v>-0.23</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>44.9</v>
@@ -15207,7 +15207,7 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>44.82</v>
@@ -15282,7 +15282,7 @@
         <v>4.26</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>44.75</v>
@@ -15357,7 +15357,7 @@
         <v>1.44</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>44.73</v>
@@ -15432,7 +15432,7 @@
         <v>4.03</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>44.73</v>
@@ -15507,7 +15507,7 @@
         <v>-1.86</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.64</v>
@@ -15582,7 +15582,7 @@
         <v>-3.08</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.59</v>
@@ -15657,7 +15657,7 @@
         <v>-1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>44.48</v>
@@ -15732,7 +15732,7 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>44.59</v>
@@ -15807,7 +15807,7 @@
         <v>0.76</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>44.72</v>
@@ -15882,7 +15882,7 @@
         <v>-1.44</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>44.8</v>
@@ -15961,7 +15961,7 @@
         <v>-1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>44.87</v>
@@ -16036,7 +16036,7 @@
         <v>2.94</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>45.08</v>
@@ -16111,7 +16111,7 @@
         <v>0.09</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>45.28</v>
@@ -16186,7 +16186,7 @@
         <v>3.71</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>45.54</v>
@@ -16261,7 +16261,7 @@
         <v>5.81</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>45.88</v>
@@ -16336,7 +16336,7 @@
         <v>2.56</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>46.3</v>
@@ -16411,7 +16411,7 @@
         <v>1.16</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>46.77</v>
@@ -16486,7 +16486,7 @@
         <v>-0.11</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>47.29</v>
@@ -16561,7 +16561,7 @@
         <v>-2.47</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>47.7</v>
@@ -16636,7 +16636,7 @@
         <v>2.3</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>48.16</v>
@@ -16711,7 +16711,7 @@
         <v>-0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>48.6</v>
@@ -16786,7 +16786,7 @@
         <v>4.67</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>49.07</v>
@@ -16861,7 +16861,7 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>49.55</v>
@@ -16936,7 +16936,7 @@
         <v>2.76</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>50.02</v>
@@ -17011,7 +17011,7 @@
         <v>-2.64</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>50.45</v>
@@ -17086,7 +17086,7 @@
         <v>3.58</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>51.06</v>
@@ -17161,7 +17161,7 @@
         <v>-0.65</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>51.67</v>
@@ -17236,7 +17236,7 @@
         <v>4.38</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>52.38</v>
@@ -17311,7 +17311,7 @@
         <v>-1.56</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>53.03</v>
@@ -17386,7 +17386,7 @@
         <v>2.71</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>53.78</v>
@@ -17461,7 +17461,7 @@
         <v>2.53</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>54.64</v>
@@ -17536,7 +17536,7 @@
         <v>3.79</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>55.55</v>
@@ -17611,7 +17611,7 @@
         <v>0.59</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>56.48</v>
@@ -17686,7 +17686,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>57.62</v>
@@ -17761,7 +17761,7 @@
         <v>-7.19</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>58.36</v>
@@ -17836,7 +17836,7 @@
         <v>4.5</v>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>59.18</v>
@@ -17911,7 +17911,7 @@
         <v>-6.61</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>59.74</v>
@@ -17986,7 +17986,7 @@
         <v>2.06</v>
       </c>
       <c r="I232" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" t="n">
         <v>60.38</v>
@@ -18061,7 +18061,7 @@
         <v>5.06</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>61.24</v>
@@ -18136,7 +18136,7 @@
         <v>6.7</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>62.28</v>
@@ -18211,7 +18211,7 @@
         <v>-3.73</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>63.19</v>
@@ -18286,7 +18286,7 @@
         <v>-1.76</v>
       </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" t="n">
         <v>63.92</v>
@@ -18361,7 +18361,7 @@
         <v>3.83</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>64.73999999999999</v>
@@ -18436,7 +18436,7 @@
         <v>6.7</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>65.72</v>
@@ -18511,7 +18511,7 @@
         <v>1.77</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>66.84</v>
@@ -18586,7 +18586,7 @@
         <v>7.58</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>68.16</v>
@@ -18661,7 +18661,7 @@
         <v>-1.47</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>69.44</v>
@@ -18736,7 +18736,7 @@
         <v>-2.76</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>70.48</v>
@@ -18811,7 +18811,7 @@
         <v>5.39</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>71.78</v>
@@ -18886,7 +18886,7 @@
         <v>-1.67</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>72.94</v>
@@ -18961,7 +18961,7 @@
         <v>3.78</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>74.17</v>
@@ -19036,7 +19036,7 @@
         <v>6.63</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>75.56999999999999</v>
@@ -19111,7 +19111,7 @@
         <v>5.84</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>77.23</v>
@@ -19186,7 +19186,7 @@
         <v>3.3</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>78.75</v>
@@ -19261,7 +19261,7 @@
         <v>3.95</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>80.73</v>
@@ -19336,7 +19336,7 @@
         <v>-0.03</v>
       </c>
       <c r="I250" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" t="n">
         <v>82.56</v>
@@ -19411,7 +19411,7 @@
         <v>-28.54</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>83.11</v>
@@ -19490,7 +19490,7 @@
         <v>-3.98</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>83.45</v>
@@ -19565,7 +19565,7 @@
         <v>6.24</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>83.84</v>
@@ -19640,7 +19640,7 @@
         <v>2.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>84.11</v>
@@ -19715,7 +19715,7 @@
         <v>-15.77</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19790,7 +19790,7 @@
         <v>5.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" t="n">
         <v>83.92</v>
@@ -19865,7 +19865,7 @@
         <v>8.33</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>84.11</v>
@@ -19940,7 +19940,7 @@
         <v>-3.46</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>83.92</v>
@@ -20015,7 +20015,7 @@
         <v>4.29</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>83.81999999999999</v>
@@ -20090,7 +20090,7 @@
         <v>-11.53</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>82.97</v>
@@ -20165,7 +20165,7 @@
         <v>2.94</v>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" t="n">
         <v>82.29000000000001</v>
@@ -20240,7 +20240,7 @@
         <v>-4.8</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>81.56</v>
@@ -20319,7 +20319,7 @@
         <v>5.6</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>80.8</v>
@@ -20394,7 +20394,7 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>80.15000000000001</v>
@@ -20469,7 +20469,7 @@
         <v>7.9</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>79.62</v>
@@ -20544,7 +20544,7 @@
         <v>5.16</v>
       </c>
       <c r="I266" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>79.01000000000001</v>
@@ -20619,7 +20619,7 @@
         <v>-1.85</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>78.04000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>1.21</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>76.97</v>
@@ -20769,7 +20769,7 @@
         <v>0.51</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>75.70999999999999</v>
@@ -20844,7 +20844,7 @@
         <v>5.64</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>74.68000000000001</v>
@@ -20919,7 +20919,7 @@
         <v>-4.02</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>74.98999999999999</v>
@@ -20994,7 +20994,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I272" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>75.09999999999999</v>
@@ -21073,7 +21073,7 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>75.02</v>
@@ -21148,7 +21148,7 @@
         <v>-1.42</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>74.77</v>
@@ -21227,7 +21227,7 @@
         <v>2.25</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>75.23</v>
@@ -21306,7 +21306,7 @@
         <v>3.06</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>75.64</v>
@@ -21381,7 +21381,7 @@
         <v>2.34</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>75.84</v>
@@ -21456,7 +21456,7 @@
         <v>-2.72</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>76.06</v>
@@ -21531,7 +21531,7 @@
         <v>-1.84</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>76.06</v>
@@ -21600,7 +21600,7 @@
         <v>-4.96</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>76.31</v>
@@ -21683,7 +21683,7 @@
         <v>0.73</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>76.48</v>
@@ -21758,7 +21758,7 @@
         <v>-2.13</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>76.75</v>
@@ -21833,7 +21833,7 @@
         <v>-4.13</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>76.68000000000001</v>
@@ -21908,7 +21908,7 @@
         <v>-4.4</v>
       </c>
       <c r="I284" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" t="n">
         <v>76.41</v>
@@ -21983,7 +21983,7 @@
         <v>-6.33</v>
       </c>
       <c r="I285" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" s="4" t="n">
         <v>75.66</v>
@@ -22066,7 +22066,7 @@
         <v>1.54</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>74.75</v>
@@ -22141,7 +22141,7 @@
         <v>0.77</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>73.95</v>
@@ -22216,7 +22216,7 @@
         <v>3.59</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>73.2</v>
@@ -22291,7 +22291,7 @@
         <v>-6.81</v>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>72.22</v>
@@ -22370,7 +22370,7 @@
         <v>4.39</v>
       </c>
       <c r="I290" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" t="n">
         <v>71.14</v>
@@ -22449,7 +22449,7 @@
         <v>0.13</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>70.23999999999999</v>
@@ -22524,7 +22524,7 @@
         <v>7.27</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>69.91</v>
@@ -22599,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>69.55</v>
@@ -22674,7 +22674,7 @@
         <v>-3.45</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>69.13</v>
@@ -22749,7 +22749,7 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>68.64</v>
@@ -22824,7 +22824,7 @@
         <v>-0.23</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>68.02</v>
@@ -22903,7 +22903,7 @@
         <v>2.32</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>67.39</v>
@@ -22978,7 +22978,7 @@
         <v>1.36</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>66.91</v>
@@ -23053,7 +23053,7 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>66.54000000000001</v>
@@ -23128,7 +23128,7 @@
         <v>-1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>66.31999999999999</v>
@@ -23203,7 +23203,7 @@
         <v>5.51</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>66.26000000000001</v>
@@ -23278,7 +23278,7 @@
         <v>-0.28</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>66.27</v>
@@ -23353,7 +23353,7 @@
         <v>-0.84</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>66.40000000000001</v>
@@ -23428,7 +23428,7 @@
         <v>3.35</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>66.8</v>
@@ -23503,7 +23503,7 @@
         <v>-2.01</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>67.33</v>
@@ -23578,7 +23578,7 @@
         <v>-5.07</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>67.63</v>
@@ -23653,7 +23653,7 @@
         <v>2.74</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>68</v>
@@ -23728,7 +23728,7 @@
         <v>-2.83</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>68.16</v>
@@ -23803,7 +23803,7 @@
         <v>0.6</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>68.56</v>
@@ -23878,7 +23878,7 @@
         <v>-0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>68.8</v>
@@ -23957,7 +23957,7 @@
         <v>-3.12</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>68.94</v>
@@ -24036,7 +24036,7 @@
         <v>-2.05</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>68.77</v>
@@ -24111,7 +24111,7 @@
         <v>2.81</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>68.7</v>
@@ -24186,7 +24186,7 @@
         <v>2.45</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>68.81999999999999</v>
@@ -24261,7 +24261,7 @@
         <v>-3.44</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>68.81999999999999</v>
@@ -24340,7 +24340,7 @@
         <v>-0.05</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>68.81999999999999</v>
@@ -24415,7 +24415,7 @@
         <v>6.4</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>68.95</v>
@@ -24490,7 +24490,7 @@
         <v>2.1</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>69.11</v>
@@ -24565,7 +24565,7 @@
         <v>1.97</v>
       </c>
       <c r="I319" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" t="n">
         <v>69.31</v>
@@ -24640,7 +24640,7 @@
         <v>6.83</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>69.79000000000001</v>
@@ -24715,7 +24715,7 @@
         <v>0.71</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>70.12</v>
@@ -24790,7 +24790,7 @@
         <v>1.02</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>70.48999999999999</v>
@@ -24865,7 +24865,7 @@
         <v>-4.84</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>70.70999999999999</v>
@@ -24940,7 +24940,7 @@
         <v>-8.57</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>70.48</v>
@@ -25019,7 +25019,7 @@
         <v>1.3</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>70.37</v>
@@ -25094,7 +25094,7 @@
         <v>-4.35</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>70.29000000000001</v>
@@ -25169,7 +25169,7 @@
         <v>2.74</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.20999999999999</v>
@@ -25244,7 +25244,7 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.26000000000001</v>
@@ -25319,7 +25319,7 @@
         <v>-1.57</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>70.23999999999999</v>
@@ -25394,7 +25394,7 @@
         <v>1.99</v>
       </c>
       <c r="I330" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" t="n">
         <v>70.31</v>
@@ -25469,7 +25469,7 @@
         <v>-3.18</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.37</v>
@@ -25544,7 +25544,7 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.55</v>
@@ -25619,7 +25619,7 @@
         <v>-0.04</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>70.63</v>
@@ -25694,7 +25694,7 @@
         <v>-0.97</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>70.59999999999999</v>
@@ -25769,7 +25769,7 @@
         <v>0.47</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>70.7</v>
@@ -25844,7 +25844,7 @@
         <v>-2.62</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>70.72</v>
@@ -25919,7 +25919,7 @@
         <v>1.16</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>70.56</v>
@@ -25994,7 +25994,7 @@
         <v>-8.08</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>70.06</v>
@@ -26069,7 +26069,7 @@
         <v>0.02</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>69.48999999999999</v>
@@ -26144,7 +26144,7 @@
         <v>-4.17</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>68.54000000000001</v>
@@ -26223,7 +26223,7 @@
         <v>-2.29</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>67.48999999999999</v>
@@ -26302,7 +26302,7 @@
         <v>5.48</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>66.56999999999999</v>
@@ -26377,7 +26377,7 @@
         <v>0.77</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>65.86</v>
@@ -26452,7 +26452,7 @@
         <v>3.56</v>
       </c>
       <c r="I344" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" t="n">
         <v>65.58</v>
@@ -26527,7 +26527,7 @@
         <v>-0.13</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>65.25</v>
@@ -26602,7 +26602,7 @@
         <v>-4.39</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>64.94</v>
@@ -26677,7 +26677,7 @@
         <v>-1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>64.47</v>
@@ -26752,7 +26752,7 @@
         <v>-1.01</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>63.95</v>
@@ -26827,7 +26827,7 @@
         <v>-5.4</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>63.32</v>
@@ -26906,7 +26906,7 @@
         <v>-7.09</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>62.42</v>
@@ -26985,7 +26985,7 @@
         <v>1.12</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>61.66</v>
@@ -27064,7 +27064,7 @@
         <v>1.76</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>60.91</v>
@@ -27139,7 +27139,7 @@
         <v>-1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>60.12</v>
@@ -27214,7 +27214,7 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>59.42</v>
@@ -27289,7 +27289,7 @@
         <v>0.21</v>
       </c>
       <c r="I355" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" t="n">
         <v>58.69</v>
@@ -27364,7 +27364,7 @@
         <v>2.69</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>58.14</v>
@@ -27439,7 +27439,7 @@
         <v>1.98</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>57.59</v>
@@ -27514,7 +27514,7 @@
         <v>-2.94</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>57.24</v>
@@ -27593,7 +27593,7 @@
         <v>-2.99</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>56.8</v>
@@ -27672,7 +27672,7 @@
         <v>2.48</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>56.55</v>
@@ -27747,7 +27747,7 @@
         <v>-0.35</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>56.37</v>
@@ -27822,7 +27822,7 @@
         <v>-3.32</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>55.94</v>
@@ -27897,7 +27897,7 @@
         <v>1.94</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>55.53</v>
@@ -27972,7 +27972,7 @@
         <v>-1.81</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>54.97</v>
@@ -28047,7 +28047,7 @@
         <v>-3.49</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>54.32</v>
@@ -28122,7 +28122,7 @@
         <v>0.77</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>53.83</v>
@@ -28197,7 +28197,7 @@
         <v>0.39</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>53.4</v>
@@ -28272,7 +28272,7 @@
         <v>4.12</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>53.11</v>
@@ -28347,7 +28347,7 @@
         <v>1.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>53.02</v>
@@ -28422,7 +28422,7 @@
         <v>-3.45</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>53.03</v>
@@ -28501,7 +28501,7 @@
         <v>1.02</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>53.04</v>
@@ -28576,7 +28576,7 @@
         <v>0.65</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>53.03</v>
@@ -28651,7 +28651,7 @@
         <v>-2.32</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>52.98</v>
@@ -28726,7 +28726,7 @@
         <v>0.14</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>52.89</v>
@@ -28801,7 +28801,7 @@
         <v>3.34</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>52.89</v>
@@ -28876,7 +28876,7 @@
         <v>-2.13</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>52.75</v>
@@ -28955,7 +28955,7 @@
         <v>0.19</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>52.57</v>
@@ -29030,7 +29030,7 @@
         <v>2.63</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>52.54</v>
@@ -29105,7 +29105,7 @@
         <v>4.14</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>52.7</v>
@@ -29180,7 +29180,7 @@
         <v>-0.39</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>52.79</v>
@@ -29255,7 +29255,7 @@
         <v>2.95</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>52.97</v>
@@ -29330,7 +29330,7 @@
         <v>3.32</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>53.33</v>
@@ -29405,7 +29405,7 @@
         <v>-1.45</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>53.6</v>
@@ -29480,7 +29480,7 @@
         <v>0.87</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>53.94</v>
@@ -29555,7 +29555,7 @@
         <v>-1.52</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>54.33</v>
@@ -29630,7 +29630,7 @@
         <v>0.55</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>54.71</v>
@@ -29705,7 +29705,7 @@
         <v>1.86</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>55.14</v>
@@ -29780,7 +29780,7 @@
         <v>-3.58</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>55.36</v>
@@ -29859,7 +29859,7 @@
         <v>4.47</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>55.67</v>
@@ -29934,7 +29934,7 @@
         <v>2.75</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>56.15</v>
@@ -30009,7 +30009,7 @@
         <v>1.72</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>56.65</v>
@@ -30084,7 +30084,7 @@
         <v>-0.83</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>57.12</v>
@@ -30159,7 +30159,7 @@
         <v>0.19</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>57.65</v>
@@ -30234,7 +30234,7 @@
         <v>-1.17</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>58.14</v>
@@ -30309,7 +30309,7 @@
         <v>1.92</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>58.6</v>
@@ -30384,7 +30384,7 @@
         <v>-4.38</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>58.98</v>
@@ -30459,7 +30459,7 @@
         <v>0.18</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>59.37</v>
@@ -30534,7 +30534,7 @@
         <v>-3.68</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>59.57</v>
@@ -30613,7 +30613,7 @@
         <v>1.99</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>59.72</v>
@@ -30688,7 +30688,7 @@
         <v>2.51</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>59.96</v>
@@ -30763,7 +30763,7 @@
         <v>-1.21</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>60.07</v>
@@ -30842,7 +30842,7 @@
         <v>-0.75</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>60.07</v>
@@ -30917,7 +30917,7 @@
         <v>2.27</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>60.18</v>
@@ -30992,7 +30992,7 @@
         <v>-5.3</v>
       </c>
       <c r="I404" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>60.1</v>
@@ -31071,7 +31071,7 @@
         <v>1.08</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>60.1</v>
@@ -31146,7 +31146,7 @@
         <v>-2.2</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>60.02</v>
@@ -31221,7 +31221,7 @@
         <v>1.21</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>59.92</v>
@@ -31296,7 +31296,7 @@
         <v>-0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>59.9</v>
@@ -31371,7 +31371,7 @@
         <v>3.37</v>
       </c>
       <c r="I409" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" t="n">
         <v>59.84</v>
@@ -31446,7 +31446,7 @@
         <v>1.63</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>59.76</v>
@@ -31521,7 +31521,7 @@
         <v>-0.5</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>59.6</v>
@@ -31596,7 +31596,7 @@
         <v>1.84</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>59.53</v>
@@ -31671,7 +31671,7 @@
         <v>-4.23</v>
       </c>
       <c r="I413" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J413" t="n">
         <v>59.32</v>
@@ -31750,7 +31750,7 @@
         <v>-0.93</v>
       </c>
       <c r="I414" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J414" t="n">
         <v>59.12</v>
@@ -31794,6 +31794,79 @@
       <c r="W414" s="2" t="n">
         <v>146</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D415" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E415" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="F415" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="G415" t="n">
+        <v>10984424</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J415" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="K415" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="L415" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31744,7 +31744,7 @@
         <v>57.62</v>
       </c>
       <c r="G414" t="n">
-        <v>15754400</v>
+        <v>15817000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-0.93</v>
@@ -31816,13 +31816,13 @@
         <v>57.25</v>
       </c>
       <c r="F415" t="n">
-        <v>58.13</v>
+        <v>58.14</v>
       </c>
       <c r="G415" t="n">
-        <v>10984424</v>
+        <v>13659571</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
@@ -31840,10 +31840,10 @@
         <v>65.95999999999999</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>44.72</v>
+        <v>44.75</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31857,16 +31857,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>1.92</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>27.87</v>
@@ -683,7 +683,7 @@
         <v>0.44</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>27.97</v>
@@ -758,7 +758,7 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>28.07</v>
@@ -833,7 +833,7 @@
         <v>-1.19</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>28.16</v>
@@ -908,7 +908,7 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>28.24</v>
@@ -983,7 +983,7 @@
         <v>-0.68</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>28.34</v>
@@ -1058,7 +1058,7 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>28.44</v>
@@ -1133,7 +1133,7 @@
         <v>0.41</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>28.52</v>
@@ -1208,7 +1208,7 @@
         <v>-0.51</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>28.58</v>
@@ -1283,7 +1283,7 @@
         <v>2.05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>28.7</v>
@@ -1358,7 +1358,7 @@
         <v>-0.33</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>28.79</v>
@@ -1433,7 +1433,7 @@
         <v>0.47</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>28.88</v>
@@ -1508,7 +1508,7 @@
         <v>-1.2</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>28.97</v>
@@ -1583,7 +1583,7 @@
         <v>-0.51</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>29.05</v>
@@ -1658,7 +1658,7 @@
         <v>-2.07</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>29.12</v>
@@ -1737,7 +1737,7 @@
         <v>0.38</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>29.18</v>
@@ -1812,7 +1812,7 @@
         <v>-1.87</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>29.2</v>
@@ -1887,7 +1887,7 @@
         <v>-0.32</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>29.18</v>
@@ -1966,7 +1966,7 @@
         <v>1.55</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>29.19</v>
@@ -2041,7 +2041,7 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>29.21</v>
@@ -2116,7 +2116,7 @@
         <v>2.66</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.24</v>
@@ -2191,7 +2191,7 @@
         <v>-0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.26</v>
@@ -2266,7 +2266,7 @@
         <v>-0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.27</v>
@@ -2341,7 +2341,7 @@
         <v>-1.62</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.27</v>
@@ -2424,7 +2424,7 @@
         <v>2.92</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.31</v>
@@ -2503,7 +2503,7 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.37</v>
@@ -2578,7 +2578,7 @@
         <v>1.72</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.44</v>
@@ -2653,7 +2653,7 @@
         <v>-0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.5</v>
@@ -2728,7 +2728,7 @@
         <v>0.33</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.58</v>
@@ -2803,7 +2803,7 @@
         <v>0.13</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.62</v>
@@ -2878,7 +2878,7 @@
         <v>-0.32</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.67</v>
@@ -2953,7 +2953,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.7</v>
@@ -3028,7 +3028,7 @@
         <v>-1.57</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.72</v>
@@ -3103,7 +3103,7 @@
         <v>-0.2</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.75</v>
@@ -3178,7 +3178,7 @@
         <v>2.07</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.83</v>
@@ -3253,7 +3253,7 @@
         <v>-0.16</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.91</v>
@@ -3328,7 +3328,7 @@
         <v>2.59</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>30.06</v>
@@ -3403,7 +3403,7 @@
         <v>-1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>30.19</v>
@@ -3478,7 +3478,7 @@
         <v>-0.03</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>30.3</v>
@@ -3553,7 +3553,7 @@
         <v>-1.16</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>30.39</v>
@@ -3628,7 +3628,7 @@
         <v>0.42</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>30.44</v>
@@ -3703,7 +3703,7 @@
         <v>-6.08</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>30.4</v>
@@ -3786,7 +3786,7 @@
         <v>-6.27</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30.27</v>
@@ -3869,7 +3869,7 @@
         <v>0.22</v>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>30.17</v>
@@ -3952,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>30.03</v>
@@ -4035,7 +4035,7 @@
         <v>3.39</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>29.92</v>
@@ -4114,7 +4114,7 @@
         <v>0.78</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>29.8</v>
@@ -4193,7 +4193,7 @@
         <v>3.22</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>29.72</v>
@@ -4272,7 +4272,7 @@
         <v>0.65</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>29.65</v>
@@ -4347,7 +4347,7 @@
         <v>0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>29.58</v>
@@ -4422,7 +4422,7 @@
         <v>1.19</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>29.53</v>
@@ -4501,7 +4501,7 @@
         <v>-0.71</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.48</v>
@@ -4580,7 +4580,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.47</v>
@@ -4655,7 +4655,7 @@
         <v>-0.97</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.45</v>
@@ -4730,7 +4730,7 @@
         <v>3.59</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.45</v>
@@ -4809,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.45</v>
@@ -4884,7 +4884,7 @@
         <v>-1.67</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.39</v>
@@ -4959,7 +4959,7 @@
         <v>0.47</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.35</v>
@@ -5034,7 +5034,7 @@
         <v>-1.19</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.29</v>
@@ -5109,7 +5109,7 @@
         <v>-0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.24</v>
@@ -5188,7 +5188,7 @@
         <v>-0.71</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.17</v>
@@ -5263,7 +5263,7 @@
         <v>-0.92</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.18</v>
@@ -5342,7 +5342,7 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.3</v>
@@ -5417,7 +5417,7 @@
         <v>2.51</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.45</v>
@@ -5492,7 +5492,7 @@
         <v>-2.42</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.57</v>
@@ -5571,7 +5571,7 @@
         <v>-0.1</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.64</v>
@@ -5646,7 +5646,7 @@
         <v>1.15</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.72</v>
@@ -5721,7 +5721,7 @@
         <v>-0.57</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.74</v>
@@ -5800,7 +5800,7 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.77</v>
@@ -5875,7 +5875,7 @@
         <v>-2.27</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.76</v>
@@ -5954,7 +5954,7 @@
         <v>1.23</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.75</v>
@@ -6029,7 +6029,7 @@
         <v>-1.05</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.74</v>
@@ -6104,7 +6104,7 @@
         <v>0.41</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.72</v>
@@ -6179,7 +6179,7 @@
         <v>2.41</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.75</v>
@@ -6254,7 +6254,7 @@
         <v>1.26</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.75</v>
@@ -6329,7 +6329,7 @@
         <v>-1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.72</v>
@@ -6404,7 +6404,7 @@
         <v>1.4</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.74</v>
@@ -6479,7 +6479,7 @@
         <v>-0.72</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.74</v>
@@ -6554,7 +6554,7 @@
         <v>-0.83</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>29.75</v>
@@ -6629,7 +6629,7 @@
         <v>1.07</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>29.79</v>
@@ -6704,7 +6704,7 @@
         <v>-0.99</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>29.82</v>
@@ -6779,7 +6779,7 @@
         <v>5.3</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>29.94</v>
@@ -6854,7 +6854,7 @@
         <v>-0.47</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>30.04</v>
@@ -6929,7 +6929,7 @@
         <v>-0.32</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>30.09</v>
@@ -7004,7 +7004,7 @@
         <v>3.54</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>30.24</v>
@@ -7079,7 +7079,7 @@
         <v>0.74</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>30.4</v>
@@ -7154,7 +7154,7 @@
         <v>2.14</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>30.58</v>
@@ -7229,7 +7229,7 @@
         <v>-0.48</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>30.76</v>
@@ -7304,7 +7304,7 @@
         <v>-0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>30.91</v>
@@ -7379,7 +7379,7 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>31.1</v>
@@ -7454,7 +7454,7 @@
         <v>-0.27</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>31.27</v>
@@ -7529,7 +7529,7 @@
         <v>0.18</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>31.46</v>
@@ -7604,7 +7604,7 @@
         <v>2.15</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>31.68</v>
@@ -7679,7 +7679,7 @@
         <v>-1.39</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>31.83</v>
@@ -7754,7 +7754,7 @@
         <v>-1.65</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>31.94</v>
@@ -7829,7 +7829,7 @@
         <v>0.73</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>32.09</v>
@@ -7904,7 +7904,7 @@
         <v>-1.06</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>32.2</v>
@@ -7979,7 +7979,7 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>32.34</v>
@@ -8054,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>32.5</v>
@@ -8129,7 +8129,7 @@
         <v>-2.16</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>32.62</v>
@@ -8204,7 +8204,7 @@
         <v>0.58</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>32.76</v>
@@ -8279,7 +8279,7 @@
         <v>-0.24</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>32.82</v>
@@ -8358,7 +8358,7 @@
         <v>1.56</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>32.91</v>
@@ -8433,7 +8433,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>33.02</v>
@@ -8508,7 +8508,7 @@
         <v>-0.24</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>33.07</v>
@@ -8583,7 +8583,7 @@
         <v>-0.42</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>33.1</v>
@@ -8658,7 +8658,7 @@
         <v>-0.87</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>33.08</v>
@@ -8737,7 +8737,7 @@
         <v>2.27</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>33.1</v>
@@ -8812,7 +8812,7 @@
         <v>3.79</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>33.21</v>
@@ -8887,7 +8887,7 @@
         <v>-1.14</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>33.28</v>
@@ -8962,7 +8962,7 @@
         <v>-1.07</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.35</v>
@@ -9037,7 +9037,7 @@
         <v>0.44</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.42</v>
@@ -9112,7 +9112,7 @@
         <v>0.7</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.46</v>
@@ -9187,7 +9187,7 @@
         <v>-0.12</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>33.53</v>
@@ -9262,7 +9262,7 @@
         <v>2.14</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>33.66</v>
@@ -9337,7 +9337,7 @@
         <v>1.05</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>33.8</v>
@@ -9412,7 +9412,7 @@
         <v>-0.08</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>33.95</v>
@@ -9487,7 +9487,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>34.08</v>
@@ -9562,7 +9562,7 @@
         <v>-2.34</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>34.14</v>
@@ -9637,7 +9637,7 @@
         <v>-0.06</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>34.24</v>
@@ -9712,7 +9712,7 @@
         <v>0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>34.34</v>
@@ -9787,7 +9787,7 @@
         <v>-3.32</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>34.38</v>
@@ -9866,7 +9866,7 @@
         <v>-0.57</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>34.38</v>
@@ -9941,7 +9941,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.38</v>
@@ -10016,7 +10016,7 @@
         <v>1.16</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.41</v>
@@ -10091,7 +10091,7 @@
         <v>1.09</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.46</v>
@@ -10166,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.53</v>
@@ -10241,7 +10241,7 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>34.58</v>
@@ -10316,7 +10316,7 @@
         <v>0.35</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.58</v>
@@ -10391,7 +10391,7 @@
         <v>-2.01</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.55</v>
@@ -10470,7 +10470,7 @@
         <v>0.67</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.56</v>
@@ -10545,7 +10545,7 @@
         <v>1.71</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.59</v>
@@ -10620,7 +10620,7 @@
         <v>-1.43</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.58</v>
@@ -10699,7 +10699,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.58</v>
@@ -10774,7 +10774,7 @@
         <v>0.14</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.54</v>
@@ -10849,7 +10849,7 @@
         <v>-1.97</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.44</v>
@@ -10928,7 +10928,7 @@
         <v>1.65</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.38</v>
@@ -11003,7 +11003,7 @@
         <v>0.52</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.34</v>
@@ -11078,7 +11078,7 @@
         <v>2.11</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.37</v>
@@ -11153,7 +11153,7 @@
         <v>-0.91</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.39</v>
@@ -11228,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.41</v>
@@ -11303,7 +11303,7 @@
         <v>-0.09</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>34.48</v>
@@ -11378,7 +11378,7 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>34.59</v>
@@ -11453,7 +11453,7 @@
         <v>1.89</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>34.72</v>
@@ -11528,7 +11528,7 @@
         <v>2.65</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>34.88</v>
@@ -11603,7 +11603,7 @@
         <v>0.51</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>35.03</v>
@@ -11678,7 +11678,7 @@
         <v>-1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>35.16</v>
@@ -11753,7 +11753,7 @@
         <v>0.76</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>35.28</v>
@@ -11828,7 +11828,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>35.41</v>
@@ -11903,7 +11903,7 @@
         <v>-0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>35.56</v>
@@ -11978,7 +11978,7 @@
         <v>0.62</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>35.71</v>
@@ -12053,7 +12053,7 @@
         <v>1.02</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>35.85</v>
@@ -12128,7 +12128,7 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>36.04</v>
@@ -12203,7 +12203,7 @@
         <v>1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>36.26</v>
@@ -12278,7 +12278,7 @@
         <v>-0.41</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>36.46</v>
@@ -12353,7 +12353,7 @@
         <v>-2.1</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>36.66</v>
@@ -12428,7 +12428,7 @@
         <v>0.53</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>36.83</v>
@@ -12503,7 +12503,7 @@
         <v>2.76</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>37.06</v>
@@ -12578,7 +12578,7 @@
         <v>2.56</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>37.29</v>
@@ -12653,7 +12653,7 @@
         <v>-0.2</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>37.54</v>
@@ -12728,7 +12728,7 @@
         <v>-0.35</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>37.78</v>
@@ -12803,7 +12803,7 @@
         <v>3.04</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>38.08</v>
@@ -12878,7 +12878,7 @@
         <v>2.02</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>38.4</v>
@@ -12953,7 +12953,7 @@
         <v>1.53</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>38.71</v>
@@ -13028,7 +13028,7 @@
         <v>-0.31</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>38.97</v>
@@ -13103,7 +13103,7 @@
         <v>1.27</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>39.25</v>
@@ -13178,7 +13178,7 @@
         <v>-0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>39.53</v>
@@ -13253,7 +13253,7 @@
         <v>2.33</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>39.85</v>
@@ -13328,7 +13328,7 @@
         <v>1.24</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>40.17</v>
@@ -13403,7 +13403,7 @@
         <v>-1.52</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>40.49</v>
@@ -13478,7 +13478,7 @@
         <v>2.7</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>40.84</v>
@@ -13553,7 +13553,7 @@
         <v>0.34</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>41.19</v>
@@ -13628,7 +13628,7 @@
         <v>1.61</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>41.54</v>
@@ -13703,7 +13703,7 @@
         <v>4.03</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>41.97</v>
@@ -13778,7 +13778,7 @@
         <v>-0.97</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>42.38</v>
@@ -13853,7 +13853,7 @@
         <v>3.27</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>42.91</v>
@@ -13928,7 +13928,7 @@
         <v>1.74</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>43.46</v>
@@ -14003,7 +14003,7 @@
         <v>-4.43</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>43.86</v>
@@ -14078,7 +14078,7 @@
         <v>1.55</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>44.25</v>
@@ -14153,7 +14153,7 @@
         <v>-8.24</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>44.44</v>
@@ -14232,7 +14232,7 @@
         <v>0.21</v>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>44.64</v>
@@ -14307,7 +14307,7 @@
         <v>0.68</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>44.8</v>
@@ -14382,7 +14382,7 @@
         <v>-0.43</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>44.9</v>
@@ -14457,7 +14457,7 @@
         <v>-3.61</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>44.9</v>
@@ -14532,7 +14532,7 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>44.92</v>
@@ -14607,7 +14607,7 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>44.93</v>
@@ -14682,7 +14682,7 @@
         <v>2.57</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>45.02</v>
@@ -14757,7 +14757,7 @@
         <v>-0.74</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>45.05</v>
@@ -14832,7 +14832,7 @@
         <v>-0.57</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>45.03</v>
@@ -14907,7 +14907,7 @@
         <v>-2.33</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>45</v>
@@ -14982,7 +14982,7 @@
         <v>2.13</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>44.95</v>
@@ -15057,7 +15057,7 @@
         <v>-0.23</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>44.9</v>
@@ -15132,7 +15132,7 @@
         <v>0.85</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>44.82</v>
@@ -15207,7 +15207,7 @@
         <v>4.26</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>44.75</v>
@@ -15282,7 +15282,7 @@
         <v>1.44</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>44.73</v>
@@ -15357,7 +15357,7 @@
         <v>4.03</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>44.73</v>
@@ -15432,7 +15432,7 @@
         <v>-1.86</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>44.64</v>
@@ -15507,7 +15507,7 @@
         <v>-3.08</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.59</v>
@@ -15582,7 +15582,7 @@
         <v>-1.07</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.48</v>
@@ -15657,7 +15657,7 @@
         <v>1.39</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>44.59</v>
@@ -15732,7 +15732,7 @@
         <v>0.76</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>44.72</v>
@@ -15807,7 +15807,7 @@
         <v>-1.44</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>44.8</v>
@@ -15886,7 +15886,7 @@
         <v>-1.05</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>44.87</v>
@@ -15961,7 +15961,7 @@
         <v>2.94</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>45.08</v>
@@ -16036,7 +16036,7 @@
         <v>0.09</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>45.28</v>
@@ -16111,7 +16111,7 @@
         <v>3.71</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>45.54</v>
@@ -16186,7 +16186,7 @@
         <v>5.81</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>45.88</v>
@@ -16261,7 +16261,7 @@
         <v>2.56</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>46.3</v>
@@ -16336,7 +16336,7 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>46.77</v>
@@ -16411,7 +16411,7 @@
         <v>-0.11</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>47.29</v>
@@ -16486,7 +16486,7 @@
         <v>-2.47</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>47.7</v>
@@ -16561,7 +16561,7 @@
         <v>2.3</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>48.16</v>
@@ -16636,7 +16636,7 @@
         <v>-0.45</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>48.6</v>
@@ -16711,7 +16711,7 @@
         <v>4.67</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>49.07</v>
@@ -16786,7 +16786,7 @@
         <v>1.63</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>49.55</v>
@@ -16861,7 +16861,7 @@
         <v>2.76</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>50.02</v>
@@ -16936,7 +16936,7 @@
         <v>-2.64</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>50.45</v>
@@ -17011,7 +17011,7 @@
         <v>3.58</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>51.06</v>
@@ -17086,7 +17086,7 @@
         <v>-0.65</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>51.67</v>
@@ -17161,7 +17161,7 @@
         <v>4.38</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>52.38</v>
@@ -17236,7 +17236,7 @@
         <v>-1.56</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>53.03</v>
@@ -17311,7 +17311,7 @@
         <v>2.71</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>53.78</v>
@@ -17386,7 +17386,7 @@
         <v>2.53</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>54.64</v>
@@ -17461,7 +17461,7 @@
         <v>3.79</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>55.55</v>
@@ -17536,7 +17536,7 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>56.48</v>
@@ -17611,7 +17611,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>57.62</v>
@@ -17686,7 +17686,7 @@
         <v>-7.19</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>58.36</v>
@@ -17761,7 +17761,7 @@
         <v>4.5</v>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" t="n">
         <v>59.18</v>
@@ -17836,7 +17836,7 @@
         <v>-6.61</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>59.74</v>
@@ -17911,7 +17911,7 @@
         <v>2.06</v>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" t="n">
         <v>60.38</v>
@@ -17986,7 +17986,7 @@
         <v>5.06</v>
       </c>
       <c r="I232" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" t="n">
         <v>61.24</v>
@@ -18061,7 +18061,7 @@
         <v>6.7</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>62.28</v>
@@ -18136,7 +18136,7 @@
         <v>-3.73</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>63.19</v>
@@ -18211,7 +18211,7 @@
         <v>-1.76</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>63.92</v>
@@ -18286,7 +18286,7 @@
         <v>3.83</v>
       </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" t="n">
         <v>64.73999999999999</v>
@@ -18361,7 +18361,7 @@
         <v>6.7</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>65.72</v>
@@ -18436,7 +18436,7 @@
         <v>1.77</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>66.84</v>
@@ -18511,7 +18511,7 @@
         <v>7.58</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>68.16</v>
@@ -18586,7 +18586,7 @@
         <v>-1.47</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>69.44</v>
@@ -18661,7 +18661,7 @@
         <v>-2.76</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>70.48</v>
@@ -18736,7 +18736,7 @@
         <v>5.39</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>71.78</v>
@@ -18811,7 +18811,7 @@
         <v>-1.67</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>72.94</v>
@@ -18886,7 +18886,7 @@
         <v>3.78</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>74.17</v>
@@ -18961,7 +18961,7 @@
         <v>6.63</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>75.56999999999999</v>
@@ -19036,7 +19036,7 @@
         <v>5.84</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>77.23</v>
@@ -19111,7 +19111,7 @@
         <v>3.3</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>78.75</v>
@@ -19186,7 +19186,7 @@
         <v>3.95</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>80.73</v>
@@ -19261,7 +19261,7 @@
         <v>-0.03</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>82.56</v>
@@ -19336,7 +19336,7 @@
         <v>-28.54</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>83.11</v>
@@ -19415,7 +19415,7 @@
         <v>-3.98</v>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" t="n">
         <v>83.45</v>
@@ -19490,7 +19490,7 @@
         <v>6.24</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>83.84</v>
@@ -19565,7 +19565,7 @@
         <v>2.88</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>84.11</v>
@@ -19640,7 +19640,7 @@
         <v>-15.77</v>
       </c>
       <c r="I254" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19715,7 +19715,7 @@
         <v>5.25</v>
       </c>
       <c r="I255" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" t="n">
         <v>83.92</v>
@@ -19790,7 +19790,7 @@
         <v>8.33</v>
       </c>
       <c r="I256" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" t="n">
         <v>84.11</v>
@@ -19865,7 +19865,7 @@
         <v>-3.46</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>83.92</v>
@@ -19940,7 +19940,7 @@
         <v>4.29</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>83.81999999999999</v>
@@ -20015,7 +20015,7 @@
         <v>-11.53</v>
       </c>
       <c r="I259" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" s="4" t="n">
         <v>82.97</v>
@@ -20090,7 +20090,7 @@
         <v>2.94</v>
       </c>
       <c r="I260" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" t="n">
         <v>82.29000000000001</v>
@@ -20165,7 +20165,7 @@
         <v>-4.8</v>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" t="n">
         <v>81.56</v>
@@ -20244,7 +20244,7 @@
         <v>5.6</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>80.8</v>
@@ -20319,7 +20319,7 @@
         <v>1.31</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>80.15000000000001</v>
@@ -20394,7 +20394,7 @@
         <v>7.9</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>79.62</v>
@@ -20469,7 +20469,7 @@
         <v>5.16</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>79.01000000000001</v>
@@ -20544,7 +20544,7 @@
         <v>-1.85</v>
       </c>
       <c r="I266" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>78.04000000000001</v>
@@ -20619,7 +20619,7 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>76.97</v>
@@ -20694,7 +20694,7 @@
         <v>0.51</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>75.70999999999999</v>
@@ -20769,7 +20769,7 @@
         <v>5.64</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>74.68000000000001</v>
@@ -20844,7 +20844,7 @@
         <v>-4.02</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>74.98999999999999</v>
@@ -20919,7 +20919,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I271" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" s="4" t="n">
         <v>75.09999999999999</v>
@@ -20998,7 +20998,7 @@
         <v>0.88</v>
       </c>
       <c r="I272" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" t="n">
         <v>75.02</v>
@@ -21073,7 +21073,7 @@
         <v>-1.42</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>74.77</v>
@@ -21152,7 +21152,7 @@
         <v>2.25</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>75.23</v>
@@ -21231,7 +21231,7 @@
         <v>3.06</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>75.64</v>
@@ -21306,7 +21306,7 @@
         <v>2.34</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>75.84</v>
@@ -21381,7 +21381,7 @@
         <v>-2.72</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>76.06</v>
@@ -21456,7 +21456,7 @@
         <v>-1.84</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>76.06</v>
@@ -21525,7 +21525,7 @@
         <v>-4.96</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>76.31</v>
@@ -21608,7 +21608,7 @@
         <v>0.73</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>76.48</v>
@@ -21683,7 +21683,7 @@
         <v>-2.13</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>76.75</v>
@@ -21758,7 +21758,7 @@
         <v>-4.13</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>76.68000000000001</v>
@@ -21833,7 +21833,7 @@
         <v>-4.4</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>76.41</v>
@@ -21908,7 +21908,7 @@
         <v>-6.33</v>
       </c>
       <c r="I284" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>75.66</v>
@@ -21991,7 +21991,7 @@
         <v>1.54</v>
       </c>
       <c r="I285" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" t="n">
         <v>74.75</v>
@@ -22066,7 +22066,7 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>73.95</v>
@@ -22141,7 +22141,7 @@
         <v>3.59</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>73.2</v>
@@ -22216,7 +22216,7 @@
         <v>-6.81</v>
       </c>
       <c r="I288" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>72.22</v>
@@ -22295,7 +22295,7 @@
         <v>4.39</v>
       </c>
       <c r="I289" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" t="n">
         <v>71.14</v>
@@ -22374,7 +22374,7 @@
         <v>0.13</v>
       </c>
       <c r="I290" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" t="n">
         <v>70.23999999999999</v>
@@ -22449,7 +22449,7 @@
         <v>7.27</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>69.91</v>
@@ -22524,7 +22524,7 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>69.55</v>
@@ -22599,7 +22599,7 @@
         <v>-3.45</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>69.13</v>
@@ -22674,7 +22674,7 @@
         <v>0.46</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>68.64</v>
@@ -22749,7 +22749,7 @@
         <v>-0.23</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>68.02</v>
@@ -22828,7 +22828,7 @@
         <v>2.32</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>67.39</v>
@@ -22903,7 +22903,7 @@
         <v>1.36</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>66.91</v>
@@ -22978,7 +22978,7 @@
         <v>1.01</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>66.54000000000001</v>
@@ -23053,7 +23053,7 @@
         <v>-1.16</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>66.31999999999999</v>
@@ -23128,7 +23128,7 @@
         <v>5.51</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>66.26000000000001</v>
@@ -23203,7 +23203,7 @@
         <v>-0.28</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>66.27</v>
@@ -23278,7 +23278,7 @@
         <v>-0.84</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>66.40000000000001</v>
@@ -23353,7 +23353,7 @@
         <v>3.35</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>66.8</v>
@@ -23428,7 +23428,7 @@
         <v>-2.01</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>67.33</v>
@@ -23503,7 +23503,7 @@
         <v>-5.07</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>67.63</v>
@@ -23578,7 +23578,7 @@
         <v>2.74</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>68</v>
@@ -23653,7 +23653,7 @@
         <v>-2.83</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>68.16</v>
@@ -23728,7 +23728,7 @@
         <v>0.6</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>68.56</v>
@@ -23803,7 +23803,7 @@
         <v>-0.67</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>68.8</v>
@@ -23882,7 +23882,7 @@
         <v>-3.12</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>68.94</v>
@@ -23961,7 +23961,7 @@
         <v>-2.05</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>68.77</v>
@@ -24036,7 +24036,7 @@
         <v>2.81</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>68.7</v>
@@ -24111,7 +24111,7 @@
         <v>2.45</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>68.81999999999999</v>
@@ -24186,7 +24186,7 @@
         <v>-3.44</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>68.81999999999999</v>
@@ -24265,7 +24265,7 @@
         <v>-0.05</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>68.81999999999999</v>
@@ -24340,7 +24340,7 @@
         <v>6.4</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>68.95</v>
@@ -24415,7 +24415,7 @@
         <v>2.1</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>69.11</v>
@@ -24490,7 +24490,7 @@
         <v>1.97</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>69.31</v>
@@ -24565,7 +24565,7 @@
         <v>6.83</v>
       </c>
       <c r="I319" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" t="n">
         <v>69.79000000000001</v>
@@ -24640,7 +24640,7 @@
         <v>0.71</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>70.12</v>
@@ -24715,7 +24715,7 @@
         <v>1.02</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>70.48999999999999</v>
@@ -24790,7 +24790,7 @@
         <v>-4.84</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>70.70999999999999</v>
@@ -24865,7 +24865,7 @@
         <v>-8.57</v>
       </c>
       <c r="I323" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" s="4" t="n">
         <v>70.48</v>
@@ -24944,7 +24944,7 @@
         <v>1.3</v>
       </c>
       <c r="I324" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" t="n">
         <v>70.37</v>
@@ -25019,7 +25019,7 @@
         <v>-4.35</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>70.29000000000001</v>
@@ -25094,7 +25094,7 @@
         <v>2.74</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>70.20999999999999</v>
@@ -25169,7 +25169,7 @@
         <v>1.05</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.26000000000001</v>
@@ -25244,7 +25244,7 @@
         <v>-1.57</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.23999999999999</v>
@@ -25319,7 +25319,7 @@
         <v>1.99</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>70.31</v>
@@ -25394,7 +25394,7 @@
         <v>-3.18</v>
       </c>
       <c r="I330" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" t="n">
         <v>70.37</v>
@@ -25469,7 +25469,7 @@
         <v>1.27</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.55</v>
@@ -25544,7 +25544,7 @@
         <v>-0.04</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.63</v>
@@ -25619,7 +25619,7 @@
         <v>-0.97</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>70.59999999999999</v>
@@ -25694,7 +25694,7 @@
         <v>0.47</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>70.7</v>
@@ -25769,7 +25769,7 @@
         <v>-2.62</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>70.72</v>
@@ -25844,7 +25844,7 @@
         <v>1.16</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>70.56</v>
@@ -25919,7 +25919,7 @@
         <v>-8.08</v>
       </c>
       <c r="I337" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>70.06</v>
@@ -25994,7 +25994,7 @@
         <v>0.02</v>
       </c>
       <c r="I338" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" t="n">
         <v>69.48999999999999</v>
@@ -26069,7 +26069,7 @@
         <v>-4.17</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>68.54000000000001</v>
@@ -26148,7 +26148,7 @@
         <v>-2.29</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>67.48999999999999</v>
@@ -26227,7 +26227,7 @@
         <v>5.48</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>66.56999999999999</v>
@@ -26302,7 +26302,7 @@
         <v>0.77</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>65.86</v>
@@ -26377,7 +26377,7 @@
         <v>3.56</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>65.58</v>
@@ -26452,7 +26452,7 @@
         <v>-0.13</v>
       </c>
       <c r="I344" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" t="n">
         <v>65.25</v>
@@ -26527,7 +26527,7 @@
         <v>-4.39</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>64.94</v>
@@ -26602,7 +26602,7 @@
         <v>-1.81</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>64.47</v>
@@ -26677,7 +26677,7 @@
         <v>-1.01</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>63.95</v>
@@ -26752,7 +26752,7 @@
         <v>-5.4</v>
       </c>
       <c r="I348" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>63.32</v>
@@ -26831,7 +26831,7 @@
         <v>-7.09</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>62.42</v>
@@ -26910,7 +26910,7 @@
         <v>1.12</v>
       </c>
       <c r="I350" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" t="n">
         <v>61.66</v>
@@ -26989,7 +26989,7 @@
         <v>1.76</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>60.91</v>
@@ -27064,7 +27064,7 @@
         <v>-1.13</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>60.12</v>
@@ -27139,7 +27139,7 @@
         <v>1.5</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>59.42</v>
@@ -27214,7 +27214,7 @@
         <v>0.21</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>58.69</v>
@@ -27289,7 +27289,7 @@
         <v>2.69</v>
       </c>
       <c r="I355" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" t="n">
         <v>58.14</v>
@@ -27364,7 +27364,7 @@
         <v>1.98</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>57.59</v>
@@ -27439,7 +27439,7 @@
         <v>-2.94</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>57.24</v>
@@ -27518,7 +27518,7 @@
         <v>-2.99</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>56.8</v>
@@ -27597,7 +27597,7 @@
         <v>2.48</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>56.55</v>
@@ -27672,7 +27672,7 @@
         <v>-0.35</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>56.37</v>
@@ -27747,7 +27747,7 @@
         <v>-3.32</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>55.94</v>
@@ -27822,7 +27822,7 @@
         <v>1.94</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>55.53</v>
@@ -27897,7 +27897,7 @@
         <v>-1.81</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>54.97</v>
@@ -27972,7 +27972,7 @@
         <v>-3.49</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>54.32</v>
@@ -28047,7 +28047,7 @@
         <v>0.77</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>53.83</v>
@@ -28122,7 +28122,7 @@
         <v>0.39</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>53.4</v>
@@ -28197,7 +28197,7 @@
         <v>4.12</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>53.11</v>
@@ -28272,7 +28272,7 @@
         <v>1.58</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>53.02</v>
@@ -28347,7 +28347,7 @@
         <v>-3.45</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>53.03</v>
@@ -28426,7 +28426,7 @@
         <v>1.02</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>53.04</v>
@@ -28501,7 +28501,7 @@
         <v>0.65</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>53.03</v>
@@ -28576,7 +28576,7 @@
         <v>-2.32</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>52.98</v>
@@ -28651,7 +28651,7 @@
         <v>0.14</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>52.89</v>
@@ -28726,7 +28726,7 @@
         <v>3.34</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>52.89</v>
@@ -28801,7 +28801,7 @@
         <v>-2.13</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>52.75</v>
@@ -28880,7 +28880,7 @@
         <v>0.19</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>52.57</v>
@@ -28955,7 +28955,7 @@
         <v>2.63</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>52.54</v>
@@ -29030,7 +29030,7 @@
         <v>4.14</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>52.7</v>
@@ -29105,7 +29105,7 @@
         <v>-0.39</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>52.79</v>
@@ -29180,7 +29180,7 @@
         <v>2.95</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>52.97</v>
@@ -29255,7 +29255,7 @@
         <v>3.32</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>53.33</v>
@@ -29330,7 +29330,7 @@
         <v>-1.45</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>53.6</v>
@@ -29405,7 +29405,7 @@
         <v>0.87</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>53.94</v>
@@ -29480,7 +29480,7 @@
         <v>-1.52</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>54.33</v>
@@ -29555,7 +29555,7 @@
         <v>0.55</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>54.71</v>
@@ -29630,7 +29630,7 @@
         <v>1.86</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>55.14</v>
@@ -29705,7 +29705,7 @@
         <v>-3.58</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>55.36</v>
@@ -29784,7 +29784,7 @@
         <v>4.47</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>55.67</v>
@@ -29859,7 +29859,7 @@
         <v>2.75</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>56.15</v>
@@ -29934,7 +29934,7 @@
         <v>1.72</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>56.65</v>
@@ -30009,7 +30009,7 @@
         <v>-0.83</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>57.12</v>
@@ -30084,7 +30084,7 @@
         <v>0.19</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>57.65</v>
@@ -30159,7 +30159,7 @@
         <v>-1.17</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>58.14</v>
@@ -30234,7 +30234,7 @@
         <v>1.92</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>58.6</v>
@@ -30309,7 +30309,7 @@
         <v>-4.38</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>58.98</v>
@@ -30384,7 +30384,7 @@
         <v>0.18</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>59.37</v>
@@ -30459,7 +30459,7 @@
         <v>-3.68</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>59.57</v>
@@ -30538,7 +30538,7 @@
         <v>1.99</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>59.72</v>
@@ -30613,7 +30613,7 @@
         <v>2.51</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>59.96</v>
@@ -30688,7 +30688,7 @@
         <v>-1.21</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>60.07</v>
@@ -30767,7 +30767,7 @@
         <v>-0.75</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>60.07</v>
@@ -30842,7 +30842,7 @@
         <v>2.27</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>60.18</v>
@@ -30917,7 +30917,7 @@
         <v>-5.3</v>
       </c>
       <c r="I403" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>60.1</v>
@@ -30996,7 +30996,7 @@
         <v>1.08</v>
       </c>
       <c r="I404" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" t="n">
         <v>60.1</v>
@@ -31071,7 +31071,7 @@
         <v>-2.2</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>60.02</v>
@@ -31146,7 +31146,7 @@
         <v>1.21</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>59.92</v>
@@ -31221,7 +31221,7 @@
         <v>-0.83</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>59.9</v>
@@ -31296,7 +31296,7 @@
         <v>3.37</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>59.84</v>
@@ -31371,7 +31371,7 @@
         <v>1.63</v>
       </c>
       <c r="I409" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" t="n">
         <v>59.76</v>
@@ -31446,7 +31446,7 @@
         <v>-0.5</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>59.6</v>
@@ -31521,7 +31521,7 @@
         <v>1.84</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>59.53</v>
@@ -31596,7 +31596,7 @@
         <v>-4.23</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>59.32</v>
@@ -31675,7 +31675,7 @@
         <v>-0.93</v>
       </c>
       <c r="I413" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J413" t="n">
         <v>59.12</v>
@@ -31731,25 +31731,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D414" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="E414" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="F414" t="n">
+        <v>58.14</v>
+      </c>
       <c r="G414" t="n">
-        <v>13659571</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>13667600</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.9</v>
       </c>
       <c r="I414" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.95999999999999</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>42.89</v>
+        <v>44.75</v>
       </c>
       <c r="O414" t="n">
         <v>37</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>28.07</v>
@@ -683,7 +683,7 @@
         <v>-1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>28.16</v>
@@ -758,7 +758,7 @@
         <v>0.59</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>28.24</v>
@@ -833,7 +833,7 @@
         <v>-0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>28.34</v>
@@ -908,7 +908,7 @@
         <v>1.17</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>28.44</v>
@@ -983,7 +983,7 @@
         <v>0.41</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>28.52</v>
@@ -1058,7 +1058,7 @@
         <v>-0.51</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>28.58</v>
@@ -1133,7 +1133,7 @@
         <v>2.05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>28.7</v>
@@ -1208,7 +1208,7 @@
         <v>-0.33</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>28.79</v>
@@ -1283,7 +1283,7 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>28.88</v>
@@ -1358,7 +1358,7 @@
         <v>-1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>28.97</v>
@@ -1433,7 +1433,7 @@
         <v>-0.51</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>29.05</v>
@@ -1508,7 +1508,7 @@
         <v>-2.07</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>29.12</v>
@@ -1587,7 +1587,7 @@
         <v>0.38</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>29.18</v>
@@ -1662,7 +1662,7 @@
         <v>-1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>29.2</v>
@@ -1737,7 +1737,7 @@
         <v>-0.32</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>29.18</v>
@@ -1816,7 +1816,7 @@
         <v>1.55</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>29.19</v>
@@ -1891,7 +1891,7 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>29.21</v>
@@ -1966,7 +1966,7 @@
         <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>29.24</v>
@@ -2041,7 +2041,7 @@
         <v>-0.27</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>29.26</v>
@@ -2116,7 +2116,7 @@
         <v>-0.34</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>29.27</v>
@@ -2191,7 +2191,7 @@
         <v>-1.62</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>29.27</v>
@@ -2274,7 +2274,7 @@
         <v>2.92</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>29.31</v>
@@ -2353,7 +2353,7 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
         <v>29.37</v>
@@ -2428,7 +2428,7 @@
         <v>1.72</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>29.44</v>
@@ -2503,7 +2503,7 @@
         <v>-0.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>29.5</v>
@@ -2578,7 +2578,7 @@
         <v>0.33</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>29.58</v>
@@ -2653,7 +2653,7 @@
         <v>0.13</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.62</v>
@@ -2728,7 +2728,7 @@
         <v>-0.32</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.67</v>
@@ -2803,7 +2803,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.7</v>
@@ -2878,7 +2878,7 @@
         <v>-1.57</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.72</v>
@@ -2953,7 +2953,7 @@
         <v>-0.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.75</v>
@@ -3028,7 +3028,7 @@
         <v>2.07</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.83</v>
@@ -3103,7 +3103,7 @@
         <v>-0.16</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.91</v>
@@ -3178,7 +3178,7 @@
         <v>2.59</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>30.06</v>
@@ -3253,7 +3253,7 @@
         <v>-1.02</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>30.19</v>
@@ -3328,7 +3328,7 @@
         <v>-0.03</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>30.3</v>
@@ -3403,7 +3403,7 @@
         <v>-1.16</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>30.39</v>
@@ -3478,7 +3478,7 @@
         <v>0.42</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>30.44</v>
@@ -3553,7 +3553,7 @@
         <v>-6.08</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>30.4</v>
@@ -3636,7 +3636,7 @@
         <v>-6.27</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>30.27</v>
@@ -3719,7 +3719,7 @@
         <v>0.22</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>30.17</v>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>30.03</v>
@@ -3885,7 +3885,7 @@
         <v>3.39</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>29.92</v>
@@ -3964,7 +3964,7 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>29.8</v>
@@ -4043,7 +4043,7 @@
         <v>3.22</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>29.72</v>
@@ -4122,7 +4122,7 @@
         <v>0.65</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>29.65</v>
@@ -4197,7 +4197,7 @@
         <v>0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>29.58</v>
@@ -4272,7 +4272,7 @@
         <v>1.19</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>29.53</v>
@@ -4351,7 +4351,7 @@
         <v>-0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>29.48</v>
@@ -4430,7 +4430,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>29.47</v>
@@ -4505,7 +4505,7 @@
         <v>-0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>29.45</v>
@@ -4580,7 +4580,7 @@
         <v>3.59</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.45</v>
@@ -4659,13 +4659,13 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.45</v>
       </c>
       <c r="K55" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
       <c r="L55" t="n">
         <v>28.72</v>
@@ -4734,7 +4734,7 @@
         <v>-1.67</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.39</v>
@@ -4809,7 +4809,7 @@
         <v>0.47</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.35</v>
@@ -4884,7 +4884,7 @@
         <v>-1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.29</v>
@@ -4959,7 +4959,7 @@
         <v>-0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.24</v>
@@ -5038,7 +5038,7 @@
         <v>-0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.17</v>
@@ -5113,7 +5113,7 @@
         <v>-0.92</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.18</v>
@@ -5192,7 +5192,7 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.3</v>
@@ -5267,7 +5267,7 @@
         <v>2.51</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.45</v>
@@ -5342,7 +5342,7 @@
         <v>-2.42</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.57</v>
@@ -5421,7 +5421,7 @@
         <v>-0.1</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.64</v>
@@ -5496,7 +5496,7 @@
         <v>1.15</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>29.72</v>
@@ -5571,7 +5571,7 @@
         <v>-0.57</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>29.74</v>
@@ -5650,7 +5650,7 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>29.77</v>
@@ -5725,7 +5725,7 @@
         <v>-2.27</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>29.76</v>
@@ -5804,7 +5804,7 @@
         <v>1.23</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>29.75</v>
@@ -5879,7 +5879,7 @@
         <v>-1.05</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>29.74</v>
@@ -5954,7 +5954,7 @@
         <v>0.41</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>29.72</v>
@@ -6029,7 +6029,7 @@
         <v>2.41</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>29.75</v>
@@ -6104,7 +6104,7 @@
         <v>1.26</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>29.75</v>
@@ -6179,7 +6179,7 @@
         <v>-1.57</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>29.72</v>
@@ -6254,7 +6254,7 @@
         <v>1.4</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>29.74</v>
@@ -6329,7 +6329,7 @@
         <v>-0.72</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>29.74</v>
@@ -6404,7 +6404,7 @@
         <v>-0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>29.75</v>
@@ -6479,7 +6479,7 @@
         <v>1.07</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>29.79</v>
@@ -6554,7 +6554,7 @@
         <v>-0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>29.82</v>
@@ -6629,7 +6629,7 @@
         <v>5.3</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>29.94</v>
@@ -6704,7 +6704,7 @@
         <v>-0.47</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>30.04</v>
@@ -6779,7 +6779,7 @@
         <v>-0.32</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>30.09</v>
@@ -6854,7 +6854,7 @@
         <v>3.54</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>30.24</v>
@@ -6929,7 +6929,7 @@
         <v>0.74</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>30.4</v>
@@ -7004,7 +7004,7 @@
         <v>2.14</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>30.58</v>
@@ -7079,7 +7079,7 @@
         <v>-0.48</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>30.76</v>
@@ -7154,7 +7154,7 @@
         <v>-0.84</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>30.91</v>
@@ -7229,7 +7229,7 @@
         <v>0.33</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>31.1</v>
@@ -7304,7 +7304,7 @@
         <v>-0.27</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>31.27</v>
@@ -7379,7 +7379,7 @@
         <v>0.18</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>31.46</v>
@@ -7454,7 +7454,7 @@
         <v>2.15</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>31.68</v>
@@ -7529,7 +7529,7 @@
         <v>-1.39</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>31.83</v>
@@ -7604,7 +7604,7 @@
         <v>-1.65</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>31.94</v>
@@ -7679,7 +7679,7 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>32.09</v>
@@ -7754,7 +7754,7 @@
         <v>-1.06</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>32.2</v>
@@ -7829,7 +7829,7 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>32.34</v>
@@ -7904,7 +7904,7 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>32.5</v>
@@ -7979,7 +7979,7 @@
         <v>-2.16</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>32.62</v>
@@ -8054,7 +8054,7 @@
         <v>0.58</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>32.76</v>
@@ -8129,7 +8129,7 @@
         <v>-0.24</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>32.82</v>
@@ -8208,7 +8208,7 @@
         <v>1.56</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>32.91</v>
@@ -8283,7 +8283,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>33.02</v>
@@ -8358,7 +8358,7 @@
         <v>-0.24</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>33.07</v>
@@ -8433,7 +8433,7 @@
         <v>-0.42</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>33.1</v>
@@ -8508,7 +8508,7 @@
         <v>-0.87</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>33.08</v>
@@ -8587,7 +8587,7 @@
         <v>2.27</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>33.1</v>
@@ -8662,7 +8662,7 @@
         <v>3.79</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>33.21</v>
@@ -8737,7 +8737,7 @@
         <v>-1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>33.28</v>
@@ -8812,7 +8812,7 @@
         <v>-1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>33.35</v>
@@ -8887,7 +8887,7 @@
         <v>0.44</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>33.42</v>
@@ -8962,7 +8962,7 @@
         <v>0.7</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>33.46</v>
@@ -9037,7 +9037,7 @@
         <v>-0.12</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>33.53</v>
@@ -9112,7 +9112,7 @@
         <v>2.14</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>33.66</v>
@@ -9187,7 +9187,7 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>33.8</v>
@@ -9262,7 +9262,7 @@
         <v>-0.08</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>33.95</v>
@@ -9337,7 +9337,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>34.08</v>
@@ -9412,7 +9412,7 @@
         <v>-2.34</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>34.14</v>
@@ -9487,10 +9487,10 @@
         <v>-0.06</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="K119" t="n">
         <v>32.22</v>
@@ -9562,7 +9562,7 @@
         <v>0.06</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>34.34</v>
@@ -9637,7 +9637,7 @@
         <v>-3.32</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>34.38</v>
@@ -9716,7 +9716,7 @@
         <v>-0.57</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>34.38</v>
@@ -9791,7 +9791,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>34.38</v>
@@ -9866,7 +9866,7 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>34.41</v>
@@ -9941,7 +9941,7 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>34.46</v>
@@ -10016,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.53</v>
@@ -10091,7 +10091,7 @@
         <v>1.19</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.58</v>
@@ -10166,7 +10166,7 @@
         <v>0.35</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.58</v>
@@ -10241,7 +10241,7 @@
         <v>-2.01</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>34.55</v>
@@ -10320,7 +10320,7 @@
         <v>0.67</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>34.56</v>
@@ -10395,7 +10395,7 @@
         <v>1.71</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>34.59</v>
@@ -10470,7 +10470,7 @@
         <v>-1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>34.58</v>
@@ -10549,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>34.58</v>
@@ -10624,7 +10624,7 @@
         <v>0.14</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>34.54</v>
@@ -10699,7 +10699,7 @@
         <v>-1.97</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>34.44</v>
@@ -10778,7 +10778,7 @@
         <v>1.65</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>34.38</v>
@@ -10853,7 +10853,7 @@
         <v>0.52</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>34.34</v>
@@ -10928,7 +10928,7 @@
         <v>2.11</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>34.37</v>
@@ -11003,7 +11003,7 @@
         <v>-0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>34.39</v>
@@ -11078,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>34.41</v>
@@ -11153,7 +11153,7 @@
         <v>-0.09</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>34.48</v>
@@ -11228,7 +11228,7 @@
         <v>1.51</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>34.59</v>
@@ -11303,7 +11303,7 @@
         <v>1.89</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>34.72</v>
@@ -11378,7 +11378,7 @@
         <v>2.65</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>34.88</v>
@@ -11453,7 +11453,7 @@
         <v>0.51</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>35.03</v>
@@ -11528,7 +11528,7 @@
         <v>-1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>35.16</v>
@@ -11603,7 +11603,7 @@
         <v>0.76</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>35.28</v>
@@ -11678,7 +11678,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>35.41</v>
@@ -11753,7 +11753,7 @@
         <v>-0.88</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>35.56</v>
@@ -11828,7 +11828,7 @@
         <v>0.62</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>35.71</v>
@@ -11903,7 +11903,7 @@
         <v>1.02</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>35.85</v>
@@ -11978,7 +11978,7 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>36.04</v>
@@ -12053,7 +12053,7 @@
         <v>1.1</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>36.26</v>
@@ -12128,7 +12128,7 @@
         <v>-0.41</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>36.46</v>
@@ -12203,7 +12203,7 @@
         <v>-2.1</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>36.66</v>
@@ -12278,7 +12278,7 @@
         <v>0.53</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>36.83</v>
@@ -12353,7 +12353,7 @@
         <v>2.76</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>37.06</v>
@@ -12428,7 +12428,7 @@
         <v>2.56</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>37.29</v>
@@ -12503,7 +12503,7 @@
         <v>-0.2</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>37.54</v>
@@ -12578,7 +12578,7 @@
         <v>-0.35</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>37.78</v>
@@ -12653,7 +12653,7 @@
         <v>3.04</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>38.08</v>
@@ -12728,7 +12728,7 @@
         <v>2.02</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>38.4</v>
@@ -12803,7 +12803,7 @@
         <v>1.53</v>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" t="n">
         <v>38.71</v>
@@ -12878,7 +12878,7 @@
         <v>-0.31</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>38.97</v>
@@ -12953,7 +12953,7 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>39.25</v>
@@ -13028,7 +13028,7 @@
         <v>-0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>39.53</v>
@@ -13103,7 +13103,7 @@
         <v>2.33</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>39.85</v>
@@ -13178,7 +13178,7 @@
         <v>1.24</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>40.17</v>
@@ -13253,7 +13253,7 @@
         <v>-1.52</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>40.49</v>
@@ -13328,7 +13328,7 @@
         <v>2.7</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>40.84</v>
@@ -13403,7 +13403,7 @@
         <v>0.34</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>41.19</v>
@@ -13478,7 +13478,7 @@
         <v>1.61</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>41.54</v>
@@ -13553,7 +13553,7 @@
         <v>4.03</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>41.97</v>
@@ -13628,7 +13628,7 @@
         <v>-0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>42.38</v>
@@ -13703,7 +13703,7 @@
         <v>3.27</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>42.91</v>
@@ -13778,7 +13778,7 @@
         <v>1.74</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>43.46</v>
@@ -13853,7 +13853,7 @@
         <v>-4.43</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>43.86</v>
@@ -13928,7 +13928,7 @@
         <v>1.55</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>44.25</v>
@@ -14003,7 +14003,7 @@
         <v>-8.24</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>44.44</v>
@@ -14082,7 +14082,7 @@
         <v>0.21</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>44.64</v>
@@ -14157,7 +14157,7 @@
         <v>0.68</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>44.8</v>
@@ -14232,7 +14232,7 @@
         <v>-0.43</v>
       </c>
       <c r="I182" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>44.9</v>
@@ -14307,7 +14307,7 @@
         <v>-3.61</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>44.9</v>
@@ -14382,7 +14382,7 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>44.92</v>
@@ -14457,7 +14457,7 @@
         <v>1.24</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>44.93</v>
@@ -14532,7 +14532,7 @@
         <v>2.57</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>45.02</v>
@@ -14607,7 +14607,7 @@
         <v>-0.74</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>45.05</v>
@@ -14682,7 +14682,7 @@
         <v>-0.57</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>45.03</v>
@@ -14757,7 +14757,7 @@
         <v>-2.33</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>45</v>
@@ -14832,7 +14832,7 @@
         <v>2.13</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>44.95</v>
@@ -14907,7 +14907,7 @@
         <v>-0.23</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>44.9</v>
@@ -14982,7 +14982,7 @@
         <v>0.85</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>44.82</v>
@@ -15057,7 +15057,7 @@
         <v>4.26</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>44.75</v>
@@ -15132,7 +15132,7 @@
         <v>1.44</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>44.73</v>
@@ -15207,7 +15207,7 @@
         <v>4.03</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>44.73</v>
@@ -15282,7 +15282,7 @@
         <v>-1.86</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>44.64</v>
@@ -15357,7 +15357,7 @@
         <v>-3.08</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>44.59</v>
@@ -15432,7 +15432,7 @@
         <v>-1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>44.48</v>
@@ -15507,7 +15507,7 @@
         <v>1.39</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>44.59</v>
@@ -15582,7 +15582,7 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>44.72</v>
@@ -15657,7 +15657,7 @@
         <v>-1.44</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>44.8</v>
@@ -15736,7 +15736,7 @@
         <v>-1.05</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>44.87</v>
@@ -15811,7 +15811,7 @@
         <v>2.94</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>45.08</v>
@@ -15886,7 +15886,7 @@
         <v>0.09</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>45.28</v>
@@ -15961,7 +15961,7 @@
         <v>3.71</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>45.54</v>
@@ -16036,7 +16036,7 @@
         <v>5.81</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>45.88</v>
@@ -16111,7 +16111,7 @@
         <v>2.56</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>46.3</v>
@@ -16186,7 +16186,7 @@
         <v>1.16</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>46.77</v>
@@ -16261,7 +16261,7 @@
         <v>-0.11</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>47.29</v>
@@ -16336,7 +16336,7 @@
         <v>-2.47</v>
       </c>
       <c r="I210" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>47.7</v>
@@ -16411,7 +16411,7 @@
         <v>2.3</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>48.16</v>
@@ -16486,7 +16486,7 @@
         <v>-0.45</v>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" t="n">
         <v>48.6</v>
@@ -16561,7 +16561,7 @@
         <v>4.67</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>49.07</v>
@@ -16636,7 +16636,7 @@
         <v>1.63</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>49.55</v>
@@ -16711,7 +16711,7 @@
         <v>2.76</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>50.02</v>
@@ -16786,7 +16786,7 @@
         <v>-2.64</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>50.45</v>
@@ -16861,7 +16861,7 @@
         <v>3.58</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>51.06</v>
@@ -16936,7 +16936,7 @@
         <v>-0.65</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>51.67</v>
@@ -17011,7 +17011,7 @@
         <v>4.38</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>52.38</v>
@@ -17086,7 +17086,7 @@
         <v>-1.56</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>53.03</v>
@@ -17161,7 +17161,7 @@
         <v>2.71</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>53.78</v>
@@ -17236,7 +17236,7 @@
         <v>2.53</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>54.64</v>
@@ -17311,7 +17311,7 @@
         <v>3.79</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>55.55</v>
@@ -17386,7 +17386,7 @@
         <v>0.59</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>56.48</v>
@@ -17461,7 +17461,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>57.62</v>
@@ -17536,7 +17536,7 @@
         <v>-7.19</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>58.36</v>
@@ -17611,7 +17611,7 @@
         <v>4.5</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>59.18</v>
@@ -17686,7 +17686,7 @@
         <v>-6.61</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>59.74</v>
@@ -17761,7 +17761,7 @@
         <v>2.06</v>
       </c>
       <c r="I229" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>60.38</v>
@@ -17836,7 +17836,7 @@
         <v>5.06</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>61.24</v>
@@ -17911,7 +17911,7 @@
         <v>6.7</v>
       </c>
       <c r="I231" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>62.28</v>
@@ -17986,7 +17986,7 @@
         <v>-3.73</v>
       </c>
       <c r="I232" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>63.19</v>
@@ -18061,7 +18061,7 @@
         <v>-1.76</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>63.92</v>
@@ -18136,7 +18136,7 @@
         <v>3.83</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>64.73999999999999</v>
@@ -18211,7 +18211,7 @@
         <v>6.7</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>65.72</v>
@@ -18286,7 +18286,7 @@
         <v>1.77</v>
       </c>
       <c r="I236" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>66.84</v>
@@ -18361,7 +18361,7 @@
         <v>7.58</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>68.16</v>
@@ -18436,7 +18436,7 @@
         <v>-1.47</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>69.44</v>
@@ -18511,7 +18511,7 @@
         <v>-2.76</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>70.48</v>
@@ -18586,7 +18586,7 @@
         <v>5.39</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>71.78</v>
@@ -18661,7 +18661,7 @@
         <v>-1.67</v>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" t="n">
         <v>72.94</v>
@@ -18736,7 +18736,7 @@
         <v>3.78</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>74.17</v>
@@ -18811,7 +18811,7 @@
         <v>6.63</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>75.56999999999999</v>
@@ -18886,7 +18886,7 @@
         <v>5.84</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>77.23</v>
@@ -18961,7 +18961,7 @@
         <v>3.3</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>78.75</v>
@@ -19036,7 +19036,7 @@
         <v>3.95</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>80.73</v>
@@ -19111,7 +19111,7 @@
         <v>-0.03</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>82.56</v>
@@ -19186,7 +19186,7 @@
         <v>-28.54</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>83.11</v>
@@ -19265,7 +19265,7 @@
         <v>-3.98</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>83.45</v>
@@ -19340,7 +19340,7 @@
         <v>6.24</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>83.84</v>
@@ -19415,7 +19415,7 @@
         <v>2.88</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>84.11</v>
@@ -19490,7 +19490,7 @@
         <v>-15.77</v>
       </c>
       <c r="I252" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19565,7 +19565,7 @@
         <v>5.25</v>
       </c>
       <c r="I253" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" t="n">
         <v>83.92</v>
@@ -19640,7 +19640,7 @@
         <v>8.33</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>84.11</v>
@@ -19715,7 +19715,7 @@
         <v>-3.46</v>
       </c>
       <c r="I255" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>83.92</v>
@@ -19790,7 +19790,7 @@
         <v>4.29</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>83.81999999999999</v>
@@ -19865,7 +19865,7 @@
         <v>-11.53</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" s="4" t="n">
         <v>82.97</v>
@@ -19940,7 +19940,7 @@
         <v>2.94</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>82.29000000000001</v>
@@ -20015,7 +20015,7 @@
         <v>-4.8</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>81.56</v>
@@ -20094,7 +20094,7 @@
         <v>5.6</v>
       </c>
       <c r="I260" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>80.8</v>
@@ -20169,7 +20169,7 @@
         <v>1.31</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>80.15000000000001</v>
@@ -20244,7 +20244,7 @@
         <v>7.9</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>79.62</v>
@@ -20319,7 +20319,7 @@
         <v>5.16</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>79.01000000000001</v>
@@ -20394,7 +20394,7 @@
         <v>-1.85</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>78.04000000000001</v>
@@ -20469,7 +20469,7 @@
         <v>1.21</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>76.97</v>
@@ -20544,7 +20544,7 @@
         <v>0.51</v>
       </c>
       <c r="I266" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" t="n">
         <v>75.70999999999999</v>
@@ -20619,7 +20619,7 @@
         <v>5.64</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>74.68000000000001</v>
@@ -20694,7 +20694,7 @@
         <v>-4.02</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>74.98999999999999</v>
@@ -20769,7 +20769,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I269" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" s="4" t="n">
         <v>75.09999999999999</v>
@@ -20848,7 +20848,7 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" t="n">
         <v>75.02</v>
@@ -20923,7 +20923,7 @@
         <v>-1.42</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>74.77</v>
@@ -21002,7 +21002,7 @@
         <v>2.25</v>
       </c>
       <c r="I272" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>75.23</v>
@@ -21081,7 +21081,7 @@
         <v>3.06</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>75.64</v>
@@ -21156,7 +21156,7 @@
         <v>2.34</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>75.84</v>
@@ -21231,7 +21231,7 @@
         <v>-2.72</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>76.06</v>
@@ -21306,7 +21306,7 @@
         <v>-1.84</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>76.06</v>
@@ -21375,7 +21375,7 @@
         <v>-4.96</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>76.31</v>
@@ -21458,7 +21458,7 @@
         <v>0.73</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>76.48</v>
@@ -21533,7 +21533,7 @@
         <v>-2.13</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>76.75</v>
@@ -21608,7 +21608,7 @@
         <v>-4.13</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>76.68000000000001</v>
@@ -21683,7 +21683,7 @@
         <v>-4.4</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>76.41</v>
@@ -21758,7 +21758,7 @@
         <v>-6.33</v>
       </c>
       <c r="I282" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>75.66</v>
@@ -21841,7 +21841,7 @@
         <v>1.54</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>74.75</v>
@@ -21916,7 +21916,7 @@
         <v>0.77</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>73.95</v>
@@ -21991,7 +21991,7 @@
         <v>3.59</v>
       </c>
       <c r="I285" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>73.2</v>
@@ -22066,7 +22066,7 @@
         <v>-6.81</v>
       </c>
       <c r="I286" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" s="4" t="n">
         <v>72.22</v>
@@ -22145,7 +22145,7 @@
         <v>4.39</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>71.14</v>
@@ -22224,7 +22224,7 @@
         <v>0.13</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>70.23999999999999</v>
@@ -22299,7 +22299,7 @@
         <v>7.27</v>
       </c>
       <c r="I289" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>69.91</v>
@@ -22374,7 +22374,7 @@
         <v>0</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>69.55</v>
@@ -22449,7 +22449,7 @@
         <v>-3.45</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>69.13</v>
@@ -22524,7 +22524,7 @@
         <v>0.46</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>68.64</v>
@@ -22599,7 +22599,7 @@
         <v>-0.23</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>68.02</v>
@@ -22678,7 +22678,7 @@
         <v>2.32</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>67.39</v>
@@ -22753,7 +22753,7 @@
         <v>1.36</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>66.91</v>
@@ -22828,7 +22828,7 @@
         <v>1.01</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>66.54000000000001</v>
@@ -22903,7 +22903,7 @@
         <v>-1.16</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>66.31999999999999</v>
@@ -22978,7 +22978,7 @@
         <v>5.51</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>66.26000000000001</v>
@@ -23053,7 +23053,7 @@
         <v>-0.28</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>66.27</v>
@@ -23128,7 +23128,7 @@
         <v>-0.84</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>66.40000000000001</v>
@@ -23203,7 +23203,7 @@
         <v>3.35</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>66.8</v>
@@ -23278,7 +23278,7 @@
         <v>-2.01</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>67.33</v>
@@ -23353,7 +23353,7 @@
         <v>-5.07</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>67.63</v>
@@ -23428,7 +23428,7 @@
         <v>2.74</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>68</v>
@@ -23503,7 +23503,7 @@
         <v>-2.83</v>
       </c>
       <c r="I305" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" t="n">
         <v>68.16</v>
@@ -23578,7 +23578,7 @@
         <v>0.6</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>68.56</v>
@@ -23653,7 +23653,7 @@
         <v>-0.67</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>68.8</v>
@@ -23732,7 +23732,7 @@
         <v>-3.12</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>68.94</v>
@@ -23811,7 +23811,7 @@
         <v>-2.05</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>68.77</v>
@@ -23886,7 +23886,7 @@
         <v>2.81</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>68.7</v>
@@ -23961,7 +23961,7 @@
         <v>2.45</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>68.81999999999999</v>
@@ -24036,7 +24036,7 @@
         <v>-3.44</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>68.81999999999999</v>
@@ -24115,7 +24115,7 @@
         <v>-0.05</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>68.81999999999999</v>
@@ -24190,7 +24190,7 @@
         <v>6.4</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>68.95</v>
@@ -24265,7 +24265,7 @@
         <v>2.1</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>69.11</v>
@@ -24340,7 +24340,7 @@
         <v>1.97</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>69.31</v>
@@ -24415,7 +24415,7 @@
         <v>6.83</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>69.79000000000001</v>
@@ -24490,7 +24490,7 @@
         <v>0.71</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>70.12</v>
@@ -24565,7 +24565,7 @@
         <v>1.02</v>
       </c>
       <c r="I319" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" t="n">
         <v>70.48999999999999</v>
@@ -24640,7 +24640,7 @@
         <v>-4.84</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>70.70999999999999</v>
@@ -24715,7 +24715,7 @@
         <v>-8.57</v>
       </c>
       <c r="I321" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" s="4" t="n">
         <v>70.48</v>
@@ -24794,7 +24794,7 @@
         <v>1.3</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>70.37</v>
@@ -24869,7 +24869,7 @@
         <v>-4.35</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>70.29000000000001</v>
@@ -24944,7 +24944,7 @@
         <v>2.74</v>
       </c>
       <c r="I324" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>70.20999999999999</v>
@@ -25019,7 +25019,7 @@
         <v>1.05</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>70.26000000000001</v>
@@ -25094,7 +25094,7 @@
         <v>-1.57</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>70.23999999999999</v>
@@ -25169,7 +25169,7 @@
         <v>1.99</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>70.31</v>
@@ -25244,7 +25244,7 @@
         <v>-3.18</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>70.37</v>
@@ -25319,7 +25319,7 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>70.55</v>
@@ -25394,7 +25394,7 @@
         <v>-0.04</v>
       </c>
       <c r="I330" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" t="n">
         <v>70.63</v>
@@ -25469,7 +25469,7 @@
         <v>-0.97</v>
       </c>
       <c r="I331" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" t="n">
         <v>70.59999999999999</v>
@@ -25544,7 +25544,7 @@
         <v>0.47</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>70.7</v>
@@ -25619,7 +25619,7 @@
         <v>-2.62</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>70.72</v>
@@ -25694,7 +25694,7 @@
         <v>1.16</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>70.56</v>
@@ -25769,7 +25769,7 @@
         <v>-8.08</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" s="4" t="n">
         <v>70.06</v>
@@ -25844,7 +25844,7 @@
         <v>0.02</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>69.48999999999999</v>
@@ -25919,7 +25919,7 @@
         <v>-4.17</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>68.54000000000001</v>
@@ -25998,7 +25998,7 @@
         <v>-2.29</v>
       </c>
       <c r="I338" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>67.48999999999999</v>
@@ -26077,7 +26077,7 @@
         <v>5.48</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>66.56999999999999</v>
@@ -26152,7 +26152,7 @@
         <v>0.77</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>65.86</v>
@@ -26227,7 +26227,7 @@
         <v>3.56</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>65.58</v>
@@ -26302,7 +26302,7 @@
         <v>-0.13</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>65.25</v>
@@ -26377,10 +26377,10 @@
         <v>-4.39</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
-        <v>64.94</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K343" t="n">
         <v>67.62</v>
@@ -26452,7 +26452,7 @@
         <v>-1.81</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>64.47</v>
@@ -26527,7 +26527,7 @@
         <v>-1.01</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>63.95</v>
@@ -26602,7 +26602,7 @@
         <v>-5.4</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>63.32</v>
@@ -26681,7 +26681,7 @@
         <v>-7.09</v>
       </c>
       <c r="I347" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>62.42</v>
@@ -26760,7 +26760,7 @@
         <v>1.12</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>61.66</v>
@@ -26839,7 +26839,7 @@
         <v>1.76</v>
       </c>
       <c r="I349" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>60.91</v>
@@ -26914,7 +26914,7 @@
         <v>-1.13</v>
       </c>
       <c r="I350" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>60.12</v>
@@ -26989,7 +26989,7 @@
         <v>1.5</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>59.42</v>
@@ -27064,7 +27064,7 @@
         <v>0.21</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>58.69</v>
@@ -27139,7 +27139,7 @@
         <v>2.69</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>58.14</v>
@@ -27214,7 +27214,7 @@
         <v>1.98</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>57.59</v>
@@ -27289,7 +27289,7 @@
         <v>-2.94</v>
       </c>
       <c r="I355" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>57.24</v>
@@ -27368,7 +27368,7 @@
         <v>-2.99</v>
       </c>
       <c r="I356" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>56.8</v>
@@ -27447,10 +27447,10 @@
         <v>2.48</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="K357" t="n">
         <v>64.95999999999999</v>
@@ -27522,7 +27522,7 @@
         <v>-0.35</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>56.37</v>
@@ -27597,7 +27597,7 @@
         <v>-3.32</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>55.94</v>
@@ -27672,7 +27672,7 @@
         <v>1.94</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>55.53</v>
@@ -27747,7 +27747,7 @@
         <v>-1.81</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>54.97</v>
@@ -27822,7 +27822,7 @@
         <v>-3.49</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>54.32</v>
@@ -27897,7 +27897,7 @@
         <v>0.77</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>53.83</v>
@@ -27972,7 +27972,7 @@
         <v>0.39</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>53.4</v>
@@ -28047,7 +28047,7 @@
         <v>4.12</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>53.11</v>
@@ -28122,7 +28122,7 @@
         <v>1.58</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>53.02</v>
@@ -28197,7 +28197,7 @@
         <v>-3.45</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>53.03</v>
@@ -28276,7 +28276,7 @@
         <v>1.02</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>53.04</v>
@@ -28351,7 +28351,7 @@
         <v>0.65</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>53.03</v>
@@ -28426,7 +28426,7 @@
         <v>-2.32</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>52.98</v>
@@ -28501,7 +28501,7 @@
         <v>0.14</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>52.89</v>
@@ -28576,7 +28576,7 @@
         <v>3.34</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>52.89</v>
@@ -28651,7 +28651,7 @@
         <v>-2.13</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>52.75</v>
@@ -28730,7 +28730,7 @@
         <v>0.19</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>52.57</v>
@@ -28805,7 +28805,7 @@
         <v>2.63</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>52.54</v>
@@ -28880,7 +28880,7 @@
         <v>4.14</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>52.7</v>
@@ -28955,7 +28955,7 @@
         <v>-0.39</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>52.79</v>
@@ -29030,7 +29030,7 @@
         <v>2.95</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>52.97</v>
@@ -29105,7 +29105,7 @@
         <v>3.32</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>53.33</v>
@@ -29180,7 +29180,7 @@
         <v>-1.45</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>53.6</v>
@@ -29255,7 +29255,7 @@
         <v>0.87</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>53.94</v>
@@ -29330,7 +29330,7 @@
         <v>-1.52</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>54.33</v>
@@ -29405,7 +29405,7 @@
         <v>0.55</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>54.71</v>
@@ -29480,7 +29480,7 @@
         <v>1.86</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>55.14</v>
@@ -29555,7 +29555,7 @@
         <v>-3.58</v>
       </c>
       <c r="I385" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" t="n">
         <v>55.36</v>
@@ -29634,7 +29634,7 @@
         <v>4.47</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>55.67</v>
@@ -29709,7 +29709,7 @@
         <v>2.75</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>56.15</v>
@@ -29784,7 +29784,7 @@
         <v>1.72</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>56.65</v>
@@ -29859,7 +29859,7 @@
         <v>-0.83</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>57.12</v>
@@ -29934,7 +29934,7 @@
         <v>0.19</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>57.65</v>
@@ -30009,7 +30009,7 @@
         <v>-1.17</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>58.14</v>
@@ -30084,7 +30084,7 @@
         <v>1.92</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>58.6</v>
@@ -30159,7 +30159,7 @@
         <v>-4.38</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>58.98</v>
@@ -30234,7 +30234,7 @@
         <v>0.18</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>59.37</v>
@@ -30309,7 +30309,7 @@
         <v>-3.68</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>59.57</v>
@@ -30388,7 +30388,7 @@
         <v>1.99</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>59.72</v>
@@ -30463,7 +30463,7 @@
         <v>2.51</v>
       </c>
       <c r="I397" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" t="n">
         <v>59.96</v>
@@ -30538,7 +30538,7 @@
         <v>-1.21</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>60.07</v>
@@ -30617,7 +30617,7 @@
         <v>-0.75</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>60.07</v>
@@ -30692,7 +30692,7 @@
         <v>2.27</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>60.18</v>
@@ -30767,7 +30767,7 @@
         <v>-5.3</v>
       </c>
       <c r="I401" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>60.1</v>
@@ -30846,7 +30846,7 @@
         <v>1.08</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>60.1</v>
@@ -30921,7 +30921,7 @@
         <v>-2.2</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>60.02</v>
@@ -30996,7 +30996,7 @@
         <v>1.21</v>
       </c>
       <c r="I404" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>59.92</v>
@@ -31071,7 +31071,7 @@
         <v>-0.83</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>59.9</v>
@@ -31146,7 +31146,7 @@
         <v>3.37</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>59.84</v>
@@ -31221,7 +31221,7 @@
         <v>1.63</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>59.76</v>
@@ -31296,7 +31296,7 @@
         <v>-0.5</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>59.6</v>
@@ -31371,7 +31371,7 @@
         <v>1.84</v>
       </c>
       <c r="I409" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" t="n">
         <v>59.53</v>
@@ -31446,7 +31446,7 @@
         <v>-4.23</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>59.32</v>
@@ -31525,7 +31525,7 @@
         <v>-0.93</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>59.12</v>
@@ -31600,7 +31600,7 @@
         <v>0.9</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>58.89</v>
@@ -31644,6 +31644,83 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="D413" s="4" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="E413" s="4" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="F413" s="4" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G413" s="4" t="n">
+        <v>10993089</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="I413" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" s="4" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="K413" s="4" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="L413" s="4" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="M413" s="4" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="N413" s="6" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="O413" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" s="4" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" s="4" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" s="4" t="inlineStr"/>
+      <c r="W413" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -4665,7 +4665,7 @@
         <v>29.45</v>
       </c>
       <c r="K55" t="n">
-        <v>29.52</v>
+        <v>29.51</v>
       </c>
       <c r="L55" t="n">
         <v>28.72</v>
@@ -9944,7 +9944,7 @@
         <v>5.2</v>
       </c>
       <c r="J125" t="n">
-        <v>34.46</v>
+        <v>34.47</v>
       </c>
       <c r="K125" t="n">
         <v>32.65</v>
@@ -31666,13 +31666,13 @@
         <v>54.87</v>
       </c>
       <c r="F413" s="4" t="n">
-        <v>55.1</v>
+        <v>54.95</v>
       </c>
       <c r="G413" s="4" t="n">
-        <v>10993089</v>
+        <v>22535254</v>
       </c>
       <c r="H413" s="5" t="n">
-        <v>-5.23</v>
+        <v>-5.49</v>
       </c>
       <c r="I413" s="4" t="n">
         <v>5.2</v>
@@ -31687,10 +31687,10 @@
         <v>61.34</v>
       </c>
       <c r="M413" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>65.95</v>
       </c>
       <c r="N413" s="6" t="n">
-        <v>38.52</v>
+        <v>38.21</v>
       </c>
       <c r="O413" s="4" t="n">
         <v>34</v>
@@ -31711,16 +31711,18 @@
         </is>
       </c>
       <c r="S413" s="4" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="6" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="6" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" s="4" t="inlineStr"/>
-      <c r="W413" s="6" t="inlineStr"/>
+      <c r="W413" s="6" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31649,6 +31649,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="D413" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="E413" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="F413" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="G413" t="n">
+        <v>5395534</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -4590,7 +4590,7 @@
         <v>29.45</v>
       </c>
       <c r="K54" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
       <c r="L54" t="n">
         <v>28.72</v>
@@ -5581,7 +5581,7 @@
         <v>29.77</v>
       </c>
       <c r="K67" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="L67" t="n">
         <v>28.82</v>
@@ -31594,7 +31594,7 @@
         <v>54.95</v>
       </c>
       <c r="G412" s="4" t="n">
-        <v>22600000</v>
+        <v>22649300</v>
       </c>
       <c r="H412" s="5" t="n">
         <v>-5.49</v>
@@ -31664,28 +31664,28 @@
         <v>55.03</v>
       </c>
       <c r="D413" t="n">
-        <v>55.41</v>
+        <v>55.49</v>
       </c>
       <c r="E413" t="n">
         <v>54.81</v>
       </c>
       <c r="F413" t="n">
-        <v>54.85</v>
+        <v>55.48</v>
       </c>
       <c r="G413" t="n">
-        <v>5395534</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.18</v>
+        <v>12318324</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.96</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
       <c r="J413" t="n">
-        <v>58.37</v>
+        <v>58.41</v>
       </c>
       <c r="K413" t="n">
-        <v>56.77</v>
+        <v>56.78</v>
       </c>
       <c r="L413" t="n">
         <v>61.24</v>
@@ -31694,10 +31694,10 @@
         <v>65.95</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>33.22</v>
+        <v>35.38</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31711,13 +31711,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31585,25 +31585,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="D412" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E412" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="F412" t="n">
+        <v>55.48</v>
+      </c>
       <c r="G412" t="n">
-        <v>12397795</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>12422400</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.96</v>
       </c>
       <c r="I412" t="n">
         <v>5.2</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="K412" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="L412" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="M412" t="n">
+        <v>65.95</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>33.41</v>
+        <v>35.38</v>
       </c>
       <c r="O412" t="n">
         <v>32</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31622,7 +31622,7 @@
         <v>35.38</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31649,6 +31649,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="D413" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="E413" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="F413" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="G413" t="n">
+        <v>13485153</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="L413" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>0.59</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>28.24</v>
@@ -683,7 +683,7 @@
         <v>-0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>28.34</v>
@@ -758,7 +758,7 @@
         <v>1.17</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>28.44</v>
@@ -833,7 +833,7 @@
         <v>0.41</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>28.52</v>
@@ -908,7 +908,7 @@
         <v>-0.51</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>28.58</v>
@@ -983,7 +983,7 @@
         <v>2.05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>28.7</v>
@@ -1058,7 +1058,7 @@
         <v>-0.33</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>28.79</v>
@@ -1133,7 +1133,7 @@
         <v>0.47</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>28.88</v>
@@ -1208,7 +1208,7 @@
         <v>-1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>28.97</v>
@@ -1283,7 +1283,7 @@
         <v>-0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>29.05</v>
@@ -1358,7 +1358,7 @@
         <v>-2.07</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>29.12</v>
@@ -1437,7 +1437,7 @@
         <v>0.38</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>29.18</v>
@@ -1512,7 +1512,7 @@
         <v>-1.87</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>29.2</v>
@@ -1587,7 +1587,7 @@
         <v>-0.32</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>29.18</v>
@@ -1666,7 +1666,7 @@
         <v>1.55</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>29.19</v>
@@ -1741,7 +1741,7 @@
         <v>0.87</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>29.21</v>
@@ -1816,7 +1816,7 @@
         <v>2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>29.24</v>
@@ -1891,7 +1891,7 @@
         <v>-0.27</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>29.26</v>
@@ -1966,7 +1966,7 @@
         <v>-0.34</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>29.27</v>
@@ -2041,7 +2041,7 @@
         <v>-1.62</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>29.27</v>
@@ -2124,7 +2124,7 @@
         <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>29.31</v>
@@ -2203,7 +2203,7 @@
         <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>29.37</v>
@@ -2278,7 +2278,7 @@
         <v>1.72</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>29.44</v>
@@ -2353,7 +2353,7 @@
         <v>-0.1</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>29.5</v>
@@ -2428,7 +2428,7 @@
         <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>29.58</v>
@@ -2503,7 +2503,7 @@
         <v>0.13</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>29.62</v>
@@ -2578,7 +2578,7 @@
         <v>-0.32</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>29.67</v>
@@ -2653,7 +2653,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.7</v>
@@ -2728,7 +2728,7 @@
         <v>-1.57</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.72</v>
@@ -2803,7 +2803,7 @@
         <v>-0.2</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.75</v>
@@ -2878,7 +2878,7 @@
         <v>2.07</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.83</v>
@@ -2953,7 +2953,7 @@
         <v>-0.16</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.91</v>
@@ -3028,7 +3028,7 @@
         <v>2.59</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>30.06</v>
@@ -3103,7 +3103,7 @@
         <v>-1.02</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>30.19</v>
@@ -3178,7 +3178,7 @@
         <v>-0.03</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>30.3</v>
@@ -3253,7 +3253,7 @@
         <v>-1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>30.39</v>
@@ -3328,7 +3328,7 @@
         <v>0.42</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>30.44</v>
@@ -3403,7 +3403,7 @@
         <v>-6.08</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>30.4</v>
@@ -3486,7 +3486,7 @@
         <v>-6.27</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>30.27</v>
@@ -3569,7 +3569,7 @@
         <v>0.22</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>30.17</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>30.03</v>
@@ -3735,7 +3735,7 @@
         <v>3.39</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>29.92</v>
@@ -3814,7 +3814,7 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>29.8</v>
@@ -3893,7 +3893,7 @@
         <v>3.22</v>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>29.72</v>
@@ -3972,7 +3972,7 @@
         <v>0.65</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>29.65</v>
@@ -4047,7 +4047,7 @@
         <v>0.1</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>29.58</v>
@@ -4122,7 +4122,7 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>29.53</v>
@@ -4201,7 +4201,7 @@
         <v>-0.71</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>29.48</v>
@@ -4280,7 +4280,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>29.47</v>
@@ -4355,7 +4355,7 @@
         <v>-0.97</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>29.45</v>
@@ -4430,7 +4430,7 @@
         <v>3.59</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>29.45</v>
@@ -4509,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.45</v>
@@ -4584,7 +4584,7 @@
         <v>-1.67</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.39</v>
@@ -4659,7 +4659,7 @@
         <v>0.47</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.35</v>
@@ -4734,7 +4734,7 @@
         <v>-1.19</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.29</v>
@@ -4809,7 +4809,7 @@
         <v>-0.77</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.24</v>
@@ -4888,7 +4888,7 @@
         <v>-0.71</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.17</v>
@@ -4963,7 +4963,7 @@
         <v>-0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.18</v>
@@ -5042,7 +5042,7 @@
         <v>1.24</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.3</v>
@@ -5117,7 +5117,7 @@
         <v>2.51</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.45</v>
@@ -5192,7 +5192,7 @@
         <v>-2.42</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.57</v>
@@ -5271,7 +5271,7 @@
         <v>-0.1</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.64</v>
@@ -5346,7 +5346,7 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.72</v>
@@ -5421,7 +5421,7 @@
         <v>-0.57</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.74</v>
@@ -5500,7 +5500,7 @@
         <v>1.01</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>29.77</v>
@@ -5575,7 +5575,7 @@
         <v>-2.27</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>29.76</v>
@@ -5654,7 +5654,7 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>29.75</v>
@@ -5729,7 +5729,7 @@
         <v>-1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>29.74</v>
@@ -5804,7 +5804,7 @@
         <v>0.41</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>29.72</v>
@@ -5879,7 +5879,7 @@
         <v>2.41</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>29.75</v>
@@ -5954,7 +5954,7 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>29.75</v>
@@ -6029,7 +6029,7 @@
         <v>-1.57</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>29.72</v>
@@ -6104,7 +6104,7 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>29.74</v>
@@ -6179,7 +6179,7 @@
         <v>-0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>29.74</v>
@@ -6254,7 +6254,7 @@
         <v>-0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>29.75</v>
@@ -6329,7 +6329,7 @@
         <v>1.07</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>29.79</v>
@@ -6404,7 +6404,7 @@
         <v>-0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>29.82</v>
@@ -6479,7 +6479,7 @@
         <v>5.3</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>29.94</v>
@@ -6554,7 +6554,7 @@
         <v>-0.47</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>30.04</v>
@@ -6629,7 +6629,7 @@
         <v>-0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>30.09</v>
@@ -6704,7 +6704,7 @@
         <v>3.54</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>30.24</v>
@@ -6779,7 +6779,7 @@
         <v>0.74</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>30.4</v>
@@ -6854,7 +6854,7 @@
         <v>2.14</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>30.58</v>
@@ -6929,7 +6929,7 @@
         <v>-0.48</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>30.76</v>
@@ -7004,7 +7004,7 @@
         <v>-0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>30.91</v>
@@ -7079,7 +7079,7 @@
         <v>0.33</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>31.1</v>
@@ -7154,7 +7154,7 @@
         <v>-0.27</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>31.27</v>
@@ -7229,7 +7229,7 @@
         <v>0.18</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>31.46</v>
@@ -7304,7 +7304,7 @@
         <v>2.15</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>31.68</v>
@@ -7379,7 +7379,7 @@
         <v>-1.39</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>31.83</v>
@@ -7454,7 +7454,7 @@
         <v>-1.65</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>31.94</v>
@@ -7529,7 +7529,7 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>32.09</v>
@@ -7604,7 +7604,7 @@
         <v>-1.06</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>32.2</v>
@@ -7679,7 +7679,7 @@
         <v>1.23</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>32.34</v>
@@ -7754,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>32.5</v>
@@ -7829,7 +7829,7 @@
         <v>-2.16</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>32.62</v>
@@ -7904,7 +7904,7 @@
         <v>0.58</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>32.76</v>
@@ -7979,7 +7979,7 @@
         <v>-0.24</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>32.82</v>
@@ -8058,7 +8058,7 @@
         <v>1.56</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>32.91</v>
@@ -8133,7 +8133,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>33.02</v>
@@ -8208,7 +8208,7 @@
         <v>-0.24</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>33.07</v>
@@ -8283,7 +8283,7 @@
         <v>-0.42</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>33.1</v>
@@ -8358,7 +8358,7 @@
         <v>-0.87</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>33.08</v>
@@ -8437,7 +8437,7 @@
         <v>2.27</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>33.1</v>
@@ -8512,7 +8512,7 @@
         <v>3.79</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>33.21</v>
@@ -8587,7 +8587,7 @@
         <v>-1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>33.28</v>
@@ -8662,7 +8662,7 @@
         <v>-1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>33.35</v>
@@ -8737,7 +8737,7 @@
         <v>0.44</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>33.42</v>
@@ -8812,7 +8812,7 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>33.46</v>
@@ -8887,7 +8887,7 @@
         <v>-0.12</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>33.53</v>
@@ -8962,7 +8962,7 @@
         <v>2.14</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>33.66</v>
@@ -9037,7 +9037,7 @@
         <v>1.05</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>33.8</v>
@@ -9112,7 +9112,7 @@
         <v>-0.08</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>33.95</v>
@@ -9187,7 +9187,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>34.08</v>
@@ -9262,7 +9262,7 @@
         <v>-2.34</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>34.14</v>
@@ -9337,7 +9337,7 @@
         <v>-0.06</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>34.25</v>
@@ -9412,7 +9412,7 @@
         <v>0.06</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>34.34</v>
@@ -9487,7 +9487,7 @@
         <v>-3.32</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>34.38</v>
@@ -9566,7 +9566,7 @@
         <v>-0.57</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>34.38</v>
@@ -9641,7 +9641,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>34.38</v>
@@ -9716,7 +9716,7 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>34.41</v>
@@ -9791,7 +9791,7 @@
         <v>1.09</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>34.47</v>
@@ -9866,7 +9866,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>34.53</v>
@@ -9941,7 +9941,7 @@
         <v>1.19</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.58</v>
@@ -10016,7 +10016,7 @@
         <v>0.35</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.58</v>
@@ -10091,7 +10091,7 @@
         <v>-2.01</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.55</v>
@@ -10170,7 +10170,7 @@
         <v>0.67</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.56</v>
@@ -10245,7 +10245,7 @@
         <v>1.71</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>34.59</v>
@@ -10320,7 +10320,7 @@
         <v>-1.43</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>34.58</v>
@@ -10399,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>34.58</v>
@@ -10474,7 +10474,7 @@
         <v>0.14</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>34.54</v>
@@ -10549,7 +10549,7 @@
         <v>-1.97</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>34.44</v>
@@ -10628,7 +10628,7 @@
         <v>1.65</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>34.38</v>
@@ -10703,7 +10703,7 @@
         <v>0.52</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>34.34</v>
@@ -10778,7 +10778,7 @@
         <v>2.11</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>34.37</v>
@@ -10853,7 +10853,7 @@
         <v>-0.91</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>34.39</v>
@@ -10928,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>34.41</v>
@@ -11003,7 +11003,7 @@
         <v>-0.09</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>34.48</v>
@@ -11078,7 +11078,7 @@
         <v>1.51</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>34.59</v>
@@ -11153,7 +11153,7 @@
         <v>1.89</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>34.72</v>
@@ -11228,7 +11228,7 @@
         <v>2.65</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>34.88</v>
@@ -11303,7 +11303,7 @@
         <v>0.51</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>35.03</v>
@@ -11378,7 +11378,7 @@
         <v>-1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>35.16</v>
@@ -11453,7 +11453,7 @@
         <v>0.76</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>35.28</v>
@@ -11528,7 +11528,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>35.41</v>
@@ -11603,7 +11603,7 @@
         <v>-0.88</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>35.56</v>
@@ -11678,7 +11678,7 @@
         <v>0.62</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>35.71</v>
@@ -11753,7 +11753,7 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>35.85</v>
@@ -11828,7 +11828,7 @@
         <v>1.46</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>36.04</v>
@@ -11903,7 +11903,7 @@
         <v>1.1</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>36.26</v>
@@ -11978,7 +11978,7 @@
         <v>-0.41</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>36.46</v>
@@ -12053,7 +12053,7 @@
         <v>-2.1</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>36.66</v>
@@ -12128,7 +12128,7 @@
         <v>0.53</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>36.83</v>
@@ -12203,7 +12203,7 @@
         <v>2.76</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>37.06</v>
@@ -12278,7 +12278,7 @@
         <v>2.56</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>37.29</v>
@@ -12353,7 +12353,7 @@
         <v>-0.2</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>37.54</v>
@@ -12428,7 +12428,7 @@
         <v>-0.35</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>37.78</v>
@@ -12503,7 +12503,7 @@
         <v>3.04</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>38.08</v>
@@ -12578,7 +12578,7 @@
         <v>2.02</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>38.4</v>
@@ -12653,7 +12653,7 @@
         <v>1.53</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>38.71</v>
@@ -12728,7 +12728,7 @@
         <v>-0.31</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>38.97</v>
@@ -12803,7 +12803,7 @@
         <v>1.27</v>
       </c>
       <c r="I163" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>39.25</v>
@@ -12878,7 +12878,7 @@
         <v>-0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>39.53</v>
@@ -12953,7 +12953,7 @@
         <v>2.33</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>39.85</v>
@@ -13028,7 +13028,7 @@
         <v>1.24</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>40.17</v>
@@ -13103,7 +13103,7 @@
         <v>-1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>40.49</v>
@@ -13178,7 +13178,7 @@
         <v>2.7</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>40.84</v>
@@ -13253,7 +13253,7 @@
         <v>0.34</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>41.19</v>
@@ -13328,7 +13328,7 @@
         <v>1.61</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>41.54</v>
@@ -13403,7 +13403,7 @@
         <v>4.03</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>41.97</v>
@@ -13478,7 +13478,7 @@
         <v>-0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>42.38</v>
@@ -13553,7 +13553,7 @@
         <v>3.27</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>42.91</v>
@@ -13628,7 +13628,7 @@
         <v>1.74</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>43.46</v>
@@ -13703,7 +13703,7 @@
         <v>-4.43</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>43.86</v>
@@ -13778,7 +13778,7 @@
         <v>1.55</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>44.25</v>
@@ -13853,7 +13853,7 @@
         <v>-8.24</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>44.44</v>
@@ -13932,7 +13932,7 @@
         <v>0.21</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>44.64</v>
@@ -14007,7 +14007,7 @@
         <v>0.68</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>44.8</v>
@@ -14082,7 +14082,7 @@
         <v>-0.43</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>44.9</v>
@@ -14157,7 +14157,7 @@
         <v>-3.61</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>44.9</v>
@@ -14232,7 +14232,7 @@
         <v>0.71</v>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>44.92</v>
@@ -14307,7 +14307,7 @@
         <v>1.24</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>44.93</v>
@@ -14382,7 +14382,7 @@
         <v>2.57</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>45.02</v>
@@ -14457,7 +14457,7 @@
         <v>-0.74</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>45.05</v>
@@ -14532,7 +14532,7 @@
         <v>-0.57</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>45.03</v>
@@ -14607,7 +14607,7 @@
         <v>-2.33</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>45</v>
@@ -14682,7 +14682,7 @@
         <v>2.13</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>44.95</v>
@@ -14757,7 +14757,7 @@
         <v>-0.23</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>44.9</v>
@@ -14832,7 +14832,7 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>44.82</v>
@@ -14907,7 +14907,7 @@
         <v>4.26</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>44.75</v>
@@ -14982,7 +14982,7 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>44.73</v>
@@ -15057,7 +15057,7 @@
         <v>4.03</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>44.73</v>
@@ -15132,7 +15132,7 @@
         <v>-1.86</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>44.64</v>
@@ -15207,7 +15207,7 @@
         <v>-3.08</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>44.59</v>
@@ -15282,7 +15282,7 @@
         <v>-1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>44.48</v>
@@ -15357,7 +15357,7 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>44.59</v>
@@ -15432,7 +15432,7 @@
         <v>0.76</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>44.72</v>
@@ -15507,7 +15507,7 @@
         <v>-1.44</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>44.8</v>
@@ -15586,7 +15586,7 @@
         <v>-1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>44.87</v>
@@ -15661,7 +15661,7 @@
         <v>2.94</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>45.08</v>
@@ -15736,7 +15736,7 @@
         <v>0.09</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>45.28</v>
@@ -15811,7 +15811,7 @@
         <v>3.71</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>45.54</v>
@@ -15886,7 +15886,7 @@
         <v>5.81</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>45.88</v>
@@ -15961,7 +15961,7 @@
         <v>2.56</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>46.3</v>
@@ -16036,7 +16036,7 @@
         <v>1.16</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>46.77</v>
@@ -16111,7 +16111,7 @@
         <v>-0.11</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>47.29</v>
@@ -16186,7 +16186,7 @@
         <v>-2.47</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>47.7</v>
@@ -16261,7 +16261,7 @@
         <v>2.3</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>48.16</v>
@@ -16336,7 +16336,7 @@
         <v>-0.45</v>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" t="n">
         <v>48.6</v>
@@ -16411,7 +16411,7 @@
         <v>4.67</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>49.07</v>
@@ -16486,7 +16486,7 @@
         <v>1.63</v>
       </c>
       <c r="I212" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>49.55</v>
@@ -16561,7 +16561,7 @@
         <v>2.76</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>50.02</v>
@@ -16636,7 +16636,7 @@
         <v>-2.64</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>50.45</v>
@@ -16711,7 +16711,7 @@
         <v>3.58</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>51.06</v>
@@ -16786,7 +16786,7 @@
         <v>-0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>51.67</v>
@@ -16861,7 +16861,7 @@
         <v>4.38</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>52.38</v>
@@ -16936,7 +16936,7 @@
         <v>-1.56</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>53.03</v>
@@ -17011,7 +17011,7 @@
         <v>2.71</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>53.78</v>
@@ -17086,7 +17086,7 @@
         <v>2.53</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>54.64</v>
@@ -17161,7 +17161,7 @@
         <v>3.79</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>55.55</v>
@@ -17236,7 +17236,7 @@
         <v>0.59</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>56.48</v>
@@ -17311,7 +17311,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>57.62</v>
@@ -17386,7 +17386,7 @@
         <v>-7.19</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>58.36</v>
@@ -17461,7 +17461,7 @@
         <v>4.5</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>59.18</v>
@@ -17536,7 +17536,7 @@
         <v>-6.61</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>59.74</v>
@@ -17611,7 +17611,7 @@
         <v>2.06</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>60.38</v>
@@ -17686,7 +17686,7 @@
         <v>5.06</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>61.24</v>
@@ -17761,7 +17761,7 @@
         <v>6.7</v>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" t="n">
         <v>62.28</v>
@@ -17836,7 +17836,7 @@
         <v>-3.73</v>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>63.19</v>
@@ -17911,7 +17911,7 @@
         <v>-1.76</v>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" t="n">
         <v>63.92</v>
@@ -17986,7 +17986,7 @@
         <v>3.83</v>
       </c>
       <c r="I232" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" t="n">
         <v>64.73999999999999</v>
@@ -18061,7 +18061,7 @@
         <v>6.7</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>65.72</v>
@@ -18136,7 +18136,7 @@
         <v>1.77</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>66.84</v>
@@ -18211,7 +18211,7 @@
         <v>7.58</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>68.16</v>
@@ -18286,7 +18286,7 @@
         <v>-1.47</v>
       </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" t="n">
         <v>69.44</v>
@@ -18361,7 +18361,7 @@
         <v>-2.76</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>70.48</v>
@@ -18436,7 +18436,7 @@
         <v>5.39</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>71.78</v>
@@ -18511,7 +18511,7 @@
         <v>-1.67</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>72.94</v>
@@ -18586,7 +18586,7 @@
         <v>3.78</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>74.17</v>
@@ -18661,7 +18661,7 @@
         <v>6.63</v>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" t="n">
         <v>75.56999999999999</v>
@@ -18736,7 +18736,7 @@
         <v>5.84</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>77.23</v>
@@ -18811,7 +18811,7 @@
         <v>3.3</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>78.75</v>
@@ -18886,7 +18886,7 @@
         <v>3.95</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>80.73</v>
@@ -18961,7 +18961,7 @@
         <v>-0.03</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>82.56</v>
@@ -19036,7 +19036,7 @@
         <v>-28.54</v>
       </c>
       <c r="I246" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>83.11</v>
@@ -19115,7 +19115,7 @@
         <v>-3.98</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>83.45</v>
@@ -19190,7 +19190,7 @@
         <v>6.24</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>83.84</v>
@@ -19265,7 +19265,7 @@
         <v>2.88</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>84.11</v>
@@ -19340,7 +19340,7 @@
         <v>-15.77</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>83.90000000000001</v>
@@ -19415,7 +19415,7 @@
         <v>5.25</v>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" t="n">
         <v>83.92</v>
@@ -19490,7 +19490,7 @@
         <v>8.33</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>84.11</v>
@@ -19565,7 +19565,7 @@
         <v>-3.46</v>
       </c>
       <c r="I253" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" t="n">
         <v>83.92</v>
@@ -19640,7 +19640,7 @@
         <v>4.29</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>83.81999999999999</v>
@@ -19715,7 +19715,7 @@
         <v>-11.53</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>82.97</v>
@@ -19790,7 +19790,7 @@
         <v>2.94</v>
       </c>
       <c r="I256" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" t="n">
         <v>82.29000000000001</v>
@@ -19865,7 +19865,7 @@
         <v>-4.8</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>81.56</v>
@@ -19944,7 +19944,7 @@
         <v>5.6</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>80.8</v>
@@ -20019,7 +20019,7 @@
         <v>1.31</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>80.15000000000001</v>
@@ -20094,7 +20094,7 @@
         <v>7.9</v>
       </c>
       <c r="I260" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" t="n">
         <v>79.62</v>
@@ -20169,7 +20169,7 @@
         <v>5.16</v>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" t="n">
         <v>79.01000000000001</v>
@@ -20244,7 +20244,7 @@
         <v>-1.85</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>78.04000000000001</v>
@@ -20319,7 +20319,7 @@
         <v>1.21</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>76.97</v>
@@ -20394,7 +20394,7 @@
         <v>0.51</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>75.70999999999999</v>
@@ -20469,7 +20469,7 @@
         <v>5.64</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>74.68000000000001</v>
@@ -20544,7 +20544,7 @@
         <v>-4.02</v>
       </c>
       <c r="I266" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>74.98999999999999</v>
@@ -20619,7 +20619,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I267" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" s="4" t="n">
         <v>75.09999999999999</v>
@@ -20698,7 +20698,7 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>75.02</v>
@@ -20773,7 +20773,7 @@
         <v>-1.42</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>74.77</v>
@@ -20852,7 +20852,7 @@
         <v>2.25</v>
       </c>
       <c r="I270" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" t="n">
         <v>75.23</v>
@@ -20931,7 +20931,7 @@
         <v>3.06</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>75.64</v>
@@ -21006,7 +21006,7 @@
         <v>2.34</v>
       </c>
       <c r="I272" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" t="n">
         <v>75.84</v>
@@ -21081,7 +21081,7 @@
         <v>-2.72</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>76.06</v>
@@ -21156,7 +21156,7 @@
         <v>-1.84</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>76.06</v>
@@ -21225,7 +21225,7 @@
         <v>-4.96</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>76.31</v>
@@ -21308,7 +21308,7 @@
         <v>0.73</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>76.48</v>
@@ -21383,7 +21383,7 @@
         <v>-2.13</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>76.75</v>
@@ -21458,7 +21458,7 @@
         <v>-4.13</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>76.68000000000001</v>
@@ -21533,7 +21533,7 @@
         <v>-4.4</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>76.41</v>
@@ -21608,7 +21608,7 @@
         <v>-6.33</v>
       </c>
       <c r="I280" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>75.66</v>
@@ -21691,7 +21691,7 @@
         <v>1.54</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>74.75</v>
@@ -21766,7 +21766,7 @@
         <v>0.77</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>73.95</v>
@@ -21841,7 +21841,7 @@
         <v>3.59</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>73.2</v>
@@ -21916,7 +21916,7 @@
         <v>-6.81</v>
       </c>
       <c r="I284" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>72.22</v>
@@ -21995,7 +21995,7 @@
         <v>4.39</v>
       </c>
       <c r="I285" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" t="n">
         <v>71.14</v>
@@ -22074,7 +22074,7 @@
         <v>0.13</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>70.23999999999999</v>
@@ -22149,7 +22149,7 @@
         <v>7.27</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>69.91</v>
@@ -22224,7 +22224,7 @@
         <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>69.55</v>
@@ -22299,7 +22299,7 @@
         <v>-3.45</v>
       </c>
       <c r="I289" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" t="n">
         <v>69.13</v>
@@ -22374,7 +22374,7 @@
         <v>0.46</v>
       </c>
       <c r="I290" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" t="n">
         <v>68.64</v>
@@ -22449,7 +22449,7 @@
         <v>-0.23</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>68.02</v>
@@ -22528,7 +22528,7 @@
         <v>2.32</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>67.39</v>
@@ -22603,7 +22603,7 @@
         <v>1.36</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>66.91</v>
@@ -22678,7 +22678,7 @@
         <v>1.01</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>66.54000000000001</v>
@@ -22753,7 +22753,7 @@
         <v>-1.16</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>66.31999999999999</v>
@@ -22828,7 +22828,7 @@
         <v>5.51</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>66.26000000000001</v>
@@ -22903,7 +22903,7 @@
         <v>-0.28</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>66.27</v>
@@ -22978,7 +22978,7 @@
         <v>-0.84</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>66.40000000000001</v>
@@ -23053,7 +23053,7 @@
         <v>3.35</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>66.8</v>
@@ -23128,7 +23128,7 @@
         <v>-2.01</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>67.33</v>
@@ -23203,7 +23203,7 @@
         <v>-5.07</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>67.63</v>
@@ -23278,7 +23278,7 @@
         <v>2.74</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>68</v>
@@ -23353,7 +23353,7 @@
         <v>-2.83</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>68.16</v>
@@ -23428,7 +23428,7 @@
         <v>0.6</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>68.56</v>
@@ -23503,7 +23503,7 @@
         <v>-0.67</v>
       </c>
       <c r="I305" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" t="n">
         <v>68.8</v>
@@ -23582,7 +23582,7 @@
         <v>-3.12</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>68.94</v>
@@ -23661,7 +23661,7 @@
         <v>-2.05</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>68.77</v>
@@ -23736,7 +23736,7 @@
         <v>2.81</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>68.7</v>
@@ -23811,7 +23811,7 @@
         <v>2.45</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>68.81999999999999</v>
@@ -23886,7 +23886,7 @@
         <v>-3.44</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>68.81999999999999</v>
@@ -23965,7 +23965,7 @@
         <v>-0.05</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>68.81999999999999</v>
@@ -24040,7 +24040,7 @@
         <v>6.4</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>68.95</v>
@@ -24115,7 +24115,7 @@
         <v>2.1</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>69.11</v>
@@ -24190,7 +24190,7 @@
         <v>1.97</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>69.31</v>
@@ -24265,7 +24265,7 @@
         <v>6.83</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>69.79000000000001</v>
@@ -24340,7 +24340,7 @@
         <v>0.71</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>70.12</v>
@@ -24415,7 +24415,7 @@
         <v>1.02</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>70.48999999999999</v>
@@ -24490,7 +24490,7 @@
         <v>-4.84</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>70.70999999999999</v>
@@ -24565,7 +24565,7 @@
         <v>-8.57</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>70.48</v>
@@ -24644,7 +24644,7 @@
         <v>1.3</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>70.37</v>
@@ -24719,7 +24719,7 @@
         <v>-4.35</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>70.29000000000001</v>
@@ -24794,7 +24794,7 @@
         <v>2.74</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>70.20999999999999</v>
@@ -24869,7 +24869,7 @@
         <v>1.05</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>70.26000000000001</v>
@@ -24944,7 +24944,7 @@
         <v>-1.57</v>
       </c>
       <c r="I324" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" t="n">
         <v>70.23999999999999</v>
@@ -25019,7 +25019,7 @@
         <v>1.99</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>70.31</v>
@@ -25094,7 +25094,7 @@
         <v>-3.18</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>70.37</v>
@@ -25169,7 +25169,7 @@
         <v>1.27</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>70.55</v>
@@ -25244,7 +25244,7 @@
         <v>-0.04</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>70.63</v>
@@ -25319,7 +25319,7 @@
         <v>-0.97</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>70.59999999999999</v>
@@ -25394,7 +25394,7 @@
         <v>0.47</v>
       </c>
       <c r="I330" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" t="n">
         <v>70.7</v>
@@ -25469,7 +25469,7 @@
         <v>-2.62</v>
       </c>
       <c r="I331" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" t="n">
         <v>70.72</v>
@@ -25544,7 +25544,7 @@
         <v>1.16</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>70.56</v>
@@ -25619,7 +25619,7 @@
         <v>-8.08</v>
       </c>
       <c r="I333" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>70.06</v>
@@ -25694,7 +25694,7 @@
         <v>0.02</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>69.48999999999999</v>
@@ -25769,7 +25769,7 @@
         <v>-4.17</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>68.54000000000001</v>
@@ -25848,7 +25848,7 @@
         <v>-2.29</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>67.48999999999999</v>
@@ -25927,7 +25927,7 @@
         <v>5.48</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>66.56999999999999</v>
@@ -26002,7 +26002,7 @@
         <v>0.77</v>
       </c>
       <c r="I338" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" t="n">
         <v>65.86</v>
@@ -26077,7 +26077,7 @@
         <v>3.56</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>65.58</v>
@@ -26152,7 +26152,7 @@
         <v>-0.13</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>65.25</v>
@@ -26227,7 +26227,7 @@
         <v>-4.39</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>64.93000000000001</v>
@@ -26302,7 +26302,7 @@
         <v>-1.81</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>64.47</v>
@@ -26377,7 +26377,7 @@
         <v>-1.01</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>63.95</v>
@@ -26452,7 +26452,7 @@
         <v>-5.4</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>63.32</v>
@@ -26531,7 +26531,7 @@
         <v>-7.09</v>
       </c>
       <c r="I345" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>62.42</v>
@@ -26610,7 +26610,7 @@
         <v>1.12</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>61.66</v>
@@ -26689,7 +26689,7 @@
         <v>1.76</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>60.91</v>
@@ -26764,7 +26764,7 @@
         <v>-1.13</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>60.12</v>
@@ -26839,7 +26839,7 @@
         <v>1.5</v>
       </c>
       <c r="I349" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" t="n">
         <v>59.42</v>
@@ -26914,7 +26914,7 @@
         <v>0.21</v>
       </c>
       <c r="I350" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" t="n">
         <v>58.69</v>
@@ -26989,7 +26989,7 @@
         <v>2.69</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>58.14</v>
@@ -27064,7 +27064,7 @@
         <v>1.98</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>57.59</v>
@@ -27139,7 +27139,7 @@
         <v>-2.94</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>57.24</v>
@@ -27218,7 +27218,7 @@
         <v>-2.99</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>56.8</v>
@@ -27297,7 +27297,7 @@
         <v>2.48</v>
       </c>
       <c r="I355" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" t="n">
         <v>56.56</v>
@@ -27372,7 +27372,7 @@
         <v>-0.35</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>56.37</v>
@@ -27447,7 +27447,7 @@
         <v>-3.32</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>55.94</v>
@@ -27522,7 +27522,7 @@
         <v>1.94</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>55.53</v>
@@ -27597,7 +27597,7 @@
         <v>-1.81</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>54.97</v>
@@ -27672,7 +27672,7 @@
         <v>-3.49</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>54.32</v>
@@ -27747,7 +27747,7 @@
         <v>0.77</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>53.83</v>
@@ -27822,7 +27822,7 @@
         <v>0.39</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>53.4</v>
@@ -27897,7 +27897,7 @@
         <v>4.12</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>53.11</v>
@@ -27972,7 +27972,7 @@
         <v>1.58</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>53.02</v>
@@ -28047,7 +28047,7 @@
         <v>-3.45</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>53.03</v>
@@ -28126,7 +28126,7 @@
         <v>1.02</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>53.04</v>
@@ -28201,7 +28201,7 @@
         <v>0.65</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>53.03</v>
@@ -28276,7 +28276,7 @@
         <v>-2.32</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>52.98</v>
@@ -28351,7 +28351,7 @@
         <v>0.14</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>52.89</v>
@@ -28426,7 +28426,7 @@
         <v>3.34</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>52.89</v>
@@ -28501,7 +28501,7 @@
         <v>-2.13</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>52.75</v>
@@ -28580,7 +28580,7 @@
         <v>0.19</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>52.57</v>
@@ -28655,7 +28655,7 @@
         <v>2.63</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>52.54</v>
@@ -28730,7 +28730,7 @@
         <v>4.14</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>52.7</v>
@@ -28805,7 +28805,7 @@
         <v>-0.39</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>52.79</v>
@@ -28880,7 +28880,7 @@
         <v>2.95</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>52.97</v>
@@ -28955,7 +28955,7 @@
         <v>3.32</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>53.33</v>
@@ -29030,7 +29030,7 @@
         <v>-1.45</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>53.6</v>
@@ -29105,7 +29105,7 @@
         <v>0.87</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>53.94</v>
@@ -29180,7 +29180,7 @@
         <v>-1.52</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>54.33</v>
@@ -29255,7 +29255,7 @@
         <v>0.55</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>54.71</v>
@@ -29330,7 +29330,7 @@
         <v>1.86</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>55.14</v>
@@ -29405,7 +29405,7 @@
         <v>-3.58</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>55.36</v>
@@ -29484,7 +29484,7 @@
         <v>4.47</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>55.67</v>
@@ -29559,7 +29559,7 @@
         <v>2.75</v>
       </c>
       <c r="I385" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" t="n">
         <v>56.15</v>
@@ -29634,7 +29634,7 @@
         <v>1.72</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>56.65</v>
@@ -29709,7 +29709,7 @@
         <v>-0.83</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>57.12</v>
@@ -29784,7 +29784,7 @@
         <v>0.19</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>57.65</v>
@@ -29859,7 +29859,7 @@
         <v>-1.17</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>58.14</v>
@@ -29934,7 +29934,7 @@
         <v>1.92</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>58.6</v>
@@ -30009,7 +30009,7 @@
         <v>-4.38</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>58.98</v>
@@ -30084,7 +30084,7 @@
         <v>0.18</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>59.37</v>
@@ -30159,7 +30159,7 @@
         <v>-3.68</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>59.57</v>
@@ -30238,7 +30238,7 @@
         <v>1.99</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>59.72</v>
@@ -30313,7 +30313,7 @@
         <v>2.51</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>59.96</v>
@@ -30388,7 +30388,7 @@
         <v>-1.21</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>60.07</v>
@@ -30467,7 +30467,7 @@
         <v>-0.75</v>
       </c>
       <c r="I397" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" t="n">
         <v>60.07</v>
@@ -30542,7 +30542,7 @@
         <v>2.27</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>60.18</v>
@@ -30617,7 +30617,7 @@
         <v>-5.3</v>
       </c>
       <c r="I399" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" s="4" t="n">
         <v>60.1</v>
@@ -30696,7 +30696,7 @@
         <v>1.08</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>60.1</v>
@@ -30771,7 +30771,7 @@
         <v>-2.2</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>60.02</v>
@@ -30846,7 +30846,7 @@
         <v>1.21</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>59.92</v>
@@ -30921,7 +30921,7 @@
         <v>-0.83</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>59.9</v>
@@ -30996,7 +30996,7 @@
         <v>3.37</v>
       </c>
       <c r="I404" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" t="n">
         <v>59.84</v>
@@ -31071,7 +31071,7 @@
         <v>1.63</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>59.76</v>
@@ -31146,7 +31146,7 @@
         <v>-0.5</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>59.6</v>
@@ -31221,7 +31221,7 @@
         <v>1.84</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>59.53</v>
@@ -31296,7 +31296,7 @@
         <v>-4.23</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>59.32</v>
@@ -31375,7 +31375,7 @@
         <v>-0.93</v>
       </c>
       <c r="I409" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" t="n">
         <v>59.12</v>
@@ -31450,7 +31450,7 @@
         <v>0.9</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>58.89</v>
@@ -31525,7 +31525,7 @@
         <v>-5.49</v>
       </c>
       <c r="I411" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>58.64</v>
@@ -31598,13 +31598,13 @@
         <v>55.48</v>
       </c>
       <c r="G412" t="n">
-        <v>12422400</v>
+        <v>12480400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.96</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>58.41</v>
@@ -31670,16 +31670,16 @@
         <v>54.22</v>
       </c>
       <c r="F413" t="n">
-        <v>54.37</v>
+        <v>54.51</v>
       </c>
       <c r="G413" t="n">
-        <v>13485153</v>
+        <v>16999896</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-2</v>
+        <v>-1.75</v>
       </c>
       <c r="I413" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J413" t="n">
         <v>58.23</v>
@@ -31688,16 +31688,16 @@
         <v>56.78</v>
       </c>
       <c r="L413" t="n">
-        <v>61.12</v>
+        <v>61.13</v>
       </c>
       <c r="M413" t="n">
         <v>65.94</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>40.1</v>
+        <v>40.46</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31711,16 +31711,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31667,13 +31667,13 @@
         <v>55.24</v>
       </c>
       <c r="E413" t="n">
-        <v>54.22</v>
+        <v>54.23</v>
       </c>
       <c r="F413" t="n">
         <v>54.51</v>
       </c>
       <c r="G413" t="n">
-        <v>16999896</v>
+        <v>17040600</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-1.75</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31697,7 +31697,7 @@
         <v>40.46</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31724,6 +31724,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="D414" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="E414" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="F414" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="G414" t="n">
+        <v>6606176</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>39.26</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31673,7 +31673,7 @@
         <v>54.51</v>
       </c>
       <c r="G413" t="n">
-        <v>17040600</v>
+        <v>17069800</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-1.75</v>
@@ -31745,19 +31745,19 @@
         <v>54.49</v>
       </c>
       <c r="F414" t="n">
-        <v>54.82</v>
+        <v>55.02</v>
       </c>
       <c r="G414" t="n">
-        <v>6606176</v>
+        <v>11987072</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
       <c r="J414" t="n">
-        <v>58.02</v>
+        <v>58.03</v>
       </c>
       <c r="K414" t="n">
         <v>56.82</v>
@@ -31769,10 +31769,10 @@
         <v>65.93000000000001</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>39.26</v>
+        <v>40.04</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31786,16 +31786,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31735,41 +31735,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="D414" t="n">
-        <v>55.35</v>
-      </c>
-      <c r="E414" t="n">
-        <v>54.49</v>
-      </c>
-      <c r="F414" t="n">
-        <v>55.02</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>11987072</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>0.9399999999999999</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
-      <c r="J414" t="n">
-        <v>58.03</v>
-      </c>
-      <c r="K414" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="L414" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="M414" t="n">
-        <v>65.93000000000001</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>40.04</v>
+        <v>38.01</v>
       </c>
       <c r="O414" t="n">
         <v>28</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31735,28 +31735,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="D414" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="E414" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="F414" t="n">
+        <v>55.02</v>
+      </c>
       <c r="G414" t="n">
-        <v>11987072</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>12025500</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="L414" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.93000000000001</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>38.01</v>
+        <v>40.04</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31772,7 +31772,7 @@
         <v>40.04</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,6 +31798,79 @@
       <c r="W414" s="2" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="D415" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="E415" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="F415" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="G415" t="n">
+        <v>9389923</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J415" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="K415" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="L415" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>55.02</v>
       </c>
       <c r="G414" t="n">
-        <v>12025500</v>
+        <v>12131500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.9399999999999999</v>
@@ -31817,34 +31817,34 @@
         <v>55.67</v>
       </c>
       <c r="E415" t="n">
-        <v>54.17</v>
+        <v>53.9</v>
       </c>
       <c r="F415" t="n">
-        <v>54.31</v>
+        <v>54.74</v>
       </c>
       <c r="G415" t="n">
-        <v>9389923</v>
+        <v>17429549</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>-1.29</v>
+        <v>-0.51</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
       <c r="J415" t="n">
-        <v>57.72</v>
+        <v>57.74</v>
       </c>
       <c r="K415" t="n">
-        <v>56.82</v>
+        <v>56.83</v>
       </c>
       <c r="L415" t="n">
-        <v>60.89</v>
+        <v>60.9</v>
       </c>
       <c r="M415" t="n">
         <v>65.91</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>41.56</v>
+        <v>42.79</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31861,13 +31861,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31735,25 +31735,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="D414" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="E414" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F414" t="n">
+        <v>54.74</v>
+      </c>
       <c r="G414" t="n">
-        <v>17476952</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>17526500</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.51</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="L414" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.91</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>43.63</v>
+        <v>42.79</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31622,7 +31622,7 @@
         <v>42.79</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5281,7 +5281,7 @@
         <v>29.77</v>
       </c>
       <c r="K63" t="n">
-        <v>29.66</v>
+        <v>29.67</v>
       </c>
       <c r="L63" t="n">
         <v>28.82</v>
@@ -9115,7 +9115,7 @@
         <v>5.1</v>
       </c>
       <c r="J114" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="K114" t="n">
         <v>32.22</v>
@@ -9569,7 +9569,7 @@
         <v>5.1</v>
       </c>
       <c r="J120" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="K120" t="n">
         <v>32.65</v>
@@ -26005,7 +26005,7 @@
         <v>5.1</v>
       </c>
       <c r="J338" t="n">
-        <v>64.93000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K338" t="n">
         <v>67.62</v>
@@ -27075,7 +27075,7 @@
         <v>5.1</v>
       </c>
       <c r="J352" t="n">
-        <v>56.56</v>
+        <v>56.55</v>
       </c>
       <c r="K352" t="n">
         <v>64.95999999999999</v>
@@ -31622,7 +31622,7 @@
         <v>42.79</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31648,6 +31648,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D413" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="E413" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="F413" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="G413" t="n">
+        <v>8141903</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="L413" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31523,7 +31523,7 @@
         <v>54.74</v>
       </c>
       <c r="G411" t="n">
-        <v>17526500</v>
+        <v>17586900</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>-0.51</v>
@@ -31585,25 +31585,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D412" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="E412" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="F412" t="n">
+        <v>55.13</v>
+      </c>
       <c r="G412" t="n">
-        <v>10704719</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>10735600</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>0.71</v>
       </c>
       <c r="I412" t="n">
         <v>5.1</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="K412" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="L412" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="M412" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>39.94</v>
+        <v>41.58</v>
       </c>
       <c r="O412" t="n">
         <v>43</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31622,7 +31622,7 @@
         <v>41.58</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31648,6 +31648,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="D413" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="E413" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="F413" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4602862</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="L413" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -5206,7 +5206,7 @@
         <v>29.77</v>
       </c>
       <c r="K62" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="L62" t="n">
         <v>28.82</v>
@@ -9494,7 +9494,7 @@
         <v>5.1</v>
       </c>
       <c r="J119" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="K119" t="n">
         <v>32.65</v>
@@ -31598,7 +31598,7 @@
         <v>55.13</v>
       </c>
       <c r="G412" t="n">
-        <v>10735600</v>
+        <v>10785300</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>0.71</v>
@@ -31664,37 +31664,37 @@
         <v>55.3</v>
       </c>
       <c r="D413" t="n">
-        <v>55.37</v>
+        <v>55.86</v>
       </c>
       <c r="E413" t="n">
         <v>54.86</v>
       </c>
       <c r="F413" t="n">
-        <v>55.04</v>
+        <v>55.45</v>
       </c>
       <c r="G413" t="n">
-        <v>4602862</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.16</v>
+        <v>11314445</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.58</v>
       </c>
       <c r="I413" t="n">
         <v>5.1</v>
       </c>
       <c r="J413" t="n">
-        <v>57.29</v>
+        <v>57.31</v>
       </c>
       <c r="K413" t="n">
         <v>56.9</v>
       </c>
       <c r="L413" t="n">
-        <v>60.61</v>
+        <v>60.62</v>
       </c>
       <c r="M413" t="n">
-        <v>65.87</v>
+        <v>65.88</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>42.75</v>
+        <v>44.33</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31711,13 +31711,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31585,25 +31585,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="D412" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="E412" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="F412" t="n">
+        <v>55.45</v>
+      </c>
       <c r="G412" t="n">
-        <v>11987760</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>11986800</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.58</v>
       </c>
       <c r="I412" t="n">
         <v>5.1</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="K412" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="L412" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="M412" t="n">
+        <v>65.88</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>43.03</v>
+        <v>44.33</v>
       </c>
       <c r="O412" t="n">
         <v>47</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31649,6 +31649,79 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D413" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="E413" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F413" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="G413" t="n">
+        <v>6943175</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="I413" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="L413" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31598,7 +31598,7 @@
         <v>55.45</v>
       </c>
       <c r="G412" t="n">
-        <v>11986800</v>
+        <v>12006400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.58</v>
@@ -31664,25 +31664,25 @@
         <v>53.9</v>
       </c>
       <c r="D413" t="n">
-        <v>53.95</v>
+        <v>54.38</v>
       </c>
       <c r="E413" t="n">
         <v>53.6</v>
       </c>
       <c r="F413" t="n">
-        <v>53.76</v>
+        <v>53.82</v>
       </c>
       <c r="G413" t="n">
-        <v>6943175</v>
+        <v>20275081</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>-3.05</v>
+        <v>-2.94</v>
       </c>
       <c r="I413" t="n">
         <v>5.1</v>
       </c>
       <c r="J413" t="n">
-        <v>56.96</v>
+        <v>56.97</v>
       </c>
       <c r="K413" t="n">
         <v>56.91</v>
@@ -31694,10 +31694,10 @@
         <v>65.84999999999999</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>31.22</v>
+        <v>31.35</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31711,13 +31711,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31660,41 +31660,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="D413" t="n">
-        <v>54.38</v>
-      </c>
-      <c r="E413" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="F413" t="n">
-        <v>53.82</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>20275081</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>-2.94</v>
+        <v>20364955</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>5.1</v>
       </c>
-      <c r="J413" t="n">
-        <v>56.97</v>
-      </c>
-      <c r="K413" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="L413" t="n">
-        <v>60.47</v>
-      </c>
-      <c r="M413" t="n">
-        <v>65.84999999999999</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="3" t="n">
-        <v>31.35</v>
+        <v>35.55</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31720,7 +31704,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31660,25 +31660,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D413" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="E413" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F413" t="n">
+        <v>53.82</v>
+      </c>
       <c r="G413" t="n">
-        <v>20364955</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0</v>
+        <v>20438400</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-2.94</v>
       </c>
       <c r="I413" t="n">
         <v>5.1</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="L413" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="M413" t="n">
+        <v>65.84999999999999</v>
+      </c>
       <c r="N413" s="3" t="n">
-        <v>35.55</v>
+        <v>31.35</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31697,7 +31697,7 @@
         <v>31.35</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31723,6 +31723,83 @@
       <c r="W413" s="3" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="D414" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="E414" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="F414" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="G414" t="n">
+        <v>7009334</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="L414" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31673,7 +31673,7 @@
         <v>53.82</v>
       </c>
       <c r="G413" t="n">
-        <v>20438400</v>
+        <v>20477700</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-2.94</v>
@@ -31742,22 +31742,22 @@
         <v>53.64</v>
       </c>
       <c r="E414" t="n">
-        <v>53.08</v>
+        <v>52.84</v>
       </c>
       <c r="F414" t="n">
-        <v>53.17</v>
+        <v>53.45</v>
       </c>
       <c r="G414" t="n">
-        <v>7009334</v>
+        <v>16510334</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>-1.21</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
       <c r="J414" t="n">
-        <v>56.75</v>
+        <v>56.76</v>
       </c>
       <c r="K414" t="n">
         <v>56.93</v>
@@ -31769,10 +31769,10 @@
         <v>65.81</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>24.96</v>
+        <v>25.49</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31790,13 +31790,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>53.45</v>
       </c>
       <c r="G414" t="n">
-        <v>16510334</v>
+        <v>16645200</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-0.6899999999999999</v>
@@ -31799,7 +31799,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31772,7 +31772,7 @@
         <v>25.49</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31802,6 +31802,79 @@
       <c r="W414" s="3" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="D415" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="E415" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="F415" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="G415" t="n">
+        <v>7442007</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J415" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="K415" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="L415" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>53.45</v>
       </c>
       <c r="G414" t="n">
-        <v>16645200</v>
+        <v>16711400</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-0.6899999999999999</v>
@@ -31821,22 +31821,22 @@
         <v>55.24</v>
       </c>
       <c r="E415" t="n">
-        <v>54.79</v>
+        <v>54.75</v>
       </c>
       <c r="F415" t="n">
-        <v>55.03</v>
+        <v>54.78</v>
       </c>
       <c r="G415" t="n">
-        <v>7442007</v>
+        <v>13482536</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>2.96</v>
+        <v>2.49</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
       <c r="J415" t="n">
-        <v>56.61</v>
+        <v>56.6</v>
       </c>
       <c r="K415" t="n">
         <v>57.01</v>
@@ -31848,10 +31848,10 @@
         <v>65.77</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>34.14</v>
+        <v>32.98</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31865,13 +31865,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31814,41 +31814,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="D415" t="n">
-        <v>55.24</v>
-      </c>
-      <c r="E415" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="F415" t="n">
-        <v>54.78</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>13482536</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>2.49</v>
+        <v>13522476</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
-      <c r="J415" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="K415" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="L415" t="n">
-        <v>60.16</v>
-      </c>
-      <c r="M415" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="N415" s="3" t="n">
-        <v>32.98</v>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="1" t="n">
+        <v>26.08</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31874,7 +31858,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31814,25 +31814,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="D415" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="E415" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="F415" t="n">
+        <v>54.78</v>
+      </c>
       <c r="G415" t="n">
-        <v>13522476</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>13593400</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>2.49</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="1" t="n">
-        <v>26.08</v>
+      <c r="J415" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K415" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="L415" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>32.98</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1684,7 +1684,7 @@
         <v>29.37</v>
       </c>
       <c r="K16" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="L16" t="n">
         <v>28.58</v>
@@ -3990,7 +3990,7 @@
         <v>29.45</v>
       </c>
       <c r="K46" t="n">
-        <v>29.52</v>
+        <v>29.51</v>
       </c>
       <c r="L46" t="n">
         <v>28.72</v>
@@ -4981,7 +4981,7 @@
         <v>29.77</v>
       </c>
       <c r="K59" t="n">
-        <v>29.66</v>
+        <v>29.67</v>
       </c>
       <c r="L59" t="n">
         <v>28.82</v>
@@ -8815,7 +8815,7 @@
         <v>5.1</v>
       </c>
       <c r="J110" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="K110" t="n">
         <v>32.22</v>
@@ -23821,7 +23821,7 @@
         <v>70.12</v>
       </c>
       <c r="K309" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="L309" t="n">
         <v>69.38</v>
@@ -25705,7 +25705,7 @@
         <v>5.1</v>
       </c>
       <c r="J334" t="n">
-        <v>64.93000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K334" t="n">
         <v>67.62</v>
@@ -26775,7 +26775,7 @@
         <v>5.1</v>
       </c>
       <c r="J348" t="n">
-        <v>56.56</v>
+        <v>56.55</v>
       </c>
       <c r="K348" t="n">
         <v>64.95999999999999</v>
@@ -31701,11 +31701,11 @@
         <v>32.98</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31726,6 +31726,85 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="D414" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="E414" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="F414" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="G414" t="n">
+        <v>6866054</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="K414" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="L414" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31732,6 +31732,83 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="D414" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="E414" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="F414" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G414" t="n">
+        <v>14102121</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="K414" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="L414" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.66</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -1609,7 +1609,7 @@
         <v>29.37</v>
       </c>
       <c r="K15" t="n">
-        <v>28.29</v>
+        <v>28.28</v>
       </c>
       <c r="L15" t="n">
         <v>28.58</v>
@@ -3915,7 +3915,7 @@
         <v>29.45</v>
       </c>
       <c r="K45" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
       <c r="L45" t="n">
         <v>28.72</v>
@@ -4906,7 +4906,7 @@
         <v>29.77</v>
       </c>
       <c r="K58" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="L58" t="n">
         <v>28.82</v>
@@ -8740,7 +8740,7 @@
         <v>5.1</v>
       </c>
       <c r="J109" t="n">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="K109" t="n">
         <v>32.22</v>
@@ -23746,7 +23746,7 @@
         <v>70.12</v>
       </c>
       <c r="K308" t="n">
-        <v>70.95</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="L308" t="n">
         <v>69.38</v>
@@ -25630,7 +25630,7 @@
         <v>5.1</v>
       </c>
       <c r="J333" t="n">
-        <v>64.94</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K333" t="n">
         <v>67.62</v>
@@ -26700,7 +26700,7 @@
         <v>5.1</v>
       </c>
       <c r="J347" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="K347" t="n">
         <v>64.95999999999999</v>
@@ -31677,7 +31677,7 @@
         <v>54.35</v>
       </c>
       <c r="G413" t="n">
-        <v>8297600</v>
+        <v>8447200</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.78</v>
@@ -31747,25 +31747,25 @@
         <v>54.28</v>
       </c>
       <c r="D414" t="n">
-        <v>54.33</v>
+        <v>54.34</v>
       </c>
       <c r="E414" t="n">
-        <v>53.19</v>
+        <v>53.18</v>
       </c>
       <c r="F414" t="n">
-        <v>53.33</v>
+        <v>53.49</v>
       </c>
       <c r="G414" t="n">
-        <v>14102121</v>
+        <v>17523818</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.88</v>
+        <v>-1.58</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
       <c r="J414" t="n">
-        <v>56.26</v>
+        <v>56.27</v>
       </c>
       <c r="K414" t="n">
         <v>57.11</v>
@@ -31776,11 +31776,11 @@
       <c r="M414" t="n">
         <v>65.66</v>
       </c>
-      <c r="N414" s="3" t="n">
-        <v>29.93</v>
+      <c r="N414" s="2" t="n">
+        <v>30.33</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31792,20 +31792,12 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31709,7 +31709,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,11 +31705,11 @@
         <v>30.33</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31731,6 +31731,83 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="D414" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="E414" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="F414" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="G414" t="n">
+        <v>14042297</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="K414" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="L414" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.56</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31733,81 +31733,81 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
+      <c r="A414" s="4" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C414" t="n">
+      <c r="C414" s="4" t="n">
         <v>51.31</v>
       </c>
-      <c r="D414" t="n">
+      <c r="D414" s="4" t="n">
         <v>51.67</v>
       </c>
-      <c r="E414" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="F414" t="n">
-        <v>50.79</v>
-      </c>
-      <c r="G414" t="n">
-        <v>14042297</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="I414" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J414" t="n">
-        <v>55.96</v>
-      </c>
-      <c r="K414" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="L414" t="n">
+      <c r="E414" s="4" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="F414" s="4" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="G414" s="4" t="n">
+        <v>29571560</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="I414" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" s="4" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="K414" s="4" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="L414" s="4" t="n">
         <v>59.75</v>
       </c>
-      <c r="M414" t="n">
+      <c r="M414" s="4" t="n">
         <v>65.56</v>
       </c>
-      <c r="N414" s="3" t="n">
-        <v>25.66</v>
-      </c>
-      <c r="O414" t="n">
-        <v>37</v>
-      </c>
-      <c r="P414" t="inlineStr">
+      <c r="N414" s="7" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="O414" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="P414" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q414" t="inlineStr">
+      <c r="Q414" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
+      <c r="R414" s="4" t="inlineStr">
         <is>
           <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
         </is>
       </c>
-      <c r="S414" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T414" s="2" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="S414" s="4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="T414" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="U414" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="V414" s="4" t="inlineStr"/>
+      <c r="W414" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -1534,7 +1534,7 @@
         <v>29.37</v>
       </c>
       <c r="K14" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="L14" t="n">
         <v>28.58</v>
@@ -3840,7 +3840,7 @@
         <v>29.45</v>
       </c>
       <c r="K44" t="n">
-        <v>29.52</v>
+        <v>29.51</v>
       </c>
       <c r="L44" t="n">
         <v>28.72</v>
@@ -8665,7 +8665,7 @@
         <v>5.1</v>
       </c>
       <c r="J108" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="K108" t="n">
         <v>32.22</v>
@@ -25555,7 +25555,7 @@
         <v>5.1</v>
       </c>
       <c r="J332" t="n">
-        <v>64.93000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K332" t="n">
         <v>67.62</v>
@@ -26625,7 +26625,7 @@
         <v>5.1</v>
       </c>
       <c r="J346" t="n">
-        <v>56.56</v>
+        <v>56.55</v>
       </c>
       <c r="K346" t="n">
         <v>64.95999999999999</v>
@@ -31681,7 +31681,7 @@
         <v>53.49</v>
       </c>
       <c r="G413" t="n">
-        <v>17502400</v>
+        <v>17619400</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-1.58</v>
@@ -31756,7 +31756,7 @@
         <v>50.22</v>
       </c>
       <c r="G414" s="4" t="n">
-        <v>29571560</v>
+        <v>36248796</v>
       </c>
       <c r="H414" s="5" t="n">
         <v>-6.11</v>
@@ -31780,7 +31780,7 @@
         <v>24.66</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
@@ -31801,13 +31801,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="6" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="6" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" s="4" t="inlineStr"/>
-      <c r="W414" s="6" t="inlineStr"/>
+      <c r="W414" s="5" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>50.22</v>
       </c>
       <c r="G414" s="4" t="n">
-        <v>36248796</v>
+        <v>36247800</v>
       </c>
       <c r="H414" s="5" t="n">
         <v>-6.11</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31780,7 +31780,7 @@
         <v>24.66</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>24.66</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
@@ -31810,6 +31810,83 @@
       <c r="W414" s="5" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="D415" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="E415" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="F415" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="G415" t="n">
+        <v>5318685</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J415" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="K415" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="L415" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31826,44 +31826,44 @@
         <v>51.25</v>
       </c>
       <c r="D415" t="n">
-        <v>51.38</v>
+        <v>51.66</v>
       </c>
       <c r="E415" t="n">
-        <v>51.02</v>
+        <v>50.97</v>
       </c>
       <c r="F415" t="n">
-        <v>51.06</v>
+        <v>51.53</v>
       </c>
       <c r="G415" t="n">
-        <v>5318685</v>
+        <v>12999569</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>1.67</v>
+        <v>2.61</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
       <c r="J415" t="n">
-        <v>55.53</v>
+        <v>55.56</v>
       </c>
       <c r="K415" t="n">
-        <v>57.01</v>
+        <v>57.02</v>
       </c>
       <c r="L415" t="n">
-        <v>59.6</v>
+        <v>59.61</v>
       </c>
       <c r="M415" t="n">
-        <v>65.48</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>26.27</v>
+        <v>28.53</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
@@ -31877,13 +31877,13 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>50.22</v>
       </c>
       <c r="G414" s="4" t="n">
-        <v>36247800</v>
+        <v>36387200</v>
       </c>
       <c r="H414" s="5" t="n">
         <v>-6.11</v>
@@ -31826,28 +31826,28 @@
         <v>51.25</v>
       </c>
       <c r="D415" t="n">
-        <v>51.66</v>
+        <v>51.94</v>
       </c>
       <c r="E415" t="n">
         <v>50.97</v>
       </c>
       <c r="F415" t="n">
-        <v>51.53</v>
+        <v>51.92</v>
       </c>
       <c r="G415" t="n">
-        <v>12999569</v>
+        <v>18324536</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>2.61</v>
+        <v>3.39</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
       <c r="J415" t="n">
-        <v>55.56</v>
+        <v>55.58</v>
       </c>
       <c r="K415" t="n">
-        <v>57.02</v>
+        <v>57.03</v>
       </c>
       <c r="L415" t="n">
         <v>59.61</v>
@@ -31855,11 +31855,11 @@
       <c r="M415" t="n">
         <v>65.48999999999999</v>
       </c>
-      <c r="N415" s="3" t="n">
-        <v>28.53</v>
+      <c r="N415" s="2" t="n">
+        <v>30.29</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31871,22 +31871,20 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31822,41 +31822,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>51.25</v>
-      </c>
-      <c r="D415" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="E415" t="n">
-        <v>50.97</v>
-      </c>
-      <c r="F415" t="n">
-        <v>51.92</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>18324536</v>
       </c>
-      <c r="H415" s="3" t="n">
-        <v>3.39</v>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
-      <c r="J415" t="n">
-        <v>55.58</v>
-      </c>
-      <c r="K415" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="L415" t="n">
-        <v>59.61</v>
-      </c>
-      <c r="M415" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="N415" s="2" t="n">
-        <v>30.29</v>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="3" t="n">
+        <v>21.87</v>
       </c>
       <c r="O415" t="n">
         <v>32</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31822,28 +31822,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="D415" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="E415" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="F415" t="n">
+        <v>51.92</v>
+      </c>
       <c r="G415" t="n">
-        <v>18324536</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>18427900</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>3.39</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="3" t="n">
-        <v>21.87</v>
+      <c r="J415" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="K415" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="L415" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>30.29</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>30.29</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>30.29</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31885,6 +31885,79 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="D416" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="E416" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="F416" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="G416" t="n">
+        <v>6305047</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I416" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J416" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="K416" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="L416" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="M416" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31904,25 +31904,25 @@
         <v>52.33</v>
       </c>
       <c r="E416" t="n">
-        <v>51.73</v>
+        <v>51.36</v>
       </c>
       <c r="F416" t="n">
-        <v>51.88</v>
+        <v>51.51</v>
       </c>
       <c r="G416" t="n">
-        <v>6305047</v>
+        <v>13366385</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-0.08</v>
+        <v>-0.79</v>
       </c>
       <c r="I416" t="n">
         <v>5.1</v>
       </c>
       <c r="J416" t="n">
-        <v>55.17</v>
+        <v>55.15</v>
       </c>
       <c r="K416" t="n">
-        <v>57.03</v>
+        <v>57.02</v>
       </c>
       <c r="L416" t="n">
         <v>59.47</v>
@@ -31931,30 +31931,30 @@
         <v>65.40000000000001</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>37.85</v>
+        <v>36.77</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>51.92</v>
       </c>
       <c r="G415" t="n">
-        <v>18427900</v>
+        <v>18492100</v>
       </c>
       <c r="H415" s="3" t="n">
         <v>3.39</v>
@@ -31910,7 +31910,7 @@
         <v>51.51</v>
       </c>
       <c r="G416" t="n">
-        <v>13366385</v>
+        <v>14778859</v>
       </c>
       <c r="H416" s="1" t="n">
         <v>-0.79</v>
@@ -31951,13 +31951,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31822,25 +31822,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="D415" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="E415" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="F415" t="n">
+        <v>51.51</v>
+      </c>
       <c r="G415" t="n">
-        <v>14778859</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>14869200</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.79</v>
       </c>
       <c r="I415" t="n">
         <v>5.1</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="K415" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="L415" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.40000000000001</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>37.97</v>
+        <v>36.77</v>
       </c>
       <c r="O415" t="n">
         <v>18</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31705,7 +31705,7 @@
         <v>36.77</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1305,7 +1305,7 @@
         <v>29.37</v>
       </c>
       <c r="K11" t="n">
-        <v>28.29</v>
+        <v>28.28</v>
       </c>
       <c r="L11" t="n">
         <v>28.58</v>
@@ -3611,7 +3611,7 @@
         <v>29.45</v>
       </c>
       <c r="K41" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
       <c r="L41" t="n">
         <v>28.72</v>
@@ -4602,7 +4602,7 @@
         <v>29.77</v>
       </c>
       <c r="K54" t="n">
-        <v>29.66</v>
+        <v>29.67</v>
       </c>
       <c r="L54" t="n">
         <v>28.82</v>
@@ -31705,7 +31705,7 @@
         <v>36.77</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="1" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="D414" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="E414" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="G414" t="n">
+        <v>10206292</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="K414" t="n">
+        <v>57</v>
+      </c>
+      <c r="L414" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31753,13 +31753,13 @@
         <v>51.51</v>
       </c>
       <c r="F414" t="n">
-        <v>51.62</v>
+        <v>51.54</v>
       </c>
       <c r="G414" t="n">
-        <v>10206292</v>
+        <v>12391024</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
@@ -31777,10 +31777,10 @@
         <v>65.34</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>34.66</v>
+        <v>34.24</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,16 +31794,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,7 +31705,7 @@
         <v>34.24</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="1" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="D414" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="E414" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="F414" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="G414" t="n">
+        <v>6371330</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="K414" t="n">
+        <v>57</v>
+      </c>
+      <c r="L414" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31753,34 +31753,34 @@
         <v>51.55</v>
       </c>
       <c r="F414" t="n">
-        <v>52.68</v>
+        <v>52.24</v>
       </c>
       <c r="G414" t="n">
-        <v>6371330</v>
+        <v>13300469</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>2.21</v>
+        <v>1.36</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
       <c r="J414" t="n">
-        <v>54.35</v>
+        <v>54.33</v>
       </c>
       <c r="K414" t="n">
-        <v>57</v>
+        <v>56.99</v>
       </c>
       <c r="L414" t="n">
-        <v>59.25</v>
+        <v>59.24</v>
       </c>
       <c r="M414" t="n">
         <v>65.27</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>42.78</v>
+        <v>40.72</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,13 +31794,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -1230,7 +1230,7 @@
         <v>29.37</v>
       </c>
       <c r="K10" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="L10" t="n">
         <v>28.58</v>
@@ -3536,7 +3536,7 @@
         <v>29.45</v>
       </c>
       <c r="K40" t="n">
-        <v>29.52</v>
+        <v>29.51</v>
       </c>
       <c r="L40" t="n">
         <v>28.72</v>
@@ -4527,7 +4527,7 @@
         <v>29.77</v>
       </c>
       <c r="K53" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="L53" t="n">
         <v>28.82</v>
@@ -23367,7 +23367,7 @@
         <v>70.12</v>
       </c>
       <c r="K303" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="L303" t="n">
         <v>69.38</v>
@@ -31681,7 +31681,7 @@
         <v>51.54</v>
       </c>
       <c r="G413" t="n">
-        <v>12421300</v>
+        <v>12479800</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.06</v>
@@ -31753,19 +31753,19 @@
         <v>51.55</v>
       </c>
       <c r="F414" t="n">
-        <v>52.24</v>
+        <v>52.12</v>
       </c>
       <c r="G414" t="n">
-        <v>13300469</v>
+        <v>15314685</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
       <c r="J414" t="n">
-        <v>54.33</v>
+        <v>54.32</v>
       </c>
       <c r="K414" t="n">
         <v>56.99</v>
@@ -31777,7 +31777,7 @@
         <v>65.27</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>40.72</v>
+        <v>40.13</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31797,13 +31797,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31701,7 +31701,7 @@
         <v>40.13</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31701,7 +31701,7 @@
         <v>40.13</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31727,6 +31727,77 @@
       <c r="W413" s="3" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="D414" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E414" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="F414" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="G414" t="n">
+        <v>881388</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="L414" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31701,7 +31701,7 @@
         <v>40.13</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31740,28 +31740,28 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>51.7</v>
+        <v>52.05</v>
       </c>
       <c r="D414" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="E414" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="F414" t="n">
         <v>52.1</v>
       </c>
-      <c r="E414" t="n">
-        <v>51.92</v>
-      </c>
-      <c r="F414" t="n">
-        <v>51.97</v>
-      </c>
       <c r="G414" t="n">
-        <v>881388</v>
+        <v>6409030</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
       <c r="J414" t="n">
-        <v>54.01</v>
+        <v>54.02</v>
       </c>
       <c r="K414" t="n">
         <v>56.99</v>
@@ -31773,10 +31773,10 @@
         <v>65.18000000000001</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>37.02</v>
+        <v>37.44</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31790,12 +31790,14 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="2" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -4448,7 +4448,7 @@
         <v>29.77</v>
       </c>
       <c r="K52" t="n">
-        <v>29.66</v>
+        <v>29.67</v>
       </c>
       <c r="L52" t="n">
         <v>28.82</v>
@@ -31677,7 +31677,7 @@
         <v>52.12</v>
       </c>
       <c r="G413" t="n">
-        <v>15359500</v>
+        <v>15407100</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>1.13</v>
@@ -31743,19 +31743,19 @@
         <v>52.05</v>
       </c>
       <c r="D414" t="n">
-        <v>52.15</v>
+        <v>52.29</v>
       </c>
       <c r="E414" t="n">
-        <v>51.74</v>
+        <v>51.4</v>
       </c>
       <c r="F414" t="n">
-        <v>52.1</v>
+        <v>52.26</v>
       </c>
       <c r="G414" t="n">
-        <v>6409030</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>-0.04</v>
+        <v>10240879</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.27</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
@@ -31764,7 +31764,7 @@
         <v>54.02</v>
       </c>
       <c r="K414" t="n">
-        <v>56.99</v>
+        <v>57</v>
       </c>
       <c r="L414" t="n">
         <v>59.12</v>
@@ -31773,10 +31773,10 @@
         <v>65.18000000000001</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>37.44</v>
+        <v>38.25</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31790,16 +31790,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31739,41 +31739,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>52.05</v>
-      </c>
-      <c r="D414" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="E414" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="F414" t="n">
-        <v>52.26</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>10240879</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>0.27</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
-      <c r="J414" t="n">
-        <v>54.02</v>
-      </c>
-      <c r="K414" t="n">
-        <v>57</v>
-      </c>
-      <c r="L414" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="M414" t="n">
-        <v>65.18000000000001</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>38.25</v>
+        <v>37.5</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31739,28 +31739,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="D414" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="E414" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F414" t="n">
+        <v>52.26</v>
+      </c>
       <c r="G414" t="n">
-        <v>10240879</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>10279100</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.27</v>
       </c>
       <c r="I414" t="n">
         <v>5.1</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="K414" t="n">
+        <v>57</v>
+      </c>
+      <c r="L414" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="M414" t="n">
+        <v>65.18000000000001</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>37.5</v>
+        <v>38.25</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31776,7 +31776,7 @@
         <v>38.25</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31802,6 +31802,77 @@
       <c r="W414" s="2" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="D415" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="E415" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="F415" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G415" t="n">
+        <v>3672643</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J415" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="K415" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="L415" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="M415" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>1.55</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>29.19</v>
@@ -683,7 +683,7 @@
         <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>29.21</v>
@@ -758,7 +758,7 @@
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>29.24</v>
@@ -833,7 +833,7 @@
         <v>-0.27</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>29.26</v>
@@ -908,7 +908,7 @@
         <v>-0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>29.27</v>
@@ -983,7 +983,7 @@
         <v>-1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>29.27</v>
@@ -1066,7 +1066,7 @@
         <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>29.31</v>
@@ -1145,7 +1145,7 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>29.37</v>
@@ -1220,7 +1220,7 @@
         <v>1.72</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>29.44</v>
@@ -1295,7 +1295,7 @@
         <v>-0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>29.5</v>
@@ -1370,7 +1370,7 @@
         <v>0.33</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>29.58</v>
@@ -1445,7 +1445,7 @@
         <v>0.13</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>29.62</v>
@@ -1520,7 +1520,7 @@
         <v>-0.32</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>29.67</v>
@@ -1595,7 +1595,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>29.7</v>
@@ -1670,7 +1670,7 @@
         <v>-1.57</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>29.72</v>
@@ -1745,7 +1745,7 @@
         <v>-0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>29.75</v>
@@ -1820,7 +1820,7 @@
         <v>2.07</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>29.83</v>
@@ -1895,7 +1895,7 @@
         <v>-0.16</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>29.91</v>
@@ -1970,7 +1970,7 @@
         <v>2.59</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>30.06</v>
@@ -2045,7 +2045,7 @@
         <v>-1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>30.19</v>
@@ -2120,7 +2120,7 @@
         <v>-0.03</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>30.3</v>
@@ -2195,7 +2195,7 @@
         <v>-1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>30.39</v>
@@ -2270,7 +2270,7 @@
         <v>0.42</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>30.44</v>
@@ -2345,7 +2345,7 @@
         <v>-6.08</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>30.4</v>
@@ -2428,7 +2428,7 @@
         <v>-6.27</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>30.27</v>
@@ -2511,7 +2511,7 @@
         <v>0.22</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>30.17</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>30.03</v>
@@ -2677,7 +2677,7 @@
         <v>3.39</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.92</v>
@@ -2756,7 +2756,7 @@
         <v>0.78</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.8</v>
@@ -2835,7 +2835,7 @@
         <v>3.22</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.72</v>
@@ -2914,7 +2914,7 @@
         <v>0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.65</v>
@@ -2989,7 +2989,7 @@
         <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.58</v>
@@ -3064,7 +3064,7 @@
         <v>1.19</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.53</v>
@@ -3143,7 +3143,7 @@
         <v>-0.71</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.48</v>
@@ -3222,7 +3222,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.47</v>
@@ -3297,7 +3297,7 @@
         <v>-0.97</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.45</v>
@@ -3372,7 +3372,7 @@
         <v>3.59</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.45</v>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>29.45</v>
@@ -3526,7 +3526,7 @@
         <v>-1.67</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>29.39</v>
@@ -3601,7 +3601,7 @@
         <v>0.47</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>29.35</v>
@@ -3676,7 +3676,7 @@
         <v>-1.19</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>29.29</v>
@@ -3751,7 +3751,7 @@
         <v>-0.77</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>29.24</v>
@@ -3830,7 +3830,7 @@
         <v>-0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>29.17</v>
@@ -3905,7 +3905,7 @@
         <v>-0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>29.18</v>
@@ -3984,7 +3984,7 @@
         <v>1.24</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>29.3</v>
@@ -4059,7 +4059,7 @@
         <v>2.51</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>29.45</v>
@@ -4134,7 +4134,7 @@
         <v>-2.42</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>29.57</v>
@@ -4213,7 +4213,7 @@
         <v>-0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>29.64</v>
@@ -4288,7 +4288,7 @@
         <v>1.15</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4363,7 +4363,7 @@
         <v>-0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>29.74</v>
@@ -4442,7 +4442,7 @@
         <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>29.77</v>
@@ -4517,7 +4517,7 @@
         <v>-2.27</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>29.76</v>
@@ -4596,7 +4596,7 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.75</v>
@@ -4671,7 +4671,7 @@
         <v>-1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.74</v>
@@ -4746,7 +4746,7 @@
         <v>0.41</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.72</v>
@@ -4821,7 +4821,7 @@
         <v>2.41</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.75</v>
@@ -4896,7 +4896,7 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.75</v>
@@ -4971,7 +4971,7 @@
         <v>-1.57</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.72</v>
@@ -5046,7 +5046,7 @@
         <v>1.4</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.74</v>
@@ -5121,7 +5121,7 @@
         <v>-0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.74</v>
@@ -5196,7 +5196,7 @@
         <v>-0.83</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.75</v>
@@ -5271,7 +5271,7 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.79</v>
@@ -5346,7 +5346,7 @@
         <v>-0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.82</v>
@@ -5421,7 +5421,7 @@
         <v>5.3</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.94</v>
@@ -5496,7 +5496,7 @@
         <v>-0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>30.04</v>
@@ -5571,7 +5571,7 @@
         <v>-0.32</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>30.09</v>
@@ -5646,7 +5646,7 @@
         <v>3.54</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>30.24</v>
@@ -5721,7 +5721,7 @@
         <v>0.74</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>30.4</v>
@@ -5796,7 +5796,7 @@
         <v>2.14</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>30.58</v>
@@ -5871,7 +5871,7 @@
         <v>-0.48</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>30.76</v>
@@ -5946,7 +5946,7 @@
         <v>-0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>30.91</v>
@@ -6021,7 +6021,7 @@
         <v>0.33</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>31.1</v>
@@ -6096,7 +6096,7 @@
         <v>-0.27</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>31.27</v>
@@ -6171,7 +6171,7 @@
         <v>0.18</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>31.46</v>
@@ -6246,7 +6246,7 @@
         <v>2.15</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>31.68</v>
@@ -6321,7 +6321,7 @@
         <v>-1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>31.83</v>
@@ -6396,7 +6396,7 @@
         <v>-1.65</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>31.94</v>
@@ -6471,7 +6471,7 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>32.09</v>
@@ -6546,7 +6546,7 @@
         <v>-1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>32.2</v>
@@ -6621,7 +6621,7 @@
         <v>1.23</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>32.34</v>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>32.5</v>
@@ -6771,7 +6771,7 @@
         <v>-2.16</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>32.62</v>
@@ -6846,7 +6846,7 @@
         <v>0.58</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>32.76</v>
@@ -6921,7 +6921,7 @@
         <v>-0.24</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>32.82</v>
@@ -7000,7 +7000,7 @@
         <v>1.56</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>32.91</v>
@@ -7075,7 +7075,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>33.02</v>
@@ -7150,7 +7150,7 @@
         <v>-0.24</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>33.07</v>
@@ -7225,7 +7225,7 @@
         <v>-0.42</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>33.1</v>
@@ -7300,7 +7300,7 @@
         <v>-0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>33.08</v>
@@ -7379,7 +7379,7 @@
         <v>2.27</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>33.1</v>
@@ -7454,7 +7454,7 @@
         <v>3.79</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>33.21</v>
@@ -7529,7 +7529,7 @@
         <v>-1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>33.28</v>
@@ -7604,7 +7604,7 @@
         <v>-1.07</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>33.35</v>
@@ -7679,7 +7679,7 @@
         <v>0.44</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>33.42</v>
@@ -7754,7 +7754,7 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>33.46</v>
@@ -7829,7 +7829,7 @@
         <v>-0.12</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>33.53</v>
@@ -7904,7 +7904,7 @@
         <v>2.14</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>33.66</v>
@@ -7979,7 +7979,7 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>33.8</v>
@@ -8054,7 +8054,7 @@
         <v>-0.08</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>33.95</v>
@@ -8129,7 +8129,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>34.08</v>
@@ -8204,7 +8204,7 @@
         <v>-2.34</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>34.14</v>
@@ -8279,7 +8279,7 @@
         <v>-0.06</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>34.24</v>
@@ -8354,7 +8354,7 @@
         <v>0.06</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>34.34</v>
@@ -8429,7 +8429,7 @@
         <v>-3.32</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>34.38</v>
@@ -8508,7 +8508,7 @@
         <v>-0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>34.38</v>
@@ -8583,7 +8583,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>34.38</v>
@@ -8658,7 +8658,7 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>34.41</v>
@@ -8733,7 +8733,7 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>34.46</v>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>34.53</v>
@@ -8883,7 +8883,7 @@
         <v>1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>34.58</v>
@@ -8958,7 +8958,7 @@
         <v>0.35</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>34.58</v>
@@ -9033,7 +9033,7 @@
         <v>-2.01</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>34.55</v>
@@ -9112,7 +9112,7 @@
         <v>0.67</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>34.56</v>
@@ -9187,7 +9187,7 @@
         <v>1.71</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>34.59</v>
@@ -9262,7 +9262,7 @@
         <v>-1.43</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>34.58</v>
@@ -9341,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>34.58</v>
@@ -9416,7 +9416,7 @@
         <v>0.14</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>34.54</v>
@@ -9491,7 +9491,7 @@
         <v>-1.97</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>34.44</v>
@@ -9570,7 +9570,7 @@
         <v>1.65</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>34.38</v>
@@ -9645,7 +9645,7 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>34.34</v>
@@ -9720,7 +9720,7 @@
         <v>2.11</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>34.37</v>
@@ -9795,7 +9795,7 @@
         <v>-0.91</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>34.39</v>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>34.41</v>
@@ -9945,7 +9945,7 @@
         <v>-0.09</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>34.48</v>
@@ -10020,7 +10020,7 @@
         <v>1.51</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.59</v>
@@ -10095,7 +10095,7 @@
         <v>1.89</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.72</v>
@@ -10170,7 +10170,7 @@
         <v>2.65</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.88</v>
@@ -10245,7 +10245,7 @@
         <v>0.51</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>35.03</v>
@@ -10320,7 +10320,7 @@
         <v>-1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>35.16</v>
@@ -10395,7 +10395,7 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>35.28</v>
@@ -10470,7 +10470,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>35.41</v>
@@ -10545,7 +10545,7 @@
         <v>-0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>35.56</v>
@@ -10620,7 +10620,7 @@
         <v>0.62</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>35.71</v>
@@ -10695,7 +10695,7 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>35.85</v>
@@ -10770,7 +10770,7 @@
         <v>1.46</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>36.04</v>
@@ -10845,7 +10845,7 @@
         <v>1.1</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>36.26</v>
@@ -10920,7 +10920,7 @@
         <v>-0.41</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>36.46</v>
@@ -10995,7 +10995,7 @@
         <v>-2.1</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>36.66</v>
@@ -11070,7 +11070,7 @@
         <v>0.53</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>36.83</v>
@@ -11145,7 +11145,7 @@
         <v>2.76</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>37.06</v>
@@ -11220,7 +11220,7 @@
         <v>2.56</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>37.29</v>
@@ -11295,7 +11295,7 @@
         <v>-0.2</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>37.54</v>
@@ -11370,7 +11370,7 @@
         <v>-0.35</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>37.78</v>
@@ -11445,7 +11445,7 @@
         <v>3.04</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>38.08</v>
@@ -11520,7 +11520,7 @@
         <v>2.02</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>38.4</v>
@@ -11595,7 +11595,7 @@
         <v>1.53</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>38.71</v>
@@ -11670,7 +11670,7 @@
         <v>-0.31</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>38.97</v>
@@ -11745,7 +11745,7 @@
         <v>1.27</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>39.25</v>
@@ -11820,7 +11820,7 @@
         <v>-0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>39.53</v>
@@ -11895,7 +11895,7 @@
         <v>2.33</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>39.85</v>
@@ -11970,7 +11970,7 @@
         <v>1.24</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>40.17</v>
@@ -12045,7 +12045,7 @@
         <v>-1.52</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>40.49</v>
@@ -12120,7 +12120,7 @@
         <v>2.7</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>40.84</v>
@@ -12195,7 +12195,7 @@
         <v>0.34</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>41.19</v>
@@ -12270,7 +12270,7 @@
         <v>1.61</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>41.54</v>
@@ -12345,7 +12345,7 @@
         <v>4.03</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>41.97</v>
@@ -12420,7 +12420,7 @@
         <v>-0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>42.38</v>
@@ -12495,7 +12495,7 @@
         <v>3.27</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>42.91</v>
@@ -12570,7 +12570,7 @@
         <v>1.74</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>43.46</v>
@@ -12645,7 +12645,7 @@
         <v>-4.43</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>43.86</v>
@@ -12720,7 +12720,7 @@
         <v>1.55</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>44.25</v>
@@ -12795,7 +12795,7 @@
         <v>-8.24</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>44.44</v>
@@ -12874,7 +12874,7 @@
         <v>0.21</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>44.64</v>
@@ -12949,7 +12949,7 @@
         <v>0.68</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>44.8</v>
@@ -13024,7 +13024,7 @@
         <v>-0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>44.9</v>
@@ -13099,7 +13099,7 @@
         <v>-3.61</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>44.9</v>
@@ -13174,7 +13174,7 @@
         <v>0.71</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>44.92</v>
@@ -13249,7 +13249,7 @@
         <v>1.24</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>44.93</v>
@@ -13324,7 +13324,7 @@
         <v>2.57</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>45.02</v>
@@ -13399,7 +13399,7 @@
         <v>-0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>45.05</v>
@@ -13474,7 +13474,7 @@
         <v>-0.57</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>45.03</v>
@@ -13549,7 +13549,7 @@
         <v>-2.33</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>45</v>
@@ -13624,7 +13624,7 @@
         <v>2.13</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>44.95</v>
@@ -13699,7 +13699,7 @@
         <v>-0.23</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>44.9</v>
@@ -13774,7 +13774,7 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>44.82</v>
@@ -13849,7 +13849,7 @@
         <v>4.26</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>44.75</v>
@@ -13924,7 +13924,7 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>44.73</v>
@@ -13999,7 +13999,7 @@
         <v>4.03</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>44.73</v>
@@ -14074,7 +14074,7 @@
         <v>-1.86</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>44.64</v>
@@ -14149,7 +14149,7 @@
         <v>-3.08</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>44.59</v>
@@ -14224,7 +14224,7 @@
         <v>-1.07</v>
       </c>
       <c r="I182" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>44.48</v>
@@ -14299,7 +14299,7 @@
         <v>1.39</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>44.59</v>
@@ -14374,7 +14374,7 @@
         <v>0.76</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>44.72</v>
@@ -14449,7 +14449,7 @@
         <v>-1.44</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>44.8</v>
@@ -14528,7 +14528,7 @@
         <v>-1.05</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>44.87</v>
@@ -14603,7 +14603,7 @@
         <v>2.94</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>45.08</v>
@@ -14678,7 +14678,7 @@
         <v>0.09</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>45.28</v>
@@ -14753,7 +14753,7 @@
         <v>3.71</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>45.54</v>
@@ -14828,7 +14828,7 @@
         <v>5.81</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>45.88</v>
@@ -14903,7 +14903,7 @@
         <v>2.56</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>46.3</v>
@@ -14978,7 +14978,7 @@
         <v>1.16</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>46.77</v>
@@ -15053,7 +15053,7 @@
         <v>-0.11</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>47.29</v>
@@ -15128,7 +15128,7 @@
         <v>-2.47</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>47.7</v>
@@ -15203,7 +15203,7 @@
         <v>2.3</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>48.16</v>
@@ -15278,7 +15278,7 @@
         <v>-0.45</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>48.6</v>
@@ -15353,7 +15353,7 @@
         <v>4.67</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>49.07</v>
@@ -15428,7 +15428,7 @@
         <v>1.63</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>49.55</v>
@@ -15503,7 +15503,7 @@
         <v>2.76</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>50.02</v>
@@ -15578,7 +15578,7 @@
         <v>-2.64</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>50.45</v>
@@ -15653,7 +15653,7 @@
         <v>3.58</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>51.06</v>
@@ -15728,7 +15728,7 @@
         <v>-0.65</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>51.67</v>
@@ -15803,7 +15803,7 @@
         <v>4.38</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>52.38</v>
@@ -15878,7 +15878,7 @@
         <v>-1.56</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>53.03</v>
@@ -15953,7 +15953,7 @@
         <v>2.71</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>53.78</v>
@@ -16028,7 +16028,7 @@
         <v>2.53</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>54.64</v>
@@ -16103,7 +16103,7 @@
         <v>3.79</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>55.55</v>
@@ -16178,7 +16178,7 @@
         <v>0.59</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>56.48</v>
@@ -16253,7 +16253,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>57.62</v>
@@ -16328,7 +16328,7 @@
         <v>-7.19</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>58.36</v>
@@ -16403,7 +16403,7 @@
         <v>4.5</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>59.18</v>
@@ -16478,7 +16478,7 @@
         <v>-6.61</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>59.74</v>
@@ -16553,7 +16553,7 @@
         <v>2.06</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>60.38</v>
@@ -16628,7 +16628,7 @@
         <v>5.06</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>61.24</v>
@@ -16703,7 +16703,7 @@
         <v>6.7</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>62.28</v>
@@ -16778,7 +16778,7 @@
         <v>-3.73</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>63.19</v>
@@ -16853,7 +16853,7 @@
         <v>-1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>63.92</v>
@@ -16928,7 +16928,7 @@
         <v>3.83</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>64.73999999999999</v>
@@ -17003,7 +17003,7 @@
         <v>6.7</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>65.72</v>
@@ -17078,7 +17078,7 @@
         <v>1.77</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>66.84</v>
@@ -17153,7 +17153,7 @@
         <v>7.58</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>68.16</v>
@@ -17228,7 +17228,7 @@
         <v>-1.47</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>69.44</v>
@@ -17303,7 +17303,7 @@
         <v>-2.76</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>70.48</v>
@@ -17378,7 +17378,7 @@
         <v>5.39</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>71.78</v>
@@ -17453,7 +17453,7 @@
         <v>-1.67</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>72.94</v>
@@ -17528,7 +17528,7 @@
         <v>3.78</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>74.17</v>
@@ -17603,7 +17603,7 @@
         <v>6.63</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>75.56999999999999</v>
@@ -17678,7 +17678,7 @@
         <v>5.84</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>77.23</v>
@@ -17753,7 +17753,7 @@
         <v>3.3</v>
       </c>
       <c r="I229" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>78.75</v>
@@ -17828,7 +17828,7 @@
         <v>3.95</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>80.73</v>
@@ -17903,7 +17903,7 @@
         <v>-0.03</v>
       </c>
       <c r="I231" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>82.56</v>
@@ -17978,7 +17978,7 @@
         <v>-28.54</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>83.11</v>
@@ -18057,7 +18057,7 @@
         <v>-3.98</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>83.45</v>
@@ -18132,7 +18132,7 @@
         <v>6.24</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>83.84</v>
@@ -18207,7 +18207,7 @@
         <v>2.88</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>84.11</v>
@@ -18282,7 +18282,7 @@
         <v>-15.77</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>83.90000000000001</v>
@@ -18357,7 +18357,7 @@
         <v>5.25</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>83.92</v>
@@ -18432,7 +18432,7 @@
         <v>8.33</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>84.11</v>
@@ -18507,7 +18507,7 @@
         <v>-3.46</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>83.92</v>
@@ -18582,7 +18582,7 @@
         <v>4.29</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>83.81999999999999</v>
@@ -18657,7 +18657,7 @@
         <v>-11.53</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>82.97</v>
@@ -18732,7 +18732,7 @@
         <v>2.94</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>82.29000000000001</v>
@@ -18807,7 +18807,7 @@
         <v>-4.8</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>81.56</v>
@@ -18886,7 +18886,7 @@
         <v>5.6</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>80.8</v>
@@ -18961,7 +18961,7 @@
         <v>1.31</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>80.15000000000001</v>
@@ -19036,7 +19036,7 @@
         <v>7.9</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>79.62</v>
@@ -19111,7 +19111,7 @@
         <v>5.16</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>79.01000000000001</v>
@@ -19186,7 +19186,7 @@
         <v>-1.85</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>78.04000000000001</v>
@@ -19261,7 +19261,7 @@
         <v>1.21</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>76.97</v>
@@ -19336,7 +19336,7 @@
         <v>0.51</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>75.70999999999999</v>
@@ -19411,7 +19411,7 @@
         <v>5.64</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>74.68000000000001</v>
@@ -19486,7 +19486,7 @@
         <v>-4.02</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>74.98999999999999</v>
@@ -19561,7 +19561,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>75.09999999999999</v>
@@ -19640,7 +19640,7 @@
         <v>0.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>75.02</v>
@@ -19715,7 +19715,7 @@
         <v>-1.42</v>
       </c>
       <c r="I255" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>74.77</v>
@@ -19794,7 +19794,7 @@
         <v>2.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>75.23</v>
@@ -19873,7 +19873,7 @@
         <v>3.06</v>
       </c>
       <c r="I257" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>75.64</v>
@@ -19948,7 +19948,7 @@
         <v>2.34</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>75.84</v>
@@ -20023,7 +20023,7 @@
         <v>-2.72</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>76.06</v>
@@ -20098,7 +20098,7 @@
         <v>-1.84</v>
       </c>
       <c r="I260" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>76.06</v>
@@ -20167,7 +20167,7 @@
         <v>-4.96</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>76.31</v>
@@ -20250,7 +20250,7 @@
         <v>0.73</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>76.48</v>
@@ -20325,7 +20325,7 @@
         <v>-2.13</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>76.75</v>
@@ -20400,7 +20400,7 @@
         <v>-4.13</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>76.68000000000001</v>
@@ -20475,7 +20475,7 @@
         <v>-4.4</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>76.41</v>
@@ -20550,7 +20550,7 @@
         <v>-6.33</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>75.66</v>
@@ -20633,7 +20633,7 @@
         <v>1.54</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>74.75</v>
@@ -20708,7 +20708,7 @@
         <v>0.77</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>73.95</v>
@@ -20783,7 +20783,7 @@
         <v>3.59</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>73.2</v>
@@ -20858,7 +20858,7 @@
         <v>-6.81</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>72.22</v>
@@ -20937,7 +20937,7 @@
         <v>4.39</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>71.14</v>
@@ -21016,7 +21016,7 @@
         <v>0.13</v>
       </c>
       <c r="I272" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>70.23999999999999</v>
@@ -21091,7 +21091,7 @@
         <v>7.27</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>69.91</v>
@@ -21166,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>69.55</v>
@@ -21241,7 +21241,7 @@
         <v>-3.45</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>69.13</v>
@@ -21316,7 +21316,7 @@
         <v>0.46</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>68.64</v>
@@ -21391,7 +21391,7 @@
         <v>-0.23</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>68.02</v>
@@ -21470,7 +21470,7 @@
         <v>2.32</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>67.39</v>
@@ -21545,7 +21545,7 @@
         <v>1.36</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>66.91</v>
@@ -21620,7 +21620,7 @@
         <v>1.01</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>66.54000000000001</v>
@@ -21695,7 +21695,7 @@
         <v>-1.16</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>66.31999999999999</v>
@@ -21770,7 +21770,7 @@
         <v>5.51</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>66.26000000000001</v>
@@ -21845,7 +21845,7 @@
         <v>-0.28</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>66.27</v>
@@ -21920,7 +21920,7 @@
         <v>-0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>66.40000000000001</v>
@@ -21995,7 +21995,7 @@
         <v>3.35</v>
       </c>
       <c r="I285" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>66.8</v>
@@ -22070,7 +22070,7 @@
         <v>-2.01</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>67.33</v>
@@ -22145,7 +22145,7 @@
         <v>-5.07</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>67.63</v>
@@ -22220,7 +22220,7 @@
         <v>2.74</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>68</v>
@@ -22295,7 +22295,7 @@
         <v>-2.83</v>
       </c>
       <c r="I289" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>68.16</v>
@@ -22370,7 +22370,7 @@
         <v>0.6</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>68.56</v>
@@ -22445,7 +22445,7 @@
         <v>-0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>68.8</v>
@@ -22524,7 +22524,7 @@
         <v>-3.12</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>68.94</v>
@@ -22603,7 +22603,7 @@
         <v>-2.05</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>68.77</v>
@@ -22678,7 +22678,7 @@
         <v>2.81</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>68.7</v>
@@ -22753,7 +22753,7 @@
         <v>2.45</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>68.81999999999999</v>
@@ -22828,7 +22828,7 @@
         <v>-3.44</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>68.81999999999999</v>
@@ -22907,7 +22907,7 @@
         <v>-0.05</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>68.81999999999999</v>
@@ -22982,7 +22982,7 @@
         <v>6.4</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>68.95</v>
@@ -23057,7 +23057,7 @@
         <v>2.1</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>69.11</v>
@@ -23132,7 +23132,7 @@
         <v>1.97</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>69.31</v>
@@ -23207,7 +23207,7 @@
         <v>6.83</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>69.79000000000001</v>
@@ -23282,7 +23282,7 @@
         <v>0.71</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>70.12</v>
@@ -23357,7 +23357,7 @@
         <v>1.02</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>70.48999999999999</v>
@@ -23432,7 +23432,7 @@
         <v>-4.84</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>70.70999999999999</v>
@@ -23507,7 +23507,7 @@
         <v>-8.57</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>70.48</v>
@@ -23586,7 +23586,7 @@
         <v>1.3</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>70.37</v>
@@ -23661,7 +23661,7 @@
         <v>-4.35</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>70.29000000000001</v>
@@ -23736,7 +23736,7 @@
         <v>2.74</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>70.20999999999999</v>
@@ -23811,7 +23811,7 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>70.26000000000001</v>
@@ -23886,7 +23886,7 @@
         <v>-1.57</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>70.23999999999999</v>
@@ -23961,7 +23961,7 @@
         <v>1.99</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>70.31</v>
@@ -24036,7 +24036,7 @@
         <v>-3.18</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>70.37</v>
@@ -24111,7 +24111,7 @@
         <v>1.27</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>70.55</v>
@@ -24186,7 +24186,7 @@
         <v>-0.04</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>70.63</v>
@@ -24261,7 +24261,7 @@
         <v>-0.97</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>70.59999999999999</v>
@@ -24336,7 +24336,7 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>70.7</v>
@@ -24411,7 +24411,7 @@
         <v>-2.62</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>70.72</v>
@@ -24486,7 +24486,7 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>70.56</v>
@@ -24561,7 +24561,7 @@
         <v>-8.08</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>70.06</v>
@@ -24636,7 +24636,7 @@
         <v>0.02</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>69.48999999999999</v>
@@ -24711,7 +24711,7 @@
         <v>-4.17</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>68.54000000000001</v>
@@ -24790,7 +24790,7 @@
         <v>-2.29</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>67.48999999999999</v>
@@ -24869,7 +24869,7 @@
         <v>5.48</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>66.56999999999999</v>
@@ -24944,7 +24944,7 @@
         <v>0.77</v>
       </c>
       <c r="I324" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>65.86</v>
@@ -25019,7 +25019,7 @@
         <v>3.56</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>65.58</v>
@@ -25094,7 +25094,7 @@
         <v>-0.13</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>65.25</v>
@@ -25169,7 +25169,7 @@
         <v>-4.39</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>64.94</v>
@@ -25244,7 +25244,7 @@
         <v>-1.81</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>64.47</v>
@@ -25319,7 +25319,7 @@
         <v>-1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>63.95</v>
@@ -25394,7 +25394,7 @@
         <v>-5.4</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>63.32</v>
@@ -25473,7 +25473,7 @@
         <v>-7.09</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>62.42</v>
@@ -25552,7 +25552,7 @@
         <v>1.12</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>61.66</v>
@@ -25631,7 +25631,7 @@
         <v>1.76</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>60.91</v>
@@ -25706,7 +25706,7 @@
         <v>-1.13</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>60.12</v>
@@ -25781,7 +25781,7 @@
         <v>1.5</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>59.42</v>
@@ -25856,7 +25856,7 @@
         <v>0.21</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>58.69</v>
@@ -25931,7 +25931,7 @@
         <v>2.69</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>58.14</v>
@@ -26006,7 +26006,7 @@
         <v>1.98</v>
       </c>
       <c r="I338" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>57.59</v>
@@ -26081,7 +26081,7 @@
         <v>-2.94</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>57.24</v>
@@ -26160,7 +26160,7 @@
         <v>-2.99</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>56.8</v>
@@ -26239,7 +26239,7 @@
         <v>2.48</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>56.55</v>
@@ -26314,7 +26314,7 @@
         <v>-0.35</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>56.37</v>
@@ -26389,7 +26389,7 @@
         <v>-3.32</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>55.94</v>
@@ -26464,7 +26464,7 @@
         <v>1.94</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>55.53</v>
@@ -26539,7 +26539,7 @@
         <v>-1.81</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>54.97</v>
@@ -26614,7 +26614,7 @@
         <v>-3.49</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>54.32</v>
@@ -26689,7 +26689,7 @@
         <v>0.77</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>53.83</v>
@@ -26764,7 +26764,7 @@
         <v>0.39</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>53.4</v>
@@ -26839,7 +26839,7 @@
         <v>4.12</v>
       </c>
       <c r="I349" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>53.11</v>
@@ -26914,7 +26914,7 @@
         <v>1.58</v>
       </c>
       <c r="I350" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>53.02</v>
@@ -26989,7 +26989,7 @@
         <v>-3.45</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>53.03</v>
@@ -27068,7 +27068,7 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>53.04</v>
@@ -27143,7 +27143,7 @@
         <v>0.65</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>53.03</v>
@@ -27218,7 +27218,7 @@
         <v>-2.32</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>52.98</v>
@@ -27293,7 +27293,7 @@
         <v>0.14</v>
       </c>
       <c r="I355" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>52.89</v>
@@ -27368,7 +27368,7 @@
         <v>3.34</v>
       </c>
       <c r="I356" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>52.89</v>
@@ -27443,7 +27443,7 @@
         <v>-2.13</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>52.75</v>
@@ -27522,7 +27522,7 @@
         <v>0.19</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>52.57</v>
@@ -27597,7 +27597,7 @@
         <v>2.63</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>52.54</v>
@@ -27672,7 +27672,7 @@
         <v>4.14</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>52.7</v>
@@ -27747,7 +27747,7 @@
         <v>-0.39</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>52.79</v>
@@ -27822,7 +27822,7 @@
         <v>2.95</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>52.97</v>
@@ -27897,7 +27897,7 @@
         <v>3.32</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>53.33</v>
@@ -27972,7 +27972,7 @@
         <v>-1.45</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>53.6</v>
@@ -28047,7 +28047,7 @@
         <v>0.87</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>53.94</v>
@@ -28122,7 +28122,7 @@
         <v>-1.52</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>54.33</v>
@@ -28197,7 +28197,7 @@
         <v>0.55</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>54.71</v>
@@ -28272,7 +28272,7 @@
         <v>1.86</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>55.14</v>
@@ -28347,7 +28347,7 @@
         <v>-3.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>55.36</v>
@@ -28426,7 +28426,7 @@
         <v>4.47</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>55.67</v>
@@ -28501,7 +28501,7 @@
         <v>2.75</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>56.15</v>
@@ -28576,7 +28576,7 @@
         <v>1.72</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>56.65</v>
@@ -28651,7 +28651,7 @@
         <v>-0.83</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>57.12</v>
@@ -28726,7 +28726,7 @@
         <v>0.19</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>57.65</v>
@@ -28801,7 +28801,7 @@
         <v>-1.17</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>58.14</v>
@@ -28876,7 +28876,7 @@
         <v>1.92</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>58.6</v>
@@ -28951,7 +28951,7 @@
         <v>-4.38</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>58.98</v>
@@ -29026,7 +29026,7 @@
         <v>0.18</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>59.37</v>
@@ -29101,7 +29101,7 @@
         <v>-3.68</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>59.57</v>
@@ -29180,7 +29180,7 @@
         <v>1.99</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>59.72</v>
@@ -29255,7 +29255,7 @@
         <v>2.51</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>59.96</v>
@@ -29330,7 +29330,7 @@
         <v>-1.21</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>60.07</v>
@@ -29409,7 +29409,7 @@
         <v>-0.75</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>60.07</v>
@@ -29484,7 +29484,7 @@
         <v>2.27</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>60.18</v>
@@ -29559,7 +29559,7 @@
         <v>-5.3</v>
       </c>
       <c r="I385" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" s="4" t="n">
         <v>60.1</v>
@@ -29638,7 +29638,7 @@
         <v>1.08</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>60.1</v>
@@ -29713,7 +29713,7 @@
         <v>-2.2</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>60.02</v>
@@ -29788,7 +29788,7 @@
         <v>1.21</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>59.92</v>
@@ -29863,7 +29863,7 @@
         <v>-0.83</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>59.9</v>
@@ -29938,7 +29938,7 @@
         <v>3.37</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>59.84</v>
@@ -30013,7 +30013,7 @@
         <v>1.63</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>59.76</v>
@@ -30088,7 +30088,7 @@
         <v>-0.5</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>59.6</v>
@@ -30163,7 +30163,7 @@
         <v>1.84</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>59.53</v>
@@ -30238,7 +30238,7 @@
         <v>-4.23</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>59.32</v>
@@ -30317,7 +30317,7 @@
         <v>-0.93</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>59.12</v>
@@ -30392,7 +30392,7 @@
         <v>0.9</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>58.89</v>
@@ -30467,7 +30467,7 @@
         <v>-5.49</v>
       </c>
       <c r="I397" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>58.64</v>
@@ -30546,7 +30546,7 @@
         <v>0.96</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>58.41</v>
@@ -30621,7 +30621,7 @@
         <v>-1.75</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>58.23</v>
@@ -30696,7 +30696,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>58.03</v>
@@ -30771,7 +30771,7 @@
         <v>-0.51</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>57.74</v>
@@ -30846,7 +30846,7 @@
         <v>0.71</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>57.51</v>
@@ -30921,7 +30921,7 @@
         <v>0.58</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>57.31</v>
@@ -30996,7 +30996,7 @@
         <v>-2.94</v>
       </c>
       <c r="I404" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>56.97</v>
@@ -31071,7 +31071,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>56.76</v>
@@ -31150,7 +31150,7 @@
         <v>2.49</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>56.6</v>
@@ -31225,7 +31225,7 @@
         <v>-0.78</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>56.47</v>
@@ -31304,7 +31304,7 @@
         <v>-1.58</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>56.27</v>
@@ -31379,7 +31379,7 @@
         <v>-6.11</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>55.93</v>
@@ -31458,7 +31458,7 @@
         <v>3.39</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>55.58</v>
@@ -31533,7 +31533,7 @@
         <v>-0.79</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>55.15</v>
@@ -31608,7 +31608,7 @@
         <v>0.06</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>54.75</v>
@@ -31683,7 +31683,7 @@
         <v>1.13</v>
       </c>
       <c r="I413" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J413" t="n">
         <v>54.32</v>
@@ -31758,7 +31758,7 @@
         <v>0.27</v>
       </c>
       <c r="I414" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J414" t="n">
         <v>54.02</v>
@@ -31776,7 +31776,7 @@
         <v>38.25</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31815,62 +31815,64 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>52.05</v>
+        <v>50.26</v>
       </c>
       <c r="D415" t="n">
         <v>50.33</v>
       </c>
       <c r="E415" t="n">
-        <v>49.85</v>
+        <v>49.33</v>
       </c>
       <c r="F415" t="n">
-        <v>49.88</v>
+        <v>49.54</v>
       </c>
       <c r="G415" t="n">
-        <v>3672643</v>
+        <v>19301529</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>-4.55</v>
+        <v>-5.2</v>
       </c>
       <c r="I415" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J415" t="n">
-        <v>53.64</v>
+        <v>53.62</v>
       </c>
       <c r="K415" t="n">
-        <v>56.97</v>
+        <v>56.96</v>
       </c>
       <c r="L415" t="n">
-        <v>58.97</v>
+        <v>58.96</v>
       </c>
       <c r="M415" t="n">
         <v>65.06</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>32.44</v>
+        <v>31.66</v>
       </c>
       <c r="O415" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="2" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31752,7 +31752,7 @@
         <v>52.26</v>
       </c>
       <c r="G414" t="n">
-        <v>10279100</v>
+        <v>10317500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.27</v>
@@ -31804,77 +31804,79 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="n">
+      <c r="C415" s="4" t="n">
         <v>50.26</v>
       </c>
-      <c r="D415" t="n">
+      <c r="D415" s="4" t="n">
         <v>50.33</v>
       </c>
-      <c r="E415" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="F415" t="n">
-        <v>49.54</v>
-      </c>
-      <c r="G415" t="n">
-        <v>19301529</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="I415" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="K415" t="n">
+      <c r="E415" s="4" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>24604800</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="K415" s="4" t="n">
         <v>56.96</v>
       </c>
-      <c r="L415" t="n">
+      <c r="L415" s="4" t="n">
         <v>58.96</v>
       </c>
-      <c r="M415" t="n">
+      <c r="M415" s="4" t="n">
         <v>65.06</v>
       </c>
-      <c r="N415" s="2" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="N415" s="6" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="O415" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P415" s="4" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T415" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="P415" t="inlineStr">
-        <is>
-          <t>extreme fear</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>3x BUY</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="T415" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="U415" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="U415" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>1.55</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>29.19</v>
@@ -683,7 +683,7 @@
         <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>29.21</v>
@@ -758,7 +758,7 @@
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>29.24</v>
@@ -833,7 +833,7 @@
         <v>-0.27</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>29.26</v>
@@ -908,7 +908,7 @@
         <v>-0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>29.27</v>
@@ -983,7 +983,7 @@
         <v>-1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>29.27</v>
@@ -1066,7 +1066,7 @@
         <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>29.31</v>
@@ -1145,7 +1145,7 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>29.37</v>
@@ -1220,7 +1220,7 @@
         <v>1.72</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>29.44</v>
@@ -1295,7 +1295,7 @@
         <v>-0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>29.5</v>
@@ -1370,7 +1370,7 @@
         <v>0.33</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>29.58</v>
@@ -1445,7 +1445,7 @@
         <v>0.13</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>29.62</v>
@@ -1520,7 +1520,7 @@
         <v>-0.32</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>29.67</v>
@@ -1595,7 +1595,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>29.7</v>
@@ -1670,7 +1670,7 @@
         <v>-1.57</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>29.72</v>
@@ -1745,7 +1745,7 @@
         <v>-0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>29.75</v>
@@ -1820,7 +1820,7 @@
         <v>2.07</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>29.83</v>
@@ -1895,7 +1895,7 @@
         <v>-0.16</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>29.91</v>
@@ -1970,7 +1970,7 @@
         <v>2.59</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>30.06</v>
@@ -2045,7 +2045,7 @@
         <v>-1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>30.19</v>
@@ -2120,7 +2120,7 @@
         <v>-0.03</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>30.3</v>
@@ -2195,7 +2195,7 @@
         <v>-1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>30.39</v>
@@ -2270,7 +2270,7 @@
         <v>0.42</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>30.44</v>
@@ -2345,7 +2345,7 @@
         <v>-6.08</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>30.4</v>
@@ -2428,7 +2428,7 @@
         <v>-6.27</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>30.27</v>
@@ -2511,7 +2511,7 @@
         <v>0.22</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>30.17</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>30.03</v>
@@ -2677,7 +2677,7 @@
         <v>3.39</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>29.92</v>
@@ -2756,7 +2756,7 @@
         <v>0.78</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>29.8</v>
@@ -2835,7 +2835,7 @@
         <v>3.22</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>29.72</v>
@@ -2914,7 +2914,7 @@
         <v>0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>29.65</v>
@@ -2989,7 +2989,7 @@
         <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>29.58</v>
@@ -3064,7 +3064,7 @@
         <v>1.19</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
         <v>29.53</v>
@@ -3143,7 +3143,7 @@
         <v>-0.71</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>29.48</v>
@@ -3222,7 +3222,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>29.47</v>
@@ -3297,7 +3297,7 @@
         <v>-0.97</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>29.45</v>
@@ -3372,7 +3372,7 @@
         <v>3.59</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>29.45</v>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>29.45</v>
@@ -3526,7 +3526,7 @@
         <v>-1.67</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>29.39</v>
@@ -3601,7 +3601,7 @@
         <v>0.47</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>29.35</v>
@@ -3676,7 +3676,7 @@
         <v>-1.19</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>29.29</v>
@@ -3751,7 +3751,7 @@
         <v>-0.77</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>29.24</v>
@@ -3830,7 +3830,7 @@
         <v>-0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>29.17</v>
@@ -3905,7 +3905,7 @@
         <v>-0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>29.18</v>
@@ -3984,7 +3984,7 @@
         <v>1.24</v>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>29.3</v>
@@ -4059,7 +4059,7 @@
         <v>2.51</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>29.45</v>
@@ -4134,7 +4134,7 @@
         <v>-2.42</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>29.57</v>
@@ -4213,7 +4213,7 @@
         <v>-0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>29.64</v>
@@ -4288,7 +4288,7 @@
         <v>1.15</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4363,7 +4363,7 @@
         <v>-0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>29.74</v>
@@ -4442,7 +4442,7 @@
         <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>29.77</v>
@@ -4517,7 +4517,7 @@
         <v>-2.27</v>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>29.76</v>
@@ -4596,7 +4596,7 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>29.75</v>
@@ -4671,7 +4671,7 @@
         <v>-1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>29.74</v>
@@ -4746,7 +4746,7 @@
         <v>0.41</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>29.72</v>
@@ -4821,7 +4821,7 @@
         <v>2.41</v>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>29.75</v>
@@ -4896,7 +4896,7 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>29.75</v>
@@ -4971,7 +4971,7 @@
         <v>-1.57</v>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>29.72</v>
@@ -5046,7 +5046,7 @@
         <v>1.4</v>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>29.74</v>
@@ -5121,7 +5121,7 @@
         <v>-0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>29.74</v>
@@ -5196,7 +5196,7 @@
         <v>-0.83</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>29.75</v>
@@ -5271,7 +5271,7 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>29.79</v>
@@ -5346,7 +5346,7 @@
         <v>-0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>29.82</v>
@@ -5421,7 +5421,7 @@
         <v>5.3</v>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>29.94</v>
@@ -5496,7 +5496,7 @@
         <v>-0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>30.04</v>
@@ -5571,7 +5571,7 @@
         <v>-0.32</v>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>30.09</v>
@@ -5646,7 +5646,7 @@
         <v>3.54</v>
       </c>
       <c r="I68" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>30.24</v>
@@ -5721,7 +5721,7 @@
         <v>0.74</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>30.4</v>
@@ -5796,7 +5796,7 @@
         <v>2.14</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>30.58</v>
@@ -5871,7 +5871,7 @@
         <v>-0.48</v>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>30.76</v>
@@ -5946,7 +5946,7 @@
         <v>-0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>30.91</v>
@@ -6021,7 +6021,7 @@
         <v>0.33</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>31.1</v>
@@ -6096,7 +6096,7 @@
         <v>-0.27</v>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>31.27</v>
@@ -6171,7 +6171,7 @@
         <v>0.18</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>31.46</v>
@@ -6246,7 +6246,7 @@
         <v>2.15</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>31.68</v>
@@ -6321,7 +6321,7 @@
         <v>-1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>31.83</v>
@@ -6396,7 +6396,7 @@
         <v>-1.65</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>31.94</v>
@@ -6471,7 +6471,7 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>32.09</v>
@@ -6546,7 +6546,7 @@
         <v>-1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>32.2</v>
@@ -6621,7 +6621,7 @@
         <v>1.23</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>32.34</v>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>32.5</v>
@@ -6771,7 +6771,7 @@
         <v>-2.16</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>32.62</v>
@@ -6846,7 +6846,7 @@
         <v>0.58</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>32.76</v>
@@ -6921,7 +6921,7 @@
         <v>-0.24</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>32.82</v>
@@ -7000,7 +7000,7 @@
         <v>1.56</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>32.91</v>
@@ -7075,7 +7075,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>33.02</v>
@@ -7150,7 +7150,7 @@
         <v>-0.24</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>33.07</v>
@@ -7225,7 +7225,7 @@
         <v>-0.42</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>33.1</v>
@@ -7300,7 +7300,7 @@
         <v>-0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>33.08</v>
@@ -7379,7 +7379,7 @@
         <v>2.27</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>33.1</v>
@@ -7454,7 +7454,7 @@
         <v>3.79</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>33.21</v>
@@ -7529,7 +7529,7 @@
         <v>-1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>33.28</v>
@@ -7604,7 +7604,7 @@
         <v>-1.07</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>33.35</v>
@@ -7679,7 +7679,7 @@
         <v>0.44</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>33.42</v>
@@ -7754,7 +7754,7 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>33.46</v>
@@ -7829,7 +7829,7 @@
         <v>-0.12</v>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>33.53</v>
@@ -7904,7 +7904,7 @@
         <v>2.14</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>33.66</v>
@@ -7979,7 +7979,7 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>33.8</v>
@@ -8054,7 +8054,7 @@
         <v>-0.08</v>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>33.95</v>
@@ -8129,7 +8129,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>34.08</v>
@@ -8204,7 +8204,7 @@
         <v>-2.34</v>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>34.14</v>
@@ -8279,7 +8279,7 @@
         <v>-0.06</v>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>34.24</v>
@@ -8354,7 +8354,7 @@
         <v>0.06</v>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>34.34</v>
@@ -8429,7 +8429,7 @@
         <v>-3.32</v>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>34.38</v>
@@ -8508,7 +8508,7 @@
         <v>-0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>34.38</v>
@@ -8583,7 +8583,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
         <v>34.38</v>
@@ -8658,7 +8658,7 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>34.41</v>
@@ -8733,7 +8733,7 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>34.46</v>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>34.53</v>
@@ -8883,7 +8883,7 @@
         <v>1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>34.58</v>
@@ -8958,7 +8958,7 @@
         <v>0.35</v>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>34.58</v>
@@ -9033,7 +9033,7 @@
         <v>-2.01</v>
       </c>
       <c r="I113" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J113" t="n">
         <v>34.55</v>
@@ -9112,7 +9112,7 @@
         <v>0.67</v>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>34.56</v>
@@ -9187,7 +9187,7 @@
         <v>1.71</v>
       </c>
       <c r="I115" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J115" t="n">
         <v>34.59</v>
@@ -9262,7 +9262,7 @@
         <v>-1.43</v>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>34.58</v>
@@ -9341,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>34.58</v>
@@ -9416,7 +9416,7 @@
         <v>0.14</v>
       </c>
       <c r="I118" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>34.54</v>
@@ -9491,7 +9491,7 @@
         <v>-1.97</v>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>34.44</v>
@@ -9570,7 +9570,7 @@
         <v>1.65</v>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>34.38</v>
@@ -9645,7 +9645,7 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>34.34</v>
@@ -9720,7 +9720,7 @@
         <v>2.11</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>34.37</v>
@@ -9795,7 +9795,7 @@
         <v>-0.91</v>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J123" t="n">
         <v>34.39</v>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>34.41</v>
@@ -9945,7 +9945,7 @@
         <v>-0.09</v>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>34.48</v>
@@ -10020,7 +10020,7 @@
         <v>1.51</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>34.59</v>
@@ -10095,7 +10095,7 @@
         <v>1.89</v>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J127" t="n">
         <v>34.72</v>
@@ -10170,7 +10170,7 @@
         <v>2.65</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>34.88</v>
@@ -10245,7 +10245,7 @@
         <v>0.51</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>35.03</v>
@@ -10320,7 +10320,7 @@
         <v>-1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>35.16</v>
@@ -10395,7 +10395,7 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>35.28</v>
@@ -10470,7 +10470,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>35.41</v>
@@ -10545,7 +10545,7 @@
         <v>-0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>35.56</v>
@@ -10620,7 +10620,7 @@
         <v>0.62</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>35.71</v>
@@ -10695,7 +10695,7 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>35.85</v>
@@ -10770,7 +10770,7 @@
         <v>1.46</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>36.04</v>
@@ -10845,7 +10845,7 @@
         <v>1.1</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>36.26</v>
@@ -10920,7 +10920,7 @@
         <v>-0.41</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>36.46</v>
@@ -10995,7 +10995,7 @@
         <v>-2.1</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>36.66</v>
@@ -11070,7 +11070,7 @@
         <v>0.53</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>36.83</v>
@@ -11145,7 +11145,7 @@
         <v>2.76</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>37.06</v>
@@ -11220,7 +11220,7 @@
         <v>2.56</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>37.29</v>
@@ -11295,7 +11295,7 @@
         <v>-0.2</v>
       </c>
       <c r="I143" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J143" t="n">
         <v>37.54</v>
@@ -11370,7 +11370,7 @@
         <v>-0.35</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J144" t="n">
         <v>37.78</v>
@@ -11445,7 +11445,7 @@
         <v>3.04</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J145" t="n">
         <v>38.08</v>
@@ -11520,7 +11520,7 @@
         <v>2.02</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>38.4</v>
@@ -11595,7 +11595,7 @@
         <v>1.53</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>38.71</v>
@@ -11670,7 +11670,7 @@
         <v>-0.31</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>38.97</v>
@@ -11745,7 +11745,7 @@
         <v>1.27</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>39.25</v>
@@ -11820,7 +11820,7 @@
         <v>-0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>39.53</v>
@@ -11895,7 +11895,7 @@
         <v>2.33</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>39.85</v>
@@ -11970,7 +11970,7 @@
         <v>1.24</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J152" t="n">
         <v>40.17</v>
@@ -12045,7 +12045,7 @@
         <v>-1.52</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>40.49</v>
@@ -12120,7 +12120,7 @@
         <v>2.7</v>
       </c>
       <c r="I154" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>40.84</v>
@@ -12195,7 +12195,7 @@
         <v>0.34</v>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>41.19</v>
@@ -12270,7 +12270,7 @@
         <v>1.61</v>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>41.54</v>
@@ -12345,7 +12345,7 @@
         <v>4.03</v>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J157" t="n">
         <v>41.97</v>
@@ -12420,7 +12420,7 @@
         <v>-0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>42.38</v>
@@ -12495,7 +12495,7 @@
         <v>3.27</v>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>42.91</v>
@@ -12570,7 +12570,7 @@
         <v>1.74</v>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J160" t="n">
         <v>43.46</v>
@@ -12645,7 +12645,7 @@
         <v>-4.43</v>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J161" t="n">
         <v>43.86</v>
@@ -12720,7 +12720,7 @@
         <v>1.55</v>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>44.25</v>
@@ -12795,7 +12795,7 @@
         <v>-8.24</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>44.44</v>
@@ -12874,7 +12874,7 @@
         <v>0.21</v>
       </c>
       <c r="I164" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J164" t="n">
         <v>44.64</v>
@@ -12949,7 +12949,7 @@
         <v>0.68</v>
       </c>
       <c r="I165" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J165" t="n">
         <v>44.8</v>
@@ -13024,7 +13024,7 @@
         <v>-0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>44.9</v>
@@ -13099,7 +13099,7 @@
         <v>-3.61</v>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>44.9</v>
@@ -13174,7 +13174,7 @@
         <v>0.71</v>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J168" t="n">
         <v>44.92</v>
@@ -13249,7 +13249,7 @@
         <v>1.24</v>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>44.93</v>
@@ -13324,7 +13324,7 @@
         <v>2.57</v>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>45.02</v>
@@ -13399,7 +13399,7 @@
         <v>-0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>45.05</v>
@@ -13474,7 +13474,7 @@
         <v>-0.57</v>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J172" t="n">
         <v>45.03</v>
@@ -13549,7 +13549,7 @@
         <v>-2.33</v>
       </c>
       <c r="I173" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>45</v>
@@ -13624,7 +13624,7 @@
         <v>2.13</v>
       </c>
       <c r="I174" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J174" t="n">
         <v>44.95</v>
@@ -13699,7 +13699,7 @@
         <v>-0.23</v>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>44.9</v>
@@ -13774,7 +13774,7 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>44.82</v>
@@ -13849,7 +13849,7 @@
         <v>4.26</v>
       </c>
       <c r="I177" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>44.75</v>
@@ -13924,7 +13924,7 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J178" t="n">
         <v>44.73</v>
@@ -13999,7 +13999,7 @@
         <v>4.03</v>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>44.73</v>
@@ -14074,7 +14074,7 @@
         <v>-1.86</v>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J180" t="n">
         <v>44.64</v>
@@ -14149,7 +14149,7 @@
         <v>-3.08</v>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>44.59</v>
@@ -14224,7 +14224,7 @@
         <v>-1.07</v>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>44.48</v>
@@ -14299,7 +14299,7 @@
         <v>1.39</v>
       </c>
       <c r="I183" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>44.59</v>
@@ -14374,7 +14374,7 @@
         <v>0.76</v>
       </c>
       <c r="I184" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J184" t="n">
         <v>44.72</v>
@@ -14449,7 +14449,7 @@
         <v>-1.44</v>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J185" t="n">
         <v>44.8</v>
@@ -14528,7 +14528,7 @@
         <v>-1.05</v>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>44.87</v>
@@ -14603,7 +14603,7 @@
         <v>2.94</v>
       </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>45.08</v>
@@ -14678,7 +14678,7 @@
         <v>0.09</v>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J188" t="n">
         <v>45.28</v>
@@ -14753,7 +14753,7 @@
         <v>3.71</v>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>45.54</v>
@@ -14828,7 +14828,7 @@
         <v>5.81</v>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J190" t="n">
         <v>45.88</v>
@@ -14903,7 +14903,7 @@
         <v>2.56</v>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>46.3</v>
@@ -14978,7 +14978,7 @@
         <v>1.16</v>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>46.77</v>
@@ -15053,7 +15053,7 @@
         <v>-0.11</v>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J193" t="n">
         <v>47.29</v>
@@ -15128,7 +15128,7 @@
         <v>-2.47</v>
       </c>
       <c r="I194" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>47.7</v>
@@ -15203,7 +15203,7 @@
         <v>2.3</v>
       </c>
       <c r="I195" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>48.16</v>
@@ -15278,7 +15278,7 @@
         <v>-0.45</v>
       </c>
       <c r="I196" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>48.6</v>
@@ -15353,7 +15353,7 @@
         <v>4.67</v>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J197" t="n">
         <v>49.07</v>
@@ -15428,7 +15428,7 @@
         <v>1.63</v>
       </c>
       <c r="I198" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J198" t="n">
         <v>49.55</v>
@@ -15503,7 +15503,7 @@
         <v>2.76</v>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>50.02</v>
@@ -15578,7 +15578,7 @@
         <v>-2.64</v>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>50.45</v>
@@ -15653,7 +15653,7 @@
         <v>3.58</v>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>51.06</v>
@@ -15728,7 +15728,7 @@
         <v>-0.65</v>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J202" t="n">
         <v>51.67</v>
@@ -15803,7 +15803,7 @@
         <v>4.38</v>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J203" t="n">
         <v>52.38</v>
@@ -15878,7 +15878,7 @@
         <v>-1.56</v>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J204" t="n">
         <v>53.03</v>
@@ -15953,7 +15953,7 @@
         <v>2.71</v>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J205" t="n">
         <v>53.78</v>
@@ -16028,7 +16028,7 @@
         <v>2.53</v>
       </c>
       <c r="I206" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>54.64</v>
@@ -16103,7 +16103,7 @@
         <v>3.79</v>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>55.55</v>
@@ -16178,7 +16178,7 @@
         <v>0.59</v>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J208" t="n">
         <v>56.48</v>
@@ -16253,7 +16253,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J209" t="n">
         <v>57.62</v>
@@ -16328,7 +16328,7 @@
         <v>-7.19</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>58.36</v>
@@ -16403,7 +16403,7 @@
         <v>4.5</v>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J211" t="n">
         <v>59.18</v>
@@ -16478,7 +16478,7 @@
         <v>-6.61</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>59.74</v>
@@ -16553,7 +16553,7 @@
         <v>2.06</v>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>60.38</v>
@@ -16628,7 +16628,7 @@
         <v>5.06</v>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J214" t="n">
         <v>61.24</v>
@@ -16703,7 +16703,7 @@
         <v>6.7</v>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>62.28</v>
@@ -16778,7 +16778,7 @@
         <v>-3.73</v>
       </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>63.19</v>
@@ -16853,7 +16853,7 @@
         <v>-1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J217" t="n">
         <v>63.92</v>
@@ -16928,7 +16928,7 @@
         <v>3.83</v>
       </c>
       <c r="I218" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>64.73999999999999</v>
@@ -17003,7 +17003,7 @@
         <v>6.7</v>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J219" t="n">
         <v>65.72</v>
@@ -17078,7 +17078,7 @@
         <v>1.77</v>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J220" t="n">
         <v>66.84</v>
@@ -17153,7 +17153,7 @@
         <v>7.58</v>
       </c>
       <c r="I221" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J221" t="n">
         <v>68.16</v>
@@ -17228,7 +17228,7 @@
         <v>-1.47</v>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J222" t="n">
         <v>69.44</v>
@@ -17303,7 +17303,7 @@
         <v>-2.76</v>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J223" t="n">
         <v>70.48</v>
@@ -17378,7 +17378,7 @@
         <v>5.39</v>
       </c>
       <c r="I224" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>71.78</v>
@@ -17453,7 +17453,7 @@
         <v>-1.67</v>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J225" t="n">
         <v>72.94</v>
@@ -17528,7 +17528,7 @@
         <v>3.78</v>
       </c>
       <c r="I226" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J226" t="n">
         <v>74.17</v>
@@ -17603,7 +17603,7 @@
         <v>6.63</v>
       </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J227" t="n">
         <v>75.56999999999999</v>
@@ -17678,7 +17678,7 @@
         <v>5.84</v>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>77.23</v>
@@ -17753,7 +17753,7 @@
         <v>3.3</v>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J229" t="n">
         <v>78.75</v>
@@ -17828,7 +17828,7 @@
         <v>3.95</v>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>80.73</v>
@@ -17903,7 +17903,7 @@
         <v>-0.03</v>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J231" t="n">
         <v>82.56</v>
@@ -17978,7 +17978,7 @@
         <v>-28.54</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>83.11</v>
@@ -18057,7 +18057,7 @@
         <v>-3.98</v>
       </c>
       <c r="I233" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J233" t="n">
         <v>83.45</v>
@@ -18132,7 +18132,7 @@
         <v>6.24</v>
       </c>
       <c r="I234" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J234" t="n">
         <v>83.84</v>
@@ -18207,7 +18207,7 @@
         <v>2.88</v>
       </c>
       <c r="I235" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>84.11</v>
@@ -18282,7 +18282,7 @@
         <v>-15.77</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>83.90000000000001</v>
@@ -18357,7 +18357,7 @@
         <v>5.25</v>
       </c>
       <c r="I237" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J237" t="n">
         <v>83.92</v>
@@ -18432,7 +18432,7 @@
         <v>8.33</v>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>84.11</v>
@@ -18507,7 +18507,7 @@
         <v>-3.46</v>
       </c>
       <c r="I239" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J239" t="n">
         <v>83.92</v>
@@ -18582,7 +18582,7 @@
         <v>4.29</v>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>83.81999999999999</v>
@@ -18657,7 +18657,7 @@
         <v>-11.53</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>82.97</v>
@@ -18732,7 +18732,7 @@
         <v>2.94</v>
       </c>
       <c r="I242" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J242" t="n">
         <v>82.29000000000001</v>
@@ -18807,7 +18807,7 @@
         <v>-4.8</v>
       </c>
       <c r="I243" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J243" t="n">
         <v>81.56</v>
@@ -18886,7 +18886,7 @@
         <v>5.6</v>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J244" t="n">
         <v>80.8</v>
@@ -18961,7 +18961,7 @@
         <v>1.31</v>
       </c>
       <c r="I245" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J245" t="n">
         <v>80.15000000000001</v>
@@ -19036,7 +19036,7 @@
         <v>7.9</v>
       </c>
       <c r="I246" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>79.62</v>
@@ -19111,7 +19111,7 @@
         <v>5.16</v>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>79.01000000000001</v>
@@ -19186,7 +19186,7 @@
         <v>-1.85</v>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J248" t="n">
         <v>78.04000000000001</v>
@@ -19261,7 +19261,7 @@
         <v>1.21</v>
       </c>
       <c r="I249" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J249" t="n">
         <v>76.97</v>
@@ -19336,7 +19336,7 @@
         <v>0.51</v>
       </c>
       <c r="I250" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J250" t="n">
         <v>75.70999999999999</v>
@@ -19411,7 +19411,7 @@
         <v>5.64</v>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J251" t="n">
         <v>74.68000000000001</v>
@@ -19486,7 +19486,7 @@
         <v>-4.02</v>
       </c>
       <c r="I252" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J252" t="n">
         <v>74.98999999999999</v>
@@ -19561,7 +19561,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>75.09999999999999</v>
@@ -19640,7 +19640,7 @@
         <v>0.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J254" t="n">
         <v>75.02</v>
@@ -19715,7 +19715,7 @@
         <v>-1.42</v>
       </c>
       <c r="I255" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J255" t="n">
         <v>74.77</v>
@@ -19794,7 +19794,7 @@
         <v>2.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J256" t="n">
         <v>75.23</v>
@@ -19873,7 +19873,7 @@
         <v>3.06</v>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J257" t="n">
         <v>75.64</v>
@@ -19948,7 +19948,7 @@
         <v>2.34</v>
       </c>
       <c r="I258" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J258" t="n">
         <v>75.84</v>
@@ -20023,7 +20023,7 @@
         <v>-2.72</v>
       </c>
       <c r="I259" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J259" t="n">
         <v>76.06</v>
@@ -20098,7 +20098,7 @@
         <v>-1.84</v>
       </c>
       <c r="I260" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J260" t="n">
         <v>76.06</v>
@@ -20167,7 +20167,7 @@
         <v>-4.96</v>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J261" t="n">
         <v>76.31</v>
@@ -20250,7 +20250,7 @@
         <v>0.73</v>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J262" t="n">
         <v>76.48</v>
@@ -20325,7 +20325,7 @@
         <v>-2.13</v>
       </c>
       <c r="I263" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>76.75</v>
@@ -20400,7 +20400,7 @@
         <v>-4.13</v>
       </c>
       <c r="I264" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J264" t="n">
         <v>76.68000000000001</v>
@@ -20475,7 +20475,7 @@
         <v>-4.4</v>
       </c>
       <c r="I265" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J265" t="n">
         <v>76.41</v>
@@ -20550,7 +20550,7 @@
         <v>-6.33</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>75.66</v>
@@ -20633,7 +20633,7 @@
         <v>1.54</v>
       </c>
       <c r="I267" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J267" t="n">
         <v>74.75</v>
@@ -20708,7 +20708,7 @@
         <v>0.77</v>
       </c>
       <c r="I268" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J268" t="n">
         <v>73.95</v>
@@ -20783,7 +20783,7 @@
         <v>3.59</v>
       </c>
       <c r="I269" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J269" t="n">
         <v>73.2</v>
@@ -20858,7 +20858,7 @@
         <v>-6.81</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>72.22</v>
@@ -20937,7 +20937,7 @@
         <v>4.39</v>
       </c>
       <c r="I271" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J271" t="n">
         <v>71.14</v>
@@ -21016,7 +21016,7 @@
         <v>0.13</v>
       </c>
       <c r="I272" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J272" t="n">
         <v>70.23999999999999</v>
@@ -21091,7 +21091,7 @@
         <v>7.27</v>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J273" t="n">
         <v>69.91</v>
@@ -21166,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J274" t="n">
         <v>69.55</v>
@@ -21241,7 +21241,7 @@
         <v>-3.45</v>
       </c>
       <c r="I275" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J275" t="n">
         <v>69.13</v>
@@ -21316,7 +21316,7 @@
         <v>0.46</v>
       </c>
       <c r="I276" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J276" t="n">
         <v>68.64</v>
@@ -21391,7 +21391,7 @@
         <v>-0.23</v>
       </c>
       <c r="I277" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J277" t="n">
         <v>68.02</v>
@@ -21470,7 +21470,7 @@
         <v>2.32</v>
       </c>
       <c r="I278" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J278" t="n">
         <v>67.39</v>
@@ -21545,7 +21545,7 @@
         <v>1.36</v>
       </c>
       <c r="I279" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J279" t="n">
         <v>66.91</v>
@@ -21620,7 +21620,7 @@
         <v>1.01</v>
       </c>
       <c r="I280" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J280" t="n">
         <v>66.54000000000001</v>
@@ -21695,7 +21695,7 @@
         <v>-1.16</v>
       </c>
       <c r="I281" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J281" t="n">
         <v>66.31999999999999</v>
@@ -21770,7 +21770,7 @@
         <v>5.51</v>
       </c>
       <c r="I282" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J282" t="n">
         <v>66.26000000000001</v>
@@ -21845,7 +21845,7 @@
         <v>-0.28</v>
       </c>
       <c r="I283" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J283" t="n">
         <v>66.27</v>
@@ -21920,7 +21920,7 @@
         <v>-0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J284" t="n">
         <v>66.40000000000001</v>
@@ -21995,7 +21995,7 @@
         <v>3.35</v>
       </c>
       <c r="I285" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J285" t="n">
         <v>66.8</v>
@@ -22070,7 +22070,7 @@
         <v>-2.01</v>
       </c>
       <c r="I286" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J286" t="n">
         <v>67.33</v>
@@ -22145,7 +22145,7 @@
         <v>-5.07</v>
       </c>
       <c r="I287" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J287" t="n">
         <v>67.63</v>
@@ -22220,7 +22220,7 @@
         <v>2.74</v>
       </c>
       <c r="I288" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J288" t="n">
         <v>68</v>
@@ -22295,7 +22295,7 @@
         <v>-2.83</v>
       </c>
       <c r="I289" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J289" t="n">
         <v>68.16</v>
@@ -22370,7 +22370,7 @@
         <v>0.6</v>
       </c>
       <c r="I290" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J290" t="n">
         <v>68.56</v>
@@ -22445,7 +22445,7 @@
         <v>-0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J291" t="n">
         <v>68.8</v>
@@ -22524,7 +22524,7 @@
         <v>-3.12</v>
       </c>
       <c r="I292" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J292" t="n">
         <v>68.94</v>
@@ -22603,7 +22603,7 @@
         <v>-2.05</v>
       </c>
       <c r="I293" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J293" t="n">
         <v>68.77</v>
@@ -22678,7 +22678,7 @@
         <v>2.81</v>
       </c>
       <c r="I294" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J294" t="n">
         <v>68.7</v>
@@ -22753,7 +22753,7 @@
         <v>2.45</v>
       </c>
       <c r="I295" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J295" t="n">
         <v>68.81999999999999</v>
@@ -22828,7 +22828,7 @@
         <v>-3.44</v>
       </c>
       <c r="I296" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J296" t="n">
         <v>68.81999999999999</v>
@@ -22907,7 +22907,7 @@
         <v>-0.05</v>
       </c>
       <c r="I297" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J297" t="n">
         <v>68.81999999999999</v>
@@ -22982,7 +22982,7 @@
         <v>6.4</v>
       </c>
       <c r="I298" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J298" t="n">
         <v>68.95</v>
@@ -23057,7 +23057,7 @@
         <v>2.1</v>
       </c>
       <c r="I299" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J299" t="n">
         <v>69.11</v>
@@ -23132,7 +23132,7 @@
         <v>1.97</v>
       </c>
       <c r="I300" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J300" t="n">
         <v>69.31</v>
@@ -23207,7 +23207,7 @@
         <v>6.83</v>
       </c>
       <c r="I301" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J301" t="n">
         <v>69.79000000000001</v>
@@ -23282,7 +23282,7 @@
         <v>0.71</v>
       </c>
       <c r="I302" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J302" t="n">
         <v>70.12</v>
@@ -23357,7 +23357,7 @@
         <v>1.02</v>
       </c>
       <c r="I303" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J303" t="n">
         <v>70.48999999999999</v>
@@ -23432,7 +23432,7 @@
         <v>-4.84</v>
       </c>
       <c r="I304" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J304" t="n">
         <v>70.70999999999999</v>
@@ -23507,7 +23507,7 @@
         <v>-8.57</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>70.48</v>
@@ -23586,7 +23586,7 @@
         <v>1.3</v>
       </c>
       <c r="I306" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J306" t="n">
         <v>70.37</v>
@@ -23661,7 +23661,7 @@
         <v>-4.35</v>
       </c>
       <c r="I307" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J307" t="n">
         <v>70.29000000000001</v>
@@ -23736,7 +23736,7 @@
         <v>2.74</v>
       </c>
       <c r="I308" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J308" t="n">
         <v>70.20999999999999</v>
@@ -23811,7 +23811,7 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J309" t="n">
         <v>70.26000000000001</v>
@@ -23886,7 +23886,7 @@
         <v>-1.57</v>
       </c>
       <c r="I310" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J310" t="n">
         <v>70.23999999999999</v>
@@ -23961,7 +23961,7 @@
         <v>1.99</v>
       </c>
       <c r="I311" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J311" t="n">
         <v>70.31</v>
@@ -24036,7 +24036,7 @@
         <v>-3.18</v>
       </c>
       <c r="I312" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J312" t="n">
         <v>70.37</v>
@@ -24111,7 +24111,7 @@
         <v>1.27</v>
       </c>
       <c r="I313" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J313" t="n">
         <v>70.55</v>
@@ -24186,7 +24186,7 @@
         <v>-0.04</v>
       </c>
       <c r="I314" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J314" t="n">
         <v>70.63</v>
@@ -24261,7 +24261,7 @@
         <v>-0.97</v>
       </c>
       <c r="I315" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J315" t="n">
         <v>70.59999999999999</v>
@@ -24336,7 +24336,7 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J316" t="n">
         <v>70.7</v>
@@ -24411,7 +24411,7 @@
         <v>-2.62</v>
       </c>
       <c r="I317" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J317" t="n">
         <v>70.72</v>
@@ -24486,7 +24486,7 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J318" t="n">
         <v>70.56</v>
@@ -24561,7 +24561,7 @@
         <v>-8.08</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>70.06</v>
@@ -24636,7 +24636,7 @@
         <v>0.02</v>
       </c>
       <c r="I320" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J320" t="n">
         <v>69.48999999999999</v>
@@ -24711,7 +24711,7 @@
         <v>-4.17</v>
       </c>
       <c r="I321" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J321" t="n">
         <v>68.54000000000001</v>
@@ -24790,7 +24790,7 @@
         <v>-2.29</v>
       </c>
       <c r="I322" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J322" t="n">
         <v>67.48999999999999</v>
@@ -24869,7 +24869,7 @@
         <v>5.48</v>
       </c>
       <c r="I323" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J323" t="n">
         <v>66.56999999999999</v>
@@ -24944,7 +24944,7 @@
         <v>0.77</v>
       </c>
       <c r="I324" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J324" t="n">
         <v>65.86</v>
@@ -25019,7 +25019,7 @@
         <v>3.56</v>
       </c>
       <c r="I325" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J325" t="n">
         <v>65.58</v>
@@ -25094,7 +25094,7 @@
         <v>-0.13</v>
       </c>
       <c r="I326" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J326" t="n">
         <v>65.25</v>
@@ -25169,7 +25169,7 @@
         <v>-4.39</v>
       </c>
       <c r="I327" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J327" t="n">
         <v>64.94</v>
@@ -25244,7 +25244,7 @@
         <v>-1.81</v>
       </c>
       <c r="I328" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J328" t="n">
         <v>64.47</v>
@@ -25319,7 +25319,7 @@
         <v>-1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J329" t="n">
         <v>63.95</v>
@@ -25394,7 +25394,7 @@
         <v>-5.4</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>63.32</v>
@@ -25473,7 +25473,7 @@
         <v>-7.09</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>62.42</v>
@@ -25552,7 +25552,7 @@
         <v>1.12</v>
       </c>
       <c r="I332" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J332" t="n">
         <v>61.66</v>
@@ -25631,7 +25631,7 @@
         <v>1.76</v>
       </c>
       <c r="I333" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J333" t="n">
         <v>60.91</v>
@@ -25706,7 +25706,7 @@
         <v>-1.13</v>
       </c>
       <c r="I334" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J334" t="n">
         <v>60.12</v>
@@ -25781,7 +25781,7 @@
         <v>1.5</v>
       </c>
       <c r="I335" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J335" t="n">
         <v>59.42</v>
@@ -25856,7 +25856,7 @@
         <v>0.21</v>
       </c>
       <c r="I336" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J336" t="n">
         <v>58.69</v>
@@ -25931,7 +25931,7 @@
         <v>2.69</v>
       </c>
       <c r="I337" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J337" t="n">
         <v>58.14</v>
@@ -26006,7 +26006,7 @@
         <v>1.98</v>
       </c>
       <c r="I338" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J338" t="n">
         <v>57.59</v>
@@ -26081,7 +26081,7 @@
         <v>-2.94</v>
       </c>
       <c r="I339" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J339" t="n">
         <v>57.24</v>
@@ -26160,7 +26160,7 @@
         <v>-2.99</v>
       </c>
       <c r="I340" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J340" t="n">
         <v>56.8</v>
@@ -26239,7 +26239,7 @@
         <v>2.48</v>
       </c>
       <c r="I341" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J341" t="n">
         <v>56.55</v>
@@ -26314,7 +26314,7 @@
         <v>-0.35</v>
       </c>
       <c r="I342" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J342" t="n">
         <v>56.37</v>
@@ -26389,7 +26389,7 @@
         <v>-3.32</v>
       </c>
       <c r="I343" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J343" t="n">
         <v>55.94</v>
@@ -26464,7 +26464,7 @@
         <v>1.94</v>
       </c>
       <c r="I344" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J344" t="n">
         <v>55.53</v>
@@ -26539,7 +26539,7 @@
         <v>-1.81</v>
       </c>
       <c r="I345" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J345" t="n">
         <v>54.97</v>
@@ -26614,7 +26614,7 @@
         <v>-3.49</v>
       </c>
       <c r="I346" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J346" t="n">
         <v>54.32</v>
@@ -26689,7 +26689,7 @@
         <v>0.77</v>
       </c>
       <c r="I347" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J347" t="n">
         <v>53.83</v>
@@ -26764,7 +26764,7 @@
         <v>0.39</v>
       </c>
       <c r="I348" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J348" t="n">
         <v>53.4</v>
@@ -26839,7 +26839,7 @@
         <v>4.12</v>
       </c>
       <c r="I349" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J349" t="n">
         <v>53.11</v>
@@ -26914,7 +26914,7 @@
         <v>1.58</v>
       </c>
       <c r="I350" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J350" t="n">
         <v>53.02</v>
@@ -26989,7 +26989,7 @@
         <v>-3.45</v>
       </c>
       <c r="I351" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J351" t="n">
         <v>53.03</v>
@@ -27068,7 +27068,7 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J352" t="n">
         <v>53.04</v>
@@ -27143,7 +27143,7 @@
         <v>0.65</v>
       </c>
       <c r="I353" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J353" t="n">
         <v>53.03</v>
@@ -27218,7 +27218,7 @@
         <v>-2.32</v>
       </c>
       <c r="I354" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J354" t="n">
         <v>52.98</v>
@@ -27293,7 +27293,7 @@
         <v>0.14</v>
       </c>
       <c r="I355" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J355" t="n">
         <v>52.89</v>
@@ -27368,7 +27368,7 @@
         <v>3.34</v>
       </c>
       <c r="I356" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J356" t="n">
         <v>52.89</v>
@@ -27443,7 +27443,7 @@
         <v>-2.13</v>
       </c>
       <c r="I357" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J357" t="n">
         <v>52.75</v>
@@ -27522,7 +27522,7 @@
         <v>0.19</v>
       </c>
       <c r="I358" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J358" t="n">
         <v>52.57</v>
@@ -27597,7 +27597,7 @@
         <v>2.63</v>
       </c>
       <c r="I359" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J359" t="n">
         <v>52.54</v>
@@ -27672,7 +27672,7 @@
         <v>4.14</v>
       </c>
       <c r="I360" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J360" t="n">
         <v>52.7</v>
@@ -27747,7 +27747,7 @@
         <v>-0.39</v>
       </c>
       <c r="I361" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J361" t="n">
         <v>52.79</v>
@@ -27822,7 +27822,7 @@
         <v>2.95</v>
       </c>
       <c r="I362" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J362" t="n">
         <v>52.97</v>
@@ -27897,7 +27897,7 @@
         <v>3.32</v>
       </c>
       <c r="I363" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J363" t="n">
         <v>53.33</v>
@@ -27972,7 +27972,7 @@
         <v>-1.45</v>
       </c>
       <c r="I364" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J364" t="n">
         <v>53.6</v>
@@ -28047,7 +28047,7 @@
         <v>0.87</v>
       </c>
       <c r="I365" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J365" t="n">
         <v>53.94</v>
@@ -28122,7 +28122,7 @@
         <v>-1.52</v>
       </c>
       <c r="I366" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J366" t="n">
         <v>54.33</v>
@@ -28197,7 +28197,7 @@
         <v>0.55</v>
       </c>
       <c r="I367" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J367" t="n">
         <v>54.71</v>
@@ -28272,7 +28272,7 @@
         <v>1.86</v>
       </c>
       <c r="I368" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J368" t="n">
         <v>55.14</v>
@@ -28347,7 +28347,7 @@
         <v>-3.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J369" t="n">
         <v>55.36</v>
@@ -28426,7 +28426,7 @@
         <v>4.47</v>
       </c>
       <c r="I370" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J370" t="n">
         <v>55.67</v>
@@ -28501,7 +28501,7 @@
         <v>2.75</v>
       </c>
       <c r="I371" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J371" t="n">
         <v>56.15</v>
@@ -28576,7 +28576,7 @@
         <v>1.72</v>
       </c>
       <c r="I372" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J372" t="n">
         <v>56.65</v>
@@ -28651,7 +28651,7 @@
         <v>-0.83</v>
       </c>
       <c r="I373" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J373" t="n">
         <v>57.12</v>
@@ -28726,7 +28726,7 @@
         <v>0.19</v>
       </c>
       <c r="I374" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J374" t="n">
         <v>57.65</v>
@@ -28801,7 +28801,7 @@
         <v>-1.17</v>
       </c>
       <c r="I375" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J375" t="n">
         <v>58.14</v>
@@ -28876,7 +28876,7 @@
         <v>1.92</v>
       </c>
       <c r="I376" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J376" t="n">
         <v>58.6</v>
@@ -28951,7 +28951,7 @@
         <v>-4.38</v>
       </c>
       <c r="I377" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J377" t="n">
         <v>58.98</v>
@@ -29026,7 +29026,7 @@
         <v>0.18</v>
       </c>
       <c r="I378" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J378" t="n">
         <v>59.37</v>
@@ -29101,7 +29101,7 @@
         <v>-3.68</v>
       </c>
       <c r="I379" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J379" t="n">
         <v>59.57</v>
@@ -29180,7 +29180,7 @@
         <v>1.99</v>
       </c>
       <c r="I380" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J380" t="n">
         <v>59.72</v>
@@ -29255,7 +29255,7 @@
         <v>2.51</v>
       </c>
       <c r="I381" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J381" t="n">
         <v>59.96</v>
@@ -29330,7 +29330,7 @@
         <v>-1.21</v>
       </c>
       <c r="I382" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J382" t="n">
         <v>60.07</v>
@@ -29409,7 +29409,7 @@
         <v>-0.75</v>
       </c>
       <c r="I383" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J383" t="n">
         <v>60.07</v>
@@ -29484,7 +29484,7 @@
         <v>2.27</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J384" t="n">
         <v>60.18</v>
@@ -29559,7 +29559,7 @@
         <v>-5.3</v>
       </c>
       <c r="I385" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J385" s="4" t="n">
         <v>60.1</v>
@@ -29638,7 +29638,7 @@
         <v>1.08</v>
       </c>
       <c r="I386" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J386" t="n">
         <v>60.1</v>
@@ -29713,7 +29713,7 @@
         <v>-2.2</v>
       </c>
       <c r="I387" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J387" t="n">
         <v>60.02</v>
@@ -29788,7 +29788,7 @@
         <v>1.21</v>
       </c>
       <c r="I388" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J388" t="n">
         <v>59.92</v>
@@ -29863,7 +29863,7 @@
         <v>-0.83</v>
       </c>
       <c r="I389" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J389" t="n">
         <v>59.9</v>
@@ -29938,7 +29938,7 @@
         <v>3.37</v>
       </c>
       <c r="I390" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J390" t="n">
         <v>59.84</v>
@@ -30013,7 +30013,7 @@
         <v>1.63</v>
       </c>
       <c r="I391" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J391" t="n">
         <v>59.76</v>
@@ -30088,7 +30088,7 @@
         <v>-0.5</v>
       </c>
       <c r="I392" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J392" t="n">
         <v>59.6</v>
@@ -30163,7 +30163,7 @@
         <v>1.84</v>
       </c>
       <c r="I393" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J393" t="n">
         <v>59.53</v>
@@ -30238,7 +30238,7 @@
         <v>-4.23</v>
       </c>
       <c r="I394" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J394" t="n">
         <v>59.32</v>
@@ -30317,7 +30317,7 @@
         <v>-0.93</v>
       </c>
       <c r="I395" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J395" t="n">
         <v>59.12</v>
@@ -30392,7 +30392,7 @@
         <v>0.9</v>
       </c>
       <c r="I396" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J396" t="n">
         <v>58.89</v>
@@ -30467,7 +30467,7 @@
         <v>-5.49</v>
       </c>
       <c r="I397" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>58.64</v>
@@ -30546,7 +30546,7 @@
         <v>0.96</v>
       </c>
       <c r="I398" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J398" t="n">
         <v>58.41</v>
@@ -30621,7 +30621,7 @@
         <v>-1.75</v>
       </c>
       <c r="I399" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J399" t="n">
         <v>58.23</v>
@@ -30696,7 +30696,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I400" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J400" t="n">
         <v>58.03</v>
@@ -30771,7 +30771,7 @@
         <v>-0.51</v>
       </c>
       <c r="I401" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J401" t="n">
         <v>57.74</v>
@@ -30846,7 +30846,7 @@
         <v>0.71</v>
       </c>
       <c r="I402" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J402" t="n">
         <v>57.51</v>
@@ -30921,7 +30921,7 @@
         <v>0.58</v>
       </c>
       <c r="I403" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J403" t="n">
         <v>57.31</v>
@@ -30996,7 +30996,7 @@
         <v>-2.94</v>
       </c>
       <c r="I404" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J404" t="n">
         <v>56.97</v>
@@ -31071,7 +31071,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I405" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J405" t="n">
         <v>56.76</v>
@@ -31150,7 +31150,7 @@
         <v>2.49</v>
       </c>
       <c r="I406" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J406" t="n">
         <v>56.6</v>
@@ -31225,7 +31225,7 @@
         <v>-0.78</v>
       </c>
       <c r="I407" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J407" t="n">
         <v>56.47</v>
@@ -31304,7 +31304,7 @@
         <v>-1.58</v>
       </c>
       <c r="I408" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J408" t="n">
         <v>56.27</v>
@@ -31379,7 +31379,7 @@
         <v>-6.11</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>55.93</v>
@@ -31458,7 +31458,7 @@
         <v>3.39</v>
       </c>
       <c r="I410" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J410" t="n">
         <v>55.58</v>
@@ -31533,7 +31533,7 @@
         <v>-0.79</v>
       </c>
       <c r="I411" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J411" t="n">
         <v>55.15</v>
@@ -31608,7 +31608,7 @@
         <v>0.06</v>
       </c>
       <c r="I412" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J412" t="n">
         <v>54.75</v>
@@ -31683,7 +31683,7 @@
         <v>1.13</v>
       </c>
       <c r="I413" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J413" t="n">
         <v>54.32</v>
@@ -31758,7 +31758,7 @@
         <v>0.27</v>
       </c>
       <c r="I414" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J414" t="n">
         <v>54.02</v>
@@ -31804,77 +31804,61 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" s="4" t="n">
-        <v>50.26</v>
-      </c>
-      <c r="D415" s="4" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="E415" s="4" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="F415" s="4" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="G415" s="4" t="n">
-        <v>24604800</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="I415" s="4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" s="4" t="n">
-        <v>53.61</v>
-      </c>
-      <c r="K415" s="4" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="L415" s="4" t="n">
-        <v>58.96</v>
-      </c>
-      <c r="M415" s="4" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="N415" s="6" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="O415" s="4" t="n">
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>24619695</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="2" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="O415" t="n">
         <v>20</v>
       </c>
-      <c r="P415" s="4" t="inlineStr">
+      <c r="P415" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" s="4" t="inlineStr">
+      <c r="Q415" t="inlineStr">
         <is>
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" s="4" t="inlineStr"/>
-      <c r="S415" s="4" t="n">
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="6" t="n">
+      <c r="T415" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="6" t="n">
+      <c r="U415" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="6" t="n">
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -608,7 +608,7 @@
         <v>1.55</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>29.19</v>
@@ -683,7 +683,7 @@
         <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>29.21</v>
@@ -758,7 +758,7 @@
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>29.24</v>
@@ -833,7 +833,7 @@
         <v>-0.27</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>29.26</v>
@@ -908,7 +908,7 @@
         <v>-0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>29.27</v>
@@ -983,7 +983,7 @@
         <v>-1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>29.27</v>
@@ -1066,7 +1066,7 @@
         <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>29.31</v>
@@ -1145,7 +1145,7 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>29.37</v>
@@ -1220,7 +1220,7 @@
         <v>1.72</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>29.44</v>
@@ -1295,7 +1295,7 @@
         <v>-0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>29.5</v>
@@ -1370,7 +1370,7 @@
         <v>0.33</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>29.58</v>
@@ -1445,7 +1445,7 @@
         <v>0.13</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>29.62</v>
@@ -1520,7 +1520,7 @@
         <v>-0.32</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>29.67</v>
@@ -1595,7 +1595,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>29.7</v>
@@ -1670,7 +1670,7 @@
         <v>-1.57</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>29.72</v>
@@ -1745,7 +1745,7 @@
         <v>-0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>29.75</v>
@@ -1820,7 +1820,7 @@
         <v>2.07</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
         <v>29.83</v>
@@ -1895,7 +1895,7 @@
         <v>-0.16</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>29.91</v>
@@ -1970,7 +1970,7 @@
         <v>2.59</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>30.06</v>
@@ -2045,7 +2045,7 @@
         <v>-1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>30.19</v>
@@ -2120,7 +2120,7 @@
         <v>-0.03</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
         <v>30.3</v>
@@ -2195,7 +2195,7 @@
         <v>-1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>30.39</v>
@@ -2270,7 +2270,7 @@
         <v>0.42</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
         <v>30.44</v>
@@ -2345,7 +2345,7 @@
         <v>-6.08</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>30.4</v>
@@ -2428,7 +2428,7 @@
         <v>-6.27</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>30.27</v>
@@ -2511,7 +2511,7 @@
         <v>0.22</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>30.17</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>30.03</v>
@@ -2677,7 +2677,7 @@
         <v>3.39</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>29.92</v>
@@ -2756,7 +2756,7 @@
         <v>0.78</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>29.8</v>
@@ -2835,7 +2835,7 @@
         <v>3.22</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>29.72</v>
@@ -2914,7 +2914,7 @@
         <v>0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>29.65</v>
@@ -2989,7 +2989,7 @@
         <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
         <v>29.58</v>
@@ -3064,7 +3064,7 @@
         <v>1.19</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>29.53</v>
@@ -3143,7 +3143,7 @@
         <v>-0.71</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>29.48</v>
@@ -3222,7 +3222,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J36" t="n">
         <v>29.47</v>
@@ -3297,7 +3297,7 @@
         <v>-0.97</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>29.45</v>
@@ -3372,7 +3372,7 @@
         <v>3.59</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>29.45</v>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>29.45</v>
@@ -3526,7 +3526,7 @@
         <v>-1.67</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>29.39</v>
@@ -3601,7 +3601,7 @@
         <v>0.47</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>29.35</v>
@@ -3676,7 +3676,7 @@
         <v>-1.19</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>29.29</v>
@@ -3751,7 +3751,7 @@
         <v>-0.77</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>29.24</v>
@@ -3830,7 +3830,7 @@
         <v>-0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>29.17</v>
@@ -3905,7 +3905,7 @@
         <v>-0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>29.18</v>
@@ -3984,7 +3984,7 @@
         <v>1.24</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>29.3</v>
@@ -4059,7 +4059,7 @@
         <v>2.51</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>29.45</v>
@@ -4134,7 +4134,7 @@
         <v>-2.42</v>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>29.57</v>
@@ -4213,7 +4213,7 @@
         <v>-0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>29.64</v>
@@ -4288,7 +4288,7 @@
         <v>1.15</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>29.72</v>
@@ -4363,7 +4363,7 @@
         <v>-0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>29.74</v>
@@ -4442,7 +4442,7 @@
         <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>29.77</v>
@@ -4517,7 +4517,7 @@
         <v>-2.27</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>29.76</v>
@@ -4596,7 +4596,7 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>29.75</v>
@@ -4671,7 +4671,7 @@
         <v>-1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>29.74</v>
@@ -4746,7 +4746,7 @@
         <v>0.41</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>29.72</v>
@@ -4821,7 +4821,7 @@
         <v>2.41</v>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>29.75</v>
@@ -4896,7 +4896,7 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>29.75</v>
@@ -4971,7 +4971,7 @@
         <v>-1.57</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>29.72</v>
@@ -5046,7 +5046,7 @@
         <v>1.4</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>29.74</v>
@@ -5121,7 +5121,7 @@
         <v>-0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>29.74</v>
@@ -5196,7 +5196,7 @@
         <v>-0.83</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>29.75</v>
@@ -5271,7 +5271,7 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>29.79</v>
@@ -5346,7 +5346,7 @@
         <v>-0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>29.82</v>
@@ -5421,7 +5421,7 @@
         <v>5.3</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>29.94</v>
@@ -5496,7 +5496,7 @@
         <v>-0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>30.04</v>
@@ -5571,7 +5571,7 @@
         <v>-0.32</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>30.09</v>
@@ -5646,7 +5646,7 @@
         <v>3.54</v>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>30.24</v>
@@ -5721,7 +5721,7 @@
         <v>0.74</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>30.4</v>
@@ -5796,7 +5796,7 @@
         <v>2.14</v>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>30.58</v>
@@ -5871,7 +5871,7 @@
         <v>-0.48</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>30.76</v>
@@ -5946,7 +5946,7 @@
         <v>-0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>30.91</v>
@@ -6021,7 +6021,7 @@
         <v>0.33</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>31.1</v>
@@ -6096,7 +6096,7 @@
         <v>-0.27</v>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>31.27</v>
@@ -6171,7 +6171,7 @@
         <v>0.18</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>31.46</v>
@@ -6246,7 +6246,7 @@
         <v>2.15</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>31.68</v>
@@ -6321,7 +6321,7 @@
         <v>-1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>31.83</v>
@@ -6396,7 +6396,7 @@
         <v>-1.65</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>31.94</v>
@@ -6471,7 +6471,7 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>32.09</v>
@@ -6546,7 +6546,7 @@
         <v>-1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>32.2</v>
@@ -6621,7 +6621,7 @@
         <v>1.23</v>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>32.34</v>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>32.5</v>
@@ -6771,7 +6771,7 @@
         <v>-2.16</v>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>32.62</v>
@@ -6846,7 +6846,7 @@
         <v>0.58</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>32.76</v>
@@ -6921,7 +6921,7 @@
         <v>-0.24</v>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>32.82</v>
@@ -7000,7 +7000,7 @@
         <v>1.56</v>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J86" t="n">
         <v>32.91</v>
@@ -7075,7 +7075,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>33.02</v>
@@ -7150,7 +7150,7 @@
         <v>-0.24</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>33.07</v>
@@ -7225,7 +7225,7 @@
         <v>-0.42</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J89" t="n">
         <v>33.1</v>
@@ -7300,7 +7300,7 @@
         <v>-0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>33.08</v>
@@ -7379,7 +7379,7 @@
         <v>2.27</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>33.1</v>
@@ -7454,7 +7454,7 @@
         <v>3.79</v>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>33.21</v>
@@ -7529,7 +7529,7 @@
         <v>-1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>33.28</v>
@@ -7604,7 +7604,7 @@
         <v>-1.07</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>33.35</v>
@@ -7679,7 +7679,7 @@
         <v>0.44</v>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>33.42</v>
@@ -7754,7 +7754,7 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>33.46</v>
@@ -7829,7 +7829,7 @@
         <v>-0.12</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>33.53</v>
@@ -7904,7 +7904,7 @@
         <v>2.14</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>33.66</v>
@@ -7979,7 +7979,7 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>33.8</v>
@@ -8054,7 +8054,7 @@
         <v>-0.08</v>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>33.95</v>
@@ -8129,7 +8129,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>34.08</v>
@@ -8204,7 +8204,7 @@
         <v>-2.34</v>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>34.14</v>
@@ -8279,7 +8279,7 @@
         <v>-0.06</v>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>34.24</v>
@@ -8354,7 +8354,7 @@
         <v>0.06</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>34.34</v>
@@ -8429,7 +8429,7 @@
         <v>-3.32</v>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>34.38</v>
@@ -8508,7 +8508,7 @@
         <v>-0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>34.38</v>
@@ -8583,7 +8583,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>34.38</v>
@@ -8658,7 +8658,7 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>34.41</v>
@@ -8733,7 +8733,7 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J109" t="n">
         <v>34.46</v>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>34.53</v>
@@ -8883,7 +8883,7 @@
         <v>1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>34.58</v>
@@ -8958,7 +8958,7 @@
         <v>0.35</v>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>34.58</v>
@@ -9033,7 +9033,7 @@
         <v>-2.01</v>
       </c>
       <c r="I113" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J113" t="n">
         <v>34.55</v>
@@ -9112,7 +9112,7 @@
         <v>0.67</v>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>34.56</v>
@@ -9187,7 +9187,7 @@
         <v>1.71</v>
       </c>
       <c r="I115" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>34.59</v>
@@ -9262,7 +9262,7 @@
         <v>-1.43</v>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>34.58</v>
@@ -9341,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>34.58</v>
@@ -9416,7 +9416,7 @@
         <v>0.14</v>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J118" t="n">
         <v>34.54</v>
@@ -9491,7 +9491,7 @@
         <v>-1.97</v>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>34.44</v>
@@ -9570,7 +9570,7 @@
         <v>1.65</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>34.38</v>
@@ -9645,7 +9645,7 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>34.34</v>
@@ -9720,7 +9720,7 @@
         <v>2.11</v>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>34.37</v>
@@ -9795,7 +9795,7 @@
         <v>-0.91</v>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>34.39</v>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J124" t="n">
         <v>34.41</v>
@@ -9945,7 +9945,7 @@
         <v>-0.09</v>
       </c>
       <c r="I125" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>34.48</v>
@@ -10020,7 +10020,7 @@
         <v>1.51</v>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>34.59</v>
@@ -10095,7 +10095,7 @@
         <v>1.89</v>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>34.72</v>
@@ -10170,7 +10170,7 @@
         <v>2.65</v>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>34.88</v>
@@ -10245,7 +10245,7 @@
         <v>0.51</v>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>35.03</v>
@@ -10320,7 +10320,7 @@
         <v>-1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>35.16</v>
@@ -10395,7 +10395,7 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J131" t="n">
         <v>35.28</v>
@@ -10470,7 +10470,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>35.41</v>
@@ -10545,7 +10545,7 @@
         <v>-0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>35.56</v>
@@ -10620,7 +10620,7 @@
         <v>0.62</v>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>35.71</v>
@@ -10695,7 +10695,7 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J135" t="n">
         <v>35.85</v>
@@ -10770,7 +10770,7 @@
         <v>1.46</v>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>36.04</v>
@@ -10845,7 +10845,7 @@
         <v>1.1</v>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>36.26</v>
@@ -10920,7 +10920,7 @@
         <v>-0.41</v>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>36.46</v>
@@ -10995,7 +10995,7 @@
         <v>-2.1</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>36.66</v>
@@ -11070,7 +11070,7 @@
         <v>0.53</v>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>36.83</v>
@@ -11145,7 +11145,7 @@
         <v>2.76</v>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>37.06</v>
@@ -11220,7 +11220,7 @@
         <v>2.56</v>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>37.29</v>
@@ -11295,7 +11295,7 @@
         <v>-0.2</v>
       </c>
       <c r="I143" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J143" t="n">
         <v>37.54</v>
@@ -11370,7 +11370,7 @@
         <v>-0.35</v>
       </c>
       <c r="I144" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>37.78</v>
@@ -11445,7 +11445,7 @@
         <v>3.04</v>
       </c>
       <c r="I145" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>38.08</v>
@@ -11520,7 +11520,7 @@
         <v>2.02</v>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>38.4</v>
@@ -11595,7 +11595,7 @@
         <v>1.53</v>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>38.71</v>
@@ -11670,7 +11670,7 @@
         <v>-0.31</v>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J148" t="n">
         <v>38.97</v>
@@ -11745,7 +11745,7 @@
         <v>1.27</v>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>39.25</v>
@@ -11820,7 +11820,7 @@
         <v>-0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>39.53</v>
@@ -11895,7 +11895,7 @@
         <v>2.33</v>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>39.85</v>
@@ -11970,7 +11970,7 @@
         <v>1.24</v>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>40.17</v>
@@ -12045,7 +12045,7 @@
         <v>-1.52</v>
       </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>40.49</v>
@@ -12120,7 +12120,7 @@
         <v>2.7</v>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>40.84</v>
@@ -12195,7 +12195,7 @@
         <v>0.34</v>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>41.19</v>
@@ -12270,7 +12270,7 @@
         <v>1.61</v>
       </c>
       <c r="I156" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>41.54</v>
@@ -12345,7 +12345,7 @@
         <v>4.03</v>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>41.97</v>
@@ -12420,7 +12420,7 @@
         <v>-0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>42.38</v>
@@ -12495,7 +12495,7 @@
         <v>3.27</v>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>42.91</v>
@@ -12570,7 +12570,7 @@
         <v>1.74</v>
       </c>
       <c r="I160" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>43.46</v>
@@ -12645,7 +12645,7 @@
         <v>-4.43</v>
       </c>
       <c r="I161" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>43.86</v>
@@ -12720,7 +12720,7 @@
         <v>1.55</v>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>44.25</v>
@@ -12795,7 +12795,7 @@
         <v>-8.24</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>44.44</v>
@@ -12874,7 +12874,7 @@
         <v>0.21</v>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J164" t="n">
         <v>44.64</v>
@@ -12949,7 +12949,7 @@
         <v>0.68</v>
       </c>
       <c r="I165" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J165" t="n">
         <v>44.8</v>
@@ -13024,7 +13024,7 @@
         <v>-0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>44.9</v>
@@ -13099,7 +13099,7 @@
         <v>-3.61</v>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>44.9</v>
@@ -13174,7 +13174,7 @@
         <v>0.71</v>
       </c>
       <c r="I168" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>44.92</v>
@@ -13249,7 +13249,7 @@
         <v>1.24</v>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>44.93</v>
@@ -13324,7 +13324,7 @@
         <v>2.57</v>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>45.02</v>
@@ -13399,7 +13399,7 @@
         <v>-0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J171" t="n">
         <v>45.05</v>
@@ -13474,7 +13474,7 @@
         <v>-0.57</v>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>45.03</v>
@@ -13549,7 +13549,7 @@
         <v>-2.33</v>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>45</v>
@@ -13624,7 +13624,7 @@
         <v>2.13</v>
       </c>
       <c r="I174" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J174" t="n">
         <v>44.95</v>
@@ -13699,7 +13699,7 @@
         <v>-0.23</v>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J175" t="n">
         <v>44.9</v>
@@ -13774,7 +13774,7 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>44.82</v>
@@ -13849,7 +13849,7 @@
         <v>4.26</v>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J177" t="n">
         <v>44.75</v>
@@ -13924,7 +13924,7 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>44.73</v>
@@ -13999,7 +13999,7 @@
         <v>4.03</v>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>44.73</v>
@@ -14074,7 +14074,7 @@
         <v>-1.86</v>
       </c>
       <c r="I180" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>44.64</v>
@@ -14149,7 +14149,7 @@
         <v>-3.08</v>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>44.59</v>
@@ -14224,7 +14224,7 @@
         <v>-1.07</v>
       </c>
       <c r="I182" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J182" t="n">
         <v>44.48</v>
@@ -14299,7 +14299,7 @@
         <v>1.39</v>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>44.59</v>
@@ -14374,7 +14374,7 @@
         <v>0.76</v>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>44.72</v>
@@ -14449,7 +14449,7 @@
         <v>-1.44</v>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>44.8</v>
@@ -14528,7 +14528,7 @@
         <v>-1.05</v>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>44.87</v>
@@ -14603,7 +14603,7 @@
         <v>2.94</v>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J187" t="n">
         <v>45.08</v>
@@ -14678,7 +14678,7 @@
         <v>0.09</v>
       </c>
       <c r="I188" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>45.28</v>
@@ -14753,7 +14753,7 @@
         <v>3.71</v>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>45.54</v>
@@ -14828,7 +14828,7 @@
         <v>5.81</v>
       </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>45.88</v>
@@ -14903,7 +14903,7 @@
         <v>2.56</v>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>46.3</v>
@@ -14978,7 +14978,7 @@
         <v>1.16</v>
       </c>
       <c r="I192" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>46.77</v>
@@ -15053,7 +15053,7 @@
         <v>-0.11</v>
       </c>
       <c r="I193" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>47.29</v>
@@ -15128,7 +15128,7 @@
         <v>-2.47</v>
       </c>
       <c r="I194" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J194" t="n">
         <v>47.7</v>
@@ -15203,7 +15203,7 @@
         <v>2.3</v>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J195" t="n">
         <v>48.16</v>
@@ -15278,7 +15278,7 @@
         <v>-0.45</v>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J196" t="n">
         <v>48.6</v>
@@ -15353,7 +15353,7 @@
         <v>4.67</v>
       </c>
       <c r="I197" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>49.07</v>
@@ -15428,7 +15428,7 @@
         <v>1.63</v>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J198" t="n">
         <v>49.55</v>
@@ -15503,7 +15503,7 @@
         <v>2.76</v>
       </c>
       <c r="I199" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>50.02</v>
@@ -15578,7 +15578,7 @@
         <v>-2.64</v>
       </c>
       <c r="I200" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J200" t="n">
         <v>50.45</v>
@@ -15653,7 +15653,7 @@
         <v>3.58</v>
       </c>
       <c r="I201" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>51.06</v>
@@ -15728,7 +15728,7 @@
         <v>-0.65</v>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>51.67</v>
@@ -15803,7 +15803,7 @@
         <v>4.38</v>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>52.38</v>
@@ -15878,7 +15878,7 @@
         <v>-1.56</v>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>53.03</v>
@@ -15953,7 +15953,7 @@
         <v>2.71</v>
       </c>
       <c r="I205" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>53.78</v>
@@ -16028,7 +16028,7 @@
         <v>2.53</v>
       </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J206" t="n">
         <v>54.64</v>
@@ -16103,7 +16103,7 @@
         <v>3.79</v>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>55.55</v>
@@ -16178,7 +16178,7 @@
         <v>0.59</v>
       </c>
       <c r="I208" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J208" t="n">
         <v>56.48</v>
@@ -16253,7 +16253,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>57.62</v>
@@ -16328,7 +16328,7 @@
         <v>-7.19</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>58.36</v>
@@ -16403,7 +16403,7 @@
         <v>4.5</v>
       </c>
       <c r="I211" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>59.18</v>
@@ -16478,7 +16478,7 @@
         <v>-6.61</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>59.74</v>
@@ -16553,7 +16553,7 @@
         <v>2.06</v>
       </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>60.38</v>
@@ -16628,7 +16628,7 @@
         <v>5.06</v>
       </c>
       <c r="I214" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>61.24</v>
@@ -16703,7 +16703,7 @@
         <v>6.7</v>
       </c>
       <c r="I215" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>62.28</v>
@@ -16778,7 +16778,7 @@
         <v>-3.73</v>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>63.19</v>
@@ -16853,7 +16853,7 @@
         <v>-1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>63.92</v>
@@ -16928,7 +16928,7 @@
         <v>3.83</v>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J218" t="n">
         <v>64.73999999999999</v>
@@ -17003,7 +17003,7 @@
         <v>6.7</v>
       </c>
       <c r="I219" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>65.72</v>
@@ -17078,7 +17078,7 @@
         <v>1.77</v>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>66.84</v>
@@ -17153,7 +17153,7 @@
         <v>7.58</v>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J221" t="n">
         <v>68.16</v>
@@ -17228,7 +17228,7 @@
         <v>-1.47</v>
       </c>
       <c r="I222" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>69.44</v>
@@ -17303,7 +17303,7 @@
         <v>-2.76</v>
       </c>
       <c r="I223" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>70.48</v>
@@ -17378,7 +17378,7 @@
         <v>5.39</v>
       </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J224" t="n">
         <v>71.78</v>
@@ -17453,7 +17453,7 @@
         <v>-1.67</v>
       </c>
       <c r="I225" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>72.94</v>
@@ -17528,7 +17528,7 @@
         <v>3.78</v>
       </c>
       <c r="I226" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J226" t="n">
         <v>74.17</v>
@@ -17603,7 +17603,7 @@
         <v>6.63</v>
       </c>
       <c r="I227" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>75.56999999999999</v>
@@ -17678,7 +17678,7 @@
         <v>5.84</v>
       </c>
       <c r="I228" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J228" t="n">
         <v>77.23</v>
@@ -17753,7 +17753,7 @@
         <v>3.3</v>
       </c>
       <c r="I229" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J229" t="n">
         <v>78.75</v>
@@ -17828,7 +17828,7 @@
         <v>3.95</v>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J230" t="n">
         <v>80.73</v>
@@ -17903,7 +17903,7 @@
         <v>-0.03</v>
       </c>
       <c r="I231" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>82.56</v>
@@ -17978,7 +17978,7 @@
         <v>-28.54</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>83.11</v>
@@ -18057,7 +18057,7 @@
         <v>-3.98</v>
       </c>
       <c r="I233" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>83.45</v>
@@ -18132,7 +18132,7 @@
         <v>6.24</v>
       </c>
       <c r="I234" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>83.84</v>
@@ -18207,7 +18207,7 @@
         <v>2.88</v>
       </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J235" t="n">
         <v>84.11</v>
@@ -18282,7 +18282,7 @@
         <v>-15.77</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>83.90000000000001</v>
@@ -18357,7 +18357,7 @@
         <v>5.25</v>
       </c>
       <c r="I237" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>83.92</v>
@@ -18432,7 +18432,7 @@
         <v>8.33</v>
       </c>
       <c r="I238" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>84.11</v>
@@ -18507,7 +18507,7 @@
         <v>-3.46</v>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J239" t="n">
         <v>83.92</v>
@@ -18582,7 +18582,7 @@
         <v>4.29</v>
       </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>83.81999999999999</v>
@@ -18657,7 +18657,7 @@
         <v>-11.53</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>82.97</v>
@@ -18732,7 +18732,7 @@
         <v>2.94</v>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>82.29000000000001</v>
@@ -18807,7 +18807,7 @@
         <v>-4.8</v>
       </c>
       <c r="I243" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J243" t="n">
         <v>81.56</v>
@@ -18886,7 +18886,7 @@
         <v>5.6</v>
       </c>
       <c r="I244" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>80.8</v>
@@ -18961,7 +18961,7 @@
         <v>1.31</v>
       </c>
       <c r="I245" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J245" t="n">
         <v>80.15000000000001</v>
@@ -19036,7 +19036,7 @@
         <v>7.9</v>
       </c>
       <c r="I246" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J246" t="n">
         <v>79.62</v>
@@ -19111,7 +19111,7 @@
         <v>5.16</v>
       </c>
       <c r="I247" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>79.01000000000001</v>
@@ -19186,7 +19186,7 @@
         <v>-1.85</v>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>78.04000000000001</v>
@@ -19261,7 +19261,7 @@
         <v>1.21</v>
       </c>
       <c r="I249" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J249" t="n">
         <v>76.97</v>
@@ -19336,7 +19336,7 @@
         <v>0.51</v>
       </c>
       <c r="I250" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>75.70999999999999</v>
@@ -19411,7 +19411,7 @@
         <v>5.64</v>
       </c>
       <c r="I251" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>74.68000000000001</v>
@@ -19486,7 +19486,7 @@
         <v>-4.02</v>
       </c>
       <c r="I252" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>74.98999999999999</v>
@@ -19561,7 +19561,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>75.09999999999999</v>
@@ -19640,7 +19640,7 @@
         <v>0.88</v>
       </c>
       <c r="I254" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>75.02</v>
@@ -19715,7 +19715,7 @@
         <v>-1.42</v>
       </c>
       <c r="I255" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>74.77</v>
@@ -19794,7 +19794,7 @@
         <v>2.25</v>
       </c>
       <c r="I256" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J256" t="n">
         <v>75.23</v>
@@ -19873,7 +19873,7 @@
         <v>3.06</v>
       </c>
       <c r="I257" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J257" t="n">
         <v>75.64</v>
@@ -19948,7 +19948,7 @@
         <v>2.34</v>
       </c>
       <c r="I258" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J258" t="n">
         <v>75.84</v>
@@ -20023,7 +20023,7 @@
         <v>-2.72</v>
       </c>
       <c r="I259" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>76.06</v>
@@ -20098,7 +20098,7 @@
         <v>-1.84</v>
       </c>
       <c r="I260" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>76.06</v>
@@ -20167,7 +20167,7 @@
         <v>-4.96</v>
       </c>
       <c r="I261" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J261" t="n">
         <v>76.31</v>
@@ -20250,7 +20250,7 @@
         <v>0.73</v>
       </c>
       <c r="I262" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J262" t="n">
         <v>76.48</v>
@@ -20325,7 +20325,7 @@
         <v>-2.13</v>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J263" t="n">
         <v>76.75</v>
@@ -20400,7 +20400,7 @@
         <v>-4.13</v>
       </c>
       <c r="I264" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J264" t="n">
         <v>76.68000000000001</v>
@@ -20475,7 +20475,7 @@
         <v>-4.4</v>
       </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J265" t="n">
         <v>76.41</v>
@@ -20550,7 +20550,7 @@
         <v>-6.33</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>75.66</v>
@@ -20633,7 +20633,7 @@
         <v>1.54</v>
       </c>
       <c r="I267" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>74.75</v>
@@ -20708,7 +20708,7 @@
         <v>0.77</v>
       </c>
       <c r="I268" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J268" t="n">
         <v>73.95</v>
@@ -20783,7 +20783,7 @@
         <v>3.59</v>
       </c>
       <c r="I269" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J269" t="n">
         <v>73.2</v>
@@ -20858,7 +20858,7 @@
         <v>-6.81</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>72.22</v>
@@ -20937,7 +20937,7 @@
         <v>4.39</v>
       </c>
       <c r="I271" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J271" t="n">
         <v>71.14</v>
@@ -21016,7 +21016,7 @@
         <v>0.13</v>
       </c>
       <c r="I272" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J272" t="n">
         <v>70.23999999999999</v>
@@ -21091,7 +21091,7 @@
         <v>7.27</v>
       </c>
       <c r="I273" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J273" t="n">
         <v>69.91</v>
@@ -21166,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J274" t="n">
         <v>69.55</v>
@@ -21241,7 +21241,7 @@
         <v>-3.45</v>
       </c>
       <c r="I275" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J275" t="n">
         <v>69.13</v>
@@ -21316,7 +21316,7 @@
         <v>0.46</v>
       </c>
       <c r="I276" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J276" t="n">
         <v>68.64</v>
@@ -21391,7 +21391,7 @@
         <v>-0.23</v>
       </c>
       <c r="I277" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J277" t="n">
         <v>68.02</v>
@@ -21470,7 +21470,7 @@
         <v>2.32</v>
       </c>
       <c r="I278" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J278" t="n">
         <v>67.39</v>
@@ -21545,7 +21545,7 @@
         <v>1.36</v>
       </c>
       <c r="I279" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J279" t="n">
         <v>66.91</v>
@@ -21620,7 +21620,7 @@
         <v>1.01</v>
       </c>
       <c r="I280" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J280" t="n">
         <v>66.54000000000001</v>
@@ -21695,7 +21695,7 @@
         <v>-1.16</v>
       </c>
       <c r="I281" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J281" t="n">
         <v>66.31999999999999</v>
@@ -21770,7 +21770,7 @@
         <v>5.51</v>
       </c>
       <c r="I282" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J282" t="n">
         <v>66.26000000000001</v>
@@ -21845,7 +21845,7 @@
         <v>-0.28</v>
       </c>
       <c r="I283" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J283" t="n">
         <v>66.27</v>
@@ -21920,7 +21920,7 @@
         <v>-0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J284" t="n">
         <v>66.40000000000001</v>
@@ -21995,7 +21995,7 @@
         <v>3.35</v>
       </c>
       <c r="I285" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J285" t="n">
         <v>66.8</v>
@@ -22070,7 +22070,7 @@
         <v>-2.01</v>
       </c>
       <c r="I286" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J286" t="n">
         <v>67.33</v>
@@ -22145,7 +22145,7 @@
         <v>-5.07</v>
       </c>
       <c r="I287" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J287" t="n">
         <v>67.63</v>
@@ -22220,7 +22220,7 @@
         <v>2.74</v>
       </c>
       <c r="I288" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J288" t="n">
         <v>68</v>
@@ -22295,7 +22295,7 @@
         <v>-2.83</v>
       </c>
       <c r="I289" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J289" t="n">
         <v>68.16</v>
@@ -22370,7 +22370,7 @@
         <v>0.6</v>
       </c>
       <c r="I290" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J290" t="n">
         <v>68.56</v>
@@ -22445,7 +22445,7 @@
         <v>-0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J291" t="n">
         <v>68.8</v>
@@ -22524,7 +22524,7 @@
         <v>-3.12</v>
       </c>
       <c r="I292" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J292" t="n">
         <v>68.94</v>
@@ -22603,7 +22603,7 @@
         <v>-2.05</v>
       </c>
       <c r="I293" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J293" t="n">
         <v>68.77</v>
@@ -22678,7 +22678,7 @@
         <v>2.81</v>
       </c>
       <c r="I294" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J294" t="n">
         <v>68.7</v>
@@ -22753,7 +22753,7 @@
         <v>2.45</v>
       </c>
       <c r="I295" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J295" t="n">
         <v>68.81999999999999</v>
@@ -22828,7 +22828,7 @@
         <v>-3.44</v>
       </c>
       <c r="I296" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J296" t="n">
         <v>68.81999999999999</v>
@@ -22907,7 +22907,7 @@
         <v>-0.05</v>
       </c>
       <c r="I297" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J297" t="n">
         <v>68.81999999999999</v>
@@ -22982,7 +22982,7 @@
         <v>6.4</v>
       </c>
       <c r="I298" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J298" t="n">
         <v>68.95</v>
@@ -23057,7 +23057,7 @@
         <v>2.1</v>
       </c>
       <c r="I299" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J299" t="n">
         <v>69.11</v>
@@ -23132,7 +23132,7 @@
         <v>1.97</v>
       </c>
       <c r="I300" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J300" t="n">
         <v>69.31</v>
@@ -23207,7 +23207,7 @@
         <v>6.83</v>
       </c>
       <c r="I301" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J301" t="n">
         <v>69.79000000000001</v>
@@ -23282,7 +23282,7 @@
         <v>0.71</v>
       </c>
       <c r="I302" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J302" t="n">
         <v>70.12</v>
@@ -23357,7 +23357,7 @@
         <v>1.02</v>
       </c>
       <c r="I303" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J303" t="n">
         <v>70.48999999999999</v>
@@ -23432,7 +23432,7 @@
         <v>-4.84</v>
       </c>
       <c r="I304" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J304" t="n">
         <v>70.70999999999999</v>
@@ -23507,7 +23507,7 @@
         <v>-8.57</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>70.48</v>
@@ -23586,7 +23586,7 @@
         <v>1.3</v>
       </c>
       <c r="I306" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J306" t="n">
         <v>70.37</v>
@@ -23661,7 +23661,7 @@
         <v>-4.35</v>
       </c>
       <c r="I307" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J307" t="n">
         <v>70.29000000000001</v>
@@ -23736,7 +23736,7 @@
         <v>2.74</v>
       </c>
       <c r="I308" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J308" t="n">
         <v>70.20999999999999</v>
@@ -23811,7 +23811,7 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J309" t="n">
         <v>70.26000000000001</v>
@@ -23886,7 +23886,7 @@
         <v>-1.57</v>
       </c>
       <c r="I310" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J310" t="n">
         <v>70.23999999999999</v>
@@ -23961,7 +23961,7 @@
         <v>1.99</v>
       </c>
       <c r="I311" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J311" t="n">
         <v>70.31</v>
@@ -24036,7 +24036,7 @@
         <v>-3.18</v>
       </c>
       <c r="I312" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J312" t="n">
         <v>70.37</v>
@@ -24111,7 +24111,7 @@
         <v>1.27</v>
       </c>
       <c r="I313" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J313" t="n">
         <v>70.55</v>
@@ -24186,7 +24186,7 @@
         <v>-0.04</v>
       </c>
       <c r="I314" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J314" t="n">
         <v>70.63</v>
@@ -24261,7 +24261,7 @@
         <v>-0.97</v>
       </c>
       <c r="I315" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J315" t="n">
         <v>70.59999999999999</v>
@@ -24336,7 +24336,7 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J316" t="n">
         <v>70.7</v>
@@ -24411,7 +24411,7 @@
         <v>-2.62</v>
       </c>
       <c r="I317" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J317" t="n">
         <v>70.72</v>
@@ -24486,7 +24486,7 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J318" t="n">
         <v>70.56</v>
@@ -24561,7 +24561,7 @@
         <v>-8.08</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>70.06</v>
@@ -24636,7 +24636,7 @@
         <v>0.02</v>
       </c>
       <c r="I320" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J320" t="n">
         <v>69.48999999999999</v>
@@ -24711,7 +24711,7 @@
         <v>-4.17</v>
       </c>
       <c r="I321" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J321" t="n">
         <v>68.54000000000001</v>
@@ -24790,7 +24790,7 @@
         <v>-2.29</v>
       </c>
       <c r="I322" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J322" t="n">
         <v>67.48999999999999</v>
@@ -24869,7 +24869,7 @@
         <v>5.48</v>
       </c>
       <c r="I323" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J323" t="n">
         <v>66.56999999999999</v>
@@ -24944,7 +24944,7 @@
         <v>0.77</v>
       </c>
       <c r="I324" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J324" t="n">
         <v>65.86</v>
@@ -25019,7 +25019,7 @@
         <v>3.56</v>
       </c>
       <c r="I325" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J325" t="n">
         <v>65.58</v>
@@ -25094,7 +25094,7 @@
         <v>-0.13</v>
       </c>
       <c r="I326" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J326" t="n">
         <v>65.25</v>
@@ -25169,7 +25169,7 @@
         <v>-4.39</v>
       </c>
       <c r="I327" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J327" t="n">
         <v>64.94</v>
@@ -25244,7 +25244,7 @@
         <v>-1.81</v>
       </c>
       <c r="I328" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J328" t="n">
         <v>64.47</v>
@@ -25319,7 +25319,7 @@
         <v>-1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J329" t="n">
         <v>63.95</v>
@@ -25394,7 +25394,7 @@
         <v>-5.4</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>63.32</v>
@@ -25473,7 +25473,7 @@
         <v>-7.09</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>62.42</v>
@@ -25552,7 +25552,7 @@
         <v>1.12</v>
       </c>
       <c r="I332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J332" t="n">
         <v>61.66</v>
@@ -25631,7 +25631,7 @@
         <v>1.76</v>
       </c>
       <c r="I333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J333" t="n">
         <v>60.91</v>
@@ -25706,7 +25706,7 @@
         <v>-1.13</v>
       </c>
       <c r="I334" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J334" t="n">
         <v>60.12</v>
@@ -25781,7 +25781,7 @@
         <v>1.5</v>
       </c>
       <c r="I335" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J335" t="n">
         <v>59.42</v>
@@ -25856,7 +25856,7 @@
         <v>0.21</v>
       </c>
       <c r="I336" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J336" t="n">
         <v>58.69</v>
@@ -25931,7 +25931,7 @@
         <v>2.69</v>
       </c>
       <c r="I337" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J337" t="n">
         <v>58.14</v>
@@ -26006,7 +26006,7 @@
         <v>1.98</v>
       </c>
       <c r="I338" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J338" t="n">
         <v>57.59</v>
@@ -26081,7 +26081,7 @@
         <v>-2.94</v>
       </c>
       <c r="I339" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J339" t="n">
         <v>57.24</v>
@@ -26160,7 +26160,7 @@
         <v>-2.99</v>
       </c>
       <c r="I340" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J340" t="n">
         <v>56.8</v>
@@ -26239,7 +26239,7 @@
         <v>2.48</v>
       </c>
       <c r="I341" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J341" t="n">
         <v>56.55</v>
@@ -26314,7 +26314,7 @@
         <v>-0.35</v>
       </c>
       <c r="I342" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J342" t="n">
         <v>56.37</v>
@@ -26389,7 +26389,7 @@
         <v>-3.32</v>
       </c>
       <c r="I343" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J343" t="n">
         <v>55.94</v>
@@ -26464,7 +26464,7 @@
         <v>1.94</v>
       </c>
       <c r="I344" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J344" t="n">
         <v>55.53</v>
@@ -26539,7 +26539,7 @@
         <v>-1.81</v>
       </c>
       <c r="I345" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J345" t="n">
         <v>54.97</v>
@@ -26614,7 +26614,7 @@
         <v>-3.49</v>
       </c>
       <c r="I346" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J346" t="n">
         <v>54.32</v>
@@ -26689,7 +26689,7 @@
         <v>0.77</v>
       </c>
       <c r="I347" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J347" t="n">
         <v>53.83</v>
@@ -26764,7 +26764,7 @@
         <v>0.39</v>
       </c>
       <c r="I348" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J348" t="n">
         <v>53.4</v>
@@ -26839,7 +26839,7 @@
         <v>4.12</v>
       </c>
       <c r="I349" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J349" t="n">
         <v>53.11</v>
@@ -26914,7 +26914,7 @@
         <v>1.58</v>
       </c>
       <c r="I350" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J350" t="n">
         <v>53.02</v>
@@ -26989,7 +26989,7 @@
         <v>-3.45</v>
       </c>
       <c r="I351" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J351" t="n">
         <v>53.03</v>
@@ -27068,7 +27068,7 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J352" t="n">
         <v>53.04</v>
@@ -27143,7 +27143,7 @@
         <v>0.65</v>
       </c>
       <c r="I353" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J353" t="n">
         <v>53.03</v>
@@ -27218,7 +27218,7 @@
         <v>-2.32</v>
       </c>
       <c r="I354" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J354" t="n">
         <v>52.98</v>
@@ -27293,7 +27293,7 @@
         <v>0.14</v>
       </c>
       <c r="I355" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J355" t="n">
         <v>52.89</v>
@@ -27368,7 +27368,7 @@
         <v>3.34</v>
       </c>
       <c r="I356" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J356" t="n">
         <v>52.89</v>
@@ -27443,7 +27443,7 @@
         <v>-2.13</v>
       </c>
       <c r="I357" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J357" t="n">
         <v>52.75</v>
@@ -27522,7 +27522,7 @@
         <v>0.19</v>
       </c>
       <c r="I358" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J358" t="n">
         <v>52.57</v>
@@ -27597,7 +27597,7 @@
         <v>2.63</v>
       </c>
       <c r="I359" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J359" t="n">
         <v>52.54</v>
@@ -27672,7 +27672,7 @@
         <v>4.14</v>
       </c>
       <c r="I360" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J360" t="n">
         <v>52.7</v>
@@ -27747,7 +27747,7 @@
         <v>-0.39</v>
       </c>
       <c r="I361" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J361" t="n">
         <v>52.79</v>
@@ -27822,7 +27822,7 @@
         <v>2.95</v>
       </c>
       <c r="I362" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J362" t="n">
         <v>52.97</v>
@@ -27897,7 +27897,7 @@
         <v>3.32</v>
       </c>
       <c r="I363" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J363" t="n">
         <v>53.33</v>
@@ -27972,7 +27972,7 @@
         <v>-1.45</v>
       </c>
       <c r="I364" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J364" t="n">
         <v>53.6</v>
@@ -28047,7 +28047,7 @@
         <v>0.87</v>
       </c>
       <c r="I365" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J365" t="n">
         <v>53.94</v>
@@ -28122,7 +28122,7 @@
         <v>-1.52</v>
       </c>
       <c r="I366" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J366" t="n">
         <v>54.33</v>
@@ -28197,7 +28197,7 @@
         <v>0.55</v>
       </c>
       <c r="I367" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J367" t="n">
         <v>54.71</v>
@@ -28272,7 +28272,7 @@
         <v>1.86</v>
       </c>
       <c r="I368" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J368" t="n">
         <v>55.14</v>
@@ -28347,7 +28347,7 @@
         <v>-3.58</v>
       </c>
       <c r="I369" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J369" t="n">
         <v>55.36</v>
@@ -28426,7 +28426,7 @@
         <v>4.47</v>
       </c>
       <c r="I370" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J370" t="n">
         <v>55.67</v>
@@ -28501,7 +28501,7 @@
         <v>2.75</v>
       </c>
       <c r="I371" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J371" t="n">
         <v>56.15</v>
@@ -28576,7 +28576,7 @@
         <v>1.72</v>
       </c>
       <c r="I372" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J372" t="n">
         <v>56.65</v>
@@ -28651,7 +28651,7 @@
         <v>-0.83</v>
       </c>
       <c r="I373" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J373" t="n">
         <v>57.12</v>
@@ -28726,7 +28726,7 @@
         <v>0.19</v>
       </c>
       <c r="I374" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J374" t="n">
         <v>57.65</v>
@@ -28801,7 +28801,7 @@
         <v>-1.17</v>
       </c>
       <c r="I375" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J375" t="n">
         <v>58.14</v>
@@ -28876,7 +28876,7 @@
         <v>1.92</v>
       </c>
       <c r="I376" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J376" t="n">
         <v>58.6</v>
@@ -28951,7 +28951,7 @@
         <v>-4.38</v>
       </c>
       <c r="I377" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J377" t="n">
         <v>58.98</v>
@@ -29026,7 +29026,7 @@
         <v>0.18</v>
       </c>
       <c r="I378" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J378" t="n">
         <v>59.37</v>
@@ -29101,7 +29101,7 @@
         <v>-3.68</v>
       </c>
       <c r="I379" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J379" t="n">
         <v>59.57</v>
@@ -29180,7 +29180,7 @@
         <v>1.99</v>
       </c>
       <c r="I380" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J380" t="n">
         <v>59.72</v>
@@ -29255,7 +29255,7 @@
         <v>2.51</v>
       </c>
       <c r="I381" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J381" t="n">
         <v>59.96</v>
@@ -29330,7 +29330,7 @@
         <v>-1.21</v>
       </c>
       <c r="I382" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J382" t="n">
         <v>60.07</v>
@@ -29409,7 +29409,7 @@
         <v>-0.75</v>
       </c>
       <c r="I383" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J383" t="n">
         <v>60.07</v>
@@ -29484,7 +29484,7 @@
         <v>2.27</v>
       </c>
       <c r="I384" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J384" t="n">
         <v>60.18</v>
@@ -29559,7 +29559,7 @@
         <v>-5.3</v>
       </c>
       <c r="I385" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J385" s="4" t="n">
         <v>60.1</v>
@@ -29638,7 +29638,7 @@
         <v>1.08</v>
       </c>
       <c r="I386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J386" t="n">
         <v>60.1</v>
@@ -29713,7 +29713,7 @@
         <v>-2.2</v>
       </c>
       <c r="I387" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J387" t="n">
         <v>60.02</v>
@@ -29788,7 +29788,7 @@
         <v>1.21</v>
       </c>
       <c r="I388" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J388" t="n">
         <v>59.92</v>
@@ -29863,7 +29863,7 @@
         <v>-0.83</v>
       </c>
       <c r="I389" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J389" t="n">
         <v>59.9</v>
@@ -29938,7 +29938,7 @@
         <v>3.37</v>
       </c>
       <c r="I390" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J390" t="n">
         <v>59.84</v>
@@ -30013,7 +30013,7 @@
         <v>1.63</v>
       </c>
       <c r="I391" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J391" t="n">
         <v>59.76</v>
@@ -30088,7 +30088,7 @@
         <v>-0.5</v>
       </c>
       <c r="I392" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J392" t="n">
         <v>59.6</v>
@@ -30163,7 +30163,7 @@
         <v>1.84</v>
       </c>
       <c r="I393" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J393" t="n">
         <v>59.53</v>
@@ -30238,7 +30238,7 @@
         <v>-4.23</v>
       </c>
       <c r="I394" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J394" t="n">
         <v>59.32</v>
@@ -30317,7 +30317,7 @@
         <v>-0.93</v>
       </c>
       <c r="I395" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J395" t="n">
         <v>59.12</v>
@@ -30392,7 +30392,7 @@
         <v>0.9</v>
       </c>
       <c r="I396" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J396" t="n">
         <v>58.89</v>
@@ -30467,7 +30467,7 @@
         <v>-5.49</v>
       </c>
       <c r="I397" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>58.64</v>
@@ -30546,7 +30546,7 @@
         <v>0.96</v>
       </c>
       <c r="I398" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J398" t="n">
         <v>58.41</v>
@@ -30621,7 +30621,7 @@
         <v>-1.75</v>
       </c>
       <c r="I399" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J399" t="n">
         <v>58.23</v>
@@ -30696,7 +30696,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I400" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J400" t="n">
         <v>58.03</v>
@@ -30771,7 +30771,7 @@
         <v>-0.51</v>
       </c>
       <c r="I401" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J401" t="n">
         <v>57.74</v>
@@ -30846,7 +30846,7 @@
         <v>0.71</v>
       </c>
       <c r="I402" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J402" t="n">
         <v>57.51</v>
@@ -30921,7 +30921,7 @@
         <v>0.58</v>
       </c>
       <c r="I403" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J403" t="n">
         <v>57.31</v>
@@ -30996,7 +30996,7 @@
         <v>-2.94</v>
       </c>
       <c r="I404" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J404" t="n">
         <v>56.97</v>
@@ -31071,7 +31071,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I405" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J405" t="n">
         <v>56.76</v>
@@ -31150,7 +31150,7 @@
         <v>2.49</v>
       </c>
       <c r="I406" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J406" t="n">
         <v>56.6</v>
@@ -31225,7 +31225,7 @@
         <v>-0.78</v>
       </c>
       <c r="I407" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J407" t="n">
         <v>56.47</v>
@@ -31304,7 +31304,7 @@
         <v>-1.58</v>
       </c>
       <c r="I408" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J408" t="n">
         <v>56.27</v>
@@ -31379,7 +31379,7 @@
         <v>-6.11</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>55.93</v>
@@ -31458,7 +31458,7 @@
         <v>3.39</v>
       </c>
       <c r="I410" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J410" t="n">
         <v>55.58</v>
@@ -31533,7 +31533,7 @@
         <v>-0.79</v>
       </c>
       <c r="I411" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J411" t="n">
         <v>55.15</v>
@@ -31608,7 +31608,7 @@
         <v>0.06</v>
       </c>
       <c r="I412" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J412" t="n">
         <v>54.75</v>
@@ -31683,7 +31683,7 @@
         <v>1.13</v>
       </c>
       <c r="I413" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J413" t="n">
         <v>54.32</v>
@@ -31758,7 +31758,7 @@
         <v>0.27</v>
       </c>
       <c r="I414" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J414" t="n">
         <v>54.02</v>
@@ -31804,61 +31804,77 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>24619695</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="2" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>24620500</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31851,7 +31851,7 @@
         <v>31.22</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31851,7 +31851,7 @@
         <v>31.22</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31877,6 +31877,83 @@
       <c r="W415" s="6" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D416" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="E416" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="F416" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="G416" t="n">
+        <v>15454045</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I416" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J416" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="K416" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="L416" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="M416" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="N416" s="1" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31827,7 +31827,7 @@
         <v>49.34</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>24620500</v>
+        <v>24708800</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-5.59</v>
@@ -31899,13 +31899,13 @@
         <v>47.87</v>
       </c>
       <c r="F416" t="n">
-        <v>48.74</v>
+        <v>48.72</v>
       </c>
       <c r="G416" t="n">
-        <v>15454045</v>
+        <v>18295162</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.26</v>
       </c>
       <c r="I416" t="n">
         <v>5.2</v>
@@ -31923,10 +31923,10 @@
         <v>64.95</v>
       </c>
       <c r="N416" s="1" t="n">
-        <v>28.1</v>
+        <v>28.06</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31944,16 +31944,18 @@
         </is>
       </c>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31814,25 +31814,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D415" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="E415" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="F415" t="n">
+        <v>48.72</v>
+      </c>
       <c r="G415" t="n">
-        <v>18295162</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>18322100</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="K415" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="L415" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="M415" t="n">
+        <v>64.95</v>
+      </c>
       <c r="N415" s="1" t="n">
-        <v>29.31</v>
+        <v>28.06</v>
       </c>
       <c r="O415" t="n">
         <v>21</v>
@@ -31847,7 +31863,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -926,7 +926,7 @@
         <v>29.37</v>
       </c>
       <c r="K6" t="n">
-        <v>28.29</v>
+        <v>28.28</v>
       </c>
       <c r="L6" t="n">
         <v>28.58</v>
@@ -8057,7 +8057,7 @@
         <v>5.2</v>
       </c>
       <c r="J100" t="n">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="K100" t="n">
         <v>32.22</v>
@@ -8511,7 +8511,7 @@
         <v>5.2</v>
       </c>
       <c r="J106" t="n">
-        <v>34.46</v>
+        <v>34.47</v>
       </c>
       <c r="K106" t="n">
         <v>32.65</v>
@@ -23063,7 +23063,7 @@
         <v>70.12</v>
       </c>
       <c r="K299" t="n">
-        <v>70.95</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="L299" t="n">
         <v>69.38</v>
@@ -24947,7 +24947,7 @@
         <v>5.2</v>
       </c>
       <c r="J324" t="n">
-        <v>64.94</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K324" t="n">
         <v>67.62</v>
@@ -26017,7 +26017,7 @@
         <v>5.2</v>
       </c>
       <c r="J338" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="K338" t="n">
         <v>64.95999999999999</v>
@@ -31701,7 +31701,7 @@
         <v>28.06</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,83 @@
       <c r="W413" s="2" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="D414" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="E414" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="F414" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="G414" t="n">
+        <v>9876465</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="L414" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="M414" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -8511,7 +8511,7 @@
         <v>5.2</v>
       </c>
       <c r="J106" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="K106" t="n">
         <v>32.65</v>
@@ -31747,25 +31747,25 @@
         <v>48.53</v>
       </c>
       <c r="D414" t="n">
-        <v>49.01</v>
+        <v>49.03</v>
       </c>
       <c r="E414" t="n">
         <v>47.86</v>
       </c>
       <c r="F414" t="n">
-        <v>48.87</v>
+        <v>48.66</v>
       </c>
       <c r="G414" t="n">
-        <v>9876465</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0.31</v>
+        <v>14615558</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.12</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>52.84</v>
+        <v>52.83</v>
       </c>
       <c r="K414" t="n">
         <v>56.82</v>
@@ -31777,7 +31777,7 @@
         <v>64.84999999999999</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>27.22</v>
+        <v>26.34</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31798,16 +31798,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31602,7 +31602,7 @@
         <v>48.72</v>
       </c>
       <c r="G412" t="n">
-        <v>18322100</v>
+        <v>18478800</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-1.26</v>
@@ -31668,28 +31668,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="D413" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="E413" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="F413" t="n">
+        <v>48.66</v>
+      </c>
       <c r="G413" t="n">
-        <v>14615558</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>14672600</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.12</v>
       </c>
       <c r="I413" t="n">
         <v>5.2</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="K413" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="L413" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="M413" t="n">
+        <v>64.84999999999999</v>
+      </c>
       <c r="N413" s="3" t="n">
-        <v>26.45</v>
+        <v>26.34</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31701,7 +31717,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,7 +31705,7 @@
         <v>26.34</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D414" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="E414" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="F414" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3296493</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="L414" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="M414" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31681,7 +31681,7 @@
         <v>48.66</v>
       </c>
       <c r="G413" t="n">
-        <v>14672600</v>
+        <v>14719700</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.12</v>
@@ -31751,25 +31751,25 @@
         <v>48.5</v>
       </c>
       <c r="D414" t="n">
-        <v>48.89</v>
+        <v>49.24</v>
       </c>
       <c r="E414" t="n">
         <v>48.48</v>
       </c>
       <c r="F414" t="n">
-        <v>48.82</v>
+        <v>49.13</v>
       </c>
       <c r="G414" t="n">
-        <v>3296493</v>
+        <v>10064503</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>0.33</v>
+        <v>0.97</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>52.49</v>
+        <v>52.51</v>
       </c>
       <c r="K414" t="n">
         <v>56.76</v>
@@ -31781,10 +31781,10 @@
         <v>64.73</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>30.59</v>
+        <v>32.22</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -851,7 +851,7 @@
         <v>29.37</v>
       </c>
       <c r="K5" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="L5" t="n">
         <v>28.58</v>
@@ -7982,7 +7982,7 @@
         <v>5.2</v>
       </c>
       <c r="J99" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="K99" t="n">
         <v>32.22</v>
@@ -22988,7 +22988,7 @@
         <v>70.12</v>
       </c>
       <c r="K298" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="L298" t="n">
         <v>69.38</v>
@@ -24872,7 +24872,7 @@
         <v>5.2</v>
       </c>
       <c r="J323" t="n">
-        <v>64.93000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K323" t="n">
         <v>67.62</v>
@@ -25942,7 +25942,7 @@
         <v>5.2</v>
       </c>
       <c r="J337" t="n">
-        <v>56.56</v>
+        <v>56.55</v>
       </c>
       <c r="K337" t="n">
         <v>64.95999999999999</v>
@@ -29431,7 +29431,7 @@
         <v>34.58</v>
       </c>
       <c r="O383" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>36.66</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>39.7</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>49.73</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>47.35</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>40.96</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>38.21</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>35.38</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>42.79</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>41.58</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>31.35</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>25.49</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30868,11 +30868,11 @@
         <v>32.98</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30943,7 +30943,7 @@
         <v>26.51</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31022,11 +31022,11 @@
         <v>30.33</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31097,7 +31097,7 @@
         <v>24.66</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>30.29</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>36.77</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>34.24</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>40.13</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>38.25</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>31.22</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>28.06</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>26.34</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31757,13 +31757,13 @@
         <v>48.48</v>
       </c>
       <c r="F414" t="n">
-        <v>49.13</v>
+        <v>49.16</v>
       </c>
       <c r="G414" t="n">
-        <v>10064503</v>
+        <v>10954397</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
@@ -31781,10 +31781,10 @@
         <v>64.73</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>32.22</v>
+        <v>32.38</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31807,7 +31807,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>32.38</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="D414" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="E414" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="F414" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="G414" t="n">
+        <v>8261830</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="I414" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="K414" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="L414" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="M414" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -4073,7 +4073,7 @@
         <v>29.77</v>
       </c>
       <c r="K47" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="L47" t="n">
         <v>28.82</v>
@@ -31685,7 +31685,7 @@
         <v>49.16</v>
       </c>
       <c r="G413" t="n">
-        <v>10986700</v>
+        <v>11044600</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>1.03</v>
@@ -31751,28 +31751,28 @@
         <v>48.83</v>
       </c>
       <c r="D414" t="n">
-        <v>48.86</v>
+        <v>49.08</v>
       </c>
       <c r="E414" t="n">
-        <v>48.28</v>
+        <v>48.12</v>
       </c>
       <c r="F414" t="n">
-        <v>48.49</v>
+        <v>49.06</v>
       </c>
       <c r="G414" t="n">
-        <v>8261830</v>
+        <v>18884060</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.36</v>
+        <v>-0.2</v>
       </c>
       <c r="I414" t="n">
         <v>5.2</v>
       </c>
       <c r="J414" t="n">
-        <v>52.21</v>
+        <v>52.24</v>
       </c>
       <c r="K414" t="n">
-        <v>56.67</v>
+        <v>56.68</v>
       </c>
       <c r="L414" t="n">
         <v>58.31</v>
@@ -31781,10 +31781,10 @@
         <v>64.59</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>31.66</v>
+        <v>33.05</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>49.06</v>
       </c>
       <c r="G414" t="n">
-        <v>18884060</v>
+        <v>18875600</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.2</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>33.05</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,83 @@
       <c r="W414" s="2" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="D415" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="E415" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="F415" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="G415" t="n">
+        <v>14442492</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="I415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="K415" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="L415" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="M415" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>49.06</v>
       </c>
       <c r="G414" t="n">
-        <v>18875600</v>
+        <v>18913500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.2</v>
@@ -31829,16 +31829,16 @@
         <v>47.63</v>
       </c>
       <c r="E415" t="n">
-        <v>46.93</v>
+        <v>46.92</v>
       </c>
       <c r="F415" t="n">
-        <v>47.34</v>
+        <v>47.28</v>
       </c>
       <c r="G415" t="n">
-        <v>14442492</v>
+        <v>23821938</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-3.51</v>
+        <v>-3.63</v>
       </c>
       <c r="I415" t="n">
         <v>5.2</v>
@@ -31847,7 +31847,7 @@
         <v>51.85</v>
       </c>
       <c r="K415" t="n">
-        <v>56.54</v>
+        <v>56.53</v>
       </c>
       <c r="L415" t="n">
         <v>58.1</v>
@@ -31856,7 +31856,7 @@
         <v>64.43000000000001</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>22.11</v>
+        <v>22.01</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31877,16 +31877,18 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>47.28</v>
       </c>
       <c r="G415" t="n">
-        <v>23821938</v>
+        <v>23941600</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-3.63</v>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>22.01</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>22.01</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31889,6 +31889,83 @@
       <c r="W415" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="D416" s="4" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="F416" s="4" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="G416" s="4" t="n">
+        <v>23519648</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="I416" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J416" s="4" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="K416" s="4" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="L416" s="4" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="M416" s="4" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="N416" s="7" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="O416" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" s="4" t="inlineStr"/>
+      <c r="W416" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>47.28</v>
       </c>
       <c r="G415" t="n">
-        <v>23941600</v>
+        <v>24109400</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-3.63</v>
@@ -31908,25 +31908,25 @@
         <v>45.06</v>
       </c>
       <c r="E416" s="4" t="n">
-        <v>44.29</v>
+        <v>44.11</v>
       </c>
       <c r="F416" s="4" t="n">
-        <v>44.42</v>
+        <v>44.6</v>
       </c>
       <c r="G416" s="4" t="n">
-        <v>23519648</v>
+        <v>37368730</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>-6.05</v>
+        <v>-5.67</v>
       </c>
       <c r="I416" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="J416" s="4" t="n">
-        <v>51.33</v>
+        <v>51.34</v>
       </c>
       <c r="K416" s="4" t="n">
-        <v>56.34</v>
+        <v>56.35</v>
       </c>
       <c r="L416" s="4" t="n">
         <v>57.82</v>
@@ -31935,10 +31935,10 @@
         <v>64.23</v>
       </c>
       <c r="N416" s="7" t="n">
-        <v>18.64</v>
+        <v>18.85</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="S416" s="4" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="6" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="6" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" s="4" t="inlineStr"/>
       <c r="W416" s="6" t="inlineStr"/>

--- a/US_stock/SILVER_table.xlsx
+++ b/US_stock/SILVER_table.xlsx
@@ -31808,61 +31808,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>40249053</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="1" t="n">
-        <v>22.74</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>40341200</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>149.8</v>
       </c>
     </row>
